--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="81">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -218,12 +218,54 @@
   </si>
   <si>
     <t>Nº</t>
+  </si>
+  <si>
+    <t>Republic of Ireland Premier Division</t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
+    <t>St Patrick's Athl.</t>
+  </si>
+  <si>
+    <t>Galway United</t>
+  </si>
+  <si>
+    <t>Derry City</t>
+  </si>
+  <si>
+    <t>Drogheda United</t>
+  </si>
+  <si>
+    <t>['34', '51']</t>
+  </si>
+  <si>
+    <t>['11', '15', '45']</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>['45+1', '81']</t>
+  </si>
+  <si>
+    <t>['14']</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -276,11 +318,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -575,7 +618,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP1"/>
+  <dimension ref="A1:BP4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -784,6 +827,624 @@
         <v>66</v>
       </c>
     </row>
+    <row r="2" spans="1:68">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>7775616</v>
+      </c>
+      <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="2">
+        <v>45702.69791666666</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+      <c r="N2">
+        <v>4</v>
+      </c>
+      <c r="O2" t="s">
+        <v>76</v>
+      </c>
+      <c r="P2" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q2">
+        <v>4.4</v>
+      </c>
+      <c r="R2">
+        <v>2.09</v>
+      </c>
+      <c r="S2">
+        <v>2.6</v>
+      </c>
+      <c r="T2">
+        <v>1.46</v>
+      </c>
+      <c r="U2">
+        <v>2.55</v>
+      </c>
+      <c r="V2">
+        <v>3</v>
+      </c>
+      <c r="W2">
+        <v>1.34</v>
+      </c>
+      <c r="X2">
+        <v>10</v>
+      </c>
+      <c r="Y2">
+        <v>1.06</v>
+      </c>
+      <c r="Z2">
+        <v>3.69</v>
+      </c>
+      <c r="AA2">
+        <v>3.34</v>
+      </c>
+      <c r="AB2">
+        <v>2</v>
+      </c>
+      <c r="AC2">
+        <v>1.02</v>
+      </c>
+      <c r="AD2">
+        <v>8.1</v>
+      </c>
+      <c r="AE2">
+        <v>1.36</v>
+      </c>
+      <c r="AF2">
+        <v>2.85</v>
+      </c>
+      <c r="AG2">
+        <v>2</v>
+      </c>
+      <c r="AH2">
+        <v>1.67</v>
+      </c>
+      <c r="AI2">
+        <v>1.95</v>
+      </c>
+      <c r="AJ2">
+        <v>1.8</v>
+      </c>
+      <c r="AK2">
+        <v>1.75</v>
+      </c>
+      <c r="AL2">
+        <v>1.29</v>
+      </c>
+      <c r="AM2">
+        <v>1.26</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>4</v>
+      </c>
+      <c r="AV2">
+        <v>5</v>
+      </c>
+      <c r="AW2">
+        <v>12</v>
+      </c>
+      <c r="AX2">
+        <v>10</v>
+      </c>
+      <c r="AY2">
+        <v>16</v>
+      </c>
+      <c r="AZ2">
+        <v>15</v>
+      </c>
+      <c r="BA2">
+        <v>6</v>
+      </c>
+      <c r="BB2">
+        <v>4</v>
+      </c>
+      <c r="BC2">
+        <v>10</v>
+      </c>
+      <c r="BD2">
+        <v>2.48</v>
+      </c>
+      <c r="BE2">
+        <v>6.4</v>
+      </c>
+      <c r="BF2">
+        <v>1.67</v>
+      </c>
+      <c r="BG2">
+        <v>1.43</v>
+      </c>
+      <c r="BH2">
+        <v>2.55</v>
+      </c>
+      <c r="BI2">
+        <v>1.73</v>
+      </c>
+      <c r="BJ2">
+        <v>1.94</v>
+      </c>
+      <c r="BK2">
+        <v>1.98</v>
+      </c>
+      <c r="BL2">
+        <v>1.82</v>
+      </c>
+      <c r="BM2">
+        <v>2.8</v>
+      </c>
+      <c r="BN2">
+        <v>1.36</v>
+      </c>
+      <c r="BO2">
+        <v>3.8</v>
+      </c>
+      <c r="BP2">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:68">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>7775617</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="2">
+        <v>45702.69791666666</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" t="s">
+        <v>74</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>4</v>
+      </c>
+      <c r="L3">
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>4</v>
+      </c>
+      <c r="O3" t="s">
+        <v>77</v>
+      </c>
+      <c r="P3" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q3">
+        <v>4</v>
+      </c>
+      <c r="R3">
+        <v>1.92</v>
+      </c>
+      <c r="S3">
+        <v>3.2</v>
+      </c>
+      <c r="T3">
+        <v>1.59</v>
+      </c>
+      <c r="U3">
+        <v>2.24</v>
+      </c>
+      <c r="V3">
+        <v>3.6</v>
+      </c>
+      <c r="W3">
+        <v>1.25</v>
+      </c>
+      <c r="X3">
+        <v>11.25</v>
+      </c>
+      <c r="Y3">
+        <v>1.01</v>
+      </c>
+      <c r="Z3">
+        <v>3.07</v>
+      </c>
+      <c r="AA3">
+        <v>3.04</v>
+      </c>
+      <c r="AB3">
+        <v>2.41</v>
+      </c>
+      <c r="AC3">
+        <v>1.1</v>
+      </c>
+      <c r="AD3">
+        <v>6.6</v>
+      </c>
+      <c r="AE3">
+        <v>1.48</v>
+      </c>
+      <c r="AF3">
+        <v>2.37</v>
+      </c>
+      <c r="AG3">
+        <v>2.62</v>
+      </c>
+      <c r="AH3">
+        <v>1.43</v>
+      </c>
+      <c r="AI3">
+        <v>2.12</v>
+      </c>
+      <c r="AJ3">
+        <v>1.65</v>
+      </c>
+      <c r="AK3">
+        <v>1.54</v>
+      </c>
+      <c r="AL3">
+        <v>1.34</v>
+      </c>
+      <c r="AM3">
+        <v>1.34</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>3</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>4</v>
+      </c>
+      <c r="AV3">
+        <v>6</v>
+      </c>
+      <c r="AW3">
+        <v>15</v>
+      </c>
+      <c r="AX3">
+        <v>5</v>
+      </c>
+      <c r="AY3">
+        <v>19</v>
+      </c>
+      <c r="AZ3">
+        <v>11</v>
+      </c>
+      <c r="BA3">
+        <v>2</v>
+      </c>
+      <c r="BB3">
+        <v>3</v>
+      </c>
+      <c r="BC3">
+        <v>5</v>
+      </c>
+      <c r="BD3">
+        <v>2.15</v>
+      </c>
+      <c r="BE3">
+        <v>6.25</v>
+      </c>
+      <c r="BF3">
+        <v>1.86</v>
+      </c>
+      <c r="BG3">
+        <v>1.53</v>
+      </c>
+      <c r="BH3">
+        <v>2.28</v>
+      </c>
+      <c r="BI3">
+        <v>1.88</v>
+      </c>
+      <c r="BJ3">
+        <v>1.78</v>
+      </c>
+      <c r="BK3">
+        <v>2.43</v>
+      </c>
+      <c r="BL3">
+        <v>1.47</v>
+      </c>
+      <c r="BM3">
+        <v>3.2</v>
+      </c>
+      <c r="BN3">
+        <v>1.28</v>
+      </c>
+      <c r="BO3">
+        <v>4.3</v>
+      </c>
+      <c r="BP3">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:68">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>7775618</v>
+      </c>
+      <c r="C4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="2">
+        <v>45702.69791666666</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H4" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>78</v>
+      </c>
+      <c r="P4" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q4">
+        <v>2.1</v>
+      </c>
+      <c r="R4">
+        <v>2.25</v>
+      </c>
+      <c r="S4">
+        <v>6.5</v>
+      </c>
+      <c r="T4">
+        <v>1.4</v>
+      </c>
+      <c r="U4">
+        <v>2.75</v>
+      </c>
+      <c r="V4">
+        <v>2.75</v>
+      </c>
+      <c r="W4">
+        <v>1.4</v>
+      </c>
+      <c r="X4">
+        <v>8</v>
+      </c>
+      <c r="Y4">
+        <v>1.08</v>
+      </c>
+      <c r="Z4">
+        <v>1.49</v>
+      </c>
+      <c r="AA4">
+        <v>4.1</v>
+      </c>
+      <c r="AB4">
+        <v>6.3</v>
+      </c>
+      <c r="AC4">
+        <v>1.02</v>
+      </c>
+      <c r="AD4">
+        <v>10</v>
+      </c>
+      <c r="AE4">
+        <v>1.25</v>
+      </c>
+      <c r="AF4">
+        <v>3.4</v>
+      </c>
+      <c r="AG4">
+        <v>1.88</v>
+      </c>
+      <c r="AH4">
+        <v>1.83</v>
+      </c>
+      <c r="AI4">
+        <v>2.05</v>
+      </c>
+      <c r="AJ4">
+        <v>1.7</v>
+      </c>
+      <c r="AK4">
+        <v>1.1</v>
+      </c>
+      <c r="AL4">
+        <v>1.22</v>
+      </c>
+      <c r="AM4">
+        <v>2.61</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>1</v>
+      </c>
+      <c r="AQ4">
+        <v>1</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>7</v>
+      </c>
+      <c r="AV4">
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <v>10</v>
+      </c>
+      <c r="AX4">
+        <v>6</v>
+      </c>
+      <c r="AY4">
+        <v>17</v>
+      </c>
+      <c r="AZ4">
+        <v>6</v>
+      </c>
+      <c r="BA4">
+        <v>9</v>
+      </c>
+      <c r="BB4">
+        <v>4</v>
+      </c>
+      <c r="BC4">
+        <v>13</v>
+      </c>
+      <c r="BD4">
+        <v>1.42</v>
+      </c>
+      <c r="BE4">
+        <v>7</v>
+      </c>
+      <c r="BF4">
+        <v>3.2</v>
+      </c>
+      <c r="BG4">
+        <v>1.41</v>
+      </c>
+      <c r="BH4">
+        <v>2.63</v>
+      </c>
+      <c r="BI4">
+        <v>1.7</v>
+      </c>
+      <c r="BJ4">
+        <v>2</v>
+      </c>
+      <c r="BK4">
+        <v>2.1</v>
+      </c>
+      <c r="BL4">
+        <v>1.62</v>
+      </c>
+      <c r="BM4">
+        <v>2.7</v>
+      </c>
+      <c r="BN4">
+        <v>1.38</v>
+      </c>
+      <c r="BO4">
+        <v>3.65</v>
+      </c>
+      <c r="BP4">
+        <v>1.22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="85">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -235,6 +235,9 @@
     <t>St Patrick's Athl.</t>
   </si>
   <si>
+    <t>Sligo Rovers</t>
+  </si>
+  <si>
     <t>Galway United</t>
   </si>
   <si>
@@ -244,6 +247,9 @@
     <t>Drogheda United</t>
   </si>
   <si>
+    <t>Waterford</t>
+  </si>
+  <si>
     <t>['34', '51']</t>
   </si>
   <si>
@@ -253,10 +259,16 @@
     <t>[]</t>
   </si>
   <si>
+    <t>['50', '82']</t>
+  </si>
+  <si>
     <t>['45+1', '81']</t>
   </si>
   <si>
     <t>['14']</t>
+  </si>
+  <si>
+    <t>['13', '33', '58']</t>
   </si>
 </sst>
 </file>
@@ -618,7 +630,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP4"/>
+  <dimension ref="A1:BP5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -850,7 +862,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -871,10 +883,10 @@
         <v>4</v>
       </c>
       <c r="O2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q2">
         <v>4.4</v>
@@ -1056,7 +1068,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I3">
         <v>3</v>
@@ -1077,10 +1089,10 @@
         <v>4</v>
       </c>
       <c r="O3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="Q3">
         <v>4</v>
@@ -1262,7 +1274,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1283,10 +1295,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -1442,6 +1454,212 @@
         <v>3.65</v>
       </c>
       <c r="BP4">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:68">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>7775619</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="2">
+        <v>45703.69791666666</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
+      </c>
+      <c r="N5">
+        <v>5</v>
+      </c>
+      <c r="O5" t="s">
+        <v>81</v>
+      </c>
+      <c r="P5" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q5">
+        <v>3</v>
+      </c>
+      <c r="R5">
+        <v>2.14</v>
+      </c>
+      <c r="S5">
+        <v>3.6</v>
+      </c>
+      <c r="T5">
+        <v>1.42</v>
+      </c>
+      <c r="U5">
+        <v>2.7</v>
+      </c>
+      <c r="V5">
+        <v>2.8</v>
+      </c>
+      <c r="W5">
+        <v>1.39</v>
+      </c>
+      <c r="X5">
+        <v>7.9</v>
+      </c>
+      <c r="Y5">
+        <v>1.02</v>
+      </c>
+      <c r="Z5">
+        <v>2.36</v>
+      </c>
+      <c r="AA5">
+        <v>3.23</v>
+      </c>
+      <c r="AB5">
+        <v>2.97</v>
+      </c>
+      <c r="AC5">
+        <v>1.06</v>
+      </c>
+      <c r="AD5">
+        <v>8.5</v>
+      </c>
+      <c r="AE5">
+        <v>1.31</v>
+      </c>
+      <c r="AF5">
+        <v>3.15</v>
+      </c>
+      <c r="AG5">
+        <v>1.95</v>
+      </c>
+      <c r="AH5">
+        <v>1.79</v>
+      </c>
+      <c r="AI5">
+        <v>1.74</v>
+      </c>
+      <c r="AJ5">
+        <v>1.98</v>
+      </c>
+      <c r="AK5">
+        <v>1.38</v>
+      </c>
+      <c r="AL5">
+        <v>1.3</v>
+      </c>
+      <c r="AM5">
+        <v>1.56</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>3</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>11</v>
+      </c>
+      <c r="AV5">
+        <v>5</v>
+      </c>
+      <c r="AW5">
+        <v>12</v>
+      </c>
+      <c r="AX5">
+        <v>1</v>
+      </c>
+      <c r="AY5">
+        <v>23</v>
+      </c>
+      <c r="AZ5">
+        <v>6</v>
+      </c>
+      <c r="BA5">
+        <v>6</v>
+      </c>
+      <c r="BB5">
+        <v>1</v>
+      </c>
+      <c r="BC5">
+        <v>7</v>
+      </c>
+      <c r="BD5">
+        <v>1.89</v>
+      </c>
+      <c r="BE5">
+        <v>6.25</v>
+      </c>
+      <c r="BF5">
+        <v>2.15</v>
+      </c>
+      <c r="BG5">
+        <v>1.4</v>
+      </c>
+      <c r="BH5">
+        <v>2.65</v>
+      </c>
+      <c r="BI5">
+        <v>1.7</v>
+      </c>
+      <c r="BJ5">
+        <v>2</v>
+      </c>
+      <c r="BK5">
+        <v>2.12</v>
+      </c>
+      <c r="BL5">
+        <v>1.62</v>
+      </c>
+      <c r="BM5">
+        <v>2.7</v>
+      </c>
+      <c r="BN5">
+        <v>1.38</v>
+      </c>
+      <c r="BO5">
+        <v>3.55</v>
+      </c>
+      <c r="BP5">
         <v>1.22</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="88">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -238,6 +238,9 @@
     <t>Sligo Rovers</t>
   </si>
   <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
     <t>Galway United</t>
   </si>
   <si>
@@ -250,6 +253,9 @@
     <t>Waterford</t>
   </si>
   <si>
+    <t>Shamrock Rovers</t>
+  </si>
+  <si>
     <t>['34', '51']</t>
   </si>
   <si>
@@ -260,6 +266,9 @@
   </si>
   <si>
     <t>['50', '82']</t>
+  </si>
+  <si>
+    <t>['25']</t>
   </si>
   <si>
     <t>['45+1', '81']</t>
@@ -630,7 +639,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP5"/>
+  <dimension ref="A1:BP6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -862,7 +871,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -883,10 +892,10 @@
         <v>4</v>
       </c>
       <c r="O2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="Q2">
         <v>4.4</v>
@@ -1068,7 +1077,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I3">
         <v>3</v>
@@ -1089,10 +1098,10 @@
         <v>4</v>
       </c>
       <c r="O3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="Q3">
         <v>4</v>
@@ -1274,7 +1283,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1295,10 +1304,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -1480,7 +1489,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1501,10 +1510,10 @@
         <v>5</v>
       </c>
       <c r="O5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -1661,6 +1670,212 @@
       </c>
       <c r="BP5">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:68">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>7775620</v>
+      </c>
+      <c r="C6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="2">
+        <v>45704.45833333334</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H6" t="s">
+        <v>79</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P6" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q6">
+        <v>3.4</v>
+      </c>
+      <c r="R6">
+        <v>2.1</v>
+      </c>
+      <c r="S6">
+        <v>3.2</v>
+      </c>
+      <c r="T6">
+        <v>1.4</v>
+      </c>
+      <c r="U6">
+        <v>2.75</v>
+      </c>
+      <c r="V6">
+        <v>3</v>
+      </c>
+      <c r="W6">
+        <v>1.36</v>
+      </c>
+      <c r="X6">
+        <v>8</v>
+      </c>
+      <c r="Y6">
+        <v>1.08</v>
+      </c>
+      <c r="Z6">
+        <v>2.59</v>
+      </c>
+      <c r="AA6">
+        <v>3.41</v>
+      </c>
+      <c r="AB6">
+        <v>2.56</v>
+      </c>
+      <c r="AC6">
+        <v>1.03</v>
+      </c>
+      <c r="AD6">
+        <v>9</v>
+      </c>
+      <c r="AE6">
+        <v>1.31</v>
+      </c>
+      <c r="AF6">
+        <v>3.15</v>
+      </c>
+      <c r="AG6">
+        <v>1.98</v>
+      </c>
+      <c r="AH6">
+        <v>1.77</v>
+      </c>
+      <c r="AI6">
+        <v>1.75</v>
+      </c>
+      <c r="AJ6">
+        <v>2</v>
+      </c>
+      <c r="AK6">
+        <v>1.55</v>
+      </c>
+      <c r="AL6">
+        <v>1.29</v>
+      </c>
+      <c r="AM6">
+        <v>1.39</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>3</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>4</v>
+      </c>
+      <c r="AV6">
+        <v>5</v>
+      </c>
+      <c r="AW6">
+        <v>3</v>
+      </c>
+      <c r="AX6">
+        <v>10</v>
+      </c>
+      <c r="AY6">
+        <v>7</v>
+      </c>
+      <c r="AZ6">
+        <v>15</v>
+      </c>
+      <c r="BA6">
+        <v>5</v>
+      </c>
+      <c r="BB6">
+        <v>2</v>
+      </c>
+      <c r="BC6">
+        <v>7</v>
+      </c>
+      <c r="BD6">
+        <v>2.23</v>
+      </c>
+      <c r="BE6">
+        <v>7</v>
+      </c>
+      <c r="BF6">
+        <v>1.76</v>
+      </c>
+      <c r="BG6">
+        <v>1.14</v>
+      </c>
+      <c r="BH6">
+        <v>4.6</v>
+      </c>
+      <c r="BI6">
+        <v>1.27</v>
+      </c>
+      <c r="BJ6">
+        <v>3.3</v>
+      </c>
+      <c r="BK6">
+        <v>1.46</v>
+      </c>
+      <c r="BL6">
+        <v>2.45</v>
+      </c>
+      <c r="BM6">
+        <v>1.73</v>
+      </c>
+      <c r="BN6">
+        <v>1.94</v>
+      </c>
+      <c r="BO6">
+        <v>2.12</v>
+      </c>
+      <c r="BP6">
+        <v>1.61</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="92">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -241,15 +241,15 @@
     <t>Bohemians</t>
   </si>
   <si>
+    <t>Derry City</t>
+  </si>
+  <si>
+    <t>Drogheda United</t>
+  </si>
+  <si>
     <t>Galway United</t>
   </si>
   <si>
-    <t>Derry City</t>
-  </si>
-  <si>
-    <t>Drogheda United</t>
-  </si>
-  <si>
     <t>Waterford</t>
   </si>
   <si>
@@ -271,6 +271,15 @@
     <t>['25']</t>
   </si>
   <si>
+    <t>['10']</t>
+  </si>
+  <si>
+    <t>['41', '74', '90+4']</t>
+  </si>
+  <si>
+    <t>['18', '25']</t>
+  </si>
+  <si>
     <t>['45+1', '81']</t>
   </si>
   <si>
@@ -278,6 +287,9 @@
   </si>
   <si>
     <t>['13', '33', '58']</t>
+  </si>
+  <si>
+    <t>['30']</t>
   </si>
 </sst>
 </file>
@@ -639,7 +651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP6"/>
+  <dimension ref="A1:BP10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -871,7 +883,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -895,7 +907,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="Q2">
         <v>4.4</v>
@@ -1077,7 +1089,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I3">
         <v>3</v>
@@ -1101,7 +1113,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Q3">
         <v>4</v>
@@ -1283,7 +1295,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1513,7 +1525,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -1876,6 +1888,830 @@
       </c>
       <c r="BP6">
         <v>1.61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:68">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>7775621</v>
+      </c>
+      <c r="C7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45709.69791666666</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H7" t="s">
+        <v>74</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7" t="s">
+        <v>85</v>
+      </c>
+      <c r="P7" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q7">
+        <v>2.44</v>
+      </c>
+      <c r="R7">
+        <v>2.17</v>
+      </c>
+      <c r="S7">
+        <v>4.6</v>
+      </c>
+      <c r="T7">
+        <v>1.42</v>
+      </c>
+      <c r="U7">
+        <v>2.7</v>
+      </c>
+      <c r="V7">
+        <v>2.8</v>
+      </c>
+      <c r="W7">
+        <v>1.38</v>
+      </c>
+      <c r="X7">
+        <v>6.9</v>
+      </c>
+      <c r="Y7">
+        <v>1.04</v>
+      </c>
+      <c r="Z7">
+        <v>1.89</v>
+      </c>
+      <c r="AA7">
+        <v>3.41</v>
+      </c>
+      <c r="AB7">
+        <v>4</v>
+      </c>
+      <c r="AC7">
+        <v>1.06</v>
+      </c>
+      <c r="AD7">
+        <v>8.5</v>
+      </c>
+      <c r="AE7">
+        <v>1.32</v>
+      </c>
+      <c r="AF7">
+        <v>3.1</v>
+      </c>
+      <c r="AG7">
+        <v>1.91</v>
+      </c>
+      <c r="AH7">
+        <v>1.73</v>
+      </c>
+      <c r="AI7">
+        <v>1.83</v>
+      </c>
+      <c r="AJ7">
+        <v>1.88</v>
+      </c>
+      <c r="AK7">
+        <v>1.23</v>
+      </c>
+      <c r="AL7">
+        <v>1.27</v>
+      </c>
+      <c r="AM7">
+        <v>1.86</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>3</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>5</v>
+      </c>
+      <c r="AV7">
+        <v>2</v>
+      </c>
+      <c r="AW7">
+        <v>7</v>
+      </c>
+      <c r="AX7">
+        <v>7</v>
+      </c>
+      <c r="AY7">
+        <v>12</v>
+      </c>
+      <c r="AZ7">
+        <v>9</v>
+      </c>
+      <c r="BA7">
+        <v>4</v>
+      </c>
+      <c r="BB7">
+        <v>2</v>
+      </c>
+      <c r="BC7">
+        <v>6</v>
+      </c>
+      <c r="BD7">
+        <v>1.58</v>
+      </c>
+      <c r="BE7">
+        <v>6.4</v>
+      </c>
+      <c r="BF7">
+        <v>2.65</v>
+      </c>
+      <c r="BG7">
+        <v>1.42</v>
+      </c>
+      <c r="BH7">
+        <v>2.55</v>
+      </c>
+      <c r="BI7">
+        <v>1.73</v>
+      </c>
+      <c r="BJ7">
+        <v>1.95</v>
+      </c>
+      <c r="BK7">
+        <v>2.18</v>
+      </c>
+      <c r="BL7">
+        <v>1.58</v>
+      </c>
+      <c r="BM7">
+        <v>2.8</v>
+      </c>
+      <c r="BN7">
+        <v>1.36</v>
+      </c>
+      <c r="BO7">
+        <v>3.8</v>
+      </c>
+      <c r="BP7">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:68">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>7775622</v>
+      </c>
+      <c r="C8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="2">
+        <v>45709.69791666666</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>3</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>3</v>
+      </c>
+      <c r="O8" t="s">
+        <v>86</v>
+      </c>
+      <c r="P8" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q8">
+        <v>2.82</v>
+      </c>
+      <c r="R8">
+        <v>2.08</v>
+      </c>
+      <c r="S8">
+        <v>3.88</v>
+      </c>
+      <c r="T8">
+        <v>1.38</v>
+      </c>
+      <c r="U8">
+        <v>2.76</v>
+      </c>
+      <c r="V8">
+        <v>2.93</v>
+      </c>
+      <c r="W8">
+        <v>1.34</v>
+      </c>
+      <c r="X8">
+        <v>8.1</v>
+      </c>
+      <c r="Y8">
+        <v>1.02</v>
+      </c>
+      <c r="Z8">
+        <v>2.29</v>
+      </c>
+      <c r="AA8">
+        <v>3.08</v>
+      </c>
+      <c r="AB8">
+        <v>3.25</v>
+      </c>
+      <c r="AC8">
+        <v>1.02</v>
+      </c>
+      <c r="AD8">
+        <v>8.1</v>
+      </c>
+      <c r="AE8">
+        <v>1.28</v>
+      </c>
+      <c r="AF8">
+        <v>3.2</v>
+      </c>
+      <c r="AG8">
+        <v>1.91</v>
+      </c>
+      <c r="AH8">
+        <v>1.73</v>
+      </c>
+      <c r="AI8">
+        <v>1.78</v>
+      </c>
+      <c r="AJ8">
+        <v>1.93</v>
+      </c>
+      <c r="AK8">
+        <v>1.34</v>
+      </c>
+      <c r="AL8">
+        <v>1.31</v>
+      </c>
+      <c r="AM8">
+        <v>1.68</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>3</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>8</v>
+      </c>
+      <c r="AV8">
+        <v>3</v>
+      </c>
+      <c r="AW8">
+        <v>3</v>
+      </c>
+      <c r="AX8">
+        <v>6</v>
+      </c>
+      <c r="AY8">
+        <v>11</v>
+      </c>
+      <c r="AZ8">
+        <v>9</v>
+      </c>
+      <c r="BA8">
+        <v>5</v>
+      </c>
+      <c r="BB8">
+        <v>6</v>
+      </c>
+      <c r="BC8">
+        <v>11</v>
+      </c>
+      <c r="BD8">
+        <v>1.74</v>
+      </c>
+      <c r="BE8">
+        <v>6.4</v>
+      </c>
+      <c r="BF8">
+        <v>2.32</v>
+      </c>
+      <c r="BG8">
+        <v>1.4</v>
+      </c>
+      <c r="BH8">
+        <v>2.65</v>
+      </c>
+      <c r="BI8">
+        <v>1.68</v>
+      </c>
+      <c r="BJ8">
+        <v>2</v>
+      </c>
+      <c r="BK8">
+        <v>2.1</v>
+      </c>
+      <c r="BL8">
+        <v>1.62</v>
+      </c>
+      <c r="BM8">
+        <v>2.7</v>
+      </c>
+      <c r="BN8">
+        <v>1.38</v>
+      </c>
+      <c r="BO8">
+        <v>3.55</v>
+      </c>
+      <c r="BP8">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:68">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>7775623</v>
+      </c>
+      <c r="C9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="2">
+        <v>45709.69791666666</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9" t="s">
+        <v>77</v>
+      </c>
+      <c r="H9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>3</v>
+      </c>
+      <c r="L9">
+        <v>2</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>3</v>
+      </c>
+      <c r="O9" t="s">
+        <v>87</v>
+      </c>
+      <c r="P9" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q9">
+        <v>3.5</v>
+      </c>
+      <c r="R9">
+        <v>1.98</v>
+      </c>
+      <c r="S9">
+        <v>3.45</v>
+      </c>
+      <c r="T9">
+        <v>1.53</v>
+      </c>
+      <c r="U9">
+        <v>2.37</v>
+      </c>
+      <c r="V9">
+        <v>3.3</v>
+      </c>
+      <c r="W9">
+        <v>1.29</v>
+      </c>
+      <c r="X9">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Y9">
+        <v>1.01</v>
+      </c>
+      <c r="Z9">
+        <v>2.93</v>
+      </c>
+      <c r="AA9">
+        <v>3.04</v>
+      </c>
+      <c r="AB9">
+        <v>2.5</v>
+      </c>
+      <c r="AC9">
+        <v>1.09</v>
+      </c>
+      <c r="AD9">
+        <v>7</v>
+      </c>
+      <c r="AE9">
+        <v>1.43</v>
+      </c>
+      <c r="AF9">
+        <v>2.55</v>
+      </c>
+      <c r="AG9">
+        <v>2.2</v>
+      </c>
+      <c r="AH9">
+        <v>1.55</v>
+      </c>
+      <c r="AI9">
+        <v>1.96</v>
+      </c>
+      <c r="AJ9">
+        <v>1.76</v>
+      </c>
+      <c r="AK9">
+        <v>1.45</v>
+      </c>
+      <c r="AL9">
+        <v>1.33</v>
+      </c>
+      <c r="AM9">
+        <v>1.43</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>3</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>6</v>
+      </c>
+      <c r="AV9">
+        <v>9</v>
+      </c>
+      <c r="AW9">
+        <v>7</v>
+      </c>
+      <c r="AX9">
+        <v>4</v>
+      </c>
+      <c r="AY9">
+        <v>13</v>
+      </c>
+      <c r="AZ9">
+        <v>13</v>
+      </c>
+      <c r="BA9">
+        <v>4</v>
+      </c>
+      <c r="BB9">
+        <v>8</v>
+      </c>
+      <c r="BC9">
+        <v>12</v>
+      </c>
+      <c r="BD9">
+        <v>1.98</v>
+      </c>
+      <c r="BE9">
+        <v>6.25</v>
+      </c>
+      <c r="BF9">
+        <v>2.02</v>
+      </c>
+      <c r="BG9">
+        <v>1.5</v>
+      </c>
+      <c r="BH9">
+        <v>2.35</v>
+      </c>
+      <c r="BI9">
+        <v>1.84</v>
+      </c>
+      <c r="BJ9">
+        <v>1.83</v>
+      </c>
+      <c r="BK9">
+        <v>2.33</v>
+      </c>
+      <c r="BL9">
+        <v>1.5</v>
+      </c>
+      <c r="BM9">
+        <v>3.05</v>
+      </c>
+      <c r="BN9">
+        <v>1.3</v>
+      </c>
+      <c r="BO9">
+        <v>4.1</v>
+      </c>
+      <c r="BP9">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:68">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>7775624</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="2">
+        <v>45709.69791666666</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H10" t="s">
+        <v>71</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10" t="s">
+        <v>82</v>
+      </c>
+      <c r="P10" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q10">
+        <v>4.33</v>
+      </c>
+      <c r="R10">
+        <v>1.99</v>
+      </c>
+      <c r="S10">
+        <v>2.79</v>
+      </c>
+      <c r="T10">
+        <v>1.44</v>
+      </c>
+      <c r="U10">
+        <v>2.53</v>
+      </c>
+      <c r="V10">
+        <v>3.26</v>
+      </c>
+      <c r="W10">
+        <v>1.28</v>
+      </c>
+      <c r="X10">
+        <v>8</v>
+      </c>
+      <c r="Y10">
+        <v>1.02</v>
+      </c>
+      <c r="Z10">
+        <v>3.71</v>
+      </c>
+      <c r="AA10">
+        <v>3.1</v>
+      </c>
+      <c r="AB10">
+        <v>2.09</v>
+      </c>
+      <c r="AC10">
+        <v>1.01</v>
+      </c>
+      <c r="AD10">
+        <v>8.6</v>
+      </c>
+      <c r="AE10">
+        <v>1.36</v>
+      </c>
+      <c r="AF10">
+        <v>2.78</v>
+      </c>
+      <c r="AG10">
+        <v>2.2</v>
+      </c>
+      <c r="AH10">
+        <v>1.55</v>
+      </c>
+      <c r="AI10">
+        <v>1.96</v>
+      </c>
+      <c r="AJ10">
+        <v>1.75</v>
+      </c>
+      <c r="AK10">
+        <v>1.73</v>
+      </c>
+      <c r="AL10">
+        <v>1.33</v>
+      </c>
+      <c r="AM10">
+        <v>1.29</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <v>3</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>2</v>
+      </c>
+      <c r="AV10">
+        <v>5</v>
+      </c>
+      <c r="AW10">
+        <v>8</v>
+      </c>
+      <c r="AX10">
+        <v>10</v>
+      </c>
+      <c r="AY10">
+        <v>10</v>
+      </c>
+      <c r="AZ10">
+        <v>15</v>
+      </c>
+      <c r="BA10">
+        <v>5</v>
+      </c>
+      <c r="BB10">
+        <v>2</v>
+      </c>
+      <c r="BC10">
+        <v>7</v>
+      </c>
+      <c r="BD10">
+        <v>2.33</v>
+      </c>
+      <c r="BE10">
+        <v>6.4</v>
+      </c>
+      <c r="BF10">
+        <v>1.74</v>
+      </c>
+      <c r="BG10">
+        <v>1.45</v>
+      </c>
+      <c r="BH10">
+        <v>2.48</v>
+      </c>
+      <c r="BI10">
+        <v>1.76</v>
+      </c>
+      <c r="BJ10">
+        <v>1.9</v>
+      </c>
+      <c r="BK10">
+        <v>2.23</v>
+      </c>
+      <c r="BL10">
+        <v>1.56</v>
+      </c>
+      <c r="BM10">
+        <v>2.9</v>
+      </c>
+      <c r="BN10">
+        <v>1.34</v>
+      </c>
+      <c r="BO10">
+        <v>3.9</v>
+      </c>
+      <c r="BP10">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="102">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -280,6 +280,21 @@
     <t>['18', '25']</t>
   </si>
   <si>
+    <t>['36', '37', '52', '79']</t>
+  </si>
+  <si>
+    <t>['2']</t>
+  </si>
+  <si>
+    <t>['35', '83']</t>
+  </si>
+  <si>
+    <t>['64']</t>
+  </si>
+  <si>
+    <t>['40']</t>
+  </si>
+  <si>
     <t>['45+1', '81']</t>
   </si>
   <si>
@@ -290,6 +305,21 @@
   </si>
   <si>
     <t>['30']</t>
+  </si>
+  <si>
+    <t>['40', '65', '78']</t>
+  </si>
+  <si>
+    <t>['16']</t>
+  </si>
+  <si>
+    <t>['21']</t>
+  </si>
+  <si>
+    <t>['9', '39']</t>
+  </si>
+  <si>
+    <t>['76']</t>
   </si>
 </sst>
 </file>
@@ -651,7 +681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP10"/>
+  <dimension ref="A1:BP15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -907,7 +937,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="Q2">
         <v>4.4</v>
@@ -985,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ2">
         <v>1</v>
@@ -1113,7 +1143,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="Q3">
         <v>4</v>
@@ -1191,7 +1221,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ3">
         <v>0</v>
@@ -1397,7 +1427,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ4">
         <v>1</v>
@@ -1525,7 +1555,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -1812,7 +1842,7 @@
         <v>3</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2015,7 +2045,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AQ7">
         <v>0</v>
@@ -2221,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ8">
         <v>0</v>
@@ -2349,7 +2379,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -2555,7 +2585,7 @@
         <v>82</v>
       </c>
       <c r="P10" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="Q10">
         <v>4.33</v>
@@ -2712,6 +2742,1036 @@
       </c>
       <c r="BP10">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:68">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>7775630</v>
+      </c>
+      <c r="C11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="2">
+        <v>45716.69791666666</v>
+      </c>
+      <c r="F11">
+        <v>3</v>
+      </c>
+      <c r="G11" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11" t="s">
+        <v>73</v>
+      </c>
+      <c r="I11">
+        <v>2</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>3</v>
+      </c>
+      <c r="L11">
+        <v>4</v>
+      </c>
+      <c r="M11">
+        <v>3</v>
+      </c>
+      <c r="N11">
+        <v>7</v>
+      </c>
+      <c r="O11" t="s">
+        <v>88</v>
+      </c>
+      <c r="P11" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q11">
+        <v>1.94</v>
+      </c>
+      <c r="R11">
+        <v>2.44</v>
+      </c>
+      <c r="S11">
+        <v>6.4</v>
+      </c>
+      <c r="T11">
+        <v>1.33</v>
+      </c>
+      <c r="U11">
+        <v>3.05</v>
+      </c>
+      <c r="V11">
+        <v>2.45</v>
+      </c>
+      <c r="W11">
+        <v>1.48</v>
+      </c>
+      <c r="X11">
+        <v>5.7</v>
+      </c>
+      <c r="Y11">
+        <v>1.11</v>
+      </c>
+      <c r="Z11">
+        <v>1.41</v>
+      </c>
+      <c r="AA11">
+        <v>4.6</v>
+      </c>
+      <c r="AB11">
+        <v>7.1</v>
+      </c>
+      <c r="AC11">
+        <v>1.02</v>
+      </c>
+      <c r="AD11">
+        <v>10</v>
+      </c>
+      <c r="AE11">
+        <v>1.24</v>
+      </c>
+      <c r="AF11">
+        <v>3.65</v>
+      </c>
+      <c r="AG11">
+        <v>1.89</v>
+      </c>
+      <c r="AH11">
+        <v>1.85</v>
+      </c>
+      <c r="AI11">
+        <v>1.89</v>
+      </c>
+      <c r="AJ11">
+        <v>1.81</v>
+      </c>
+      <c r="AK11">
+        <v>1.12</v>
+      </c>
+      <c r="AL11">
+        <v>1.19</v>
+      </c>
+      <c r="AM11">
+        <v>2.5</v>
+      </c>
+      <c r="AN11">
+        <v>1</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>2</v>
+      </c>
+      <c r="AQ11">
+        <v>0</v>
+      </c>
+      <c r="AR11">
+        <v>2.05</v>
+      </c>
+      <c r="AS11">
+        <v>1.12</v>
+      </c>
+      <c r="AT11">
+        <v>3.17</v>
+      </c>
+      <c r="AU11">
+        <v>9</v>
+      </c>
+      <c r="AV11">
+        <v>6</v>
+      </c>
+      <c r="AW11">
+        <v>8</v>
+      </c>
+      <c r="AX11">
+        <v>2</v>
+      </c>
+      <c r="AY11">
+        <v>17</v>
+      </c>
+      <c r="AZ11">
+        <v>8</v>
+      </c>
+      <c r="BA11">
+        <v>9</v>
+      </c>
+      <c r="BB11">
+        <v>2</v>
+      </c>
+      <c r="BC11">
+        <v>11</v>
+      </c>
+      <c r="BD11">
+        <v>1.42</v>
+      </c>
+      <c r="BE11">
+        <v>6.75</v>
+      </c>
+      <c r="BF11">
+        <v>3.3</v>
+      </c>
+      <c r="BG11">
+        <v>1.4</v>
+      </c>
+      <c r="BH11">
+        <v>2.65</v>
+      </c>
+      <c r="BI11">
+        <v>1.67</v>
+      </c>
+      <c r="BJ11">
+        <v>2.02</v>
+      </c>
+      <c r="BK11">
+        <v>2.08</v>
+      </c>
+      <c r="BL11">
+        <v>1.63</v>
+      </c>
+      <c r="BM11">
+        <v>2.7</v>
+      </c>
+      <c r="BN11">
+        <v>1.38</v>
+      </c>
+      <c r="BO11">
+        <v>3.55</v>
+      </c>
+      <c r="BP11">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:68">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>7775629</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="2">
+        <v>45716.69791666666</v>
+      </c>
+      <c r="F12">
+        <v>3</v>
+      </c>
+      <c r="G12" t="s">
+        <v>71</v>
+      </c>
+      <c r="H12" t="s">
+        <v>79</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>2</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>2</v>
+      </c>
+      <c r="O12" t="s">
+        <v>89</v>
+      </c>
+      <c r="P12" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q12">
+        <v>3.95</v>
+      </c>
+      <c r="R12">
+        <v>1.95</v>
+      </c>
+      <c r="S12">
+        <v>3.15</v>
+      </c>
+      <c r="T12">
+        <v>1.56</v>
+      </c>
+      <c r="U12">
+        <v>2.3</v>
+      </c>
+      <c r="V12">
+        <v>3.45</v>
+      </c>
+      <c r="W12">
+        <v>1.27</v>
+      </c>
+      <c r="X12">
+        <v>8.5</v>
+      </c>
+      <c r="Y12">
+        <v>1.01</v>
+      </c>
+      <c r="Z12">
+        <v>2.8</v>
+      </c>
+      <c r="AA12">
+        <v>3.06</v>
+      </c>
+      <c r="AB12">
+        <v>2.59</v>
+      </c>
+      <c r="AC12">
+        <v>1.09</v>
+      </c>
+      <c r="AD12">
+        <v>7</v>
+      </c>
+      <c r="AE12">
+        <v>1.61</v>
+      </c>
+      <c r="AF12">
+        <v>2.11</v>
+      </c>
+      <c r="AG12">
+        <v>2.3</v>
+      </c>
+      <c r="AH12">
+        <v>1.5</v>
+      </c>
+      <c r="AI12">
+        <v>2.05</v>
+      </c>
+      <c r="AJ12">
+        <v>1.7</v>
+      </c>
+      <c r="AK12">
+        <v>1.56</v>
+      </c>
+      <c r="AL12">
+        <v>1.32</v>
+      </c>
+      <c r="AM12">
+        <v>1.35</v>
+      </c>
+      <c r="AN12">
+        <v>3</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>2</v>
+      </c>
+      <c r="AQ12">
+        <v>0.5</v>
+      </c>
+      <c r="AR12">
+        <v>1.77</v>
+      </c>
+      <c r="AS12">
+        <v>1.71</v>
+      </c>
+      <c r="AT12">
+        <v>3.48</v>
+      </c>
+      <c r="AU12">
+        <v>4</v>
+      </c>
+      <c r="AV12">
+        <v>5</v>
+      </c>
+      <c r="AW12">
+        <v>14</v>
+      </c>
+      <c r="AX12">
+        <v>7</v>
+      </c>
+      <c r="AY12">
+        <v>18</v>
+      </c>
+      <c r="AZ12">
+        <v>12</v>
+      </c>
+      <c r="BA12">
+        <v>7</v>
+      </c>
+      <c r="BB12">
+        <v>3</v>
+      </c>
+      <c r="BC12">
+        <v>10</v>
+      </c>
+      <c r="BD12">
+        <v>2.17</v>
+      </c>
+      <c r="BE12">
+        <v>6.25</v>
+      </c>
+      <c r="BF12">
+        <v>1.85</v>
+      </c>
+      <c r="BG12">
+        <v>1.47</v>
+      </c>
+      <c r="BH12">
+        <v>2.4</v>
+      </c>
+      <c r="BI12">
+        <v>1.81</v>
+      </c>
+      <c r="BJ12">
+        <v>1.85</v>
+      </c>
+      <c r="BK12">
+        <v>2.3</v>
+      </c>
+      <c r="BL12">
+        <v>1.52</v>
+      </c>
+      <c r="BM12">
+        <v>3.05</v>
+      </c>
+      <c r="BN12">
+        <v>1.3</v>
+      </c>
+      <c r="BO12">
+        <v>4.1</v>
+      </c>
+      <c r="BP12">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:68">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>7775626</v>
+      </c>
+      <c r="C13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" s="2">
+        <v>45716.69791666666</v>
+      </c>
+      <c r="F13">
+        <v>3</v>
+      </c>
+      <c r="G13" t="s">
+        <v>70</v>
+      </c>
+      <c r="H13" t="s">
+        <v>74</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>2</v>
+      </c>
+      <c r="L13">
+        <v>2</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>3</v>
+      </c>
+      <c r="O13" t="s">
+        <v>90</v>
+      </c>
+      <c r="P13" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q13">
+        <v>3.9</v>
+      </c>
+      <c r="R13">
+        <v>1.95</v>
+      </c>
+      <c r="S13">
+        <v>2.8</v>
+      </c>
+      <c r="T13">
+        <v>1.49</v>
+      </c>
+      <c r="U13">
+        <v>2.45</v>
+      </c>
+      <c r="V13">
+        <v>3.25</v>
+      </c>
+      <c r="W13">
+        <v>1.29</v>
+      </c>
+      <c r="X13">
+        <v>9.25</v>
+      </c>
+      <c r="Y13">
+        <v>1.05</v>
+      </c>
+      <c r="Z13">
+        <v>3.5</v>
+      </c>
+      <c r="AA13">
+        <v>3.07</v>
+      </c>
+      <c r="AB13">
+        <v>2.18</v>
+      </c>
+      <c r="AC13">
+        <v>1.07</v>
+      </c>
+      <c r="AD13">
+        <v>8</v>
+      </c>
+      <c r="AE13">
+        <v>1.4</v>
+      </c>
+      <c r="AF13">
+        <v>2.7</v>
+      </c>
+      <c r="AG13">
+        <v>2.2</v>
+      </c>
+      <c r="AH13">
+        <v>1.55</v>
+      </c>
+      <c r="AI13">
+        <v>1.98</v>
+      </c>
+      <c r="AJ13">
+        <v>1.71</v>
+      </c>
+      <c r="AK13">
+        <v>1.65</v>
+      </c>
+      <c r="AL13">
+        <v>1.32</v>
+      </c>
+      <c r="AM13">
+        <v>1.31</v>
+      </c>
+      <c r="AN13">
+        <v>1</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>2</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>1.46</v>
+      </c>
+      <c r="AS13">
+        <v>0.93</v>
+      </c>
+      <c r="AT13">
+        <v>2.39</v>
+      </c>
+      <c r="AU13">
+        <v>4</v>
+      </c>
+      <c r="AV13">
+        <v>5</v>
+      </c>
+      <c r="AW13">
+        <v>8</v>
+      </c>
+      <c r="AX13">
+        <v>15</v>
+      </c>
+      <c r="AY13">
+        <v>12</v>
+      </c>
+      <c r="AZ13">
+        <v>20</v>
+      </c>
+      <c r="BA13">
+        <v>4</v>
+      </c>
+      <c r="BB13">
+        <v>9</v>
+      </c>
+      <c r="BC13">
+        <v>13</v>
+      </c>
+      <c r="BD13">
+        <v>2.3</v>
+      </c>
+      <c r="BE13">
+        <v>6.25</v>
+      </c>
+      <c r="BF13">
+        <v>1.76</v>
+      </c>
+      <c r="BG13">
+        <v>1.48</v>
+      </c>
+      <c r="BH13">
+        <v>2.4</v>
+      </c>
+      <c r="BI13">
+        <v>1.81</v>
+      </c>
+      <c r="BJ13">
+        <v>1.86</v>
+      </c>
+      <c r="BK13">
+        <v>2.28</v>
+      </c>
+      <c r="BL13">
+        <v>1.53</v>
+      </c>
+      <c r="BM13">
+        <v>3.05</v>
+      </c>
+      <c r="BN13">
+        <v>1.32</v>
+      </c>
+      <c r="BO13">
+        <v>4</v>
+      </c>
+      <c r="BP13">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:68">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>7775627</v>
+      </c>
+      <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="2">
+        <v>45716.69791666666</v>
+      </c>
+      <c r="F14">
+        <v>3</v>
+      </c>
+      <c r="G14" t="s">
+        <v>75</v>
+      </c>
+      <c r="H14" t="s">
+        <v>78</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>2</v>
+      </c>
+      <c r="K14">
+        <v>2</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>2</v>
+      </c>
+      <c r="N14">
+        <v>3</v>
+      </c>
+      <c r="O14" t="s">
+        <v>91</v>
+      </c>
+      <c r="P14" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q14">
+        <v>2.06</v>
+      </c>
+      <c r="R14">
+        <v>2.28</v>
+      </c>
+      <c r="S14">
+        <v>6.2</v>
+      </c>
+      <c r="T14">
+        <v>1.39</v>
+      </c>
+      <c r="U14">
+        <v>2.8</v>
+      </c>
+      <c r="V14">
+        <v>2.75</v>
+      </c>
+      <c r="W14">
+        <v>1.4</v>
+      </c>
+      <c r="X14">
+        <v>6.7</v>
+      </c>
+      <c r="Y14">
+        <v>1.05</v>
+      </c>
+      <c r="Z14">
+        <v>1.54</v>
+      </c>
+      <c r="AA14">
+        <v>3.88</v>
+      </c>
+      <c r="AB14">
+        <v>6.2</v>
+      </c>
+      <c r="AC14">
+        <v>1.01</v>
+      </c>
+      <c r="AD14">
+        <v>8.5</v>
+      </c>
+      <c r="AE14">
+        <v>1.31</v>
+      </c>
+      <c r="AF14">
+        <v>3.1</v>
+      </c>
+      <c r="AG14">
+        <v>1.98</v>
+      </c>
+      <c r="AH14">
+        <v>1.77</v>
+      </c>
+      <c r="AI14">
+        <v>2.03</v>
+      </c>
+      <c r="AJ14">
+        <v>1.7</v>
+      </c>
+      <c r="AK14">
+        <v>1.13</v>
+      </c>
+      <c r="AL14">
+        <v>1.21</v>
+      </c>
+      <c r="AM14">
+        <v>2.35</v>
+      </c>
+      <c r="AN14">
+        <v>3</v>
+      </c>
+      <c r="AO14">
+        <v>3</v>
+      </c>
+      <c r="AP14">
+        <v>1.5</v>
+      </c>
+      <c r="AQ14">
+        <v>3</v>
+      </c>
+      <c r="AR14">
+        <v>1.43</v>
+      </c>
+      <c r="AS14">
+        <v>0.85</v>
+      </c>
+      <c r="AT14">
+        <v>2.28</v>
+      </c>
+      <c r="AU14">
+        <v>8</v>
+      </c>
+      <c r="AV14">
+        <v>4</v>
+      </c>
+      <c r="AW14">
+        <v>8</v>
+      </c>
+      <c r="AX14">
+        <v>6</v>
+      </c>
+      <c r="AY14">
+        <v>16</v>
+      </c>
+      <c r="AZ14">
+        <v>10</v>
+      </c>
+      <c r="BA14">
+        <v>7</v>
+      </c>
+      <c r="BB14">
+        <v>1</v>
+      </c>
+      <c r="BC14">
+        <v>8</v>
+      </c>
+      <c r="BD14">
+        <v>1.42</v>
+      </c>
+      <c r="BE14">
+        <v>6.75</v>
+      </c>
+      <c r="BF14">
+        <v>3.3</v>
+      </c>
+      <c r="BG14">
+        <v>1.43</v>
+      </c>
+      <c r="BH14">
+        <v>2.55</v>
+      </c>
+      <c r="BI14">
+        <v>1.71</v>
+      </c>
+      <c r="BJ14">
+        <v>1.98</v>
+      </c>
+      <c r="BK14">
+        <v>2.14</v>
+      </c>
+      <c r="BL14">
+        <v>1.6</v>
+      </c>
+      <c r="BM14">
+        <v>2.8</v>
+      </c>
+      <c r="BN14">
+        <v>1.36</v>
+      </c>
+      <c r="BO14">
+        <v>3.65</v>
+      </c>
+      <c r="BP14">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:68">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>7775628</v>
+      </c>
+      <c r="C15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="2">
+        <v>45716.69791666666</v>
+      </c>
+      <c r="F15">
+        <v>3</v>
+      </c>
+      <c r="G15" t="s">
+        <v>76</v>
+      </c>
+      <c r="H15" t="s">
+        <v>77</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>2</v>
+      </c>
+      <c r="O15" t="s">
+        <v>92</v>
+      </c>
+      <c r="P15" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q15">
+        <v>4.5</v>
+      </c>
+      <c r="R15">
+        <v>2.01</v>
+      </c>
+      <c r="S15">
+        <v>2.7</v>
+      </c>
+      <c r="T15">
+        <v>1.52</v>
+      </c>
+      <c r="U15">
+        <v>2.4</v>
+      </c>
+      <c r="V15">
+        <v>3.25</v>
+      </c>
+      <c r="W15">
+        <v>1.3</v>
+      </c>
+      <c r="X15">
+        <v>8.1</v>
+      </c>
+      <c r="Y15">
+        <v>1.02</v>
+      </c>
+      <c r="Z15">
+        <v>4.2</v>
+      </c>
+      <c r="AA15">
+        <v>3.09</v>
+      </c>
+      <c r="AB15">
+        <v>1.96</v>
+      </c>
+      <c r="AC15">
+        <v>1.04</v>
+      </c>
+      <c r="AD15">
+        <v>6.85</v>
+      </c>
+      <c r="AE15">
+        <v>1.49</v>
+      </c>
+      <c r="AF15">
+        <v>2.36</v>
+      </c>
+      <c r="AG15">
+        <v>2.2</v>
+      </c>
+      <c r="AH15">
+        <v>1.55</v>
+      </c>
+      <c r="AI15">
+        <v>2.01</v>
+      </c>
+      <c r="AJ15">
+        <v>1.72</v>
+      </c>
+      <c r="AK15">
+        <v>1.7</v>
+      </c>
+      <c r="AL15">
+        <v>1.32</v>
+      </c>
+      <c r="AM15">
+        <v>1.26</v>
+      </c>
+      <c r="AN15">
+        <v>3</v>
+      </c>
+      <c r="AO15">
+        <v>1</v>
+      </c>
+      <c r="AP15">
+        <v>2</v>
+      </c>
+      <c r="AQ15">
+        <v>1</v>
+      </c>
+      <c r="AR15">
+        <v>1.54</v>
+      </c>
+      <c r="AS15">
+        <v>1.55</v>
+      </c>
+      <c r="AT15">
+        <v>3.09</v>
+      </c>
+      <c r="AU15">
+        <v>3</v>
+      </c>
+      <c r="AV15">
+        <v>4</v>
+      </c>
+      <c r="AW15">
+        <v>13</v>
+      </c>
+      <c r="AX15">
+        <v>10</v>
+      </c>
+      <c r="AY15">
+        <v>16</v>
+      </c>
+      <c r="AZ15">
+        <v>14</v>
+      </c>
+      <c r="BA15">
+        <v>3</v>
+      </c>
+      <c r="BB15">
+        <v>6</v>
+      </c>
+      <c r="BC15">
+        <v>9</v>
+      </c>
+      <c r="BD15">
+        <v>2.55</v>
+      </c>
+      <c r="BE15">
+        <v>6.25</v>
+      </c>
+      <c r="BF15">
+        <v>1.66</v>
+      </c>
+      <c r="BG15">
+        <v>1.45</v>
+      </c>
+      <c r="BH15">
+        <v>2.48</v>
+      </c>
+      <c r="BI15">
+        <v>1.77</v>
+      </c>
+      <c r="BJ15">
+        <v>1.89</v>
+      </c>
+      <c r="BK15">
+        <v>2.25</v>
+      </c>
+      <c r="BL15">
+        <v>1.55</v>
+      </c>
+      <c r="BM15">
+        <v>2.95</v>
+      </c>
+      <c r="BN15">
+        <v>1.33</v>
+      </c>
+      <c r="BO15">
+        <v>3.9</v>
+      </c>
+      <c r="BP15">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="110">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -295,6 +295,18 @@
     <t>['40']</t>
   </si>
   <si>
+    <t>['58']</t>
+  </si>
+  <si>
+    <t>['38', '78']</t>
+  </si>
+  <si>
+    <t>['16', '67']</t>
+  </si>
+  <si>
+    <t>['47', '87']</t>
+  </si>
+  <si>
     <t>['45+1', '81']</t>
   </si>
   <si>
@@ -320,6 +332,18 @@
   </si>
   <si>
     <t>['76']</t>
+  </si>
+  <si>
+    <t>['17']</t>
+  </si>
+  <si>
+    <t>['52']</t>
+  </si>
+  <si>
+    <t>['68']</t>
+  </si>
+  <si>
+    <t>['8']</t>
   </si>
 </sst>
 </file>
@@ -681,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP15"/>
+  <dimension ref="A1:BP20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -937,7 +961,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="Q2">
         <v>4.4</v>
@@ -1143,7 +1167,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="Q3">
         <v>4</v>
@@ -1427,10 +1451,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1555,7 +1579,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -1633,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ5">
         <v>3</v>
@@ -1839,10 +1863,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AQ6">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2379,7 +2403,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -2457,7 +2481,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ9">
         <v>0</v>
@@ -2585,7 +2609,7 @@
         <v>82</v>
       </c>
       <c r="P10" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="Q10">
         <v>4.33</v>
@@ -2663,10 +2687,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -2791,7 +2815,7 @@
         <v>88</v>
       </c>
       <c r="P11" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="Q11">
         <v>1.94</v>
@@ -2869,7 +2893,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ11">
         <v>0</v>
@@ -2997,7 +3021,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="Q12">
         <v>3.95</v>
@@ -3078,7 +3102,7 @@
         <v>2</v>
       </c>
       <c r="AQ12">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR12">
         <v>1.77</v>
@@ -3203,7 +3227,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="Q13">
         <v>3.9</v>
@@ -3409,7 +3433,7 @@
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="Q14">
         <v>2.06</v>
@@ -3615,7 +3639,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="Q15">
         <v>4.5</v>
@@ -3772,6 +3796,1036 @@
       </c>
       <c r="BP15">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:68">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>7775631</v>
+      </c>
+      <c r="C16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="2">
+        <v>45719.69791666666</v>
+      </c>
+      <c r="F16">
+        <v>4</v>
+      </c>
+      <c r="G16" t="s">
+        <v>74</v>
+      </c>
+      <c r="H16" t="s">
+        <v>76</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="O16" t="s">
+        <v>82</v>
+      </c>
+      <c r="P16" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q16">
+        <v>2.6</v>
+      </c>
+      <c r="R16">
+        <v>2</v>
+      </c>
+      <c r="S16">
+        <v>4.1</v>
+      </c>
+      <c r="T16">
+        <v>1.44</v>
+      </c>
+      <c r="U16">
+        <v>2.55</v>
+      </c>
+      <c r="V16">
+        <v>2.95</v>
+      </c>
+      <c r="W16">
+        <v>1.34</v>
+      </c>
+      <c r="X16">
+        <v>8</v>
+      </c>
+      <c r="Y16">
+        <v>1.07</v>
+      </c>
+      <c r="Z16">
+        <v>1.85</v>
+      </c>
+      <c r="AA16">
+        <v>3.36</v>
+      </c>
+      <c r="AB16">
+        <v>4.33</v>
+      </c>
+      <c r="AC16">
+        <v>1.06</v>
+      </c>
+      <c r="AD16">
+        <v>7.5</v>
+      </c>
+      <c r="AE16">
+        <v>1.36</v>
+      </c>
+      <c r="AF16">
+        <v>2.88</v>
+      </c>
+      <c r="AG16">
+        <v>2.1</v>
+      </c>
+      <c r="AH16">
+        <v>1.6</v>
+      </c>
+      <c r="AI16">
+        <v>1.93</v>
+      </c>
+      <c r="AJ16">
+        <v>1.75</v>
+      </c>
+      <c r="AK16">
+        <v>1.26</v>
+      </c>
+      <c r="AL16">
+        <v>1.33</v>
+      </c>
+      <c r="AM16">
+        <v>1.75</v>
+      </c>
+      <c r="AN16">
+        <v>3</v>
+      </c>
+      <c r="AO16">
+        <v>1</v>
+      </c>
+      <c r="AP16">
+        <v>1.5</v>
+      </c>
+      <c r="AQ16">
+        <v>2</v>
+      </c>
+      <c r="AR16">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AS16">
+        <v>0.59</v>
+      </c>
+      <c r="AT16">
+        <v>1.53</v>
+      </c>
+      <c r="AU16">
+        <v>3</v>
+      </c>
+      <c r="AV16">
+        <v>4</v>
+      </c>
+      <c r="AW16">
+        <v>8</v>
+      </c>
+      <c r="AX16">
+        <v>9</v>
+      </c>
+      <c r="AY16">
+        <v>11</v>
+      </c>
+      <c r="AZ16">
+        <v>13</v>
+      </c>
+      <c r="BA16">
+        <v>3</v>
+      </c>
+      <c r="BB16">
+        <v>4</v>
+      </c>
+      <c r="BC16">
+        <v>7</v>
+      </c>
+      <c r="BD16">
+        <v>1.58</v>
+      </c>
+      <c r="BE16">
+        <v>6.75</v>
+      </c>
+      <c r="BF16">
+        <v>2.65</v>
+      </c>
+      <c r="BG16">
+        <v>1.43</v>
+      </c>
+      <c r="BH16">
+        <v>2.55</v>
+      </c>
+      <c r="BI16">
+        <v>1.72</v>
+      </c>
+      <c r="BJ16">
+        <v>1.95</v>
+      </c>
+      <c r="BK16">
+        <v>2.18</v>
+      </c>
+      <c r="BL16">
+        <v>1.58</v>
+      </c>
+      <c r="BM16">
+        <v>2.8</v>
+      </c>
+      <c r="BN16">
+        <v>1.36</v>
+      </c>
+      <c r="BO16">
+        <v>3.8</v>
+      </c>
+      <c r="BP16">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:68">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>7775632</v>
+      </c>
+      <c r="C17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="2">
+        <v>45719.69791666666</v>
+      </c>
+      <c r="F17">
+        <v>4</v>
+      </c>
+      <c r="G17" t="s">
+        <v>77</v>
+      </c>
+      <c r="H17" t="s">
+        <v>71</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>2</v>
+      </c>
+      <c r="O17" t="s">
+        <v>93</v>
+      </c>
+      <c r="P17" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q17">
+        <v>3.1</v>
+      </c>
+      <c r="R17">
+        <v>1.82</v>
+      </c>
+      <c r="S17">
+        <v>4.1</v>
+      </c>
+      <c r="T17">
+        <v>1.61</v>
+      </c>
+      <c r="U17">
+        <v>2.15</v>
+      </c>
+      <c r="V17">
+        <v>3.8</v>
+      </c>
+      <c r="W17">
+        <v>1.23</v>
+      </c>
+      <c r="X17">
+        <v>11.5</v>
+      </c>
+      <c r="Y17">
+        <v>1.03</v>
+      </c>
+      <c r="Z17">
+        <v>2.38</v>
+      </c>
+      <c r="AA17">
+        <v>2.86</v>
+      </c>
+      <c r="AB17">
+        <v>3.34</v>
+      </c>
+      <c r="AC17">
+        <v>1.11</v>
+      </c>
+      <c r="AD17">
+        <v>5.5</v>
+      </c>
+      <c r="AE17">
+        <v>1.55</v>
+      </c>
+      <c r="AF17">
+        <v>2.2</v>
+      </c>
+      <c r="AG17">
+        <v>2.77</v>
+      </c>
+      <c r="AH17">
+        <v>1.39</v>
+      </c>
+      <c r="AI17">
+        <v>2.25</v>
+      </c>
+      <c r="AJ17">
+        <v>1.57</v>
+      </c>
+      <c r="AK17">
+        <v>1.3</v>
+      </c>
+      <c r="AL17">
+        <v>1.39</v>
+      </c>
+      <c r="AM17">
+        <v>1.57</v>
+      </c>
+      <c r="AN17">
+        <v>3</v>
+      </c>
+      <c r="AO17">
+        <v>3</v>
+      </c>
+      <c r="AP17">
+        <v>2</v>
+      </c>
+      <c r="AQ17">
+        <v>2</v>
+      </c>
+      <c r="AR17">
+        <v>1.58</v>
+      </c>
+      <c r="AS17">
+        <v>1.62</v>
+      </c>
+      <c r="AT17">
+        <v>3.2</v>
+      </c>
+      <c r="AU17">
+        <v>7</v>
+      </c>
+      <c r="AV17">
+        <v>5</v>
+      </c>
+      <c r="AW17">
+        <v>2</v>
+      </c>
+      <c r="AX17">
+        <v>9</v>
+      </c>
+      <c r="AY17">
+        <v>9</v>
+      </c>
+      <c r="AZ17">
+        <v>14</v>
+      </c>
+      <c r="BA17">
+        <v>3</v>
+      </c>
+      <c r="BB17">
+        <v>3</v>
+      </c>
+      <c r="BC17">
+        <v>6</v>
+      </c>
+      <c r="BD17">
+        <v>1.77</v>
+      </c>
+      <c r="BE17">
+        <v>6.1</v>
+      </c>
+      <c r="BF17">
+        <v>2.3</v>
+      </c>
+      <c r="BG17">
+        <v>1.56</v>
+      </c>
+      <c r="BH17">
+        <v>2.2</v>
+      </c>
+      <c r="BI17">
+        <v>1.95</v>
+      </c>
+      <c r="BJ17">
+        <v>1.72</v>
+      </c>
+      <c r="BK17">
+        <v>2.55</v>
+      </c>
+      <c r="BL17">
+        <v>1.43</v>
+      </c>
+      <c r="BM17">
+        <v>3.4</v>
+      </c>
+      <c r="BN17">
+        <v>1.25</v>
+      </c>
+      <c r="BO17">
+        <v>4.6</v>
+      </c>
+      <c r="BP17">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:68">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>7775633</v>
+      </c>
+      <c r="C18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" s="2">
+        <v>45719.69791666666</v>
+      </c>
+      <c r="F18">
+        <v>4</v>
+      </c>
+      <c r="G18" t="s">
+        <v>73</v>
+      </c>
+      <c r="H18" t="s">
+        <v>79</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>2</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>3</v>
+      </c>
+      <c r="O18" t="s">
+        <v>94</v>
+      </c>
+      <c r="P18" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q18">
+        <v>4.2</v>
+      </c>
+      <c r="R18">
+        <v>2.2</v>
+      </c>
+      <c r="S18">
+        <v>2.3</v>
+      </c>
+      <c r="T18">
+        <v>1.35</v>
+      </c>
+      <c r="U18">
+        <v>2.9</v>
+      </c>
+      <c r="V18">
+        <v>2.7</v>
+      </c>
+      <c r="W18">
+        <v>1.4</v>
+      </c>
+      <c r="X18">
+        <v>7</v>
+      </c>
+      <c r="Y18">
+        <v>1.08</v>
+      </c>
+      <c r="Z18">
+        <v>3.92</v>
+      </c>
+      <c r="AA18">
+        <v>4.3</v>
+      </c>
+      <c r="AB18">
+        <v>1.72</v>
+      </c>
+      <c r="AC18">
+        <v>1.02</v>
+      </c>
+      <c r="AD18">
+        <v>10</v>
+      </c>
+      <c r="AE18">
+        <v>1.29</v>
+      </c>
+      <c r="AF18">
+        <v>3.4</v>
+      </c>
+      <c r="AG18">
+        <v>1.85</v>
+      </c>
+      <c r="AH18">
+        <v>1.89</v>
+      </c>
+      <c r="AI18">
+        <v>1.82</v>
+      </c>
+      <c r="AJ18">
+        <v>1.87</v>
+      </c>
+      <c r="AK18">
+        <v>2</v>
+      </c>
+      <c r="AL18">
+        <v>1.23</v>
+      </c>
+      <c r="AM18">
+        <v>1.23</v>
+      </c>
+      <c r="AN18">
+        <v>0</v>
+      </c>
+      <c r="AO18">
+        <v>0.5</v>
+      </c>
+      <c r="AP18">
+        <v>1.5</v>
+      </c>
+      <c r="AQ18">
+        <v>0.33</v>
+      </c>
+      <c r="AR18">
+        <v>2.63</v>
+      </c>
+      <c r="AS18">
+        <v>1.56</v>
+      </c>
+      <c r="AT18">
+        <v>4.19</v>
+      </c>
+      <c r="AU18">
+        <v>5</v>
+      </c>
+      <c r="AV18">
+        <v>4</v>
+      </c>
+      <c r="AW18">
+        <v>3</v>
+      </c>
+      <c r="AX18">
+        <v>18</v>
+      </c>
+      <c r="AY18">
+        <v>8</v>
+      </c>
+      <c r="AZ18">
+        <v>22</v>
+      </c>
+      <c r="BA18">
+        <v>3</v>
+      </c>
+      <c r="BB18">
+        <v>6</v>
+      </c>
+      <c r="BC18">
+        <v>9</v>
+      </c>
+      <c r="BD18">
+        <v>2.89</v>
+      </c>
+      <c r="BE18">
+        <v>9</v>
+      </c>
+      <c r="BF18">
+        <v>1.57</v>
+      </c>
+      <c r="BG18">
+        <v>1.25</v>
+      </c>
+      <c r="BH18">
+        <v>3.6</v>
+      </c>
+      <c r="BI18">
+        <v>1.35</v>
+      </c>
+      <c r="BJ18">
+        <v>2.74</v>
+      </c>
+      <c r="BK18">
+        <v>1.69</v>
+      </c>
+      <c r="BL18">
+        <v>2.12</v>
+      </c>
+      <c r="BM18">
+        <v>2.09</v>
+      </c>
+      <c r="BN18">
+        <v>1.71</v>
+      </c>
+      <c r="BO18">
+        <v>2.67</v>
+      </c>
+      <c r="BP18">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:68">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>7775634</v>
+      </c>
+      <c r="C19" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="2">
+        <v>45719.69791666666</v>
+      </c>
+      <c r="F19">
+        <v>4</v>
+      </c>
+      <c r="G19" t="s">
+        <v>72</v>
+      </c>
+      <c r="H19" t="s">
+        <v>75</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>2</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>2</v>
+      </c>
+      <c r="O19" t="s">
+        <v>95</v>
+      </c>
+      <c r="P19" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q19">
+        <v>3.3</v>
+      </c>
+      <c r="R19">
+        <v>1.98</v>
+      </c>
+      <c r="S19">
+        <v>3.2</v>
+      </c>
+      <c r="T19">
+        <v>1.47</v>
+      </c>
+      <c r="U19">
+        <v>2.5</v>
+      </c>
+      <c r="V19">
+        <v>3.2</v>
+      </c>
+      <c r="W19">
+        <v>1.3</v>
+      </c>
+      <c r="X19">
+        <v>9</v>
+      </c>
+      <c r="Y19">
+        <v>1.06</v>
+      </c>
+      <c r="Z19">
+        <v>2.56</v>
+      </c>
+      <c r="AA19">
+        <v>3.25</v>
+      </c>
+      <c r="AB19">
+        <v>2.7</v>
+      </c>
+      <c r="AC19">
+        <v>1.06</v>
+      </c>
+      <c r="AD19">
+        <v>7.5</v>
+      </c>
+      <c r="AE19">
+        <v>1.38</v>
+      </c>
+      <c r="AF19">
+        <v>2.8</v>
+      </c>
+      <c r="AG19">
+        <v>2.15</v>
+      </c>
+      <c r="AH19">
+        <v>1.57</v>
+      </c>
+      <c r="AI19">
+        <v>1.93</v>
+      </c>
+      <c r="AJ19">
+        <v>1.75</v>
+      </c>
+      <c r="AK19">
+        <v>1.47</v>
+      </c>
+      <c r="AL19">
+        <v>1.32</v>
+      </c>
+      <c r="AM19">
+        <v>1.44</v>
+      </c>
+      <c r="AN19">
+        <v>2</v>
+      </c>
+      <c r="AO19">
+        <v>0</v>
+      </c>
+      <c r="AP19">
+        <v>2.33</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>2.01</v>
+      </c>
+      <c r="AS19">
+        <v>1.5</v>
+      </c>
+      <c r="AT19">
+        <v>3.51</v>
+      </c>
+      <c r="AU19">
+        <v>5</v>
+      </c>
+      <c r="AV19">
+        <v>0</v>
+      </c>
+      <c r="AW19">
+        <v>12</v>
+      </c>
+      <c r="AX19">
+        <v>4</v>
+      </c>
+      <c r="AY19">
+        <v>17</v>
+      </c>
+      <c r="AZ19">
+        <v>4</v>
+      </c>
+      <c r="BA19">
+        <v>7</v>
+      </c>
+      <c r="BB19">
+        <v>0</v>
+      </c>
+      <c r="BC19">
+        <v>7</v>
+      </c>
+      <c r="BD19">
+        <v>1.98</v>
+      </c>
+      <c r="BE19">
+        <v>6.1</v>
+      </c>
+      <c r="BF19">
+        <v>2</v>
+      </c>
+      <c r="BG19">
+        <v>1.45</v>
+      </c>
+      <c r="BH19">
+        <v>2.48</v>
+      </c>
+      <c r="BI19">
+        <v>1.77</v>
+      </c>
+      <c r="BJ19">
+        <v>1.9</v>
+      </c>
+      <c r="BK19">
+        <v>2.23</v>
+      </c>
+      <c r="BL19">
+        <v>1.56</v>
+      </c>
+      <c r="BM19">
+        <v>2.9</v>
+      </c>
+      <c r="BN19">
+        <v>1.34</v>
+      </c>
+      <c r="BO19">
+        <v>3.9</v>
+      </c>
+      <c r="BP19">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:68">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>7775635</v>
+      </c>
+      <c r="C20" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="2">
+        <v>45719.69791666666</v>
+      </c>
+      <c r="F20">
+        <v>4</v>
+      </c>
+      <c r="G20" t="s">
+        <v>78</v>
+      </c>
+      <c r="H20" t="s">
+        <v>70</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>2</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+      <c r="N20">
+        <v>3</v>
+      </c>
+      <c r="O20" t="s">
+        <v>96</v>
+      </c>
+      <c r="P20" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q20">
+        <v>2.65</v>
+      </c>
+      <c r="R20">
+        <v>2.05</v>
+      </c>
+      <c r="S20">
+        <v>3.9</v>
+      </c>
+      <c r="T20">
+        <v>1.4</v>
+      </c>
+      <c r="U20">
+        <v>2.7</v>
+      </c>
+      <c r="V20">
+        <v>2.8</v>
+      </c>
+      <c r="W20">
+        <v>1.38</v>
+      </c>
+      <c r="X20">
+        <v>7.25</v>
+      </c>
+      <c r="Y20">
+        <v>1.08</v>
+      </c>
+      <c r="Z20">
+        <v>2.21</v>
+      </c>
+      <c r="AA20">
+        <v>3.18</v>
+      </c>
+      <c r="AB20">
+        <v>3.29</v>
+      </c>
+      <c r="AC20">
+        <v>1.07</v>
+      </c>
+      <c r="AD20">
+        <v>8</v>
+      </c>
+      <c r="AE20">
+        <v>1.35</v>
+      </c>
+      <c r="AF20">
+        <v>3.1</v>
+      </c>
+      <c r="AG20">
+        <v>1.95</v>
+      </c>
+      <c r="AH20">
+        <v>1.73</v>
+      </c>
+      <c r="AI20">
+        <v>1.8</v>
+      </c>
+      <c r="AJ20">
+        <v>1.88</v>
+      </c>
+      <c r="AK20">
+        <v>1.29</v>
+      </c>
+      <c r="AL20">
+        <v>1.31</v>
+      </c>
+      <c r="AM20">
+        <v>1.7</v>
+      </c>
+      <c r="AN20">
+        <v>0</v>
+      </c>
+      <c r="AO20">
+        <v>0</v>
+      </c>
+      <c r="AP20">
+        <v>1.5</v>
+      </c>
+      <c r="AQ20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>0.9</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0.9</v>
+      </c>
+      <c r="AU20">
+        <v>8</v>
+      </c>
+      <c r="AV20">
+        <v>3</v>
+      </c>
+      <c r="AW20">
+        <v>19</v>
+      </c>
+      <c r="AX20">
+        <v>6</v>
+      </c>
+      <c r="AY20">
+        <v>27</v>
+      </c>
+      <c r="AZ20">
+        <v>9</v>
+      </c>
+      <c r="BA20">
+        <v>11</v>
+      </c>
+      <c r="BB20">
+        <v>5</v>
+      </c>
+      <c r="BC20">
+        <v>16</v>
+      </c>
+      <c r="BD20">
+        <v>1.79</v>
+      </c>
+      <c r="BE20">
+        <v>6.25</v>
+      </c>
+      <c r="BF20">
+        <v>2.25</v>
+      </c>
+      <c r="BG20">
+        <v>1.44</v>
+      </c>
+      <c r="BH20">
+        <v>2.5</v>
+      </c>
+      <c r="BI20">
+        <v>1.75</v>
+      </c>
+      <c r="BJ20">
+        <v>1.92</v>
+      </c>
+      <c r="BK20">
+        <v>2.2</v>
+      </c>
+      <c r="BL20">
+        <v>1.56</v>
+      </c>
+      <c r="BM20">
+        <v>2.9</v>
+      </c>
+      <c r="BN20">
+        <v>1.34</v>
+      </c>
+      <c r="BO20">
+        <v>3.9</v>
+      </c>
+      <c r="BP20">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="115">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -307,6 +307,12 @@
     <t>['47', '87']</t>
   </si>
   <si>
+    <t>['53']</t>
+  </si>
+  <si>
+    <t>['62']</t>
+  </si>
+  <si>
     <t>['45+1', '81']</t>
   </si>
   <si>
@@ -344,6 +350,15 @@
   </si>
   <si>
     <t>['8']</t>
+  </si>
+  <si>
+    <t>['15', '34', '42']</t>
+  </si>
+  <si>
+    <t>['44']</t>
+  </si>
+  <si>
+    <t>['4']</t>
   </si>
 </sst>
 </file>
@@ -705,7 +720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP20"/>
+  <dimension ref="A1:BP25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -961,7 +976,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q2">
         <v>4.4</v>
@@ -1039,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ2">
         <v>1</v>
@@ -1167,7 +1182,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Q3">
         <v>4</v>
@@ -1245,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ3">
         <v>0</v>
@@ -1454,7 +1469,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ4">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1579,7 +1594,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -2069,10 +2084,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2278,7 +2293,7 @@
         <v>2</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2403,7 +2418,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -2609,7 +2624,7 @@
         <v>82</v>
       </c>
       <c r="P10" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Q10">
         <v>4.33</v>
@@ -2687,7 +2702,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AQ10">
         <v>2</v>
@@ -2815,7 +2830,7 @@
         <v>88</v>
       </c>
       <c r="P11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q11">
         <v>1.94</v>
@@ -2896,7 +2911,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR11">
         <v>2.05</v>
@@ -3021,7 +3036,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Q12">
         <v>3.95</v>
@@ -3099,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ12">
         <v>0.33</v>
@@ -3227,7 +3242,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Q13">
         <v>3.9</v>
@@ -3305,10 +3320,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR13">
         <v>1.46</v>
@@ -3433,7 +3448,7 @@
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Q14">
         <v>2.06</v>
@@ -3511,7 +3526,7 @@
         <v>3</v>
       </c>
       <c r="AP14">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ14">
         <v>3</v>
@@ -3639,7 +3654,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Q15">
         <v>4.5</v>
@@ -3845,7 +3860,7 @@
         <v>82</v>
       </c>
       <c r="P16" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -3926,7 +3941,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ16">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR16">
         <v>0.9399999999999999</v>
@@ -4051,7 +4066,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Q17">
         <v>3.1</v>
@@ -4257,7 +4272,7 @@
         <v>94</v>
       </c>
       <c r="P18" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="Q18">
         <v>4.2</v>
@@ -4669,7 +4684,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="Q20">
         <v>2.65</v>
@@ -4747,7 +4762,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AQ20">
         <v>0</v>
@@ -4826,6 +4841,1036 @@
       </c>
       <c r="BP20">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:68">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>7775640</v>
+      </c>
+      <c r="C21" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="2">
+        <v>45723.69791666666</v>
+      </c>
+      <c r="F21">
+        <v>5</v>
+      </c>
+      <c r="G21" t="s">
+        <v>79</v>
+      </c>
+      <c r="H21" t="s">
+        <v>72</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>1</v>
+      </c>
+      <c r="O21" t="s">
+        <v>91</v>
+      </c>
+      <c r="P21" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q21">
+        <v>2.75</v>
+      </c>
+      <c r="R21">
+        <v>2</v>
+      </c>
+      <c r="S21">
+        <v>3.8</v>
+      </c>
+      <c r="T21">
+        <v>1.41</v>
+      </c>
+      <c r="U21">
+        <v>2.65</v>
+      </c>
+      <c r="V21">
+        <v>2.75</v>
+      </c>
+      <c r="W21">
+        <v>1.39</v>
+      </c>
+      <c r="X21">
+        <v>7</v>
+      </c>
+      <c r="Y21">
+        <v>1.08</v>
+      </c>
+      <c r="Z21">
+        <v>2.29</v>
+      </c>
+      <c r="AA21">
+        <v>3.07</v>
+      </c>
+      <c r="AB21">
+        <v>3.25</v>
+      </c>
+      <c r="AC21">
+        <v>1.07</v>
+      </c>
+      <c r="AD21">
+        <v>8</v>
+      </c>
+      <c r="AE21">
+        <v>1.31</v>
+      </c>
+      <c r="AF21">
+        <v>3.28</v>
+      </c>
+      <c r="AG21">
+        <v>1.91</v>
+      </c>
+      <c r="AH21">
+        <v>1.73</v>
+      </c>
+      <c r="AI21">
+        <v>1.77</v>
+      </c>
+      <c r="AJ21">
+        <v>1.93</v>
+      </c>
+      <c r="AK21">
+        <v>1.3</v>
+      </c>
+      <c r="AL21">
+        <v>1.33</v>
+      </c>
+      <c r="AM21">
+        <v>1.65</v>
+      </c>
+      <c r="AN21">
+        <v>0</v>
+      </c>
+      <c r="AO21">
+        <v>0</v>
+      </c>
+      <c r="AP21">
+        <v>3</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>1.73</v>
+      </c>
+      <c r="AT21">
+        <v>1.73</v>
+      </c>
+      <c r="AU21">
+        <v>4</v>
+      </c>
+      <c r="AV21">
+        <v>2</v>
+      </c>
+      <c r="AW21">
+        <v>9</v>
+      </c>
+      <c r="AX21">
+        <v>9</v>
+      </c>
+      <c r="AY21">
+        <v>13</v>
+      </c>
+      <c r="AZ21">
+        <v>11</v>
+      </c>
+      <c r="BA21">
+        <v>4</v>
+      </c>
+      <c r="BB21">
+        <v>2</v>
+      </c>
+      <c r="BC21">
+        <v>6</v>
+      </c>
+      <c r="BD21">
+        <v>1.67</v>
+      </c>
+      <c r="BE21">
+        <v>6.5</v>
+      </c>
+      <c r="BF21">
+        <v>2.45</v>
+      </c>
+      <c r="BG21">
+        <v>1.33</v>
+      </c>
+      <c r="BH21">
+        <v>2.95</v>
+      </c>
+      <c r="BI21">
+        <v>1.56</v>
+      </c>
+      <c r="BJ21">
+        <v>2.2</v>
+      </c>
+      <c r="BK21">
+        <v>1.91</v>
+      </c>
+      <c r="BL21">
+        <v>1.75</v>
+      </c>
+      <c r="BM21">
+        <v>2.43</v>
+      </c>
+      <c r="BN21">
+        <v>1.47</v>
+      </c>
+      <c r="BO21">
+        <v>3.15</v>
+      </c>
+      <c r="BP21">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:68">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>7775639</v>
+      </c>
+      <c r="C22" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="2">
+        <v>45723.69791666666</v>
+      </c>
+      <c r="F22">
+        <v>5</v>
+      </c>
+      <c r="G22" t="s">
+        <v>78</v>
+      </c>
+      <c r="H22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>3</v>
+      </c>
+      <c r="K22">
+        <v>3</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>3</v>
+      </c>
+      <c r="N22">
+        <v>3</v>
+      </c>
+      <c r="O22" t="s">
+        <v>82</v>
+      </c>
+      <c r="P22" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q22">
+        <v>3.5</v>
+      </c>
+      <c r="R22">
+        <v>2</v>
+      </c>
+      <c r="S22">
+        <v>2.9</v>
+      </c>
+      <c r="T22">
+        <v>1.42</v>
+      </c>
+      <c r="U22">
+        <v>2.65</v>
+      </c>
+      <c r="V22">
+        <v>2.9</v>
+      </c>
+      <c r="W22">
+        <v>1.36</v>
+      </c>
+      <c r="X22">
+        <v>7.75</v>
+      </c>
+      <c r="Y22">
+        <v>1.07</v>
+      </c>
+      <c r="Z22">
+        <v>2.73</v>
+      </c>
+      <c r="AA22">
+        <v>3.28</v>
+      </c>
+      <c r="AB22">
+        <v>2.51</v>
+      </c>
+      <c r="AC22">
+        <v>1.07</v>
+      </c>
+      <c r="AD22">
+        <v>8</v>
+      </c>
+      <c r="AE22">
+        <v>1.32</v>
+      </c>
+      <c r="AF22">
+        <v>3.19</v>
+      </c>
+      <c r="AG22">
+        <v>1.98</v>
+      </c>
+      <c r="AH22">
+        <v>1.77</v>
+      </c>
+      <c r="AI22">
+        <v>1.8</v>
+      </c>
+      <c r="AJ22">
+        <v>1.88</v>
+      </c>
+      <c r="AK22">
+        <v>1.57</v>
+      </c>
+      <c r="AL22">
+        <v>1.32</v>
+      </c>
+      <c r="AM22">
+        <v>1.36</v>
+      </c>
+      <c r="AN22">
+        <v>1.5</v>
+      </c>
+      <c r="AO22">
+        <v>0</v>
+      </c>
+      <c r="AP22">
+        <v>1</v>
+      </c>
+      <c r="AQ22">
+        <v>1</v>
+      </c>
+      <c r="AR22">
+        <v>1.81</v>
+      </c>
+      <c r="AS22">
+        <v>1.5</v>
+      </c>
+      <c r="AT22">
+        <v>3.31</v>
+      </c>
+      <c r="AU22">
+        <v>8</v>
+      </c>
+      <c r="AV22">
+        <v>4</v>
+      </c>
+      <c r="AW22">
+        <v>4</v>
+      </c>
+      <c r="AX22">
+        <v>4</v>
+      </c>
+      <c r="AY22">
+        <v>12</v>
+      </c>
+      <c r="AZ22">
+        <v>8</v>
+      </c>
+      <c r="BA22">
+        <v>6</v>
+      </c>
+      <c r="BB22">
+        <v>2</v>
+      </c>
+      <c r="BC22">
+        <v>8</v>
+      </c>
+      <c r="BD22">
+        <v>2.07</v>
+      </c>
+      <c r="BE22">
+        <v>6.4</v>
+      </c>
+      <c r="BF22">
+        <v>1.91</v>
+      </c>
+      <c r="BG22">
+        <v>1.27</v>
+      </c>
+      <c r="BH22">
+        <v>3.3</v>
+      </c>
+      <c r="BI22">
+        <v>1.46</v>
+      </c>
+      <c r="BJ22">
+        <v>2.45</v>
+      </c>
+      <c r="BK22">
+        <v>1.75</v>
+      </c>
+      <c r="BL22">
+        <v>1.92</v>
+      </c>
+      <c r="BM22">
+        <v>2.18</v>
+      </c>
+      <c r="BN22">
+        <v>1.58</v>
+      </c>
+      <c r="BO22">
+        <v>2.8</v>
+      </c>
+      <c r="BP22">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:68">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>7775637</v>
+      </c>
+      <c r="C23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="2">
+        <v>45723.69791666666</v>
+      </c>
+      <c r="F23">
+        <v>5</v>
+      </c>
+      <c r="G23" t="s">
+        <v>75</v>
+      </c>
+      <c r="H23" t="s">
+        <v>77</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+      <c r="N23">
+        <v>2</v>
+      </c>
+      <c r="O23" t="s">
+        <v>97</v>
+      </c>
+      <c r="P23" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q23">
+        <v>2.7</v>
+      </c>
+      <c r="R23">
+        <v>1.95</v>
+      </c>
+      <c r="S23">
+        <v>4.1</v>
+      </c>
+      <c r="T23">
+        <v>1.52</v>
+      </c>
+      <c r="U23">
+        <v>2.35</v>
+      </c>
+      <c r="V23">
+        <v>3.6</v>
+      </c>
+      <c r="W23">
+        <v>1.25</v>
+      </c>
+      <c r="X23">
+        <v>10.5</v>
+      </c>
+      <c r="Y23">
+        <v>1.04</v>
+      </c>
+      <c r="Z23">
+        <v>1.98</v>
+      </c>
+      <c r="AA23">
+        <v>3.33</v>
+      </c>
+      <c r="AB23">
+        <v>3.78</v>
+      </c>
+      <c r="AC23">
+        <v>1.09</v>
+      </c>
+      <c r="AD23">
+        <v>7</v>
+      </c>
+      <c r="AE23">
+        <v>1.53</v>
+      </c>
+      <c r="AF23">
+        <v>2.5</v>
+      </c>
+      <c r="AG23">
+        <v>2.25</v>
+      </c>
+      <c r="AH23">
+        <v>1.53</v>
+      </c>
+      <c r="AI23">
+        <v>2.15</v>
+      </c>
+      <c r="AJ23">
+        <v>1.6</v>
+      </c>
+      <c r="AK23">
+        <v>1.28</v>
+      </c>
+      <c r="AL23">
+        <v>1.3</v>
+      </c>
+      <c r="AM23">
+        <v>1.75</v>
+      </c>
+      <c r="AN23">
+        <v>1.5</v>
+      </c>
+      <c r="AO23">
+        <v>1</v>
+      </c>
+      <c r="AP23">
+        <v>1.33</v>
+      </c>
+      <c r="AQ23">
+        <v>1</v>
+      </c>
+      <c r="AR23">
+        <v>1.72</v>
+      </c>
+      <c r="AS23">
+        <v>1.51</v>
+      </c>
+      <c r="AT23">
+        <v>3.23</v>
+      </c>
+      <c r="AU23">
+        <v>6</v>
+      </c>
+      <c r="AV23">
+        <v>3</v>
+      </c>
+      <c r="AW23">
+        <v>20</v>
+      </c>
+      <c r="AX23">
+        <v>4</v>
+      </c>
+      <c r="AY23">
+        <v>26</v>
+      </c>
+      <c r="AZ23">
+        <v>7</v>
+      </c>
+      <c r="BA23">
+        <v>7</v>
+      </c>
+      <c r="BB23">
+        <v>1</v>
+      </c>
+      <c r="BC23">
+        <v>8</v>
+      </c>
+      <c r="BD23">
+        <v>1.7</v>
+      </c>
+      <c r="BE23">
+        <v>6.4</v>
+      </c>
+      <c r="BF23">
+        <v>2.4</v>
+      </c>
+      <c r="BG23">
+        <v>1.38</v>
+      </c>
+      <c r="BH23">
+        <v>2.7</v>
+      </c>
+      <c r="BI23">
+        <v>1.65</v>
+      </c>
+      <c r="BJ23">
+        <v>2.06</v>
+      </c>
+      <c r="BK23">
+        <v>2.05</v>
+      </c>
+      <c r="BL23">
+        <v>1.65</v>
+      </c>
+      <c r="BM23">
+        <v>2.65</v>
+      </c>
+      <c r="BN23">
+        <v>1.4</v>
+      </c>
+      <c r="BO23">
+        <v>3.45</v>
+      </c>
+      <c r="BP23">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:68">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>7775636</v>
+      </c>
+      <c r="C24" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" s="2">
+        <v>45723.69791666666</v>
+      </c>
+      <c r="F24">
+        <v>5</v>
+      </c>
+      <c r="G24" t="s">
+        <v>70</v>
+      </c>
+      <c r="H24" t="s">
+        <v>73</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="M24">
+        <v>1</v>
+      </c>
+      <c r="N24">
+        <v>2</v>
+      </c>
+      <c r="O24" t="s">
+        <v>98</v>
+      </c>
+      <c r="P24" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q24">
+        <v>2.75</v>
+      </c>
+      <c r="R24">
+        <v>2.05</v>
+      </c>
+      <c r="S24">
+        <v>3.7</v>
+      </c>
+      <c r="T24">
+        <v>1.43</v>
+      </c>
+      <c r="U24">
+        <v>2.6</v>
+      </c>
+      <c r="V24">
+        <v>3</v>
+      </c>
+      <c r="W24">
+        <v>1.33</v>
+      </c>
+      <c r="X24">
+        <v>8.25</v>
+      </c>
+      <c r="Y24">
+        <v>1.06</v>
+      </c>
+      <c r="Z24">
+        <v>2.23</v>
+      </c>
+      <c r="AA24">
+        <v>3.34</v>
+      </c>
+      <c r="AB24">
+        <v>3.1</v>
+      </c>
+      <c r="AC24">
+        <v>1.05</v>
+      </c>
+      <c r="AD24">
+        <v>8</v>
+      </c>
+      <c r="AE24">
+        <v>1</v>
+      </c>
+      <c r="AF24">
+        <v>1</v>
+      </c>
+      <c r="AG24">
+        <v>1.85</v>
+      </c>
+      <c r="AH24">
+        <v>1.89</v>
+      </c>
+      <c r="AI24">
+        <v>1.93</v>
+      </c>
+      <c r="AJ24">
+        <v>1.75</v>
+      </c>
+      <c r="AK24">
+        <v>1.33</v>
+      </c>
+      <c r="AL24">
+        <v>1.3</v>
+      </c>
+      <c r="AM24">
+        <v>1.65</v>
+      </c>
+      <c r="AN24">
+        <v>2</v>
+      </c>
+      <c r="AO24">
+        <v>0</v>
+      </c>
+      <c r="AP24">
+        <v>1.67</v>
+      </c>
+      <c r="AQ24">
+        <v>0.33</v>
+      </c>
+      <c r="AR24">
+        <v>1.36</v>
+      </c>
+      <c r="AS24">
+        <v>1.06</v>
+      </c>
+      <c r="AT24">
+        <v>2.42</v>
+      </c>
+      <c r="AU24">
+        <v>7</v>
+      </c>
+      <c r="AV24">
+        <v>3</v>
+      </c>
+      <c r="AW24">
+        <v>15</v>
+      </c>
+      <c r="AX24">
+        <v>6</v>
+      </c>
+      <c r="AY24">
+        <v>22</v>
+      </c>
+      <c r="AZ24">
+        <v>9</v>
+      </c>
+      <c r="BA24">
+        <v>12</v>
+      </c>
+      <c r="BB24">
+        <v>2</v>
+      </c>
+      <c r="BC24">
+        <v>14</v>
+      </c>
+      <c r="BD24">
+        <v>1.68</v>
+      </c>
+      <c r="BE24">
+        <v>6.5</v>
+      </c>
+      <c r="BF24">
+        <v>2.4</v>
+      </c>
+      <c r="BG24">
+        <v>1.4</v>
+      </c>
+      <c r="BH24">
+        <v>2.65</v>
+      </c>
+      <c r="BI24">
+        <v>1.66</v>
+      </c>
+      <c r="BJ24">
+        <v>2.04</v>
+      </c>
+      <c r="BK24">
+        <v>2.06</v>
+      </c>
+      <c r="BL24">
+        <v>1.65</v>
+      </c>
+      <c r="BM24">
+        <v>2.65</v>
+      </c>
+      <c r="BN24">
+        <v>1.4</v>
+      </c>
+      <c r="BO24">
+        <v>3.45</v>
+      </c>
+      <c r="BP24">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:68">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>7775638</v>
+      </c>
+      <c r="C25" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" t="s">
+        <v>69</v>
+      </c>
+      <c r="E25" s="2">
+        <v>45723.69791666666</v>
+      </c>
+      <c r="F25">
+        <v>5</v>
+      </c>
+      <c r="G25" t="s">
+        <v>71</v>
+      </c>
+      <c r="H25" t="s">
+        <v>76</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>1</v>
+      </c>
+      <c r="K25">
+        <v>1</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>1</v>
+      </c>
+      <c r="N25">
+        <v>1</v>
+      </c>
+      <c r="O25" t="s">
+        <v>82</v>
+      </c>
+      <c r="P25" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q25">
+        <v>2.35</v>
+      </c>
+      <c r="R25">
+        <v>2.05</v>
+      </c>
+      <c r="S25">
+        <v>4.8</v>
+      </c>
+      <c r="T25">
+        <v>1.44</v>
+      </c>
+      <c r="U25">
+        <v>2.55</v>
+      </c>
+      <c r="V25">
+        <v>3.1</v>
+      </c>
+      <c r="W25">
+        <v>1.32</v>
+      </c>
+      <c r="X25">
+        <v>8.5</v>
+      </c>
+      <c r="Y25">
+        <v>1.06</v>
+      </c>
+      <c r="Z25">
+        <v>1.76</v>
+      </c>
+      <c r="AA25">
+        <v>3.45</v>
+      </c>
+      <c r="AB25">
+        <v>4.75</v>
+      </c>
+      <c r="AC25">
+        <v>1.07</v>
+      </c>
+      <c r="AD25">
+        <v>7.75</v>
+      </c>
+      <c r="AE25">
+        <v>1.5</v>
+      </c>
+      <c r="AF25">
+        <v>2.4</v>
+      </c>
+      <c r="AG25">
+        <v>2.05</v>
+      </c>
+      <c r="AH25">
+        <v>1.65</v>
+      </c>
+      <c r="AI25">
+        <v>2.1</v>
+      </c>
+      <c r="AJ25">
+        <v>1.65</v>
+      </c>
+      <c r="AK25">
+        <v>1.19</v>
+      </c>
+      <c r="AL25">
+        <v>1.27</v>
+      </c>
+      <c r="AM25">
+        <v>2</v>
+      </c>
+      <c r="AN25">
+        <v>2</v>
+      </c>
+      <c r="AO25">
+        <v>2</v>
+      </c>
+      <c r="AP25">
+        <v>1.33</v>
+      </c>
+      <c r="AQ25">
+        <v>2.33</v>
+      </c>
+      <c r="AR25">
+        <v>1.82</v>
+      </c>
+      <c r="AS25">
+        <v>0.98</v>
+      </c>
+      <c r="AT25">
+        <v>2.8</v>
+      </c>
+      <c r="AU25">
+        <v>3</v>
+      </c>
+      <c r="AV25">
+        <v>5</v>
+      </c>
+      <c r="AW25">
+        <v>15</v>
+      </c>
+      <c r="AX25">
+        <v>5</v>
+      </c>
+      <c r="AY25">
+        <v>18</v>
+      </c>
+      <c r="AZ25">
+        <v>10</v>
+      </c>
+      <c r="BA25">
+        <v>6</v>
+      </c>
+      <c r="BB25">
+        <v>3</v>
+      </c>
+      <c r="BC25">
+        <v>9</v>
+      </c>
+      <c r="BD25">
+        <v>1.5</v>
+      </c>
+      <c r="BE25">
+        <v>6.4</v>
+      </c>
+      <c r="BF25">
+        <v>2.9</v>
+      </c>
+      <c r="BG25">
+        <v>1.63</v>
+      </c>
+      <c r="BH25">
+        <v>2.08</v>
+      </c>
+      <c r="BI25">
+        <v>2.05</v>
+      </c>
+      <c r="BJ25">
+        <v>1.65</v>
+      </c>
+      <c r="BK25">
+        <v>2.65</v>
+      </c>
+      <c r="BL25">
+        <v>1.4</v>
+      </c>
+      <c r="BM25">
+        <v>3.65</v>
+      </c>
+      <c r="BN25">
+        <v>1.22</v>
+      </c>
+      <c r="BO25">
+        <v>4.9</v>
+      </c>
+      <c r="BP25">
+        <v>1.12</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="121">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -313,6 +313,18 @@
     <t>['62']</t>
   </si>
   <si>
+    <t>['33']</t>
+  </si>
+  <si>
+    <t>['80']</t>
+  </si>
+  <si>
+    <t>['70']</t>
+  </si>
+  <si>
+    <t>['17', '83', '90']</t>
+  </si>
+  <si>
     <t>['45+1', '81']</t>
   </si>
   <si>
@@ -359,6 +371,12 @@
   </si>
   <si>
     <t>['4']</t>
+  </si>
+  <si>
+    <t>['41', '70']</t>
+  </si>
+  <si>
+    <t>['50']</t>
   </si>
 </sst>
 </file>
@@ -720,7 +738,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP25"/>
+  <dimension ref="A1:BP29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -976,7 +994,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="Q2">
         <v>4.4</v>
@@ -1182,7 +1200,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="Q3">
         <v>4</v>
@@ -1260,7 +1278,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ3">
         <v>0</v>
@@ -1466,7 +1484,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ4">
         <v>2.33</v>
@@ -1594,7 +1612,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -1675,7 +1693,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -1881,7 +1899,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ6">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2087,7 +2105,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2290,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ8">
         <v>0.33</v>
@@ -2418,7 +2436,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -2496,7 +2514,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ9">
         <v>0</v>
@@ -2624,7 +2642,7 @@
         <v>82</v>
       </c>
       <c r="P10" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="Q10">
         <v>4.33</v>
@@ -2830,7 +2848,7 @@
         <v>88</v>
       </c>
       <c r="P11" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="Q11">
         <v>1.94</v>
@@ -2908,7 +2926,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ11">
         <v>0.33</v>
@@ -3036,7 +3054,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="Q12">
         <v>3.95</v>
@@ -3114,10 +3132,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ12">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AR12">
         <v>1.77</v>
@@ -3242,7 +3260,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="Q13">
         <v>3.9</v>
@@ -3323,7 +3341,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ13">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AR13">
         <v>1.46</v>
@@ -3448,7 +3466,7 @@
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="Q14">
         <v>2.06</v>
@@ -3529,7 +3547,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR14">
         <v>1.43</v>
@@ -3654,7 +3672,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="Q15">
         <v>4.5</v>
@@ -3732,7 +3750,7 @@
         <v>1</v>
       </c>
       <c r="AP15">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ15">
         <v>1</v>
@@ -3860,7 +3878,7 @@
         <v>82</v>
       </c>
       <c r="P16" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4066,7 +4084,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="Q17">
         <v>3.1</v>
@@ -4144,7 +4162,7 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ17">
         <v>2</v>
@@ -4272,7 +4290,7 @@
         <v>94</v>
       </c>
       <c r="P18" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="Q18">
         <v>4.2</v>
@@ -4353,7 +4371,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ18">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AR18">
         <v>2.63</v>
@@ -4556,7 +4574,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ19">
         <v>0</v>
@@ -4684,7 +4702,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="Q20">
         <v>2.65</v>
@@ -4765,7 +4783,7 @@
         <v>1</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR20">
         <v>0.9</v>
@@ -5096,7 +5114,7 @@
         <v>82</v>
       </c>
       <c r="P22" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="Q22">
         <v>3.5</v>
@@ -5177,7 +5195,7 @@
         <v>1</v>
       </c>
       <c r="AQ22">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AR22">
         <v>1.81</v>
@@ -5302,7 +5320,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="Q23">
         <v>2.7</v>
@@ -5714,7 +5732,7 @@
         <v>82</v>
       </c>
       <c r="P25" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="Q25">
         <v>2.35</v>
@@ -5792,7 +5810,7 @@
         <v>2</v>
       </c>
       <c r="AP25">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ25">
         <v>2.33</v>
@@ -5871,6 +5889,830 @@
       </c>
       <c r="BP25">
         <v>1.12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:68">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>7775641</v>
+      </c>
+      <c r="C26" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" t="s">
+        <v>69</v>
+      </c>
+      <c r="E26" s="2">
+        <v>45730.69791666666</v>
+      </c>
+      <c r="F26">
+        <v>6</v>
+      </c>
+      <c r="G26" t="s">
+        <v>76</v>
+      </c>
+      <c r="H26" t="s">
+        <v>79</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="J26">
+        <v>1</v>
+      </c>
+      <c r="K26">
+        <v>2</v>
+      </c>
+      <c r="L26">
+        <v>1</v>
+      </c>
+      <c r="M26">
+        <v>2</v>
+      </c>
+      <c r="N26">
+        <v>3</v>
+      </c>
+      <c r="O26" t="s">
+        <v>99</v>
+      </c>
+      <c r="P26" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q26">
+        <v>4.75</v>
+      </c>
+      <c r="R26">
+        <v>2</v>
+      </c>
+      <c r="S26">
+        <v>2.63</v>
+      </c>
+      <c r="T26">
+        <v>1.5</v>
+      </c>
+      <c r="U26">
+        <v>2.5</v>
+      </c>
+      <c r="V26">
+        <v>3.5</v>
+      </c>
+      <c r="W26">
+        <v>1.29</v>
+      </c>
+      <c r="X26">
+        <v>11</v>
+      </c>
+      <c r="Y26">
+        <v>1.05</v>
+      </c>
+      <c r="Z26">
+        <v>3.86</v>
+      </c>
+      <c r="AA26">
+        <v>3.61</v>
+      </c>
+      <c r="AB26">
+        <v>1.87</v>
+      </c>
+      <c r="AC26">
+        <v>1.07</v>
+      </c>
+      <c r="AD26">
+        <v>8</v>
+      </c>
+      <c r="AE26">
+        <v>1.48</v>
+      </c>
+      <c r="AF26">
+        <v>2.39</v>
+      </c>
+      <c r="AG26">
+        <v>2.2</v>
+      </c>
+      <c r="AH26">
+        <v>1.55</v>
+      </c>
+      <c r="AI26">
+        <v>2.05</v>
+      </c>
+      <c r="AJ26">
+        <v>1.7</v>
+      </c>
+      <c r="AK26">
+        <v>1.8</v>
+      </c>
+      <c r="AL26">
+        <v>1.25</v>
+      </c>
+      <c r="AM26">
+        <v>1.25</v>
+      </c>
+      <c r="AN26">
+        <v>2</v>
+      </c>
+      <c r="AO26">
+        <v>0.33</v>
+      </c>
+      <c r="AP26">
+        <v>1.33</v>
+      </c>
+      <c r="AQ26">
+        <v>1</v>
+      </c>
+      <c r="AR26">
+        <v>1.55</v>
+      </c>
+      <c r="AS26">
+        <v>1.73</v>
+      </c>
+      <c r="AT26">
+        <v>3.28</v>
+      </c>
+      <c r="AU26">
+        <v>3</v>
+      </c>
+      <c r="AV26">
+        <v>8</v>
+      </c>
+      <c r="AW26">
+        <v>9</v>
+      </c>
+      <c r="AX26">
+        <v>12</v>
+      </c>
+      <c r="AY26">
+        <v>12</v>
+      </c>
+      <c r="AZ26">
+        <v>20</v>
+      </c>
+      <c r="BA26">
+        <v>4</v>
+      </c>
+      <c r="BB26">
+        <v>6</v>
+      </c>
+      <c r="BC26">
+        <v>10</v>
+      </c>
+      <c r="BD26">
+        <v>2.48</v>
+      </c>
+      <c r="BE26">
+        <v>6.4</v>
+      </c>
+      <c r="BF26">
+        <v>1.66</v>
+      </c>
+      <c r="BG26">
+        <v>1.41</v>
+      </c>
+      <c r="BH26">
+        <v>2.6</v>
+      </c>
+      <c r="BI26">
+        <v>1.7</v>
+      </c>
+      <c r="BJ26">
+        <v>1.98</v>
+      </c>
+      <c r="BK26">
+        <v>2.12</v>
+      </c>
+      <c r="BL26">
+        <v>1.61</v>
+      </c>
+      <c r="BM26">
+        <v>2.7</v>
+      </c>
+      <c r="BN26">
+        <v>1.38</v>
+      </c>
+      <c r="BO26">
+        <v>3.65</v>
+      </c>
+      <c r="BP26">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:68">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>7775642</v>
+      </c>
+      <c r="C27" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" s="2">
+        <v>45730.69791666666</v>
+      </c>
+      <c r="F27">
+        <v>6</v>
+      </c>
+      <c r="G27" t="s">
+        <v>77</v>
+      </c>
+      <c r="H27" t="s">
+        <v>78</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>1</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>1</v>
+      </c>
+      <c r="O27" t="s">
+        <v>100</v>
+      </c>
+      <c r="P27" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q27">
+        <v>2.5</v>
+      </c>
+      <c r="R27">
+        <v>2.05</v>
+      </c>
+      <c r="S27">
+        <v>5</v>
+      </c>
+      <c r="T27">
+        <v>1.5</v>
+      </c>
+      <c r="U27">
+        <v>2.5</v>
+      </c>
+      <c r="V27">
+        <v>3.4</v>
+      </c>
+      <c r="W27">
+        <v>1.3</v>
+      </c>
+      <c r="X27">
+        <v>10</v>
+      </c>
+      <c r="Y27">
+        <v>1.06</v>
+      </c>
+      <c r="Z27">
+        <v>1.8</v>
+      </c>
+      <c r="AA27">
+        <v>3.45</v>
+      </c>
+      <c r="AB27">
+        <v>4.5</v>
+      </c>
+      <c r="AC27">
+        <v>1.07</v>
+      </c>
+      <c r="AD27">
+        <v>8</v>
+      </c>
+      <c r="AE27">
+        <v>1.38</v>
+      </c>
+      <c r="AF27">
+        <v>3</v>
+      </c>
+      <c r="AG27">
+        <v>2.05</v>
+      </c>
+      <c r="AH27">
+        <v>1.65</v>
+      </c>
+      <c r="AI27">
+        <v>2</v>
+      </c>
+      <c r="AJ27">
+        <v>1.75</v>
+      </c>
+      <c r="AK27">
+        <v>1.2</v>
+      </c>
+      <c r="AL27">
+        <v>1.25</v>
+      </c>
+      <c r="AM27">
+        <v>1.93</v>
+      </c>
+      <c r="AN27">
+        <v>2</v>
+      </c>
+      <c r="AO27">
+        <v>3</v>
+      </c>
+      <c r="AP27">
+        <v>2.33</v>
+      </c>
+      <c r="AQ27">
+        <v>2</v>
+      </c>
+      <c r="AR27">
+        <v>1.49</v>
+      </c>
+      <c r="AS27">
+        <v>0.95</v>
+      </c>
+      <c r="AT27">
+        <v>2.44</v>
+      </c>
+      <c r="AU27">
+        <v>5</v>
+      </c>
+      <c r="AV27">
+        <v>3</v>
+      </c>
+      <c r="AW27">
+        <v>14</v>
+      </c>
+      <c r="AX27">
+        <v>8</v>
+      </c>
+      <c r="AY27">
+        <v>21</v>
+      </c>
+      <c r="AZ27">
+        <v>13</v>
+      </c>
+      <c r="BA27">
+        <v>4</v>
+      </c>
+      <c r="BB27">
+        <v>3</v>
+      </c>
+      <c r="BC27">
+        <v>7</v>
+      </c>
+      <c r="BD27">
+        <v>1.58</v>
+      </c>
+      <c r="BE27">
+        <v>6.75</v>
+      </c>
+      <c r="BF27">
+        <v>2.63</v>
+      </c>
+      <c r="BG27">
+        <v>1.36</v>
+      </c>
+      <c r="BH27">
+        <v>2.8</v>
+      </c>
+      <c r="BI27">
+        <v>1.62</v>
+      </c>
+      <c r="BJ27">
+        <v>2.1</v>
+      </c>
+      <c r="BK27">
+        <v>2</v>
+      </c>
+      <c r="BL27">
+        <v>1.68</v>
+      </c>
+      <c r="BM27">
+        <v>2.55</v>
+      </c>
+      <c r="BN27">
+        <v>1.42</v>
+      </c>
+      <c r="BO27">
+        <v>3.4</v>
+      </c>
+      <c r="BP27">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:68">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>7775643</v>
+      </c>
+      <c r="C28" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28" s="2">
+        <v>45730.69791666666</v>
+      </c>
+      <c r="F28">
+        <v>6</v>
+      </c>
+      <c r="G28" t="s">
+        <v>71</v>
+      </c>
+      <c r="H28" t="s">
+        <v>70</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
+      <c r="M28">
+        <v>1</v>
+      </c>
+      <c r="N28">
+        <v>2</v>
+      </c>
+      <c r="O28" t="s">
+        <v>101</v>
+      </c>
+      <c r="P28" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q28">
+        <v>2.3</v>
+      </c>
+      <c r="R28">
+        <v>2.05</v>
+      </c>
+      <c r="S28">
+        <v>6.5</v>
+      </c>
+      <c r="T28">
+        <v>1.5</v>
+      </c>
+      <c r="U28">
+        <v>2.5</v>
+      </c>
+      <c r="V28">
+        <v>3.5</v>
+      </c>
+      <c r="W28">
+        <v>1.29</v>
+      </c>
+      <c r="X28">
+        <v>11</v>
+      </c>
+      <c r="Y28">
+        <v>1.05</v>
+      </c>
+      <c r="Z28">
+        <v>1.61</v>
+      </c>
+      <c r="AA28">
+        <v>3.6</v>
+      </c>
+      <c r="AB28">
+        <v>5.8</v>
+      </c>
+      <c r="AC28">
+        <v>1.07</v>
+      </c>
+      <c r="AD28">
+        <v>8</v>
+      </c>
+      <c r="AE28">
+        <v>1.42</v>
+      </c>
+      <c r="AF28">
+        <v>2.8</v>
+      </c>
+      <c r="AG28">
+        <v>2.15</v>
+      </c>
+      <c r="AH28">
+        <v>1.57</v>
+      </c>
+      <c r="AI28">
+        <v>2.25</v>
+      </c>
+      <c r="AJ28">
+        <v>1.57</v>
+      </c>
+      <c r="AK28">
+        <v>1.15</v>
+      </c>
+      <c r="AL28">
+        <v>1.22</v>
+      </c>
+      <c r="AM28">
+        <v>2.15</v>
+      </c>
+      <c r="AN28">
+        <v>1.33</v>
+      </c>
+      <c r="AO28">
+        <v>0</v>
+      </c>
+      <c r="AP28">
+        <v>1.25</v>
+      </c>
+      <c r="AQ28">
+        <v>0.5</v>
+      </c>
+      <c r="AR28">
+        <v>1.81</v>
+      </c>
+      <c r="AS28">
+        <v>0.97</v>
+      </c>
+      <c r="AT28">
+        <v>2.78</v>
+      </c>
+      <c r="AU28">
+        <v>5</v>
+      </c>
+      <c r="AV28">
+        <v>3</v>
+      </c>
+      <c r="AW28">
+        <v>13</v>
+      </c>
+      <c r="AX28">
+        <v>1</v>
+      </c>
+      <c r="AY28">
+        <v>18</v>
+      </c>
+      <c r="AZ28">
+        <v>4</v>
+      </c>
+      <c r="BA28">
+        <v>5</v>
+      </c>
+      <c r="BB28">
+        <v>5</v>
+      </c>
+      <c r="BC28">
+        <v>10</v>
+      </c>
+      <c r="BD28">
+        <v>1.48</v>
+      </c>
+      <c r="BE28">
+        <v>6.75</v>
+      </c>
+      <c r="BF28">
+        <v>2.95</v>
+      </c>
+      <c r="BG28">
+        <v>1.57</v>
+      </c>
+      <c r="BH28">
+        <v>2.2</v>
+      </c>
+      <c r="BI28">
+        <v>1.95</v>
+      </c>
+      <c r="BJ28">
+        <v>1.72</v>
+      </c>
+      <c r="BK28">
+        <v>2.55</v>
+      </c>
+      <c r="BL28">
+        <v>1.43</v>
+      </c>
+      <c r="BM28">
+        <v>3.4</v>
+      </c>
+      <c r="BN28">
+        <v>1.25</v>
+      </c>
+      <c r="BO28">
+        <v>4.6</v>
+      </c>
+      <c r="BP28">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:68">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>7775644</v>
+      </c>
+      <c r="C29" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" t="s">
+        <v>69</v>
+      </c>
+      <c r="E29" s="2">
+        <v>45730.69791666666</v>
+      </c>
+      <c r="F29">
+        <v>6</v>
+      </c>
+      <c r="G29" t="s">
+        <v>72</v>
+      </c>
+      <c r="H29" t="s">
+        <v>74</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="L29">
+        <v>3</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>3</v>
+      </c>
+      <c r="O29" t="s">
+        <v>102</v>
+      </c>
+      <c r="P29" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q29">
+        <v>2.4</v>
+      </c>
+      <c r="R29">
+        <v>2.2</v>
+      </c>
+      <c r="S29">
+        <v>4.75</v>
+      </c>
+      <c r="T29">
+        <v>1.4</v>
+      </c>
+      <c r="U29">
+        <v>2.75</v>
+      </c>
+      <c r="V29">
+        <v>3</v>
+      </c>
+      <c r="W29">
+        <v>1.36</v>
+      </c>
+      <c r="X29">
+        <v>8</v>
+      </c>
+      <c r="Y29">
+        <v>1.08</v>
+      </c>
+      <c r="Z29">
+        <v>1.76</v>
+      </c>
+      <c r="AA29">
+        <v>3.63</v>
+      </c>
+      <c r="AB29">
+        <v>4.4</v>
+      </c>
+      <c r="AC29">
+        <v>1.06</v>
+      </c>
+      <c r="AD29">
+        <v>8.5</v>
+      </c>
+      <c r="AE29">
+        <v>1.3</v>
+      </c>
+      <c r="AF29">
+        <v>3.35</v>
+      </c>
+      <c r="AG29">
+        <v>1.91</v>
+      </c>
+      <c r="AH29">
+        <v>1.83</v>
+      </c>
+      <c r="AI29">
+        <v>1.8</v>
+      </c>
+      <c r="AJ29">
+        <v>1.95</v>
+      </c>
+      <c r="AK29">
+        <v>1.18</v>
+      </c>
+      <c r="AL29">
+        <v>1.25</v>
+      </c>
+      <c r="AM29">
+        <v>2</v>
+      </c>
+      <c r="AN29">
+        <v>2.33</v>
+      </c>
+      <c r="AO29">
+        <v>1</v>
+      </c>
+      <c r="AP29">
+        <v>2.5</v>
+      </c>
+      <c r="AQ29">
+        <v>0.75</v>
+      </c>
+      <c r="AR29">
+        <v>1.92</v>
+      </c>
+      <c r="AS29">
+        <v>1.36</v>
+      </c>
+      <c r="AT29">
+        <v>3.28</v>
+      </c>
+      <c r="AU29">
+        <v>5</v>
+      </c>
+      <c r="AV29">
+        <v>7</v>
+      </c>
+      <c r="AW29">
+        <v>8</v>
+      </c>
+      <c r="AX29">
+        <v>5</v>
+      </c>
+      <c r="AY29">
+        <v>13</v>
+      </c>
+      <c r="AZ29">
+        <v>12</v>
+      </c>
+      <c r="BA29">
+        <v>3</v>
+      </c>
+      <c r="BB29">
+        <v>7</v>
+      </c>
+      <c r="BC29">
+        <v>10</v>
+      </c>
+      <c r="BD29">
+        <v>1.53</v>
+      </c>
+      <c r="BE29">
+        <v>7</v>
+      </c>
+      <c r="BF29">
+        <v>2.7</v>
+      </c>
+      <c r="BG29">
+        <v>1.25</v>
+      </c>
+      <c r="BH29">
+        <v>3.4</v>
+      </c>
+      <c r="BI29">
+        <v>1.46</v>
+      </c>
+      <c r="BJ29">
+        <v>2.45</v>
+      </c>
+      <c r="BK29">
+        <v>1.76</v>
+      </c>
+      <c r="BL29">
+        <v>1.9</v>
+      </c>
+      <c r="BM29">
+        <v>2.2</v>
+      </c>
+      <c r="BN29">
+        <v>1.57</v>
+      </c>
+      <c r="BO29">
+        <v>2.8</v>
+      </c>
+      <c r="BP29">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="122">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -377,6 +377,9 @@
   </si>
   <si>
     <t>['50']</t>
+  </si>
+  <si>
+    <t>['20']</t>
   </si>
 </sst>
 </file>
@@ -738,7 +741,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP29"/>
+  <dimension ref="A1:BP30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1281,7 +1284,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1690,7 +1693,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AQ5">
         <v>2</v>
@@ -4368,7 +4371,7 @@
         <v>0.5</v>
       </c>
       <c r="AP18">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AQ18">
         <v>1</v>
@@ -4577,7 +4580,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR19">
         <v>2.01</v>
@@ -6713,6 +6716,212 @@
       </c>
       <c r="BP29">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:68">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>7775645</v>
+      </c>
+      <c r="C30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" t="s">
+        <v>69</v>
+      </c>
+      <c r="E30" s="2">
+        <v>45731.69791666666</v>
+      </c>
+      <c r="F30">
+        <v>6</v>
+      </c>
+      <c r="G30" t="s">
+        <v>73</v>
+      </c>
+      <c r="H30" t="s">
+        <v>75</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>1</v>
+      </c>
+      <c r="K30">
+        <v>1</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>1</v>
+      </c>
+      <c r="N30">
+        <v>1</v>
+      </c>
+      <c r="O30" t="s">
+        <v>82</v>
+      </c>
+      <c r="P30" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q30">
+        <v>4.5</v>
+      </c>
+      <c r="R30">
+        <v>2.1</v>
+      </c>
+      <c r="S30">
+        <v>2.6</v>
+      </c>
+      <c r="T30">
+        <v>1.44</v>
+      </c>
+      <c r="U30">
+        <v>2.63</v>
+      </c>
+      <c r="V30">
+        <v>3</v>
+      </c>
+      <c r="W30">
+        <v>1.36</v>
+      </c>
+      <c r="X30">
+        <v>9</v>
+      </c>
+      <c r="Y30">
+        <v>1.07</v>
+      </c>
+      <c r="Z30">
+        <v>3.73</v>
+      </c>
+      <c r="AA30">
+        <v>3.74</v>
+      </c>
+      <c r="AB30">
+        <v>1.87</v>
+      </c>
+      <c r="AC30">
+        <v>1.06</v>
+      </c>
+      <c r="AD30">
+        <v>8.5</v>
+      </c>
+      <c r="AE30">
+        <v>1.33</v>
+      </c>
+      <c r="AF30">
+        <v>3.25</v>
+      </c>
+      <c r="AG30">
+        <v>1.92</v>
+      </c>
+      <c r="AH30">
+        <v>1.82</v>
+      </c>
+      <c r="AI30">
+        <v>1.91</v>
+      </c>
+      <c r="AJ30">
+        <v>1.91</v>
+      </c>
+      <c r="AK30">
+        <v>1.82</v>
+      </c>
+      <c r="AL30">
+        <v>1.3</v>
+      </c>
+      <c r="AM30">
+        <v>1.25</v>
+      </c>
+      <c r="AN30">
+        <v>1.5</v>
+      </c>
+      <c r="AO30">
+        <v>0</v>
+      </c>
+      <c r="AP30">
+        <v>1</v>
+      </c>
+      <c r="AQ30">
+        <v>1</v>
+      </c>
+      <c r="AR30">
+        <v>1.87</v>
+      </c>
+      <c r="AS30">
+        <v>1.04</v>
+      </c>
+      <c r="AT30">
+        <v>2.91</v>
+      </c>
+      <c r="AU30">
+        <v>4</v>
+      </c>
+      <c r="AV30">
+        <v>4</v>
+      </c>
+      <c r="AW30">
+        <v>2</v>
+      </c>
+      <c r="AX30">
+        <v>2</v>
+      </c>
+      <c r="AY30">
+        <v>6</v>
+      </c>
+      <c r="AZ30">
+        <v>6</v>
+      </c>
+      <c r="BA30">
+        <v>3</v>
+      </c>
+      <c r="BB30">
+        <v>1</v>
+      </c>
+      <c r="BC30">
+        <v>4</v>
+      </c>
+      <c r="BD30">
+        <v>2.7</v>
+      </c>
+      <c r="BE30">
+        <v>8.5</v>
+      </c>
+      <c r="BF30">
+        <v>1.57</v>
+      </c>
+      <c r="BG30">
+        <v>1.23</v>
+      </c>
+      <c r="BH30">
+        <v>3.42</v>
+      </c>
+      <c r="BI30">
+        <v>1.46</v>
+      </c>
+      <c r="BJ30">
+        <v>2.45</v>
+      </c>
+      <c r="BK30">
+        <v>1.83</v>
+      </c>
+      <c r="BL30">
+        <v>1.87</v>
+      </c>
+      <c r="BM30">
+        <v>2.32</v>
+      </c>
+      <c r="BN30">
+        <v>1.51</v>
+      </c>
+      <c r="BO30">
+        <v>3.08</v>
+      </c>
+      <c r="BP30">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
@@ -286,15 +286,15 @@
     <t>['2']</t>
   </si>
   <si>
+    <t>['40']</t>
+  </si>
+  <si>
     <t>['35', '83']</t>
   </si>
   <si>
     <t>['64']</t>
   </si>
   <si>
-    <t>['40']</t>
-  </si>
-  <si>
     <t>['58']</t>
   </si>
   <si>
@@ -307,12 +307,12 @@
     <t>['47', '87']</t>
   </si>
   <si>
+    <t>['62']</t>
+  </si>
+  <si>
     <t>['53']</t>
   </si>
   <si>
-    <t>['62']</t>
-  </si>
-  <si>
     <t>['33']</t>
   </si>
   <si>
@@ -343,15 +343,15 @@
     <t>['16']</t>
   </si>
   <si>
+    <t>['76']</t>
+  </si>
+  <si>
     <t>['21']</t>
   </si>
   <si>
     <t>['9', '39']</t>
   </si>
   <si>
-    <t>['76']</t>
-  </si>
-  <si>
     <t>['17']</t>
   </si>
   <si>
@@ -367,10 +367,10 @@
     <t>['15', '34', '42']</t>
   </si>
   <si>
+    <t>['4']</t>
+  </si>
+  <si>
     <t>['44']</t>
-  </si>
-  <si>
-    <t>['4']</t>
   </si>
   <si>
     <t>['41', '70']</t>
@@ -3221,7 +3221,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>7775626</v>
+        <v>7775628</v>
       </c>
       <c r="C13" t="s">
         <v>68</v>
@@ -3236,28 +3236,28 @@
         <v>3</v>
       </c>
       <c r="G13" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="H13" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I13">
         <v>1</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M13">
         <v>1</v>
       </c>
       <c r="N13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O13" t="s">
         <v>90</v>
@@ -3266,52 +3266,52 @@
         <v>109</v>
       </c>
       <c r="Q13">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="R13">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="S13">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="T13">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="U13">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V13">
         <v>3.25</v>
       </c>
       <c r="W13">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X13">
-        <v>9.25</v>
+        <v>8.1</v>
       </c>
       <c r="Y13">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Z13">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA13">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="AB13">
-        <v>2.18</v>
+        <v>1.96</v>
       </c>
       <c r="AC13">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AD13">
-        <v>8</v>
+        <v>6.85</v>
       </c>
       <c r="AE13">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AF13">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="AG13">
         <v>2.2</v>
@@ -3320,106 +3320,106 @@
         <v>1.55</v>
       </c>
       <c r="AI13">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AJ13">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AK13">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AL13">
         <v>1.32</v>
       </c>
       <c r="AM13">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AN13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP13">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AQ13">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR13">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AS13">
-        <v>0.93</v>
+        <v>1.55</v>
       </c>
       <c r="AT13">
-        <v>2.39</v>
+        <v>3.09</v>
       </c>
       <c r="AU13">
+        <v>3</v>
+      </c>
+      <c r="AV13">
         <v>4</v>
       </c>
-      <c r="AV13">
-        <v>5</v>
-      </c>
       <c r="AW13">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AX13">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AY13">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AZ13">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="BA13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB13">
+        <v>6</v>
+      </c>
+      <c r="BC13">
         <v>9</v>
       </c>
-      <c r="BC13">
-        <v>13</v>
-      </c>
       <c r="BD13">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="BE13">
         <v>6.25</v>
       </c>
       <c r="BF13">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="BG13">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="BH13">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="BI13">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="BJ13">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="BK13">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="BL13">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="BM13">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="BN13">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="BO13">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BP13">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="14" spans="1:68">
@@ -3427,7 +3427,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>7775627</v>
+        <v>7775626</v>
       </c>
       <c r="C14" t="s">
         <v>68</v>
@@ -3442,25 +3442,25 @@
         <v>3</v>
       </c>
       <c r="G14" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H14" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K14">
         <v>2</v>
       </c>
       <c r="L14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N14">
         <v>3</v>
@@ -3472,160 +3472,160 @@
         <v>110</v>
       </c>
       <c r="Q14">
-        <v>2.06</v>
+        <v>3.9</v>
       </c>
       <c r="R14">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="S14">
-        <v>6.2</v>
+        <v>2.8</v>
       </c>
       <c r="T14">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="U14">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="V14">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="W14">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="X14">
-        <v>6.7</v>
+        <v>9.25</v>
       </c>
       <c r="Y14">
         <v>1.05</v>
       </c>
       <c r="Z14">
-        <v>1.54</v>
+        <v>3.5</v>
       </c>
       <c r="AA14">
-        <v>3.88</v>
+        <v>3.07</v>
       </c>
       <c r="AB14">
-        <v>6.2</v>
+        <v>2.18</v>
       </c>
       <c r="AC14">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AD14">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AE14">
+        <v>1.4</v>
+      </c>
+      <c r="AF14">
+        <v>2.7</v>
+      </c>
+      <c r="AG14">
+        <v>2.2</v>
+      </c>
+      <c r="AH14">
+        <v>1.55</v>
+      </c>
+      <c r="AI14">
+        <v>1.98</v>
+      </c>
+      <c r="AJ14">
+        <v>1.71</v>
+      </c>
+      <c r="AK14">
+        <v>1.65</v>
+      </c>
+      <c r="AL14">
+        <v>1.32</v>
+      </c>
+      <c r="AM14">
         <v>1.31</v>
       </c>
-      <c r="AF14">
-        <v>3.1</v>
-      </c>
-      <c r="AG14">
-        <v>1.98</v>
-      </c>
-      <c r="AH14">
-        <v>1.77</v>
-      </c>
-      <c r="AI14">
-        <v>2.03</v>
-      </c>
-      <c r="AJ14">
-        <v>1.7</v>
-      </c>
-      <c r="AK14">
-        <v>1.13</v>
-      </c>
-      <c r="AL14">
-        <v>1.21</v>
-      </c>
-      <c r="AM14">
-        <v>2.35</v>
-      </c>
       <c r="AN14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AQ14">
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="AR14">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AS14">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="AT14">
-        <v>2.28</v>
+        <v>2.39</v>
       </c>
       <c r="AU14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AV14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW14">
         <v>8</v>
       </c>
       <c r="AX14">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="AY14">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ14">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="BA14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BB14">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="BC14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="BD14">
-        <v>1.42</v>
+        <v>2.3</v>
       </c>
       <c r="BE14">
-        <v>6.75</v>
+        <v>6.25</v>
       </c>
       <c r="BF14">
-        <v>3.3</v>
+        <v>1.76</v>
       </c>
       <c r="BG14">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="BH14">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="BI14">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="BJ14">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="BK14">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="BL14">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="BM14">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="BN14">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="BO14">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BP14">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="15" spans="1:68">
@@ -3633,7 +3633,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>7775628</v>
+        <v>7775627</v>
       </c>
       <c r="C15" t="s">
         <v>68</v>
@@ -3648,28 +3648,28 @@
         <v>3</v>
       </c>
       <c r="G15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L15">
         <v>1</v>
       </c>
       <c r="M15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O15" t="s">
         <v>92</v>
@@ -3678,160 +3678,160 @@
         <v>111</v>
       </c>
       <c r="Q15">
-        <v>4.5</v>
+        <v>2.06</v>
       </c>
       <c r="R15">
-        <v>2.01</v>
+        <v>2.28</v>
       </c>
       <c r="S15">
-        <v>2.7</v>
+        <v>6.2</v>
       </c>
       <c r="T15">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="U15">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="V15">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="W15">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="X15">
-        <v>8.1</v>
+        <v>6.7</v>
       </c>
       <c r="Y15">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Z15">
-        <v>4.2</v>
+        <v>1.54</v>
       </c>
       <c r="AA15">
-        <v>3.09</v>
+        <v>3.88</v>
       </c>
       <c r="AB15">
-        <v>1.96</v>
+        <v>6.2</v>
       </c>
       <c r="AC15">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AD15">
-        <v>6.85</v>
+        <v>8.5</v>
       </c>
       <c r="AE15">
-        <v>1.49</v>
+        <v>1.31</v>
       </c>
       <c r="AF15">
-        <v>2.36</v>
+        <v>3.1</v>
       </c>
       <c r="AG15">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AH15">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AI15">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AJ15">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AK15">
-        <v>1.7</v>
+        <v>1.13</v>
       </c>
       <c r="AL15">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AM15">
-        <v>1.26</v>
+        <v>2.35</v>
       </c>
       <c r="AN15">
         <v>3</v>
       </c>
       <c r="AO15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AP15">
         <v>1.33</v>
       </c>
       <c r="AQ15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR15">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AS15">
-        <v>1.55</v>
+        <v>0.85</v>
       </c>
       <c r="AT15">
-        <v>3.09</v>
+        <v>2.28</v>
       </c>
       <c r="AU15">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AV15">
         <v>4</v>
       </c>
       <c r="AW15">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AX15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AY15">
         <v>16</v>
       </c>
       <c r="AZ15">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA15">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BB15">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BC15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD15">
+        <v>1.42</v>
+      </c>
+      <c r="BE15">
+        <v>6.75</v>
+      </c>
+      <c r="BF15">
+        <v>3.3</v>
+      </c>
+      <c r="BG15">
+        <v>1.43</v>
+      </c>
+      <c r="BH15">
         <v>2.55</v>
       </c>
-      <c r="BE15">
-        <v>6.25</v>
-      </c>
-      <c r="BF15">
-        <v>1.66</v>
-      </c>
-      <c r="BG15">
-        <v>1.45</v>
-      </c>
-      <c r="BH15">
-        <v>2.48</v>
-      </c>
       <c r="BI15">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="BJ15">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="BK15">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="BL15">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="BM15">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="BN15">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="BO15">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="BP15">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="16" spans="1:68">
@@ -4869,7 +4869,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>7775640</v>
+        <v>7775639</v>
       </c>
       <c r="C21" t="s">
         <v>68</v>
@@ -4884,70 +4884,70 @@
         <v>5</v>
       </c>
       <c r="G21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H21" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I21">
         <v>0</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O21" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="P21" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="Q21">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="R21">
         <v>2</v>
       </c>
       <c r="S21">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="T21">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="U21">
         <v>2.65</v>
       </c>
       <c r="V21">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="W21">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="Y21">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z21">
-        <v>2.29</v>
+        <v>2.73</v>
       </c>
       <c r="AA21">
-        <v>3.07</v>
+        <v>3.28</v>
       </c>
       <c r="AB21">
-        <v>3.25</v>
+        <v>2.51</v>
       </c>
       <c r="AC21">
         <v>1.07</v>
@@ -4956,118 +4956,118 @@
         <v>8</v>
       </c>
       <c r="AE21">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AF21">
-        <v>3.28</v>
+        <v>3.19</v>
       </c>
       <c r="AG21">
+        <v>1.98</v>
+      </c>
+      <c r="AH21">
+        <v>1.77</v>
+      </c>
+      <c r="AI21">
+        <v>1.8</v>
+      </c>
+      <c r="AJ21">
+        <v>1.88</v>
+      </c>
+      <c r="AK21">
+        <v>1.57</v>
+      </c>
+      <c r="AL21">
+        <v>1.32</v>
+      </c>
+      <c r="AM21">
+        <v>1.36</v>
+      </c>
+      <c r="AN21">
+        <v>1.5</v>
+      </c>
+      <c r="AO21">
+        <v>0</v>
+      </c>
+      <c r="AP21">
+        <v>1</v>
+      </c>
+      <c r="AQ21">
+        <v>0.75</v>
+      </c>
+      <c r="AR21">
+        <v>1.81</v>
+      </c>
+      <c r="AS21">
+        <v>1.5</v>
+      </c>
+      <c r="AT21">
+        <v>3.31</v>
+      </c>
+      <c r="AU21">
+        <v>8</v>
+      </c>
+      <c r="AV21">
+        <v>4</v>
+      </c>
+      <c r="AW21">
+        <v>4</v>
+      </c>
+      <c r="AX21">
+        <v>4</v>
+      </c>
+      <c r="AY21">
+        <v>12</v>
+      </c>
+      <c r="AZ21">
+        <v>8</v>
+      </c>
+      <c r="BA21">
+        <v>6</v>
+      </c>
+      <c r="BB21">
+        <v>2</v>
+      </c>
+      <c r="BC21">
+        <v>8</v>
+      </c>
+      <c r="BD21">
+        <v>2.07</v>
+      </c>
+      <c r="BE21">
+        <v>6.4</v>
+      </c>
+      <c r="BF21">
         <v>1.91</v>
       </c>
-      <c r="AH21">
-        <v>1.73</v>
-      </c>
-      <c r="AI21">
-        <v>1.77</v>
-      </c>
-      <c r="AJ21">
-        <v>1.93</v>
-      </c>
-      <c r="AK21">
-        <v>1.3</v>
-      </c>
-      <c r="AL21">
-        <v>1.33</v>
-      </c>
-      <c r="AM21">
-        <v>1.65</v>
-      </c>
-      <c r="AN21">
-        <v>0</v>
-      </c>
-      <c r="AO21">
-        <v>0</v>
-      </c>
-      <c r="AP21">
-        <v>3</v>
-      </c>
-      <c r="AQ21">
-        <v>0</v>
-      </c>
-      <c r="AR21">
-        <v>0</v>
-      </c>
-      <c r="AS21">
-        <v>1.73</v>
-      </c>
-      <c r="AT21">
-        <v>1.73</v>
-      </c>
-      <c r="AU21">
-        <v>4</v>
-      </c>
-      <c r="AV21">
-        <v>2</v>
-      </c>
-      <c r="AW21">
-        <v>9</v>
-      </c>
-      <c r="AX21">
-        <v>9</v>
-      </c>
-      <c r="AY21">
-        <v>13</v>
-      </c>
-      <c r="AZ21">
-        <v>11</v>
-      </c>
-      <c r="BA21">
-        <v>4</v>
-      </c>
-      <c r="BB21">
-        <v>2</v>
-      </c>
-      <c r="BC21">
-        <v>6</v>
-      </c>
-      <c r="BD21">
-        <v>1.67</v>
-      </c>
-      <c r="BE21">
-        <v>6.5</v>
-      </c>
-      <c r="BF21">
+      <c r="BG21">
+        <v>1.27</v>
+      </c>
+      <c r="BH21">
+        <v>3.3</v>
+      </c>
+      <c r="BI21">
+        <v>1.46</v>
+      </c>
+      <c r="BJ21">
         <v>2.45</v>
       </c>
-      <c r="BG21">
-        <v>1.33</v>
-      </c>
-      <c r="BH21">
-        <v>2.95</v>
-      </c>
-      <c r="BI21">
-        <v>1.56</v>
-      </c>
-      <c r="BJ21">
-        <v>2.2</v>
-      </c>
       <c r="BK21">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="BL21">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="BM21">
-        <v>2.43</v>
+        <v>2.18</v>
       </c>
       <c r="BN21">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="BO21">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="BP21">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="22" spans="1:68">
@@ -5075,7 +5075,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>7775639</v>
+        <v>7775640</v>
       </c>
       <c r="C22" t="s">
         <v>68</v>
@@ -5090,70 +5090,70 @@
         <v>5</v>
       </c>
       <c r="G22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H22" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
       <c r="J22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O22" t="s">
+        <v>92</v>
+      </c>
+      <c r="P22" t="s">
         <v>82</v>
       </c>
-      <c r="P22" t="s">
-        <v>116</v>
-      </c>
       <c r="Q22">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="R22">
         <v>2</v>
       </c>
       <c r="S22">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="T22">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="U22">
         <v>2.65</v>
       </c>
       <c r="V22">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="W22">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="X22">
-        <v>7.75</v>
+        <v>7</v>
       </c>
       <c r="Y22">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z22">
-        <v>2.73</v>
+        <v>2.29</v>
       </c>
       <c r="AA22">
-        <v>3.28</v>
+        <v>3.07</v>
       </c>
       <c r="AB22">
-        <v>2.51</v>
+        <v>3.25</v>
       </c>
       <c r="AC22">
         <v>1.07</v>
@@ -5162,118 +5162,118 @@
         <v>8</v>
       </c>
       <c r="AE22">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AF22">
-        <v>3.19</v>
+        <v>3.28</v>
       </c>
       <c r="AG22">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AH22">
+        <v>1.73</v>
+      </c>
+      <c r="AI22">
         <v>1.77</v>
       </c>
-      <c r="AI22">
-        <v>1.8</v>
-      </c>
       <c r="AJ22">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AK22">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AL22">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AM22">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AN22">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO22">
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AQ22">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AR22">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AS22">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AT22">
-        <v>3.31</v>
+        <v>1.73</v>
       </c>
       <c r="AU22">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AV22">
+        <v>2</v>
+      </c>
+      <c r="AW22">
+        <v>9</v>
+      </c>
+      <c r="AX22">
+        <v>9</v>
+      </c>
+      <c r="AY22">
+        <v>13</v>
+      </c>
+      <c r="AZ22">
+        <v>11</v>
+      </c>
+      <c r="BA22">
         <v>4</v>
       </c>
-      <c r="AW22">
-        <v>4</v>
-      </c>
-      <c r="AX22">
-        <v>4</v>
-      </c>
-      <c r="AY22">
-        <v>12</v>
-      </c>
-      <c r="AZ22">
-        <v>8</v>
-      </c>
-      <c r="BA22">
+      <c r="BB22">
+        <v>2</v>
+      </c>
+      <c r="BC22">
         <v>6</v>
       </c>
-      <c r="BB22">
-        <v>2</v>
-      </c>
-      <c r="BC22">
-        <v>8</v>
-      </c>
       <c r="BD22">
-        <v>2.07</v>
+        <v>1.67</v>
       </c>
       <c r="BE22">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="BF22">
+        <v>2.45</v>
+      </c>
+      <c r="BG22">
+        <v>1.33</v>
+      </c>
+      <c r="BH22">
+        <v>2.95</v>
+      </c>
+      <c r="BI22">
+        <v>1.56</v>
+      </c>
+      <c r="BJ22">
+        <v>2.2</v>
+      </c>
+      <c r="BK22">
         <v>1.91</v>
       </c>
-      <c r="BG22">
-        <v>1.27</v>
-      </c>
-      <c r="BH22">
-        <v>3.3</v>
-      </c>
-      <c r="BI22">
-        <v>1.46</v>
-      </c>
-      <c r="BJ22">
-        <v>2.45</v>
-      </c>
-      <c r="BK22">
+      <c r="BL22">
         <v>1.75</v>
       </c>
-      <c r="BL22">
-        <v>1.92</v>
-      </c>
       <c r="BM22">
-        <v>2.18</v>
+        <v>2.43</v>
       </c>
       <c r="BN22">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="BO22">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="BP22">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="23" spans="1:68">
@@ -5281,7 +5281,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>7775637</v>
+        <v>7775638</v>
       </c>
       <c r="C23" t="s">
         <v>68</v>
@@ -5296,10 +5296,10 @@
         <v>5</v>
       </c>
       <c r="G23" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="H23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -5311,175 +5311,175 @@
         <v>1</v>
       </c>
       <c r="L23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23">
         <v>1</v>
       </c>
       <c r="N23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O23" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="P23" t="s">
         <v>117</v>
       </c>
       <c r="Q23">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="R23">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="S23">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="T23">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="U23">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="V23">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="W23">
+        <v>1.32</v>
+      </c>
+      <c r="X23">
+        <v>8.5</v>
+      </c>
+      <c r="Y23">
+        <v>1.06</v>
+      </c>
+      <c r="Z23">
+        <v>1.76</v>
+      </c>
+      <c r="AA23">
+        <v>3.45</v>
+      </c>
+      <c r="AB23">
+        <v>4.75</v>
+      </c>
+      <c r="AC23">
+        <v>1.07</v>
+      </c>
+      <c r="AD23">
+        <v>7.75</v>
+      </c>
+      <c r="AE23">
+        <v>1.5</v>
+      </c>
+      <c r="AF23">
+        <v>2.4</v>
+      </c>
+      <c r="AG23">
+        <v>2.05</v>
+      </c>
+      <c r="AH23">
+        <v>1.65</v>
+      </c>
+      <c r="AI23">
+        <v>2.1</v>
+      </c>
+      <c r="AJ23">
+        <v>1.65</v>
+      </c>
+      <c r="AK23">
+        <v>1.19</v>
+      </c>
+      <c r="AL23">
+        <v>1.27</v>
+      </c>
+      <c r="AM23">
+        <v>2</v>
+      </c>
+      <c r="AN23">
+        <v>2</v>
+      </c>
+      <c r="AO23">
+        <v>2</v>
+      </c>
+      <c r="AP23">
         <v>1.25</v>
       </c>
-      <c r="X23">
-        <v>10.5</v>
-      </c>
-      <c r="Y23">
-        <v>1.04</v>
-      </c>
-      <c r="Z23">
-        <v>1.98</v>
-      </c>
-      <c r="AA23">
-        <v>3.33</v>
-      </c>
-      <c r="AB23">
-        <v>3.78</v>
-      </c>
-      <c r="AC23">
-        <v>1.09</v>
-      </c>
-      <c r="AD23">
-        <v>7</v>
-      </c>
-      <c r="AE23">
-        <v>1.53</v>
-      </c>
-      <c r="AF23">
-        <v>2.5</v>
-      </c>
-      <c r="AG23">
-        <v>2.25</v>
-      </c>
-      <c r="AH23">
-        <v>1.53</v>
-      </c>
-      <c r="AI23">
-        <v>2.15</v>
-      </c>
-      <c r="AJ23">
-        <v>1.6</v>
-      </c>
-      <c r="AK23">
-        <v>1.28</v>
-      </c>
-      <c r="AL23">
-        <v>1.3</v>
-      </c>
-      <c r="AM23">
-        <v>1.75</v>
-      </c>
-      <c r="AN23">
+      <c r="AQ23">
+        <v>2.33</v>
+      </c>
+      <c r="AR23">
+        <v>1.82</v>
+      </c>
+      <c r="AS23">
+        <v>0.98</v>
+      </c>
+      <c r="AT23">
+        <v>2.8</v>
+      </c>
+      <c r="AU23">
+        <v>3</v>
+      </c>
+      <c r="AV23">
+        <v>5</v>
+      </c>
+      <c r="AW23">
+        <v>15</v>
+      </c>
+      <c r="AX23">
+        <v>5</v>
+      </c>
+      <c r="AY23">
+        <v>18</v>
+      </c>
+      <c r="AZ23">
+        <v>10</v>
+      </c>
+      <c r="BA23">
+        <v>6</v>
+      </c>
+      <c r="BB23">
+        <v>3</v>
+      </c>
+      <c r="BC23">
+        <v>9</v>
+      </c>
+      <c r="BD23">
         <v>1.5</v>
-      </c>
-      <c r="AO23">
-        <v>1</v>
-      </c>
-      <c r="AP23">
-        <v>1.33</v>
-      </c>
-      <c r="AQ23">
-        <v>1</v>
-      </c>
-      <c r="AR23">
-        <v>1.72</v>
-      </c>
-      <c r="AS23">
-        <v>1.51</v>
-      </c>
-      <c r="AT23">
-        <v>3.23</v>
-      </c>
-      <c r="AU23">
-        <v>6</v>
-      </c>
-      <c r="AV23">
-        <v>3</v>
-      </c>
-      <c r="AW23">
-        <v>20</v>
-      </c>
-      <c r="AX23">
-        <v>4</v>
-      </c>
-      <c r="AY23">
-        <v>26</v>
-      </c>
-      <c r="AZ23">
-        <v>7</v>
-      </c>
-      <c r="BA23">
-        <v>7</v>
-      </c>
-      <c r="BB23">
-        <v>1</v>
-      </c>
-      <c r="BC23">
-        <v>8</v>
-      </c>
-      <c r="BD23">
-        <v>1.7</v>
       </c>
       <c r="BE23">
         <v>6.4</v>
       </c>
       <c r="BF23">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="BG23">
-        <v>1.38</v>
+        <v>1.63</v>
       </c>
       <c r="BH23">
-        <v>2.7</v>
+        <v>2.08</v>
       </c>
       <c r="BI23">
+        <v>2.05</v>
+      </c>
+      <c r="BJ23">
         <v>1.65</v>
       </c>
-      <c r="BJ23">
-        <v>2.06</v>
-      </c>
       <c r="BK23">
-        <v>2.05</v>
+        <v>2.65</v>
       </c>
       <c r="BL23">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="BM23">
-        <v>2.65</v>
+        <v>3.65</v>
       </c>
       <c r="BN23">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="BO23">
-        <v>3.45</v>
+        <v>4.9</v>
       </c>
       <c r="BP23">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="24" spans="1:68">
@@ -5526,7 +5526,7 @@
         <v>2</v>
       </c>
       <c r="O24" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P24" t="s">
         <v>84</v>
@@ -5693,7 +5693,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>7775638</v>
+        <v>7775637</v>
       </c>
       <c r="C25" t="s">
         <v>68</v>
@@ -5708,10 +5708,10 @@
         <v>5</v>
       </c>
       <c r="G25" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="H25" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -5723,175 +5723,175 @@
         <v>1</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25">
         <v>1</v>
       </c>
       <c r="N25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O25" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="P25" t="s">
         <v>118</v>
       </c>
       <c r="Q25">
+        <v>2.7</v>
+      </c>
+      <c r="R25">
+        <v>1.95</v>
+      </c>
+      <c r="S25">
+        <v>4.1</v>
+      </c>
+      <c r="T25">
+        <v>1.52</v>
+      </c>
+      <c r="U25">
         <v>2.35</v>
       </c>
-      <c r="R25">
-        <v>2.05</v>
-      </c>
-      <c r="S25">
-        <v>4.8</v>
-      </c>
-      <c r="T25">
-        <v>1.44</v>
-      </c>
-      <c r="U25">
-        <v>2.55</v>
-      </c>
       <c r="V25">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="W25">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="X25">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y25">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Z25">
-        <v>1.76</v>
+        <v>1.98</v>
       </c>
       <c r="AA25">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
       <c r="AB25">
-        <v>4.75</v>
+        <v>3.78</v>
       </c>
       <c r="AC25">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AD25">
-        <v>7.75</v>
+        <v>7</v>
       </c>
       <c r="AE25">
+        <v>1.53</v>
+      </c>
+      <c r="AF25">
+        <v>2.5</v>
+      </c>
+      <c r="AG25">
+        <v>2.25</v>
+      </c>
+      <c r="AH25">
+        <v>1.53</v>
+      </c>
+      <c r="AI25">
+        <v>2.15</v>
+      </c>
+      <c r="AJ25">
+        <v>1.6</v>
+      </c>
+      <c r="AK25">
+        <v>1.28</v>
+      </c>
+      <c r="AL25">
+        <v>1.3</v>
+      </c>
+      <c r="AM25">
+        <v>1.75</v>
+      </c>
+      <c r="AN25">
         <v>1.5</v>
       </c>
-      <c r="AF25">
-        <v>2.4</v>
-      </c>
-      <c r="AG25">
-        <v>2.05</v>
-      </c>
-      <c r="AH25">
-        <v>1.65</v>
-      </c>
-      <c r="AI25">
-        <v>2.1</v>
-      </c>
-      <c r="AJ25">
-        <v>1.65</v>
-      </c>
-      <c r="AK25">
-        <v>1.19</v>
-      </c>
-      <c r="AL25">
-        <v>1.27</v>
-      </c>
-      <c r="AM25">
-        <v>2</v>
-      </c>
-      <c r="AN25">
-        <v>2</v>
-      </c>
       <c r="AO25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AQ25">
-        <v>2.33</v>
+        <v>1</v>
       </c>
       <c r="AR25">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AS25">
-        <v>0.98</v>
+        <v>1.51</v>
       </c>
       <c r="AT25">
-        <v>2.8</v>
+        <v>3.23</v>
       </c>
       <c r="AU25">
+        <v>6</v>
+      </c>
+      <c r="AV25">
         <v>3</v>
       </c>
-      <c r="AV25">
-        <v>5</v>
-      </c>
       <c r="AW25">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AX25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY25">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="AZ25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BC25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD25">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="BE25">
         <v>6.4</v>
       </c>
       <c r="BF25">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="BG25">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="BH25">
-        <v>2.08</v>
+        <v>2.7</v>
       </c>
       <c r="BI25">
+        <v>1.65</v>
+      </c>
+      <c r="BJ25">
+        <v>2.06</v>
+      </c>
+      <c r="BK25">
         <v>2.05</v>
       </c>
-      <c r="BJ25">
+      <c r="BL25">
         <v>1.65</v>
       </c>
-      <c r="BK25">
+      <c r="BM25">
         <v>2.65</v>
       </c>
-      <c r="BL25">
+      <c r="BN25">
         <v>1.4</v>
       </c>
-      <c r="BM25">
-        <v>3.65</v>
-      </c>
-      <c r="BN25">
-        <v>1.22</v>
-      </c>
       <c r="BO25">
-        <v>4.9</v>
+        <v>3.45</v>
       </c>
       <c r="BP25">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="26" spans="1:68">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="126">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -325,12 +325,15 @@
     <t>['17', '83', '90']</t>
   </si>
   <si>
+    <t>['14']</t>
+  </si>
+  <si>
+    <t>['45+1']</t>
+  </si>
+  <si>
     <t>['45+1', '81']</t>
   </si>
   <si>
-    <t>['14']</t>
-  </si>
-  <si>
     <t>['13', '33', '58']</t>
   </si>
   <si>
@@ -380,6 +383,15 @@
   </si>
   <si>
     <t>['20']</t>
+  </si>
+  <si>
+    <t>['88', '90']</t>
+  </si>
+  <si>
+    <t>['19', '66']</t>
+  </si>
+  <si>
+    <t>['3', '12']</t>
   </si>
 </sst>
 </file>
@@ -741,7 +753,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP30"/>
+  <dimension ref="A1:BP35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -997,7 +1009,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Q2">
         <v>4.4</v>
@@ -1075,10 +1087,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ2">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1203,7 +1215,7 @@
         <v>81</v>
       </c>
       <c r="P3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Q3">
         <v>4</v>
@@ -1490,7 +1502,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ4">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1615,7 +1627,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -1693,7 +1705,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ5">
         <v>2</v>
@@ -1899,7 +1911,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AQ6">
         <v>1</v>
@@ -2439,7 +2451,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -2520,7 +2532,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2645,7 +2657,7 @@
         <v>82</v>
       </c>
       <c r="P10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Q10">
         <v>4.33</v>
@@ -2723,10 +2735,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ10">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -2851,7 +2863,7 @@
         <v>88</v>
       </c>
       <c r="P11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q11">
         <v>1.94</v>
@@ -3057,7 +3069,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q12">
         <v>3.95</v>
@@ -3263,7 +3275,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q13">
         <v>4.5</v>
@@ -3344,7 +3356,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ13">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AR13">
         <v>1.54</v>
@@ -3469,7 +3481,7 @@
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q14">
         <v>3.9</v>
@@ -3547,7 +3559,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ14">
         <v>0.75</v>
@@ -3675,7 +3687,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q15">
         <v>2.06</v>
@@ -3881,7 +3893,7 @@
         <v>82</v>
       </c>
       <c r="P16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -3959,10 +3971,10 @@
         <v>1</v>
       </c>
       <c r="AP16">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AQ16">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AR16">
         <v>0.9399999999999999</v>
@@ -4087,7 +4099,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q17">
         <v>3.1</v>
@@ -4168,7 +4180,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ17">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR17">
         <v>1.58</v>
@@ -4293,7 +4305,7 @@
         <v>94</v>
       </c>
       <c r="P18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q18">
         <v>4.2</v>
@@ -4371,7 +4383,7 @@
         <v>0.5</v>
       </c>
       <c r="AP18">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ18">
         <v>1</v>
@@ -4705,7 +4717,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q20">
         <v>2.65</v>
@@ -4783,7 +4795,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ20">
         <v>0.5</v>
@@ -4911,7 +4923,7 @@
         <v>82</v>
       </c>
       <c r="P21" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -4989,7 +5001,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ21">
         <v>0.75</v>
@@ -5195,10 +5207,10 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -5323,7 +5335,7 @@
         <v>82</v>
       </c>
       <c r="P23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q23">
         <v>2.35</v>
@@ -5404,7 +5416,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ23">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AR23">
         <v>1.82</v>
@@ -5607,7 +5619,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ24">
         <v>0.33</v>
@@ -5735,7 +5747,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q25">
         <v>2.7</v>
@@ -5816,7 +5828,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ25">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AR25">
         <v>1.72</v>
@@ -5941,7 +5953,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q26">
         <v>4.75</v>
@@ -6353,7 +6365,7 @@
         <v>101</v>
       </c>
       <c r="P28" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -6765,7 +6777,7 @@
         <v>82</v>
       </c>
       <c r="P30" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q30">
         <v>4.5</v>
@@ -6843,7 +6855,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AQ30">
         <v>1</v>
@@ -6922,6 +6934,1036 @@
       </c>
       <c r="BP30">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:68">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>7775648</v>
+      </c>
+      <c r="C31" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" t="s">
+        <v>69</v>
+      </c>
+      <c r="E31" s="2">
+        <v>45744.69791666666</v>
+      </c>
+      <c r="F31">
+        <v>7</v>
+      </c>
+      <c r="G31" t="s">
+        <v>78</v>
+      </c>
+      <c r="H31" t="s">
+        <v>72</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>1</v>
+      </c>
+      <c r="L31">
+        <v>1</v>
+      </c>
+      <c r="M31">
+        <v>2</v>
+      </c>
+      <c r="N31">
+        <v>3</v>
+      </c>
+      <c r="O31" t="s">
+        <v>103</v>
+      </c>
+      <c r="P31" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q31">
+        <v>4.75</v>
+      </c>
+      <c r="R31">
+        <v>2.2</v>
+      </c>
+      <c r="S31">
+        <v>2.4</v>
+      </c>
+      <c r="T31">
+        <v>1.4</v>
+      </c>
+      <c r="U31">
+        <v>2.75</v>
+      </c>
+      <c r="V31">
+        <v>3</v>
+      </c>
+      <c r="W31">
+        <v>1.36</v>
+      </c>
+      <c r="X31">
+        <v>8</v>
+      </c>
+      <c r="Y31">
+        <v>1.08</v>
+      </c>
+      <c r="Z31">
+        <v>4.1</v>
+      </c>
+      <c r="AA31">
+        <v>3.4</v>
+      </c>
+      <c r="AB31">
+        <v>1.8</v>
+      </c>
+      <c r="AC31">
+        <v>1.01</v>
+      </c>
+      <c r="AD31">
+        <v>8.4</v>
+      </c>
+      <c r="AE31">
+        <v>1.28</v>
+      </c>
+      <c r="AF31">
+        <v>3.2</v>
+      </c>
+      <c r="AG31">
+        <v>1.91</v>
+      </c>
+      <c r="AH31">
+        <v>1.75</v>
+      </c>
+      <c r="AI31">
+        <v>1.91</v>
+      </c>
+      <c r="AJ31">
+        <v>1.91</v>
+      </c>
+      <c r="AK31">
+        <v>1.91</v>
+      </c>
+      <c r="AL31">
+        <v>1.3</v>
+      </c>
+      <c r="AM31">
+        <v>1.22</v>
+      </c>
+      <c r="AN31">
+        <v>1</v>
+      </c>
+      <c r="AO31">
+        <v>0</v>
+      </c>
+      <c r="AP31">
+        <v>0.75</v>
+      </c>
+      <c r="AQ31">
+        <v>1</v>
+      </c>
+      <c r="AR31">
+        <v>1.77</v>
+      </c>
+      <c r="AS31">
+        <v>1.5</v>
+      </c>
+      <c r="AT31">
+        <v>3.27</v>
+      </c>
+      <c r="AU31">
+        <v>4</v>
+      </c>
+      <c r="AV31">
+        <v>8</v>
+      </c>
+      <c r="AW31">
+        <v>9</v>
+      </c>
+      <c r="AX31">
+        <v>12</v>
+      </c>
+      <c r="AY31">
+        <v>13</v>
+      </c>
+      <c r="AZ31">
+        <v>20</v>
+      </c>
+      <c r="BA31">
+        <v>2</v>
+      </c>
+      <c r="BB31">
+        <v>7</v>
+      </c>
+      <c r="BC31">
+        <v>9</v>
+      </c>
+      <c r="BD31">
+        <v>2.55</v>
+      </c>
+      <c r="BE31">
+        <v>6.1</v>
+      </c>
+      <c r="BF31">
+        <v>1.65</v>
+      </c>
+      <c r="BG31">
+        <v>1.34</v>
+      </c>
+      <c r="BH31">
+        <v>2.9</v>
+      </c>
+      <c r="BI31">
+        <v>1.57</v>
+      </c>
+      <c r="BJ31">
+        <v>2.2</v>
+      </c>
+      <c r="BK31">
+        <v>1.93</v>
+      </c>
+      <c r="BL31">
+        <v>1.74</v>
+      </c>
+      <c r="BM31">
+        <v>2.43</v>
+      </c>
+      <c r="BN31">
+        <v>1.46</v>
+      </c>
+      <c r="BO31">
+        <v>3.15</v>
+      </c>
+      <c r="BP31">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:68">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>7775646</v>
+      </c>
+      <c r="C32" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" t="s">
+        <v>69</v>
+      </c>
+      <c r="E32" s="2">
+        <v>45744.69791666666</v>
+      </c>
+      <c r="F32">
+        <v>7</v>
+      </c>
+      <c r="G32" t="s">
+        <v>74</v>
+      </c>
+      <c r="H32" t="s">
+        <v>77</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>1</v>
+      </c>
+      <c r="K32">
+        <v>1</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>2</v>
+      </c>
+      <c r="N32">
+        <v>2</v>
+      </c>
+      <c r="O32" t="s">
+        <v>82</v>
+      </c>
+      <c r="P32" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q32">
+        <v>3</v>
+      </c>
+      <c r="R32">
+        <v>2.05</v>
+      </c>
+      <c r="S32">
+        <v>4</v>
+      </c>
+      <c r="T32">
+        <v>1.5</v>
+      </c>
+      <c r="U32">
+        <v>2.5</v>
+      </c>
+      <c r="V32">
+        <v>3.4</v>
+      </c>
+      <c r="W32">
+        <v>1.3</v>
+      </c>
+      <c r="X32">
+        <v>10</v>
+      </c>
+      <c r="Y32">
+        <v>1.06</v>
+      </c>
+      <c r="Z32">
+        <v>2.35</v>
+      </c>
+      <c r="AA32">
+        <v>3.2</v>
+      </c>
+      <c r="AB32">
+        <v>2.9</v>
+      </c>
+      <c r="AC32">
+        <v>1.07</v>
+      </c>
+      <c r="AD32">
+        <v>8</v>
+      </c>
+      <c r="AE32">
+        <v>1.4</v>
+      </c>
+      <c r="AF32">
+        <v>2.9</v>
+      </c>
+      <c r="AG32">
+        <v>2.1</v>
+      </c>
+      <c r="AH32">
+        <v>1.6</v>
+      </c>
+      <c r="AI32">
+        <v>1.95</v>
+      </c>
+      <c r="AJ32">
+        <v>1.8</v>
+      </c>
+      <c r="AK32">
+        <v>1.33</v>
+      </c>
+      <c r="AL32">
+        <v>1.28</v>
+      </c>
+      <c r="AM32">
+        <v>1.62</v>
+      </c>
+      <c r="AN32">
+        <v>1.5</v>
+      </c>
+      <c r="AO32">
+        <v>1</v>
+      </c>
+      <c r="AP32">
+        <v>1</v>
+      </c>
+      <c r="AQ32">
+        <v>1.5</v>
+      </c>
+      <c r="AR32">
+        <v>1.2</v>
+      </c>
+      <c r="AS32">
+        <v>1.29</v>
+      </c>
+      <c r="AT32">
+        <v>2.49</v>
+      </c>
+      <c r="AU32">
+        <v>5</v>
+      </c>
+      <c r="AV32">
+        <v>4</v>
+      </c>
+      <c r="AW32">
+        <v>27</v>
+      </c>
+      <c r="AX32">
+        <v>4</v>
+      </c>
+      <c r="AY32">
+        <v>32</v>
+      </c>
+      <c r="AZ32">
+        <v>8</v>
+      </c>
+      <c r="BA32">
+        <v>11</v>
+      </c>
+      <c r="BB32">
+        <v>3</v>
+      </c>
+      <c r="BC32">
+        <v>14</v>
+      </c>
+      <c r="BD32">
+        <v>1.74</v>
+      </c>
+      <c r="BE32">
+        <v>6.75</v>
+      </c>
+      <c r="BF32">
+        <v>2.3</v>
+      </c>
+      <c r="BG32">
+        <v>1.2</v>
+      </c>
+      <c r="BH32">
+        <v>3.8</v>
+      </c>
+      <c r="BI32">
+        <v>1.37</v>
+      </c>
+      <c r="BJ32">
+        <v>2.8</v>
+      </c>
+      <c r="BK32">
+        <v>1.6</v>
+      </c>
+      <c r="BL32">
+        <v>2.12</v>
+      </c>
+      <c r="BM32">
+        <v>1.95</v>
+      </c>
+      <c r="BN32">
+        <v>1.72</v>
+      </c>
+      <c r="BO32">
+        <v>2.45</v>
+      </c>
+      <c r="BP32">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="33" spans="1:68">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>7775647</v>
+      </c>
+      <c r="C33" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" t="s">
+        <v>69</v>
+      </c>
+      <c r="E33" s="2">
+        <v>45744.69791666666</v>
+      </c>
+      <c r="F33">
+        <v>7</v>
+      </c>
+      <c r="G33" t="s">
+        <v>70</v>
+      </c>
+      <c r="H33" t="s">
+        <v>76</v>
+      </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>1</v>
+      </c>
+      <c r="L33">
+        <v>1</v>
+      </c>
+      <c r="M33">
+        <v>1</v>
+      </c>
+      <c r="N33">
+        <v>2</v>
+      </c>
+      <c r="O33" t="s">
+        <v>99</v>
+      </c>
+      <c r="P33" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q33">
+        <v>3.2</v>
+      </c>
+      <c r="R33">
+        <v>2</v>
+      </c>
+      <c r="S33">
+        <v>3.75</v>
+      </c>
+      <c r="T33">
+        <v>1.53</v>
+      </c>
+      <c r="U33">
+        <v>2.38</v>
+      </c>
+      <c r="V33">
+        <v>3.5</v>
+      </c>
+      <c r="W33">
+        <v>1.29</v>
+      </c>
+      <c r="X33">
+        <v>11</v>
+      </c>
+      <c r="Y33">
+        <v>1.05</v>
+      </c>
+      <c r="Z33">
+        <v>2.3</v>
+      </c>
+      <c r="AA33">
+        <v>3.25</v>
+      </c>
+      <c r="AB33">
+        <v>2.95</v>
+      </c>
+      <c r="AC33">
+        <v>1.09</v>
+      </c>
+      <c r="AD33">
+        <v>7</v>
+      </c>
+      <c r="AE33">
+        <v>1.45</v>
+      </c>
+      <c r="AF33">
+        <v>2.7</v>
+      </c>
+      <c r="AG33">
+        <v>2.2</v>
+      </c>
+      <c r="AH33">
+        <v>1.55</v>
+      </c>
+      <c r="AI33">
+        <v>2</v>
+      </c>
+      <c r="AJ33">
+        <v>1.75</v>
+      </c>
+      <c r="AK33">
+        <v>1.36</v>
+      </c>
+      <c r="AL33">
+        <v>1.3</v>
+      </c>
+      <c r="AM33">
+        <v>1.55</v>
+      </c>
+      <c r="AN33">
+        <v>1.67</v>
+      </c>
+      <c r="AO33">
+        <v>2.33</v>
+      </c>
+      <c r="AP33">
+        <v>1.5</v>
+      </c>
+      <c r="AQ33">
+        <v>2</v>
+      </c>
+      <c r="AR33">
+        <v>1.68</v>
+      </c>
+      <c r="AS33">
+        <v>1.06</v>
+      </c>
+      <c r="AT33">
+        <v>2.74</v>
+      </c>
+      <c r="AU33">
+        <v>3</v>
+      </c>
+      <c r="AV33">
+        <v>9</v>
+      </c>
+      <c r="AW33">
+        <v>12</v>
+      </c>
+      <c r="AX33">
+        <v>16</v>
+      </c>
+      <c r="AY33">
+        <v>15</v>
+      </c>
+      <c r="AZ33">
+        <v>25</v>
+      </c>
+      <c r="BA33">
+        <v>8</v>
+      </c>
+      <c r="BB33">
+        <v>5</v>
+      </c>
+      <c r="BC33">
+        <v>13</v>
+      </c>
+      <c r="BD33">
+        <v>1.65</v>
+      </c>
+      <c r="BE33">
+        <v>6.5</v>
+      </c>
+      <c r="BF33">
+        <v>2.5</v>
+      </c>
+      <c r="BG33">
+        <v>1.33</v>
+      </c>
+      <c r="BH33">
+        <v>2.95</v>
+      </c>
+      <c r="BI33">
+        <v>1.56</v>
+      </c>
+      <c r="BJ33">
+        <v>2.2</v>
+      </c>
+      <c r="BK33">
+        <v>1.9</v>
+      </c>
+      <c r="BL33">
+        <v>1.76</v>
+      </c>
+      <c r="BM33">
+        <v>2.4</v>
+      </c>
+      <c r="BN33">
+        <v>1.48</v>
+      </c>
+      <c r="BO33">
+        <v>3.15</v>
+      </c>
+      <c r="BP33">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:68">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>7775650</v>
+      </c>
+      <c r="C34" t="s">
+        <v>68</v>
+      </c>
+      <c r="D34" t="s">
+        <v>69</v>
+      </c>
+      <c r="E34" s="2">
+        <v>45744.69791666666</v>
+      </c>
+      <c r="F34">
+        <v>7</v>
+      </c>
+      <c r="G34" t="s">
+        <v>73</v>
+      </c>
+      <c r="H34" t="s">
+        <v>71</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+      <c r="J34">
+        <v>2</v>
+      </c>
+      <c r="K34">
+        <v>3</v>
+      </c>
+      <c r="L34">
+        <v>1</v>
+      </c>
+      <c r="M34">
+        <v>2</v>
+      </c>
+      <c r="N34">
+        <v>3</v>
+      </c>
+      <c r="O34" t="s">
+        <v>104</v>
+      </c>
+      <c r="P34" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q34">
+        <v>4.33</v>
+      </c>
+      <c r="R34">
+        <v>2</v>
+      </c>
+      <c r="S34">
+        <v>2.88</v>
+      </c>
+      <c r="T34">
+        <v>1.5</v>
+      </c>
+      <c r="U34">
+        <v>2.5</v>
+      </c>
+      <c r="V34">
+        <v>3.4</v>
+      </c>
+      <c r="W34">
+        <v>1.3</v>
+      </c>
+      <c r="X34">
+        <v>10</v>
+      </c>
+      <c r="Y34">
+        <v>1.06</v>
+      </c>
+      <c r="Z34">
+        <v>3.4</v>
+      </c>
+      <c r="AA34">
+        <v>3.1</v>
+      </c>
+      <c r="AB34">
+        <v>2.05</v>
+      </c>
+      <c r="AC34">
+        <v>1.08</v>
+      </c>
+      <c r="AD34">
+        <v>7.5</v>
+      </c>
+      <c r="AE34">
+        <v>1.42</v>
+      </c>
+      <c r="AF34">
+        <v>2.8</v>
+      </c>
+      <c r="AG34">
+        <v>2.15</v>
+      </c>
+      <c r="AH34">
+        <v>1.57</v>
+      </c>
+      <c r="AI34">
+        <v>2</v>
+      </c>
+      <c r="AJ34">
+        <v>1.75</v>
+      </c>
+      <c r="AK34">
+        <v>1.7</v>
+      </c>
+      <c r="AL34">
+        <v>1.28</v>
+      </c>
+      <c r="AM34">
+        <v>1.28</v>
+      </c>
+      <c r="AN34">
+        <v>1</v>
+      </c>
+      <c r="AO34">
+        <v>2</v>
+      </c>
+      <c r="AP34">
+        <v>0.75</v>
+      </c>
+      <c r="AQ34">
+        <v>2.33</v>
+      </c>
+      <c r="AR34">
+        <v>1.64</v>
+      </c>
+      <c r="AS34">
+        <v>1.54</v>
+      </c>
+      <c r="AT34">
+        <v>3.18</v>
+      </c>
+      <c r="AU34">
+        <v>3</v>
+      </c>
+      <c r="AV34">
+        <v>8</v>
+      </c>
+      <c r="AW34">
+        <v>12</v>
+      </c>
+      <c r="AX34">
+        <v>3</v>
+      </c>
+      <c r="AY34">
+        <v>15</v>
+      </c>
+      <c r="AZ34">
+        <v>11</v>
+      </c>
+      <c r="BA34">
+        <v>6</v>
+      </c>
+      <c r="BB34">
+        <v>3</v>
+      </c>
+      <c r="BC34">
+        <v>9</v>
+      </c>
+      <c r="BD34">
+        <v>1.98</v>
+      </c>
+      <c r="BE34">
+        <v>6.4</v>
+      </c>
+      <c r="BF34">
+        <v>1.98</v>
+      </c>
+      <c r="BG34">
+        <v>1.36</v>
+      </c>
+      <c r="BH34">
+        <v>2.8</v>
+      </c>
+      <c r="BI34">
+        <v>1.63</v>
+      </c>
+      <c r="BJ34">
+        <v>2.1</v>
+      </c>
+      <c r="BK34">
+        <v>2.02</v>
+      </c>
+      <c r="BL34">
+        <v>1.67</v>
+      </c>
+      <c r="BM34">
+        <v>2.55</v>
+      </c>
+      <c r="BN34">
+        <v>1.42</v>
+      </c>
+      <c r="BO34">
+        <v>3.4</v>
+      </c>
+      <c r="BP34">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:68">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>7775649</v>
+      </c>
+      <c r="C35" t="s">
+        <v>68</v>
+      </c>
+      <c r="D35" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" s="2">
+        <v>45744.70833333334</v>
+      </c>
+      <c r="F35">
+        <v>7</v>
+      </c>
+      <c r="G35" t="s">
+        <v>79</v>
+      </c>
+      <c r="H35" t="s">
+        <v>75</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35" t="s">
+        <v>82</v>
+      </c>
+      <c r="P35" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q35">
+        <v>3.1</v>
+      </c>
+      <c r="R35">
+        <v>1.95</v>
+      </c>
+      <c r="S35">
+        <v>4</v>
+      </c>
+      <c r="T35">
+        <v>1.53</v>
+      </c>
+      <c r="U35">
+        <v>2.38</v>
+      </c>
+      <c r="V35">
+        <v>3.5</v>
+      </c>
+      <c r="W35">
+        <v>1.29</v>
+      </c>
+      <c r="X35">
+        <v>11</v>
+      </c>
+      <c r="Y35">
+        <v>1.05</v>
+      </c>
+      <c r="Z35">
+        <v>2.25</v>
+      </c>
+      <c r="AA35">
+        <v>3</v>
+      </c>
+      <c r="AB35">
+        <v>3.2</v>
+      </c>
+      <c r="AC35">
+        <v>1.09</v>
+      </c>
+      <c r="AD35">
+        <v>7</v>
+      </c>
+      <c r="AE35">
+        <v>1.45</v>
+      </c>
+      <c r="AF35">
+        <v>2.7</v>
+      </c>
+      <c r="AG35">
+        <v>2.2</v>
+      </c>
+      <c r="AH35">
+        <v>1.55</v>
+      </c>
+      <c r="AI35">
+        <v>2</v>
+      </c>
+      <c r="AJ35">
+        <v>1.75</v>
+      </c>
+      <c r="AK35">
+        <v>1.33</v>
+      </c>
+      <c r="AL35">
+        <v>1.3</v>
+      </c>
+      <c r="AM35">
+        <v>1.6</v>
+      </c>
+      <c r="AN35">
+        <v>3</v>
+      </c>
+      <c r="AO35">
+        <v>1</v>
+      </c>
+      <c r="AP35">
+        <v>2</v>
+      </c>
+      <c r="AQ35">
+        <v>1</v>
+      </c>
+      <c r="AR35">
+        <v>1.34</v>
+      </c>
+      <c r="AS35">
+        <v>1.07</v>
+      </c>
+      <c r="AT35">
+        <v>2.41</v>
+      </c>
+      <c r="AU35">
+        <v>4</v>
+      </c>
+      <c r="AV35">
+        <v>2</v>
+      </c>
+      <c r="AW35">
+        <v>9</v>
+      </c>
+      <c r="AX35">
+        <v>7</v>
+      </c>
+      <c r="AY35">
+        <v>13</v>
+      </c>
+      <c r="AZ35">
+        <v>9</v>
+      </c>
+      <c r="BA35">
+        <v>5</v>
+      </c>
+      <c r="BB35">
+        <v>2</v>
+      </c>
+      <c r="BC35">
+        <v>7</v>
+      </c>
+      <c r="BD35">
+        <v>1.95</v>
+      </c>
+      <c r="BE35">
+        <v>6.4</v>
+      </c>
+      <c r="BF35">
+        <v>2.05</v>
+      </c>
+      <c r="BG35">
+        <v>1.36</v>
+      </c>
+      <c r="BH35">
+        <v>2.8</v>
+      </c>
+      <c r="BI35">
+        <v>1.62</v>
+      </c>
+      <c r="BJ35">
+        <v>2.1</v>
+      </c>
+      <c r="BK35">
+        <v>2</v>
+      </c>
+      <c r="BL35">
+        <v>1.68</v>
+      </c>
+      <c r="BM35">
+        <v>2.55</v>
+      </c>
+      <c r="BN35">
+        <v>1.43</v>
+      </c>
+      <c r="BO35">
+        <v>3.3</v>
+      </c>
+      <c r="BP35">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="131">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -331,6 +331,15 @@
     <t>['45+1']</t>
   </si>
   <si>
+    <t>['3', '5', '74', '90+6']</t>
+  </si>
+  <si>
+    <t>['65', '74']</t>
+  </si>
+  <si>
+    <t>['45', '67']</t>
+  </si>
+  <si>
     <t>['45+1', '81']</t>
   </si>
   <si>
@@ -392,6 +401,12 @@
   </si>
   <si>
     <t>['3', '12']</t>
+  </si>
+  <si>
+    <t>['24', '29']</t>
+  </si>
+  <si>
+    <t>['48']</t>
   </si>
 </sst>
 </file>
@@ -753,7 +768,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP35"/>
+  <dimension ref="A1:BP40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1009,7 +1024,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="Q2">
         <v>4.4</v>
@@ -1499,7 +1514,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AQ4">
         <v>2</v>
@@ -1627,7 +1642,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -1708,7 +1723,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ5">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -1911,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ6">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2117,7 +2132,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ7">
         <v>0.75</v>
@@ -2323,10 +2338,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ8">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2451,7 +2466,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -2529,7 +2544,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ9">
         <v>1</v>
@@ -2738,7 +2753,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ10">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -2863,7 +2878,7 @@
         <v>88</v>
       </c>
       <c r="P11" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="Q11">
         <v>1.94</v>
@@ -2941,10 +2956,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AQ11">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR11">
         <v>2.05</v>
@@ -3069,7 +3084,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="Q12">
         <v>3.95</v>
@@ -3150,7 +3165,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ12">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR12">
         <v>1.77</v>
@@ -3275,7 +3290,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="Q13">
         <v>4.5</v>
@@ -3353,7 +3368,7 @@
         <v>1</v>
       </c>
       <c r="AP13">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ13">
         <v>1.5</v>
@@ -3481,7 +3496,7 @@
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Q14">
         <v>3.9</v>
@@ -3687,7 +3702,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="Q15">
         <v>2.06</v>
@@ -3765,10 +3780,10 @@
         <v>3</v>
       </c>
       <c r="AP15">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ15">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AR15">
         <v>1.43</v>
@@ -3893,7 +3908,7 @@
         <v>82</v>
       </c>
       <c r="P16" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -3971,7 +3986,7 @@
         <v>1</v>
       </c>
       <c r="AP16">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ16">
         <v>2</v>
@@ -4099,7 +4114,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="Q17">
         <v>3.1</v>
@@ -4177,10 +4192,10 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ17">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AR17">
         <v>1.58</v>
@@ -4305,7 +4320,7 @@
         <v>94</v>
       </c>
       <c r="P18" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="Q18">
         <v>4.2</v>
@@ -4386,7 +4401,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ18">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR18">
         <v>2.63</v>
@@ -4589,7 +4604,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AQ19">
         <v>1</v>
@@ -4717,7 +4732,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="Q20">
         <v>2.65</v>
@@ -4798,7 +4813,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ20">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR20">
         <v>0.9</v>
@@ -4923,7 +4938,7 @@
         <v>82</v>
       </c>
       <c r="P21" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5335,7 +5350,7 @@
         <v>82</v>
       </c>
       <c r="P23" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Q23">
         <v>2.35</v>
@@ -5622,7 +5637,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ24">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR24">
         <v>1.36</v>
@@ -5747,7 +5762,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="Q25">
         <v>2.7</v>
@@ -5825,7 +5840,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ25">
         <v>1.5</v>
@@ -5953,7 +5968,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="Q26">
         <v>4.75</v>
@@ -6031,10 +6046,10 @@
         <v>0.33</v>
       </c>
       <c r="AP26">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ26">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR26">
         <v>1.55</v>
@@ -6237,10 +6252,10 @@
         <v>3</v>
       </c>
       <c r="AP27">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ27">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AR27">
         <v>1.49</v>
@@ -6365,7 +6380,7 @@
         <v>101</v>
       </c>
       <c r="P28" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -6446,7 +6461,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ28">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR28">
         <v>1.81</v>
@@ -6649,7 +6664,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AQ29">
         <v>0.75</v>
@@ -6777,7 +6792,7 @@
         <v>82</v>
       </c>
       <c r="P30" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="Q30">
         <v>4.5</v>
@@ -6983,7 +6998,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="Q31">
         <v>4.75</v>
@@ -7189,7 +7204,7 @@
         <v>82</v>
       </c>
       <c r="P32" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="Q32">
         <v>3</v>
@@ -7267,7 +7282,7 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ32">
         <v>1.5</v>
@@ -7601,7 +7616,7 @@
         <v>104</v>
       </c>
       <c r="P34" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="Q34">
         <v>4.33</v>
@@ -7682,7 +7697,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ34">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AR34">
         <v>1.64</v>
@@ -7963,6 +7978,1036 @@
         <v>3.3</v>
       </c>
       <c r="BP35">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="36" spans="1:68">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>7775655</v>
+      </c>
+      <c r="C36" t="s">
+        <v>68</v>
+      </c>
+      <c r="D36" t="s">
+        <v>69</v>
+      </c>
+      <c r="E36" s="2">
+        <v>45751.65625</v>
+      </c>
+      <c r="F36">
+        <v>8</v>
+      </c>
+      <c r="G36" t="s">
+        <v>72</v>
+      </c>
+      <c r="H36" t="s">
+        <v>71</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36" t="s">
+        <v>82</v>
+      </c>
+      <c r="P36" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q36">
+        <v>2.63</v>
+      </c>
+      <c r="R36">
+        <v>2</v>
+      </c>
+      <c r="S36">
+        <v>5</v>
+      </c>
+      <c r="T36">
+        <v>1.53</v>
+      </c>
+      <c r="U36">
+        <v>2.38</v>
+      </c>
+      <c r="V36">
+        <v>3.75</v>
+      </c>
+      <c r="W36">
+        <v>1.25</v>
+      </c>
+      <c r="X36">
+        <v>11</v>
+      </c>
+      <c r="Y36">
+        <v>1.05</v>
+      </c>
+      <c r="Z36">
+        <v>1.87</v>
+      </c>
+      <c r="AA36">
+        <v>3.28</v>
+      </c>
+      <c r="AB36">
+        <v>4.33</v>
+      </c>
+      <c r="AC36">
+        <v>1.03</v>
+      </c>
+      <c r="AD36">
+        <v>7.5</v>
+      </c>
+      <c r="AE36">
+        <v>1.41</v>
+      </c>
+      <c r="AF36">
+        <v>2.6</v>
+      </c>
+      <c r="AG36">
+        <v>2.25</v>
+      </c>
+      <c r="AH36">
+        <v>1.53</v>
+      </c>
+      <c r="AI36">
+        <v>2.1</v>
+      </c>
+      <c r="AJ36">
+        <v>1.67</v>
+      </c>
+      <c r="AK36">
+        <v>1.22</v>
+      </c>
+      <c r="AL36">
+        <v>1.33</v>
+      </c>
+      <c r="AM36">
+        <v>1.85</v>
+      </c>
+      <c r="AN36">
+        <v>2.5</v>
+      </c>
+      <c r="AO36">
+        <v>2.33</v>
+      </c>
+      <c r="AP36">
+        <v>2.2</v>
+      </c>
+      <c r="AQ36">
+        <v>2</v>
+      </c>
+      <c r="AR36">
+        <v>1.81</v>
+      </c>
+      <c r="AS36">
+        <v>1.52</v>
+      </c>
+      <c r="AT36">
+        <v>3.33</v>
+      </c>
+      <c r="AU36">
+        <v>3</v>
+      </c>
+      <c r="AV36">
+        <v>8</v>
+      </c>
+      <c r="AW36">
+        <v>16</v>
+      </c>
+      <c r="AX36">
+        <v>4</v>
+      </c>
+      <c r="AY36">
+        <v>19</v>
+      </c>
+      <c r="AZ36">
+        <v>12</v>
+      </c>
+      <c r="BA36">
+        <v>10</v>
+      </c>
+      <c r="BB36">
+        <v>4</v>
+      </c>
+      <c r="BC36">
+        <v>14</v>
+      </c>
+      <c r="BD36">
+        <v>1.57</v>
+      </c>
+      <c r="BE36">
+        <v>6.5</v>
+      </c>
+      <c r="BF36">
+        <v>2.65</v>
+      </c>
+      <c r="BG36">
+        <v>1.5</v>
+      </c>
+      <c r="BH36">
+        <v>2.33</v>
+      </c>
+      <c r="BI36">
+        <v>1.84</v>
+      </c>
+      <c r="BJ36">
+        <v>1.82</v>
+      </c>
+      <c r="BK36">
+        <v>2.33</v>
+      </c>
+      <c r="BL36">
+        <v>1.5</v>
+      </c>
+      <c r="BM36">
+        <v>3.15</v>
+      </c>
+      <c r="BN36">
+        <v>1.29</v>
+      </c>
+      <c r="BO36">
+        <v>4.3</v>
+      </c>
+      <c r="BP36">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:68">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>7775651</v>
+      </c>
+      <c r="C37" t="s">
+        <v>68</v>
+      </c>
+      <c r="D37" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37" s="2">
+        <v>45751.65625</v>
+      </c>
+      <c r="F37">
+        <v>8</v>
+      </c>
+      <c r="G37" t="s">
+        <v>74</v>
+      </c>
+      <c r="H37" t="s">
+        <v>73</v>
+      </c>
+      <c r="I37">
+        <v>2</v>
+      </c>
+      <c r="J37">
+        <v>2</v>
+      </c>
+      <c r="K37">
+        <v>4</v>
+      </c>
+      <c r="L37">
+        <v>4</v>
+      </c>
+      <c r="M37">
+        <v>2</v>
+      </c>
+      <c r="N37">
+        <v>6</v>
+      </c>
+      <c r="O37" t="s">
+        <v>105</v>
+      </c>
+      <c r="P37" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q37">
+        <v>2.38</v>
+      </c>
+      <c r="R37">
+        <v>2.2</v>
+      </c>
+      <c r="S37">
+        <v>5</v>
+      </c>
+      <c r="T37">
+        <v>1.4</v>
+      </c>
+      <c r="U37">
+        <v>2.75</v>
+      </c>
+      <c r="V37">
+        <v>2.75</v>
+      </c>
+      <c r="W37">
+        <v>1.4</v>
+      </c>
+      <c r="X37">
+        <v>8</v>
+      </c>
+      <c r="Y37">
+        <v>1.08</v>
+      </c>
+      <c r="Z37">
+        <v>1.7</v>
+      </c>
+      <c r="AA37">
+        <v>3.76</v>
+      </c>
+      <c r="AB37">
+        <v>4.6</v>
+      </c>
+      <c r="AC37">
+        <v>1.05</v>
+      </c>
+      <c r="AD37">
+        <v>9.5</v>
+      </c>
+      <c r="AE37">
+        <v>1.3</v>
+      </c>
+      <c r="AF37">
+        <v>3.45</v>
+      </c>
+      <c r="AG37">
+        <v>1.85</v>
+      </c>
+      <c r="AH37">
+        <v>1.89</v>
+      </c>
+      <c r="AI37">
+        <v>1.8</v>
+      </c>
+      <c r="AJ37">
+        <v>1.95</v>
+      </c>
+      <c r="AK37">
+        <v>1.2</v>
+      </c>
+      <c r="AL37">
+        <v>1.22</v>
+      </c>
+      <c r="AM37">
+        <v>2</v>
+      </c>
+      <c r="AN37">
+        <v>1</v>
+      </c>
+      <c r="AO37">
+        <v>0.33</v>
+      </c>
+      <c r="AP37">
+        <v>1.5</v>
+      </c>
+      <c r="AQ37">
+        <v>0.25</v>
+      </c>
+      <c r="AR37">
+        <v>1.78</v>
+      </c>
+      <c r="AS37">
+        <v>1.01</v>
+      </c>
+      <c r="AT37">
+        <v>2.79</v>
+      </c>
+      <c r="AU37">
+        <v>12</v>
+      </c>
+      <c r="AV37">
+        <v>6</v>
+      </c>
+      <c r="AW37">
+        <v>9</v>
+      </c>
+      <c r="AX37">
+        <v>7</v>
+      </c>
+      <c r="AY37">
+        <v>21</v>
+      </c>
+      <c r="AZ37">
+        <v>13</v>
+      </c>
+      <c r="BA37">
+        <v>5</v>
+      </c>
+      <c r="BB37">
+        <v>4</v>
+      </c>
+      <c r="BC37">
+        <v>9</v>
+      </c>
+      <c r="BD37">
+        <v>1.56</v>
+      </c>
+      <c r="BE37">
+        <v>7</v>
+      </c>
+      <c r="BF37">
+        <v>2.65</v>
+      </c>
+      <c r="BG37">
+        <v>1.21</v>
+      </c>
+      <c r="BH37">
+        <v>3.7</v>
+      </c>
+      <c r="BI37">
+        <v>1.37</v>
+      </c>
+      <c r="BJ37">
+        <v>2.75</v>
+      </c>
+      <c r="BK37">
+        <v>1.62</v>
+      </c>
+      <c r="BL37">
+        <v>2.12</v>
+      </c>
+      <c r="BM37">
+        <v>1.96</v>
+      </c>
+      <c r="BN37">
+        <v>1.71</v>
+      </c>
+      <c r="BO37">
+        <v>2.45</v>
+      </c>
+      <c r="BP37">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="38" spans="1:68">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>7775652</v>
+      </c>
+      <c r="C38" t="s">
+        <v>68</v>
+      </c>
+      <c r="D38" t="s">
+        <v>69</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45751.65625</v>
+      </c>
+      <c r="F38">
+        <v>8</v>
+      </c>
+      <c r="G38" t="s">
+        <v>75</v>
+      </c>
+      <c r="H38" t="s">
+        <v>70</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>1</v>
+      </c>
+      <c r="K38">
+        <v>1</v>
+      </c>
+      <c r="L38">
+        <v>2</v>
+      </c>
+      <c r="M38">
+        <v>1</v>
+      </c>
+      <c r="N38">
+        <v>3</v>
+      </c>
+      <c r="O38" t="s">
+        <v>106</v>
+      </c>
+      <c r="P38" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q38">
+        <v>2.1</v>
+      </c>
+      <c r="R38">
+        <v>2.2</v>
+      </c>
+      <c r="S38">
+        <v>7</v>
+      </c>
+      <c r="T38">
+        <v>1.44</v>
+      </c>
+      <c r="U38">
+        <v>2.63</v>
+      </c>
+      <c r="V38">
+        <v>3.25</v>
+      </c>
+      <c r="W38">
+        <v>1.33</v>
+      </c>
+      <c r="X38">
+        <v>9</v>
+      </c>
+      <c r="Y38">
+        <v>1.07</v>
+      </c>
+      <c r="Z38">
+        <v>1.48</v>
+      </c>
+      <c r="AA38">
+        <v>3.97</v>
+      </c>
+      <c r="AB38">
+        <v>7</v>
+      </c>
+      <c r="AC38">
+        <v>1.06</v>
+      </c>
+      <c r="AD38">
+        <v>8.5</v>
+      </c>
+      <c r="AE38">
+        <v>1.35</v>
+      </c>
+      <c r="AF38">
+        <v>3.1</v>
+      </c>
+      <c r="AG38">
+        <v>1.98</v>
+      </c>
+      <c r="AH38">
+        <v>1.77</v>
+      </c>
+      <c r="AI38">
+        <v>2.2</v>
+      </c>
+      <c r="AJ38">
+        <v>1.62</v>
+      </c>
+      <c r="AK38">
+        <v>1.11</v>
+      </c>
+      <c r="AL38">
+        <v>1.18</v>
+      </c>
+      <c r="AM38">
+        <v>2.5</v>
+      </c>
+      <c r="AN38">
+        <v>1.33</v>
+      </c>
+      <c r="AO38">
+        <v>0.5</v>
+      </c>
+      <c r="AP38">
+        <v>1.75</v>
+      </c>
+      <c r="AQ38">
+        <v>0.33</v>
+      </c>
+      <c r="AR38">
+        <v>1.99</v>
+      </c>
+      <c r="AS38">
+        <v>0.89</v>
+      </c>
+      <c r="AT38">
+        <v>2.88</v>
+      </c>
+      <c r="AU38">
+        <v>8</v>
+      </c>
+      <c r="AV38">
+        <v>3</v>
+      </c>
+      <c r="AW38">
+        <v>11</v>
+      </c>
+      <c r="AX38">
+        <v>3</v>
+      </c>
+      <c r="AY38">
+        <v>19</v>
+      </c>
+      <c r="AZ38">
+        <v>6</v>
+      </c>
+      <c r="BA38">
+        <v>7</v>
+      </c>
+      <c r="BB38">
+        <v>6</v>
+      </c>
+      <c r="BC38">
+        <v>13</v>
+      </c>
+      <c r="BD38">
+        <v>1.33</v>
+      </c>
+      <c r="BE38">
+        <v>7</v>
+      </c>
+      <c r="BF38">
+        <v>3.65</v>
+      </c>
+      <c r="BG38">
+        <v>1.34</v>
+      </c>
+      <c r="BH38">
+        <v>2.9</v>
+      </c>
+      <c r="BI38">
+        <v>1.58</v>
+      </c>
+      <c r="BJ38">
+        <v>2.18</v>
+      </c>
+      <c r="BK38">
+        <v>1.93</v>
+      </c>
+      <c r="BL38">
+        <v>1.74</v>
+      </c>
+      <c r="BM38">
+        <v>2.45</v>
+      </c>
+      <c r="BN38">
+        <v>1.46</v>
+      </c>
+      <c r="BO38">
+        <v>3.15</v>
+      </c>
+      <c r="BP38">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="39" spans="1:68">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>7775653</v>
+      </c>
+      <c r="C39" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" t="s">
+        <v>69</v>
+      </c>
+      <c r="E39" s="2">
+        <v>45751.65625</v>
+      </c>
+      <c r="F39">
+        <v>8</v>
+      </c>
+      <c r="G39" t="s">
+        <v>76</v>
+      </c>
+      <c r="H39" t="s">
+        <v>78</v>
+      </c>
+      <c r="I39">
+        <v>1</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>1</v>
+      </c>
+      <c r="L39">
+        <v>2</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>2</v>
+      </c>
+      <c r="O39" t="s">
+        <v>107</v>
+      </c>
+      <c r="P39" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q39">
+        <v>2.88</v>
+      </c>
+      <c r="R39">
+        <v>2.05</v>
+      </c>
+      <c r="S39">
+        <v>4</v>
+      </c>
+      <c r="T39">
+        <v>1.44</v>
+      </c>
+      <c r="U39">
+        <v>2.63</v>
+      </c>
+      <c r="V39">
+        <v>3.25</v>
+      </c>
+      <c r="W39">
+        <v>1.33</v>
+      </c>
+      <c r="X39">
+        <v>9</v>
+      </c>
+      <c r="Y39">
+        <v>1.07</v>
+      </c>
+      <c r="Z39">
+        <v>2.22</v>
+      </c>
+      <c r="AA39">
+        <v>3.18</v>
+      </c>
+      <c r="AB39">
+        <v>3.29</v>
+      </c>
+      <c r="AC39">
+        <v>1.09</v>
+      </c>
+      <c r="AD39">
+        <v>7</v>
+      </c>
+      <c r="AE39">
+        <v>1.42</v>
+      </c>
+      <c r="AF39">
+        <v>2.8</v>
+      </c>
+      <c r="AG39">
+        <v>2.25</v>
+      </c>
+      <c r="AH39">
+        <v>1.53</v>
+      </c>
+      <c r="AI39">
+        <v>1.8</v>
+      </c>
+      <c r="AJ39">
+        <v>1.95</v>
+      </c>
+      <c r="AK39">
+        <v>1.3</v>
+      </c>
+      <c r="AL39">
+        <v>1.3</v>
+      </c>
+      <c r="AM39">
+        <v>1.62</v>
+      </c>
+      <c r="AN39">
+        <v>1.33</v>
+      </c>
+      <c r="AO39">
+        <v>2</v>
+      </c>
+      <c r="AP39">
+        <v>1.75</v>
+      </c>
+      <c r="AQ39">
+        <v>1.5</v>
+      </c>
+      <c r="AR39">
+        <v>1.46</v>
+      </c>
+      <c r="AS39">
+        <v>1.05</v>
+      </c>
+      <c r="AT39">
+        <v>2.51</v>
+      </c>
+      <c r="AU39">
+        <v>4</v>
+      </c>
+      <c r="AV39">
+        <v>4</v>
+      </c>
+      <c r="AW39">
+        <v>12</v>
+      </c>
+      <c r="AX39">
+        <v>3</v>
+      </c>
+      <c r="AY39">
+        <v>16</v>
+      </c>
+      <c r="AZ39">
+        <v>7</v>
+      </c>
+      <c r="BA39">
+        <v>8</v>
+      </c>
+      <c r="BB39">
+        <v>9</v>
+      </c>
+      <c r="BC39">
+        <v>17</v>
+      </c>
+      <c r="BD39">
+        <v>1.86</v>
+      </c>
+      <c r="BE39">
+        <v>6.25</v>
+      </c>
+      <c r="BF39">
+        <v>2.17</v>
+      </c>
+      <c r="BG39">
+        <v>1.5</v>
+      </c>
+      <c r="BH39">
+        <v>2.33</v>
+      </c>
+      <c r="BI39">
+        <v>1.85</v>
+      </c>
+      <c r="BJ39">
+        <v>1.82</v>
+      </c>
+      <c r="BK39">
+        <v>2.35</v>
+      </c>
+      <c r="BL39">
+        <v>1.49</v>
+      </c>
+      <c r="BM39">
+        <v>3.1</v>
+      </c>
+      <c r="BN39">
+        <v>1.3</v>
+      </c>
+      <c r="BO39">
+        <v>4.1</v>
+      </c>
+      <c r="BP39">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:68">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>7775654</v>
+      </c>
+      <c r="C40" t="s">
+        <v>68</v>
+      </c>
+      <c r="D40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E40" s="2">
+        <v>45751.65625</v>
+      </c>
+      <c r="F40">
+        <v>8</v>
+      </c>
+      <c r="G40" t="s">
+        <v>77</v>
+      </c>
+      <c r="H40" t="s">
+        <v>79</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>1</v>
+      </c>
+      <c r="N40">
+        <v>1</v>
+      </c>
+      <c r="O40" t="s">
+        <v>82</v>
+      </c>
+      <c r="P40" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q40">
+        <v>4</v>
+      </c>
+      <c r="R40">
+        <v>1.91</v>
+      </c>
+      <c r="S40">
+        <v>3.2</v>
+      </c>
+      <c r="T40">
+        <v>1.57</v>
+      </c>
+      <c r="U40">
+        <v>2.25</v>
+      </c>
+      <c r="V40">
+        <v>3.75</v>
+      </c>
+      <c r="W40">
+        <v>1.25</v>
+      </c>
+      <c r="X40">
+        <v>13</v>
+      </c>
+      <c r="Y40">
+        <v>1.04</v>
+      </c>
+      <c r="Z40">
+        <v>3.38</v>
+      </c>
+      <c r="AA40">
+        <v>3.17</v>
+      </c>
+      <c r="AB40">
+        <v>2.18</v>
+      </c>
+      <c r="AC40">
+        <v>1.1</v>
+      </c>
+      <c r="AD40">
+        <v>6.5</v>
+      </c>
+      <c r="AE40">
+        <v>1.5</v>
+      </c>
+      <c r="AF40">
+        <v>2.3</v>
+      </c>
+      <c r="AG40">
+        <v>2.38</v>
+      </c>
+      <c r="AH40">
+        <v>1.58</v>
+      </c>
+      <c r="AI40">
+        <v>2.2</v>
+      </c>
+      <c r="AJ40">
+        <v>1.62</v>
+      </c>
+      <c r="AK40">
+        <v>1.53</v>
+      </c>
+      <c r="AL40">
+        <v>1.33</v>
+      </c>
+      <c r="AM40">
+        <v>1.35</v>
+      </c>
+      <c r="AN40">
+        <v>2.33</v>
+      </c>
+      <c r="AO40">
+        <v>1</v>
+      </c>
+      <c r="AP40">
+        <v>1.75</v>
+      </c>
+      <c r="AQ40">
+        <v>1.4</v>
+      </c>
+      <c r="AR40">
+        <v>1.69</v>
+      </c>
+      <c r="AS40">
+        <v>1.83</v>
+      </c>
+      <c r="AT40">
+        <v>3.52</v>
+      </c>
+      <c r="AU40">
+        <v>3</v>
+      </c>
+      <c r="AV40">
+        <v>3</v>
+      </c>
+      <c r="AW40">
+        <v>8</v>
+      </c>
+      <c r="AX40">
+        <v>9</v>
+      </c>
+      <c r="AY40">
+        <v>11</v>
+      </c>
+      <c r="AZ40">
+        <v>12</v>
+      </c>
+      <c r="BA40">
+        <v>2</v>
+      </c>
+      <c r="BB40">
+        <v>5</v>
+      </c>
+      <c r="BC40">
+        <v>7</v>
+      </c>
+      <c r="BD40">
+        <v>2.07</v>
+      </c>
+      <c r="BE40">
+        <v>6.5</v>
+      </c>
+      <c r="BF40">
+        <v>1.9</v>
+      </c>
+      <c r="BG40">
+        <v>1.34</v>
+      </c>
+      <c r="BH40">
+        <v>2.85</v>
+      </c>
+      <c r="BI40">
+        <v>1.58</v>
+      </c>
+      <c r="BJ40">
+        <v>2.16</v>
+      </c>
+      <c r="BK40">
+        <v>1.95</v>
+      </c>
+      <c r="BL40">
+        <v>1.72</v>
+      </c>
+      <c r="BM40">
+        <v>2.5</v>
+      </c>
+      <c r="BN40">
+        <v>1.44</v>
+      </c>
+      <c r="BO40">
+        <v>3.3</v>
+      </c>
+      <c r="BP40">
         <v>1.27</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="203">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -463,6 +463,12 @@
     <t>['19', '81']</t>
   </si>
   <si>
+    <t>['32']</t>
+  </si>
+  <si>
+    <t>['18']</t>
+  </si>
+  <si>
     <t>['45+1', '81']</t>
   </si>
   <si>
@@ -611,6 +617,12 @@
   </si>
   <si>
     <t>['23', '90+3']</t>
+  </si>
+  <si>
+    <t>['12', '83']</t>
+  </si>
+  <si>
+    <t>['11', '44']</t>
   </si>
 </sst>
 </file>
@@ -972,7 +984,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP93"/>
+  <dimension ref="A1:BP97"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1228,7 +1240,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Q2">
         <v>4.4</v>
@@ -1306,10 +1318,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ2">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1512,7 +1524,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ3">
         <v>1.22</v>
@@ -1718,10 +1730,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ4">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1846,7 +1858,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -2133,7 +2145,7 @@
         <v>2</v>
       </c>
       <c r="AQ6">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2336,10 +2348,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ7">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2670,7 +2682,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3082,7 +3094,7 @@
         <v>88</v>
       </c>
       <c r="P11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Q11">
         <v>1.94</v>
@@ -3160,7 +3172,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ11">
         <v>0.78</v>
@@ -3288,7 +3300,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q12">
         <v>3.95</v>
@@ -3366,10 +3378,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ12">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR12">
         <v>1.77</v>
@@ -3494,7 +3506,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q13">
         <v>4.5</v>
@@ -3575,7 +3587,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ13">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR13">
         <v>1.54</v>
@@ -3700,7 +3712,7 @@
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q14">
         <v>3.9</v>
@@ -3778,10 +3790,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ14">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR14">
         <v>1.46</v>
@@ -3906,7 +3918,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q15">
         <v>2.06</v>
@@ -3984,7 +3996,7 @@
         <v>3</v>
       </c>
       <c r="AP15">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ15">
         <v>1.44</v>
@@ -4112,7 +4124,7 @@
         <v>82</v>
       </c>
       <c r="P16" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4193,7 +4205,7 @@
         <v>2</v>
       </c>
       <c r="AQ16">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR16">
         <v>0.9399999999999999</v>
@@ -4318,7 +4330,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q17">
         <v>3.1</v>
@@ -4524,7 +4536,7 @@
         <v>94</v>
       </c>
       <c r="P18" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q18">
         <v>4.2</v>
@@ -4605,7 +4617,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ18">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR18">
         <v>2.63</v>
@@ -4808,7 +4820,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ19">
         <v>1.22</v>
@@ -4936,7 +4948,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q20">
         <v>2.65</v>
@@ -5142,7 +5154,7 @@
         <v>82</v>
       </c>
       <c r="P21" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5223,7 +5235,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ21">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR21">
         <v>1.81</v>
@@ -5554,7 +5566,7 @@
         <v>82</v>
       </c>
       <c r="P23" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q23">
         <v>2.35</v>
@@ -5632,10 +5644,10 @@
         <v>2</v>
       </c>
       <c r="AP23">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ23">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR23">
         <v>1.82</v>
@@ -5838,7 +5850,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ24">
         <v>0.78</v>
@@ -5966,7 +5978,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q25">
         <v>2.7</v>
@@ -6044,10 +6056,10 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ25">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR25">
         <v>1.72</v>
@@ -6172,7 +6184,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q26">
         <v>4.75</v>
@@ -6253,7 +6265,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ26">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR26">
         <v>1.55</v>
@@ -6584,7 +6596,7 @@
         <v>101</v>
       </c>
       <c r="P28" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -6662,7 +6674,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ28">
         <v>0.22</v>
@@ -6868,10 +6880,10 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ29">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR29">
         <v>1.92</v>
@@ -6996,7 +7008,7 @@
         <v>82</v>
       </c>
       <c r="P30" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q30">
         <v>4.5</v>
@@ -7202,7 +7214,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q31">
         <v>4.75</v>
@@ -7408,7 +7420,7 @@
         <v>82</v>
       </c>
       <c r="P32" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q32">
         <v>3</v>
@@ -7489,7 +7501,7 @@
         <v>2</v>
       </c>
       <c r="AQ32">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR32">
         <v>1.2</v>
@@ -7692,10 +7704,10 @@
         <v>2.33</v>
       </c>
       <c r="AP33">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ33">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR33">
         <v>1.68</v>
@@ -7820,7 +7832,7 @@
         <v>104</v>
       </c>
       <c r="P34" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q34">
         <v>4.33</v>
@@ -8310,7 +8322,7 @@
         <v>2.33</v>
       </c>
       <c r="AP36">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ36">
         <v>1.22</v>
@@ -8438,7 +8450,7 @@
         <v>105</v>
       </c>
       <c r="P37" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q37">
         <v>2.38</v>
@@ -8722,7 +8734,7 @@
         <v>0.5</v>
       </c>
       <c r="AP38">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ38">
         <v>0.22</v>
@@ -9137,7 +9149,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ40">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR40">
         <v>1.69</v>
@@ -9262,7 +9274,7 @@
         <v>82</v>
       </c>
       <c r="P41" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q41">
         <v>5.2</v>
@@ -9340,7 +9352,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ41">
         <v>1</v>
@@ -9546,10 +9558,10 @@
         <v>0.75</v>
       </c>
       <c r="AP42">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ42">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR42">
         <v>1.9</v>
@@ -9674,7 +9686,7 @@
         <v>109</v>
       </c>
       <c r="P43" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q43">
         <v>2.38</v>
@@ -9752,10 +9764,10 @@
         <v>2</v>
       </c>
       <c r="AP43">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ43">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR43">
         <v>2.04</v>
@@ -10086,7 +10098,7 @@
         <v>111</v>
       </c>
       <c r="P45" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q45">
         <v>4.04</v>
@@ -10167,7 +10179,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ45">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR45">
         <v>1.63</v>
@@ -10292,7 +10304,7 @@
         <v>112</v>
       </c>
       <c r="P46" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q46">
         <v>1.7</v>
@@ -10704,7 +10716,7 @@
         <v>114</v>
       </c>
       <c r="P48" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q48">
         <v>3.88</v>
@@ -10910,7 +10922,7 @@
         <v>115</v>
       </c>
       <c r="P49" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q49">
         <v>3.55</v>
@@ -11116,7 +11128,7 @@
         <v>116</v>
       </c>
       <c r="P50" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q50">
         <v>3.7</v>
@@ -11194,10 +11206,10 @@
         <v>1.4</v>
       </c>
       <c r="AP50">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ50">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR50">
         <v>1.81</v>
@@ -11322,7 +11334,7 @@
         <v>82</v>
       </c>
       <c r="P51" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q51">
         <v>2.6</v>
@@ -11528,7 +11540,7 @@
         <v>117</v>
       </c>
       <c r="P52" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q52">
         <v>2.24</v>
@@ -11609,7 +11621,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ52">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR52">
         <v>1.89</v>
@@ -12018,7 +12030,7 @@
         <v>1.2</v>
       </c>
       <c r="AP54">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ54">
         <v>1.44</v>
@@ -12146,7 +12158,7 @@
         <v>119</v>
       </c>
       <c r="P55" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q55">
         <v>2.6</v>
@@ -12224,10 +12236,10 @@
         <v>1.8</v>
       </c>
       <c r="AP55">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ55">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR55">
         <v>1.84</v>
@@ -12430,7 +12442,7 @@
         <v>0.8</v>
       </c>
       <c r="AP56">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ56">
         <v>0.78</v>
@@ -12558,7 +12570,7 @@
         <v>121</v>
       </c>
       <c r="P57" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -12845,7 +12857,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ58">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR58">
         <v>1.65</v>
@@ -12970,7 +12982,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q59">
         <v>4.75</v>
@@ -13176,7 +13188,7 @@
         <v>124</v>
       </c>
       <c r="P60" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q60">
         <v>2.61</v>
@@ -13382,7 +13394,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q61">
         <v>3.05</v>
@@ -13666,10 +13678,10 @@
         <v>1.67</v>
       </c>
       <c r="AP62">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ62">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR62">
         <v>1.73</v>
@@ -13794,7 +13806,7 @@
         <v>127</v>
       </c>
       <c r="P63" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q63">
         <v>3.28</v>
@@ -13875,7 +13887,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ63">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR63">
         <v>1.53</v>
@@ -14000,7 +14012,7 @@
         <v>128</v>
       </c>
       <c r="P64" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q64">
         <v>6.5</v>
@@ -14078,10 +14090,10 @@
         <v>1.33</v>
       </c>
       <c r="AP64">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ64">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR64">
         <v>1.6</v>
@@ -14206,7 +14218,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q65">
         <v>2.04</v>
@@ -14490,7 +14502,7 @@
         <v>1.67</v>
       </c>
       <c r="AP66">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ66">
         <v>1.22</v>
@@ -14618,7 +14630,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q67">
         <v>2.45</v>
@@ -14824,7 +14836,7 @@
         <v>132</v>
       </c>
       <c r="P68" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q68">
         <v>3.2</v>
@@ -14905,7 +14917,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ68">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR68">
         <v>1.65</v>
@@ -15030,7 +15042,7 @@
         <v>82</v>
       </c>
       <c r="P69" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q69">
         <v>2.04</v>
@@ -15108,7 +15120,7 @@
         <v>1.29</v>
       </c>
       <c r="AP69">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ69">
         <v>1.44</v>
@@ -15520,7 +15532,7 @@
         <v>1.17</v>
       </c>
       <c r="AP71">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ71">
         <v>1</v>
@@ -15648,7 +15660,7 @@
         <v>135</v>
       </c>
       <c r="P72" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q72">
         <v>3.26</v>
@@ -15726,7 +15738,7 @@
         <v>1</v>
       </c>
       <c r="AP72">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ72">
         <v>1</v>
@@ -15854,7 +15866,7 @@
         <v>97</v>
       </c>
       <c r="P73" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q73">
         <v>4.6</v>
@@ -15932,7 +15944,7 @@
         <v>1.17</v>
       </c>
       <c r="AP73">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ73">
         <v>1.22</v>
@@ -16141,7 +16153,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ74">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR74">
         <v>1.51</v>
@@ -16347,7 +16359,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ75">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR75">
         <v>1.88</v>
@@ -16472,7 +16484,7 @@
         <v>82</v>
       </c>
       <c r="P76" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q76">
         <v>3.65</v>
@@ -16553,7 +16565,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ76">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR76">
         <v>1.54</v>
@@ -16678,7 +16690,7 @@
         <v>82</v>
       </c>
       <c r="P77" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q77">
         <v>2.05</v>
@@ -16884,7 +16896,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q78">
         <v>1.89</v>
@@ -16962,7 +16974,7 @@
         <v>0.29</v>
       </c>
       <c r="AP78">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ78">
         <v>0.22</v>
@@ -17502,7 +17514,7 @@
         <v>85</v>
       </c>
       <c r="P81" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q81">
         <v>5.25</v>
@@ -17583,7 +17595,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ81">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR81">
         <v>1.57</v>
@@ -17786,10 +17798,10 @@
         <v>1.5</v>
       </c>
       <c r="AP82">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ82">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR82">
         <v>2.02</v>
@@ -18201,7 +18213,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ84">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR84">
         <v>1.45</v>
@@ -18326,7 +18338,7 @@
         <v>143</v>
       </c>
       <c r="P85" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q85">
         <v>2.2</v>
@@ -18532,7 +18544,7 @@
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q86">
         <v>2.11</v>
@@ -18610,7 +18622,7 @@
         <v>0.88</v>
       </c>
       <c r="AP86">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ86">
         <v>0.78</v>
@@ -18738,7 +18750,7 @@
         <v>145</v>
       </c>
       <c r="P87" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q87">
         <v>2.04</v>
@@ -18816,7 +18828,7 @@
         <v>1.5</v>
       </c>
       <c r="AP87">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ87">
         <v>1.44</v>
@@ -18944,7 +18956,7 @@
         <v>146</v>
       </c>
       <c r="P88" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19022,10 +19034,10 @@
         <v>1.5</v>
       </c>
       <c r="AP88">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ88">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR88">
         <v>1.76</v>
@@ -19356,7 +19368,7 @@
         <v>147</v>
       </c>
       <c r="P90" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q90">
         <v>3.81</v>
@@ -19434,7 +19446,7 @@
         <v>1.25</v>
       </c>
       <c r="AP90">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ90">
         <v>1.22</v>
@@ -19562,7 +19574,7 @@
         <v>148</v>
       </c>
       <c r="P91" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q91">
         <v>3.3</v>
@@ -19643,7 +19655,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ91">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR91">
         <v>1.53</v>
@@ -20055,7 +20067,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ93">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR93">
         <v>1.9</v>
@@ -20131,6 +20143,830 @@
       </c>
       <c r="BP93">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="94" spans="1:68">
+      <c r="A94" s="1">
+        <v>93</v>
+      </c>
+      <c r="B94">
+        <v>7775708</v>
+      </c>
+      <c r="C94" t="s">
+        <v>68</v>
+      </c>
+      <c r="D94" t="s">
+        <v>69</v>
+      </c>
+      <c r="E94" s="2">
+        <v>45821.65625</v>
+      </c>
+      <c r="F94">
+        <v>19</v>
+      </c>
+      <c r="G94" t="s">
+        <v>71</v>
+      </c>
+      <c r="H94" t="s">
+        <v>79</v>
+      </c>
+      <c r="I94">
+        <v>1</v>
+      </c>
+      <c r="J94">
+        <v>1</v>
+      </c>
+      <c r="K94">
+        <v>2</v>
+      </c>
+      <c r="L94">
+        <v>1</v>
+      </c>
+      <c r="M94">
+        <v>2</v>
+      </c>
+      <c r="N94">
+        <v>3</v>
+      </c>
+      <c r="O94" t="s">
+        <v>149</v>
+      </c>
+      <c r="P94" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q94">
+        <v>3.8</v>
+      </c>
+      <c r="R94">
+        <v>1.87</v>
+      </c>
+      <c r="S94">
+        <v>3.12</v>
+      </c>
+      <c r="T94">
+        <v>1.57</v>
+      </c>
+      <c r="U94">
+        <v>2.4</v>
+      </c>
+      <c r="V94">
+        <v>3.4</v>
+      </c>
+      <c r="W94">
+        <v>1.27</v>
+      </c>
+      <c r="X94">
+        <v>9.75</v>
+      </c>
+      <c r="Y94">
+        <v>1.04</v>
+      </c>
+      <c r="Z94">
+        <v>2.88</v>
+      </c>
+      <c r="AA94">
+        <v>3.03</v>
+      </c>
+      <c r="AB94">
+        <v>2.26</v>
+      </c>
+      <c r="AC94">
+        <v>1.09</v>
+      </c>
+      <c r="AD94">
+        <v>6.5</v>
+      </c>
+      <c r="AE94">
+        <v>1.48</v>
+      </c>
+      <c r="AF94">
+        <v>2.66</v>
+      </c>
+      <c r="AG94">
+        <v>2.37</v>
+      </c>
+      <c r="AH94">
+        <v>1.48</v>
+      </c>
+      <c r="AI94">
+        <v>2.05</v>
+      </c>
+      <c r="AJ94">
+        <v>1.66</v>
+      </c>
+      <c r="AK94">
+        <v>1.37</v>
+      </c>
+      <c r="AL94">
+        <v>1.3</v>
+      </c>
+      <c r="AM94">
+        <v>1.31</v>
+      </c>
+      <c r="AN94">
+        <v>1.6</v>
+      </c>
+      <c r="AO94">
+        <v>1.67</v>
+      </c>
+      <c r="AP94">
+        <v>1.45</v>
+      </c>
+      <c r="AQ94">
+        <v>1.8</v>
+      </c>
+      <c r="AR94">
+        <v>2.08</v>
+      </c>
+      <c r="AS94">
+        <v>1.64</v>
+      </c>
+      <c r="AT94">
+        <v>3.72</v>
+      </c>
+      <c r="AU94">
+        <v>2</v>
+      </c>
+      <c r="AV94">
+        <v>7</v>
+      </c>
+      <c r="AW94">
+        <v>8</v>
+      </c>
+      <c r="AX94">
+        <v>9</v>
+      </c>
+      <c r="AY94">
+        <v>10</v>
+      </c>
+      <c r="AZ94">
+        <v>16</v>
+      </c>
+      <c r="BA94">
+        <v>2</v>
+      </c>
+      <c r="BB94">
+        <v>4</v>
+      </c>
+      <c r="BC94">
+        <v>6</v>
+      </c>
+      <c r="BD94">
+        <v>2.05</v>
+      </c>
+      <c r="BE94">
+        <v>7</v>
+      </c>
+      <c r="BF94">
+        <v>2.15</v>
+      </c>
+      <c r="BG94">
+        <v>1.26</v>
+      </c>
+      <c r="BH94">
+        <v>3.3</v>
+      </c>
+      <c r="BI94">
+        <v>1.49</v>
+      </c>
+      <c r="BJ94">
+        <v>2.2</v>
+      </c>
+      <c r="BK94">
+        <v>1.91</v>
+      </c>
+      <c r="BL94">
+        <v>1.8</v>
+      </c>
+      <c r="BM94">
+        <v>2.5</v>
+      </c>
+      <c r="BN94">
+        <v>1.44</v>
+      </c>
+      <c r="BO94">
+        <v>3.5</v>
+      </c>
+      <c r="BP94">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="95" spans="1:68">
+      <c r="A95" s="1">
+        <v>94</v>
+      </c>
+      <c r="B95">
+        <v>7775709</v>
+      </c>
+      <c r="C95" t="s">
+        <v>68</v>
+      </c>
+      <c r="D95" t="s">
+        <v>69</v>
+      </c>
+      <c r="E95" s="2">
+        <v>45821.65625</v>
+      </c>
+      <c r="F95">
+        <v>19</v>
+      </c>
+      <c r="G95" t="s">
+        <v>72</v>
+      </c>
+      <c r="H95" t="s">
+        <v>76</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0</v>
+      </c>
+      <c r="K95">
+        <v>0</v>
+      </c>
+      <c r="L95">
+        <v>0</v>
+      </c>
+      <c r="M95">
+        <v>0</v>
+      </c>
+      <c r="N95">
+        <v>0</v>
+      </c>
+      <c r="O95" t="s">
+        <v>82</v>
+      </c>
+      <c r="P95" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q95">
+        <v>2.3</v>
+      </c>
+      <c r="R95">
+        <v>2.2</v>
+      </c>
+      <c r="S95">
+        <v>4</v>
+      </c>
+      <c r="T95">
+        <v>1.41</v>
+      </c>
+      <c r="U95">
+        <v>2.81</v>
+      </c>
+      <c r="V95">
+        <v>2.85</v>
+      </c>
+      <c r="W95">
+        <v>1.37</v>
+      </c>
+      <c r="X95">
+        <v>7.5</v>
+      </c>
+      <c r="Y95">
+        <v>1.08</v>
+      </c>
+      <c r="Z95">
+        <v>1.67</v>
+      </c>
+      <c r="AA95">
+        <v>3.41</v>
+      </c>
+      <c r="AB95">
+        <v>4.4</v>
+      </c>
+      <c r="AC95">
+        <v>1.05</v>
+      </c>
+      <c r="AD95">
+        <v>8.75</v>
+      </c>
+      <c r="AE95">
+        <v>1.3</v>
+      </c>
+      <c r="AF95">
+        <v>3.1</v>
+      </c>
+      <c r="AG95">
+        <v>1.95</v>
+      </c>
+      <c r="AH95">
+        <v>1.75</v>
+      </c>
+      <c r="AI95">
+        <v>1.9</v>
+      </c>
+      <c r="AJ95">
+        <v>1.93</v>
+      </c>
+      <c r="AK95">
+        <v>1.28</v>
+      </c>
+      <c r="AL95">
+        <v>1.25</v>
+      </c>
+      <c r="AM95">
+        <v>2.13</v>
+      </c>
+      <c r="AN95">
+        <v>2.11</v>
+      </c>
+      <c r="AO95">
+        <v>1.4</v>
+      </c>
+      <c r="AP95">
+        <v>2</v>
+      </c>
+      <c r="AQ95">
+        <v>1.36</v>
+      </c>
+      <c r="AR95">
+        <v>1.63</v>
+      </c>
+      <c r="AS95">
+        <v>1.42</v>
+      </c>
+      <c r="AT95">
+        <v>3.05</v>
+      </c>
+      <c r="AU95">
+        <v>3</v>
+      </c>
+      <c r="AV95">
+        <v>3</v>
+      </c>
+      <c r="AW95">
+        <v>16</v>
+      </c>
+      <c r="AX95">
+        <v>6</v>
+      </c>
+      <c r="AY95">
+        <v>19</v>
+      </c>
+      <c r="AZ95">
+        <v>9</v>
+      </c>
+      <c r="BA95">
+        <v>4</v>
+      </c>
+      <c r="BB95">
+        <v>4</v>
+      </c>
+      <c r="BC95">
+        <v>8</v>
+      </c>
+      <c r="BD95">
+        <v>1.44</v>
+      </c>
+      <c r="BE95">
+        <v>9.5</v>
+      </c>
+      <c r="BF95">
+        <v>3.65</v>
+      </c>
+      <c r="BG95">
+        <v>1.23</v>
+      </c>
+      <c r="BH95">
+        <v>3.6</v>
+      </c>
+      <c r="BI95">
+        <v>1.44</v>
+      </c>
+      <c r="BJ95">
+        <v>2.45</v>
+      </c>
+      <c r="BK95">
+        <v>1.8</v>
+      </c>
+      <c r="BL95">
+        <v>1.91</v>
+      </c>
+      <c r="BM95">
+        <v>2.35</v>
+      </c>
+      <c r="BN95">
+        <v>1.49</v>
+      </c>
+      <c r="BO95">
+        <v>3.2</v>
+      </c>
+      <c r="BP95">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="96" spans="1:68">
+      <c r="A96" s="1">
+        <v>95</v>
+      </c>
+      <c r="B96">
+        <v>7775706</v>
+      </c>
+      <c r="C96" t="s">
+        <v>68</v>
+      </c>
+      <c r="D96" t="s">
+        <v>69</v>
+      </c>
+      <c r="E96" s="2">
+        <v>45821.65625</v>
+      </c>
+      <c r="F96">
+        <v>19</v>
+      </c>
+      <c r="G96" t="s">
+        <v>70</v>
+      </c>
+      <c r="H96" t="s">
+        <v>74</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>2</v>
+      </c>
+      <c r="K96">
+        <v>2</v>
+      </c>
+      <c r="L96">
+        <v>0</v>
+      </c>
+      <c r="M96">
+        <v>2</v>
+      </c>
+      <c r="N96">
+        <v>2</v>
+      </c>
+      <c r="O96" t="s">
+        <v>82</v>
+      </c>
+      <c r="P96" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q96">
+        <v>4.1</v>
+      </c>
+      <c r="R96">
+        <v>2.1</v>
+      </c>
+      <c r="S96">
+        <v>2.4</v>
+      </c>
+      <c r="T96">
+        <v>1.4</v>
+      </c>
+      <c r="U96">
+        <v>2.75</v>
+      </c>
+      <c r="V96">
+        <v>2.98</v>
+      </c>
+      <c r="W96">
+        <v>1.39</v>
+      </c>
+      <c r="X96">
+        <v>7</v>
+      </c>
+      <c r="Y96">
+        <v>1.08</v>
+      </c>
+      <c r="Z96">
+        <v>3.94</v>
+      </c>
+      <c r="AA96">
+        <v>3.27</v>
+      </c>
+      <c r="AB96">
+        <v>1.79</v>
+      </c>
+      <c r="AC96">
+        <v>1.06</v>
+      </c>
+      <c r="AD96">
+        <v>9</v>
+      </c>
+      <c r="AE96">
+        <v>1.3</v>
+      </c>
+      <c r="AF96">
+        <v>3.25</v>
+      </c>
+      <c r="AG96">
+        <v>1.94</v>
+      </c>
+      <c r="AH96">
+        <v>1.76</v>
+      </c>
+      <c r="AI96">
+        <v>1.8</v>
+      </c>
+      <c r="AJ96">
+        <v>1.91</v>
+      </c>
+      <c r="AK96">
+        <v>1.28</v>
+      </c>
+      <c r="AL96">
+        <v>1.25</v>
+      </c>
+      <c r="AM96">
+        <v>1.24</v>
+      </c>
+      <c r="AN96">
+        <v>1.22</v>
+      </c>
+      <c r="AO96">
+        <v>1.33</v>
+      </c>
+      <c r="AP96">
+        <v>1.1</v>
+      </c>
+      <c r="AQ96">
+        <v>1.5</v>
+      </c>
+      <c r="AR96">
+        <v>1.55</v>
+      </c>
+      <c r="AS96">
+        <v>1.55</v>
+      </c>
+      <c r="AT96">
+        <v>3.1</v>
+      </c>
+      <c r="AU96">
+        <v>2</v>
+      </c>
+      <c r="AV96">
+        <v>9</v>
+      </c>
+      <c r="AW96">
+        <v>6</v>
+      </c>
+      <c r="AX96">
+        <v>9</v>
+      </c>
+      <c r="AY96">
+        <v>8</v>
+      </c>
+      <c r="AZ96">
+        <v>18</v>
+      </c>
+      <c r="BA96">
+        <v>1</v>
+      </c>
+      <c r="BB96">
+        <v>7</v>
+      </c>
+      <c r="BC96">
+        <v>8</v>
+      </c>
+      <c r="BD96">
+        <v>3.1</v>
+      </c>
+      <c r="BE96">
+        <v>7.5</v>
+      </c>
+      <c r="BF96">
+        <v>1.55</v>
+      </c>
+      <c r="BG96">
+        <v>1.22</v>
+      </c>
+      <c r="BH96">
+        <v>3.8</v>
+      </c>
+      <c r="BI96">
+        <v>1.32</v>
+      </c>
+      <c r="BJ96">
+        <v>3</v>
+      </c>
+      <c r="BK96">
+        <v>1.58</v>
+      </c>
+      <c r="BL96">
+        <v>2.15</v>
+      </c>
+      <c r="BM96">
+        <v>2</v>
+      </c>
+      <c r="BN96">
+        <v>1.68</v>
+      </c>
+      <c r="BO96">
+        <v>2.5</v>
+      </c>
+      <c r="BP96">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="97" spans="1:68">
+      <c r="A97" s="1">
+        <v>96</v>
+      </c>
+      <c r="B97">
+        <v>7775707</v>
+      </c>
+      <c r="C97" t="s">
+        <v>68</v>
+      </c>
+      <c r="D97" t="s">
+        <v>69</v>
+      </c>
+      <c r="E97" s="2">
+        <v>45821.65625</v>
+      </c>
+      <c r="F97">
+        <v>19</v>
+      </c>
+      <c r="G97" t="s">
+        <v>75</v>
+      </c>
+      <c r="H97" t="s">
+        <v>77</v>
+      </c>
+      <c r="I97">
+        <v>1</v>
+      </c>
+      <c r="J97">
+        <v>1</v>
+      </c>
+      <c r="K97">
+        <v>2</v>
+      </c>
+      <c r="L97">
+        <v>1</v>
+      </c>
+      <c r="M97">
+        <v>1</v>
+      </c>
+      <c r="N97">
+        <v>2</v>
+      </c>
+      <c r="O97" t="s">
+        <v>150</v>
+      </c>
+      <c r="P97" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q97">
+        <v>2.15</v>
+      </c>
+      <c r="R97">
+        <v>2.1</v>
+      </c>
+      <c r="S97">
+        <v>4.5</v>
+      </c>
+      <c r="T97">
+        <v>1.42</v>
+      </c>
+      <c r="U97">
+        <v>2.78</v>
+      </c>
+      <c r="V97">
+        <v>3.32</v>
+      </c>
+      <c r="W97">
+        <v>1.34</v>
+      </c>
+      <c r="X97">
+        <v>7.5</v>
+      </c>
+      <c r="Y97">
+        <v>1.05</v>
+      </c>
+      <c r="Z97">
+        <v>1.75</v>
+      </c>
+      <c r="AA97">
+        <v>3.18</v>
+      </c>
+      <c r="AB97">
+        <v>4.2</v>
+      </c>
+      <c r="AC97">
+        <v>1.06</v>
+      </c>
+      <c r="AD97">
+        <v>8</v>
+      </c>
+      <c r="AE97">
+        <v>1.33</v>
+      </c>
+      <c r="AF97">
+        <v>3.1</v>
+      </c>
+      <c r="AG97">
+        <v>2.2</v>
+      </c>
+      <c r="AH97">
+        <v>1.53</v>
+      </c>
+      <c r="AI97">
+        <v>1.98</v>
+      </c>
+      <c r="AJ97">
+        <v>1.83</v>
+      </c>
+      <c r="AK97">
+        <v>1.31</v>
+      </c>
+      <c r="AL97">
+        <v>1.28</v>
+      </c>
+      <c r="AM97">
+        <v>2.05</v>
+      </c>
+      <c r="AN97">
+        <v>1.78</v>
+      </c>
+      <c r="AO97">
+        <v>1.22</v>
+      </c>
+      <c r="AP97">
+        <v>1.7</v>
+      </c>
+      <c r="AQ97">
+        <v>1.2</v>
+      </c>
+      <c r="AR97">
+        <v>1.72</v>
+      </c>
+      <c r="AS97">
+        <v>1.54</v>
+      </c>
+      <c r="AT97">
+        <v>3.26</v>
+      </c>
+      <c r="AU97">
+        <v>4</v>
+      </c>
+      <c r="AV97">
+        <v>2</v>
+      </c>
+      <c r="AW97">
+        <v>15</v>
+      </c>
+      <c r="AX97">
+        <v>4</v>
+      </c>
+      <c r="AY97">
+        <v>19</v>
+      </c>
+      <c r="AZ97">
+        <v>6</v>
+      </c>
+      <c r="BA97">
+        <v>5</v>
+      </c>
+      <c r="BB97">
+        <v>1</v>
+      </c>
+      <c r="BC97">
+        <v>6</v>
+      </c>
+      <c r="BD97">
+        <v>1.3</v>
+      </c>
+      <c r="BE97">
+        <v>8</v>
+      </c>
+      <c r="BF97">
+        <v>4.75</v>
+      </c>
+      <c r="BG97">
+        <v>1.24</v>
+      </c>
+      <c r="BH97">
+        <v>3.6</v>
+      </c>
+      <c r="BI97">
+        <v>1.44</v>
+      </c>
+      <c r="BJ97">
+        <v>2.45</v>
+      </c>
+      <c r="BK97">
+        <v>1.85</v>
+      </c>
+      <c r="BL97">
+        <v>1.85</v>
+      </c>
+      <c r="BM97">
+        <v>2.35</v>
+      </c>
+      <c r="BN97">
+        <v>1.49</v>
+      </c>
+      <c r="BO97">
+        <v>3.25</v>
+      </c>
+      <c r="BP97">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="203">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -469,6 +469,9 @@
     <t>['18']</t>
   </si>
   <si>
+    <t>['20']</t>
+  </si>
+  <si>
     <t>['45+1', '81']</t>
   </si>
   <si>
@@ -518,9 +521,6 @@
   </si>
   <si>
     <t>['50']</t>
-  </si>
-  <si>
-    <t>['20']</t>
   </si>
   <si>
     <t>['88', '90']</t>
@@ -984,7 +984,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP97"/>
+  <dimension ref="A1:BP98"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1240,7 +1240,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q2">
         <v>4.4</v>
@@ -1858,7 +1858,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -1936,10 +1936,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AQ5">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2682,7 +2682,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3094,7 +3094,7 @@
         <v>88</v>
       </c>
       <c r="P11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q11">
         <v>1.94</v>
@@ -3300,7 +3300,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q12">
         <v>3.95</v>
@@ -3506,7 +3506,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q13">
         <v>4.5</v>
@@ -3712,7 +3712,7 @@
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q14">
         <v>3.9</v>
@@ -3918,7 +3918,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q15">
         <v>2.06</v>
@@ -3999,7 +3999,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ15">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR15">
         <v>1.43</v>
@@ -4124,7 +4124,7 @@
         <v>82</v>
       </c>
       <c r="P16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4330,7 +4330,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q17">
         <v>3.1</v>
@@ -4536,7 +4536,7 @@
         <v>94</v>
       </c>
       <c r="P18" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q18">
         <v>4.2</v>
@@ -4614,7 +4614,7 @@
         <v>0.5</v>
       </c>
       <c r="AP18">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AQ18">
         <v>1.8</v>
@@ -4948,7 +4948,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q20">
         <v>2.65</v>
@@ -5154,7 +5154,7 @@
         <v>82</v>
       </c>
       <c r="P21" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5566,7 +5566,7 @@
         <v>82</v>
       </c>
       <c r="P23" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q23">
         <v>2.35</v>
@@ -5978,7 +5978,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q25">
         <v>2.7</v>
@@ -6184,7 +6184,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q26">
         <v>4.75</v>
@@ -6471,7 +6471,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ27">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR27">
         <v>1.49</v>
@@ -6596,7 +6596,7 @@
         <v>101</v>
       </c>
       <c r="P28" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -7008,7 +7008,7 @@
         <v>82</v>
       </c>
       <c r="P30" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="Q30">
         <v>4.5</v>
@@ -7086,7 +7086,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AQ30">
         <v>1.22</v>
@@ -7910,7 +7910,7 @@
         <v>2</v>
       </c>
       <c r="AP34">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AQ34">
         <v>1.22</v>
@@ -8943,7 +8943,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ39">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR39">
         <v>1.46</v>
@@ -9973,7 +9973,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ44">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR44">
         <v>1.38</v>
@@ -10176,7 +10176,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AQ45">
         <v>1.2</v>
@@ -12033,7 +12033,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ54">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR54">
         <v>1.59</v>
@@ -13394,7 +13394,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q61">
         <v>3.05</v>
@@ -13472,7 +13472,7 @@
         <v>0.2</v>
       </c>
       <c r="AP61">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AQ61">
         <v>0.22</v>
@@ -13884,7 +13884,7 @@
         <v>1.83</v>
       </c>
       <c r="AP63">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AQ63">
         <v>1.36</v>
@@ -14012,7 +14012,7 @@
         <v>128</v>
       </c>
       <c r="P64" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q64">
         <v>6.5</v>
@@ -14299,7 +14299,7 @@
         <v>2</v>
       </c>
       <c r="AQ65">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR65">
         <v>1.97</v>
@@ -15123,7 +15123,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ69">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR69">
         <v>2.05</v>
@@ -16562,7 +16562,7 @@
         <v>1.29</v>
       </c>
       <c r="AP76">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AQ76">
         <v>1.5</v>
@@ -16690,7 +16690,7 @@
         <v>82</v>
       </c>
       <c r="P77" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q77">
         <v>2.05</v>
@@ -18338,7 +18338,7 @@
         <v>143</v>
       </c>
       <c r="P85" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q85">
         <v>2.2</v>
@@ -18831,7 +18831,7 @@
         <v>2</v>
       </c>
       <c r="AQ87">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR87">
         <v>1.69</v>
@@ -19240,7 +19240,7 @@
         <v>0.78</v>
       </c>
       <c r="AP89">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AQ89">
         <v>1</v>
@@ -20162,7 +20162,7 @@
         <v>45821.65625</v>
       </c>
       <c r="F94">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G94" t="s">
         <v>71</v>
@@ -20368,7 +20368,7 @@
         <v>45821.65625</v>
       </c>
       <c r="F95">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G95" t="s">
         <v>72</v>
@@ -20574,7 +20574,7 @@
         <v>45821.65625</v>
       </c>
       <c r="F96">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G96" t="s">
         <v>70</v>
@@ -20780,7 +20780,7 @@
         <v>45821.65625</v>
       </c>
       <c r="F97">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G97" t="s">
         <v>75</v>
@@ -20967,6 +20967,212 @@
       </c>
       <c r="BP97">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="98" spans="1:68">
+      <c r="A98" s="1">
+        <v>97</v>
+      </c>
+      <c r="B98">
+        <v>7775710</v>
+      </c>
+      <c r="C98" t="s">
+        <v>68</v>
+      </c>
+      <c r="D98" t="s">
+        <v>69</v>
+      </c>
+      <c r="E98" s="2">
+        <v>45822.65625</v>
+      </c>
+      <c r="F98">
+        <v>0</v>
+      </c>
+      <c r="G98" t="s">
+        <v>73</v>
+      </c>
+      <c r="H98" t="s">
+        <v>78</v>
+      </c>
+      <c r="I98">
+        <v>1</v>
+      </c>
+      <c r="J98">
+        <v>0</v>
+      </c>
+      <c r="K98">
+        <v>1</v>
+      </c>
+      <c r="L98">
+        <v>1</v>
+      </c>
+      <c r="M98">
+        <v>0</v>
+      </c>
+      <c r="N98">
+        <v>1</v>
+      </c>
+      <c r="O98" t="s">
+        <v>151</v>
+      </c>
+      <c r="P98" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q98">
+        <v>2.9</v>
+      </c>
+      <c r="R98">
+        <v>1.95</v>
+      </c>
+      <c r="S98">
+        <v>3.2</v>
+      </c>
+      <c r="T98">
+        <v>1.32</v>
+      </c>
+      <c r="U98">
+        <v>3</v>
+      </c>
+      <c r="V98">
+        <v>2.54</v>
+      </c>
+      <c r="W98">
+        <v>1.43</v>
+      </c>
+      <c r="X98">
+        <v>6.1</v>
+      </c>
+      <c r="Y98">
+        <v>1.06</v>
+      </c>
+      <c r="Z98">
+        <v>2.4</v>
+      </c>
+      <c r="AA98">
+        <v>3.4</v>
+      </c>
+      <c r="AB98">
+        <v>2.65</v>
+      </c>
+      <c r="AC98">
+        <v>1.05</v>
+      </c>
+      <c r="AD98">
+        <v>11</v>
+      </c>
+      <c r="AE98">
+        <v>1.22</v>
+      </c>
+      <c r="AF98">
+        <v>3.8</v>
+      </c>
+      <c r="AG98">
+        <v>1.76</v>
+      </c>
+      <c r="AH98">
+        <v>1.95</v>
+      </c>
+      <c r="AI98">
+        <v>1.62</v>
+      </c>
+      <c r="AJ98">
+        <v>2.16</v>
+      </c>
+      <c r="AK98">
+        <v>1.3</v>
+      </c>
+      <c r="AL98">
+        <v>1.25</v>
+      </c>
+      <c r="AM98">
+        <v>1.44</v>
+      </c>
+      <c r="AN98">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AO98">
+        <v>1.44</v>
+      </c>
+      <c r="AP98">
+        <v>0.8</v>
+      </c>
+      <c r="AQ98">
+        <v>1.3</v>
+      </c>
+      <c r="AR98">
+        <v>1.43</v>
+      </c>
+      <c r="AS98">
+        <v>1.07</v>
+      </c>
+      <c r="AT98">
+        <v>2.5</v>
+      </c>
+      <c r="AU98">
+        <v>3</v>
+      </c>
+      <c r="AV98">
+        <v>6</v>
+      </c>
+      <c r="AW98">
+        <v>4</v>
+      </c>
+      <c r="AX98">
+        <v>9</v>
+      </c>
+      <c r="AY98">
+        <v>7</v>
+      </c>
+      <c r="AZ98">
+        <v>15</v>
+      </c>
+      <c r="BA98">
+        <v>1</v>
+      </c>
+      <c r="BB98">
+        <v>6</v>
+      </c>
+      <c r="BC98">
+        <v>7</v>
+      </c>
+      <c r="BD98">
+        <v>2.12</v>
+      </c>
+      <c r="BE98">
+        <v>6.75</v>
+      </c>
+      <c r="BF98">
+        <v>2.01</v>
+      </c>
+      <c r="BG98">
+        <v>1.25</v>
+      </c>
+      <c r="BH98">
+        <v>3.65</v>
+      </c>
+      <c r="BI98">
+        <v>1.34</v>
+      </c>
+      <c r="BJ98">
+        <v>2.62</v>
+      </c>
+      <c r="BK98">
+        <v>1.65</v>
+      </c>
+      <c r="BL98">
+        <v>2.1</v>
+      </c>
+      <c r="BM98">
+        <v>2.1</v>
+      </c>
+      <c r="BN98">
+        <v>1.67</v>
+      </c>
+      <c r="BO98">
+        <v>2.67</v>
+      </c>
+      <c r="BP98">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="204">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -472,6 +472,9 @@
     <t>['20']</t>
   </si>
   <si>
+    <t>['4']</t>
+  </si>
+  <si>
     <t>['45+1', '81']</t>
   </si>
   <si>
@@ -509,9 +512,6 @@
   </si>
   <si>
     <t>['15', '34', '42']</t>
-  </si>
-  <si>
-    <t>['4']</t>
   </si>
   <si>
     <t>['44']</t>
@@ -623,6 +623,9 @@
   </si>
   <si>
     <t>['11', '44']</t>
+  </si>
+  <si>
+    <t>['42', '74']</t>
   </si>
 </sst>
 </file>
@@ -984,7 +987,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP98"/>
+  <dimension ref="A1:BP100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1240,7 +1243,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q2">
         <v>4.4</v>
@@ -1730,7 +1733,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ4">
         <v>1.36</v>
@@ -1858,7 +1861,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -2145,7 +2148,7 @@
         <v>2</v>
       </c>
       <c r="AQ6">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2554,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ8">
         <v>0.78</v>
@@ -2682,7 +2685,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -2969,7 +2972,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ10">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3094,7 +3097,7 @@
         <v>88</v>
       </c>
       <c r="P11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q11">
         <v>1.94</v>
@@ -3172,7 +3175,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ11">
         <v>0.78</v>
@@ -3300,7 +3303,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q12">
         <v>3.95</v>
@@ -3381,7 +3384,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ12">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR12">
         <v>1.77</v>
@@ -3506,7 +3509,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q13">
         <v>4.5</v>
@@ -3584,7 +3587,7 @@
         <v>1</v>
       </c>
       <c r="AP13">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ13">
         <v>1.2</v>
@@ -3712,7 +3715,7 @@
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q14">
         <v>3.9</v>
@@ -3918,7 +3921,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q15">
         <v>2.06</v>
@@ -4124,7 +4127,7 @@
         <v>82</v>
       </c>
       <c r="P16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4330,7 +4333,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q17">
         <v>3.1</v>
@@ -4411,7 +4414,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ17">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR17">
         <v>1.58</v>
@@ -4536,7 +4539,7 @@
         <v>94</v>
       </c>
       <c r="P18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q18">
         <v>4.2</v>
@@ -4617,7 +4620,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ18">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR18">
         <v>2.63</v>
@@ -4820,7 +4823,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ19">
         <v>1.22</v>
@@ -4948,7 +4951,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q20">
         <v>2.65</v>
@@ -5154,7 +5157,7 @@
         <v>82</v>
       </c>
       <c r="P21" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5566,7 +5569,7 @@
         <v>82</v>
       </c>
       <c r="P23" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="Q23">
         <v>2.35</v>
@@ -6262,10 +6265,10 @@
         <v>0.33</v>
       </c>
       <c r="AP26">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ26">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR26">
         <v>1.55</v>
@@ -6880,7 +6883,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ29">
         <v>1.5</v>
@@ -7913,7 +7916,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ34">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR34">
         <v>1.64</v>
@@ -8322,10 +8325,10 @@
         <v>2.33</v>
       </c>
       <c r="AP36">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ36">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR36">
         <v>1.81</v>
@@ -8940,7 +8943,7 @@
         <v>2</v>
       </c>
       <c r="AP39">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ39">
         <v>1.3</v>
@@ -9149,7 +9152,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ40">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR40">
         <v>1.69</v>
@@ -10794,10 +10797,10 @@
         <v>2</v>
       </c>
       <c r="AP48">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ48">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR48">
         <v>1.51</v>
@@ -11206,10 +11209,10 @@
         <v>1.4</v>
       </c>
       <c r="AP50">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ50">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR50">
         <v>1.81</v>
@@ -11824,7 +11827,7 @@
         <v>1.5</v>
       </c>
       <c r="AP53">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ53">
         <v>1</v>
@@ -13269,7 +13272,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ60">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR60">
         <v>1.76</v>
@@ -13394,7 +13397,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q61">
         <v>3.05</v>
@@ -13678,7 +13681,7 @@
         <v>1.67</v>
       </c>
       <c r="AP62">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ62">
         <v>1.2</v>
@@ -14012,7 +14015,7 @@
         <v>128</v>
       </c>
       <c r="P64" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q64">
         <v>6.5</v>
@@ -14093,7 +14096,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ64">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR64">
         <v>1.6</v>
@@ -14505,7 +14508,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ66">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR66">
         <v>1.92</v>
@@ -14708,7 +14711,7 @@
         <v>0.33</v>
       </c>
       <c r="AP67">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ67">
         <v>0.22</v>
@@ -16690,7 +16693,7 @@
         <v>82</v>
       </c>
       <c r="P77" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q77">
         <v>2.05</v>
@@ -16974,7 +16977,7 @@
         <v>0.29</v>
       </c>
       <c r="AP78">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ78">
         <v>0.22</v>
@@ -17183,7 +17186,7 @@
         <v>2</v>
       </c>
       <c r="AQ79">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR79">
         <v>1.98</v>
@@ -17386,7 +17389,7 @@
         <v>1.43</v>
       </c>
       <c r="AP80">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ80">
         <v>1.22</v>
@@ -17595,7 +17598,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ81">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR81">
         <v>1.57</v>
@@ -18210,7 +18213,7 @@
         <v>1.5</v>
       </c>
       <c r="AP84">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ84">
         <v>1.5</v>
@@ -18338,7 +18341,7 @@
         <v>143</v>
       </c>
       <c r="P85" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q85">
         <v>2.2</v>
@@ -18828,7 +18831,7 @@
         <v>1.5</v>
       </c>
       <c r="AP87">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ87">
         <v>1.3</v>
@@ -19037,7 +19040,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ88">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR88">
         <v>1.76</v>
@@ -19449,7 +19452,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ90">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR90">
         <v>1.52</v>
@@ -20273,7 +20276,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ94">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR94">
         <v>2.08</v>
@@ -20476,7 +20479,7 @@
         <v>1.4</v>
       </c>
       <c r="AP95">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ95">
         <v>1.36</v>
@@ -21173,6 +21176,418 @@
       </c>
       <c r="BP98">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="99" spans="1:68">
+      <c r="A99" s="1">
+        <v>98</v>
+      </c>
+      <c r="B99">
+        <v>7775740</v>
+      </c>
+      <c r="C99" t="s">
+        <v>68</v>
+      </c>
+      <c r="D99" t="s">
+        <v>69</v>
+      </c>
+      <c r="E99" s="2">
+        <v>45824.65625</v>
+      </c>
+      <c r="F99">
+        <v>0</v>
+      </c>
+      <c r="G99" t="s">
+        <v>76</v>
+      </c>
+      <c r="H99" t="s">
+        <v>79</v>
+      </c>
+      <c r="I99">
+        <v>1</v>
+      </c>
+      <c r="J99">
+        <v>1</v>
+      </c>
+      <c r="K99">
+        <v>2</v>
+      </c>
+      <c r="L99">
+        <v>1</v>
+      </c>
+      <c r="M99">
+        <v>2</v>
+      </c>
+      <c r="N99">
+        <v>3</v>
+      </c>
+      <c r="O99" t="s">
+        <v>152</v>
+      </c>
+      <c r="P99" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q99">
+        <v>4.85</v>
+      </c>
+      <c r="R99">
+        <v>2.06</v>
+      </c>
+      <c r="S99">
+        <v>2.44</v>
+      </c>
+      <c r="T99">
+        <v>1.45</v>
+      </c>
+      <c r="U99">
+        <v>2.75</v>
+      </c>
+      <c r="V99">
+        <v>2.9</v>
+      </c>
+      <c r="W99">
+        <v>1.36</v>
+      </c>
+      <c r="X99">
+        <v>8.5</v>
+      </c>
+      <c r="Y99">
+        <v>1.07</v>
+      </c>
+      <c r="Z99">
+        <v>4.33</v>
+      </c>
+      <c r="AA99">
+        <v>3.3</v>
+      </c>
+      <c r="AB99">
+        <v>1.74</v>
+      </c>
+      <c r="AC99">
+        <v>1.06</v>
+      </c>
+      <c r="AD99">
+        <v>7.8</v>
+      </c>
+      <c r="AE99">
+        <v>1.33</v>
+      </c>
+      <c r="AF99">
+        <v>2.9</v>
+      </c>
+      <c r="AG99">
+        <v>2.05</v>
+      </c>
+      <c r="AH99">
+        <v>1.73</v>
+      </c>
+      <c r="AI99">
+        <v>2.08</v>
+      </c>
+      <c r="AJ99">
+        <v>1.83</v>
+      </c>
+      <c r="AK99">
+        <v>1.22</v>
+      </c>
+      <c r="AL99">
+        <v>1.3</v>
+      </c>
+      <c r="AM99">
+        <v>1.12</v>
+      </c>
+      <c r="AN99">
+        <v>1.78</v>
+      </c>
+      <c r="AO99">
+        <v>1.8</v>
+      </c>
+      <c r="AP99">
+        <v>1.6</v>
+      </c>
+      <c r="AQ99">
+        <v>1.91</v>
+      </c>
+      <c r="AR99">
+        <v>1.43</v>
+      </c>
+      <c r="AS99">
+        <v>1.66</v>
+      </c>
+      <c r="AT99">
+        <v>3.09</v>
+      </c>
+      <c r="AU99">
+        <v>2</v>
+      </c>
+      <c r="AV99">
+        <v>7</v>
+      </c>
+      <c r="AW99">
+        <v>10</v>
+      </c>
+      <c r="AX99">
+        <v>4</v>
+      </c>
+      <c r="AY99">
+        <v>12</v>
+      </c>
+      <c r="AZ99">
+        <v>11</v>
+      </c>
+      <c r="BA99">
+        <v>5</v>
+      </c>
+      <c r="BB99">
+        <v>5</v>
+      </c>
+      <c r="BC99">
+        <v>10</v>
+      </c>
+      <c r="BD99">
+        <v>2.8</v>
+      </c>
+      <c r="BE99">
+        <v>7</v>
+      </c>
+      <c r="BF99">
+        <v>1.67</v>
+      </c>
+      <c r="BG99">
+        <v>1.33</v>
+      </c>
+      <c r="BH99">
+        <v>3.12</v>
+      </c>
+      <c r="BI99">
+        <v>1.58</v>
+      </c>
+      <c r="BJ99">
+        <v>2.34</v>
+      </c>
+      <c r="BK99">
+        <v>2.22</v>
+      </c>
+      <c r="BL99">
+        <v>1.75</v>
+      </c>
+      <c r="BM99">
+        <v>2.4</v>
+      </c>
+      <c r="BN99">
+        <v>1.5</v>
+      </c>
+      <c r="BO99">
+        <v>3.15</v>
+      </c>
+      <c r="BP99">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:68">
+      <c r="A100" s="1">
+        <v>99</v>
+      </c>
+      <c r="B100">
+        <v>7775741</v>
+      </c>
+      <c r="C100" t="s">
+        <v>68</v>
+      </c>
+      <c r="D100" t="s">
+        <v>69</v>
+      </c>
+      <c r="E100" s="2">
+        <v>45824.65625</v>
+      </c>
+      <c r="F100">
+        <v>0</v>
+      </c>
+      <c r="G100" t="s">
+        <v>72</v>
+      </c>
+      <c r="H100" t="s">
+        <v>71</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>1</v>
+      </c>
+      <c r="K100">
+        <v>1</v>
+      </c>
+      <c r="L100">
+        <v>0</v>
+      </c>
+      <c r="M100">
+        <v>1</v>
+      </c>
+      <c r="N100">
+        <v>1</v>
+      </c>
+      <c r="O100" t="s">
+        <v>82</v>
+      </c>
+      <c r="P100" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q100">
+        <v>2.72</v>
+      </c>
+      <c r="R100">
+        <v>1.95</v>
+      </c>
+      <c r="S100">
+        <v>3.71</v>
+      </c>
+      <c r="T100">
+        <v>1.45</v>
+      </c>
+      <c r="U100">
+        <v>2.69</v>
+      </c>
+      <c r="V100">
+        <v>3</v>
+      </c>
+      <c r="W100">
+        <v>1.33</v>
+      </c>
+      <c r="X100">
+        <v>8.5</v>
+      </c>
+      <c r="Y100">
+        <v>1.06</v>
+      </c>
+      <c r="Z100">
+        <v>2.33</v>
+      </c>
+      <c r="AA100">
+        <v>3.15</v>
+      </c>
+      <c r="AB100">
+        <v>3.44</v>
+      </c>
+      <c r="AC100">
+        <v>1.04</v>
+      </c>
+      <c r="AD100">
+        <v>7.8</v>
+      </c>
+      <c r="AE100">
+        <v>1.37</v>
+      </c>
+      <c r="AF100">
+        <v>3</v>
+      </c>
+      <c r="AG100">
+        <v>2.23</v>
+      </c>
+      <c r="AH100">
+        <v>1.66</v>
+      </c>
+      <c r="AI100">
+        <v>1.93</v>
+      </c>
+      <c r="AJ100">
+        <v>1.75</v>
+      </c>
+      <c r="AK100">
+        <v>1.27</v>
+      </c>
+      <c r="AL100">
+        <v>1.34</v>
+      </c>
+      <c r="AM100">
+        <v>1.7</v>
+      </c>
+      <c r="AN100">
+        <v>2</v>
+      </c>
+      <c r="AO100">
+        <v>1.22</v>
+      </c>
+      <c r="AP100">
+        <v>1.82</v>
+      </c>
+      <c r="AQ100">
+        <v>1.4</v>
+      </c>
+      <c r="AR100">
+        <v>1.64</v>
+      </c>
+      <c r="AS100">
+        <v>1.49</v>
+      </c>
+      <c r="AT100">
+        <v>3.13</v>
+      </c>
+      <c r="AU100">
+        <v>7</v>
+      </c>
+      <c r="AV100">
+        <v>2</v>
+      </c>
+      <c r="AW100">
+        <v>7</v>
+      </c>
+      <c r="AX100">
+        <v>2</v>
+      </c>
+      <c r="AY100">
+        <v>14</v>
+      </c>
+      <c r="AZ100">
+        <v>4</v>
+      </c>
+      <c r="BA100">
+        <v>9</v>
+      </c>
+      <c r="BB100">
+        <v>0</v>
+      </c>
+      <c r="BC100">
+        <v>9</v>
+      </c>
+      <c r="BD100">
+        <v>1.67</v>
+      </c>
+      <c r="BE100">
+        <v>6.7</v>
+      </c>
+      <c r="BF100">
+        <v>2.96</v>
+      </c>
+      <c r="BG100">
+        <v>1.27</v>
+      </c>
+      <c r="BH100">
+        <v>3.22</v>
+      </c>
+      <c r="BI100">
+        <v>1.51</v>
+      </c>
+      <c r="BJ100">
+        <v>2.2</v>
+      </c>
+      <c r="BK100">
+        <v>1.9</v>
+      </c>
+      <c r="BL100">
+        <v>1.8</v>
+      </c>
+      <c r="BM100">
+        <v>2.4</v>
+      </c>
+      <c r="BN100">
+        <v>1.43</v>
+      </c>
+      <c r="BO100">
+        <v>3.28</v>
+      </c>
+      <c r="BP100">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="209">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -475,6 +475,18 @@
     <t>['4']</t>
   </si>
   <si>
+    <t>['3']</t>
+  </si>
+  <si>
+    <t>['2', '11', '35']</t>
+  </si>
+  <si>
+    <t>['45', '45+3']</t>
+  </si>
+  <si>
+    <t>['6', '29', '26', '49']</t>
+  </si>
+  <si>
     <t>['45+1', '81']</t>
   </si>
   <si>
@@ -586,9 +598,6 @@
     <t>['59', '90+7']</t>
   </si>
   <si>
-    <t>['3']</t>
-  </si>
-  <si>
     <t>['29']</t>
   </si>
   <si>
@@ -626,6 +635,12 @@
   </si>
   <si>
     <t>['42', '74']</t>
+  </si>
+  <si>
+    <t>['55']</t>
+  </si>
+  <si>
+    <t>['69']</t>
   </si>
 </sst>
 </file>
@@ -987,7 +1002,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP100"/>
+  <dimension ref="A1:BP105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1243,7 +1258,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="Q2">
         <v>4.4</v>
@@ -1527,10 +1542,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ3">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1861,7 +1876,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -2354,7 +2369,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ7">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2557,10 +2572,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ8">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2685,7 +2700,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -2763,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ9">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2969,7 +2984,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ10">
         <v>1.4</v>
@@ -3097,7 +3112,7 @@
         <v>88</v>
       </c>
       <c r="P11" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="Q11">
         <v>1.94</v>
@@ -3178,7 +3193,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ11">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR11">
         <v>2.05</v>
@@ -3303,7 +3318,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="Q12">
         <v>3.95</v>
@@ -3381,7 +3396,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ12">
         <v>1.91</v>
@@ -3509,7 +3524,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="Q13">
         <v>4.5</v>
@@ -3587,7 +3602,7 @@
         <v>1</v>
       </c>
       <c r="AP13">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ13">
         <v>1.2</v>
@@ -3715,7 +3730,7 @@
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="Q14">
         <v>3.9</v>
@@ -3796,7 +3811,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ14">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR14">
         <v>1.46</v>
@@ -3921,7 +3936,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="Q15">
         <v>2.06</v>
@@ -4127,7 +4142,7 @@
         <v>82</v>
       </c>
       <c r="P16" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4333,7 +4348,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="Q17">
         <v>3.1</v>
@@ -4411,7 +4426,7 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ17">
         <v>1.4</v>
@@ -4539,7 +4554,7 @@
         <v>94</v>
       </c>
       <c r="P18" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="Q18">
         <v>4.2</v>
@@ -4826,7 +4841,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ19">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR19">
         <v>2.01</v>
@@ -4951,7 +4966,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Q20">
         <v>2.65</v>
@@ -5029,10 +5044,10 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ20">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AR20">
         <v>0.9</v>
@@ -5157,7 +5172,7 @@
         <v>82</v>
       </c>
       <c r="P21" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5235,10 +5250,10 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ21">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR21">
         <v>1.81</v>
@@ -5441,10 +5456,10 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ22">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -5647,7 +5662,7 @@
         <v>2</v>
       </c>
       <c r="AP23">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ23">
         <v>1.36</v>
@@ -5856,7 +5871,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ24">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR24">
         <v>1.36</v>
@@ -5981,7 +5996,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="Q25">
         <v>2.7</v>
@@ -6187,7 +6202,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="Q26">
         <v>4.75</v>
@@ -6265,7 +6280,7 @@
         <v>0.33</v>
       </c>
       <c r="AP26">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ26">
         <v>1.91</v>
@@ -6471,7 +6486,7 @@
         <v>3</v>
       </c>
       <c r="AP27">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ27">
         <v>1.3</v>
@@ -6599,7 +6614,7 @@
         <v>101</v>
       </c>
       <c r="P28" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -6677,10 +6692,10 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ28">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AR28">
         <v>1.81</v>
@@ -6886,7 +6901,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ29">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR29">
         <v>1.92</v>
@@ -7092,7 +7107,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ30">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR30">
         <v>1.87</v>
@@ -7217,7 +7232,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="Q31">
         <v>4.75</v>
@@ -7295,10 +7310,10 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ31">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR31">
         <v>1.77</v>
@@ -7423,7 +7438,7 @@
         <v>82</v>
       </c>
       <c r="P32" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="Q32">
         <v>3</v>
@@ -7835,7 +7850,7 @@
         <v>104</v>
       </c>
       <c r="P34" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="Q34">
         <v>4.33</v>
@@ -8119,10 +8134,10 @@
         <v>1</v>
       </c>
       <c r="AP35">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ35">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR35">
         <v>1.34</v>
@@ -8453,7 +8468,7 @@
         <v>105</v>
       </c>
       <c r="P37" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="Q37">
         <v>2.38</v>
@@ -8534,7 +8549,7 @@
         <v>2</v>
       </c>
       <c r="AQ37">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR37">
         <v>1.78</v>
@@ -8740,7 +8755,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ38">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AR38">
         <v>1.99</v>
@@ -8943,7 +8958,7 @@
         <v>2</v>
       </c>
       <c r="AP39">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ39">
         <v>1.3</v>
@@ -9149,7 +9164,7 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ40">
         <v>1.91</v>
@@ -9277,7 +9292,7 @@
         <v>82</v>
       </c>
       <c r="P41" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="Q41">
         <v>5.2</v>
@@ -9358,7 +9373,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ41">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR41">
         <v>1.63</v>
@@ -9561,10 +9576,10 @@
         <v>0.75</v>
       </c>
       <c r="AP42">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ42">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR42">
         <v>1.9</v>
@@ -9689,7 +9704,7 @@
         <v>109</v>
       </c>
       <c r="P43" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="Q43">
         <v>2.38</v>
@@ -9973,7 +9988,7 @@
         <v>1.5</v>
       </c>
       <c r="AP44">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ44">
         <v>1.3</v>
@@ -10101,7 +10116,7 @@
         <v>111</v>
       </c>
       <c r="P45" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Q45">
         <v>4.04</v>
@@ -10307,7 +10322,7 @@
         <v>112</v>
       </c>
       <c r="P46" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="Q46">
         <v>1.7</v>
@@ -10385,10 +10400,10 @@
         <v>0.33</v>
       </c>
       <c r="AP46">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ46">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AR46">
         <v>1.69</v>
@@ -10594,7 +10609,7 @@
         <v>2</v>
       </c>
       <c r="AQ47">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AR47">
         <v>1.97</v>
@@ -10719,7 +10734,7 @@
         <v>114</v>
       </c>
       <c r="P48" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="Q48">
         <v>3.88</v>
@@ -10797,7 +10812,7 @@
         <v>2</v>
       </c>
       <c r="AP48">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ48">
         <v>1.4</v>
@@ -10925,7 +10940,7 @@
         <v>115</v>
       </c>
       <c r="P49" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="Q49">
         <v>3.55</v>
@@ -11003,10 +11018,10 @@
         <v>1</v>
       </c>
       <c r="AP49">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ49">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR49">
         <v>1.6</v>
@@ -11131,7 +11146,7 @@
         <v>116</v>
       </c>
       <c r="P50" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="Q50">
         <v>3.7</v>
@@ -11337,7 +11352,7 @@
         <v>82</v>
       </c>
       <c r="P51" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Q51">
         <v>2.6</v>
@@ -11415,10 +11430,10 @@
         <v>0.25</v>
       </c>
       <c r="AP51">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ51">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR51">
         <v>1.67</v>
@@ -11543,7 +11558,7 @@
         <v>117</v>
       </c>
       <c r="P52" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="Q52">
         <v>2.24</v>
@@ -11621,10 +11636,10 @@
         <v>0.6</v>
       </c>
       <c r="AP52">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ52">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR52">
         <v>1.89</v>
@@ -11827,10 +11842,10 @@
         <v>1.5</v>
       </c>
       <c r="AP53">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ53">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR53">
         <v>1.38</v>
@@ -12161,7 +12176,7 @@
         <v>119</v>
       </c>
       <c r="P55" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="Q55">
         <v>2.6</v>
@@ -12239,7 +12254,7 @@
         <v>1.8</v>
       </c>
       <c r="AP55">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ55">
         <v>1.2</v>
@@ -12448,7 +12463,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ56">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR56">
         <v>1.88</v>
@@ -12573,7 +12588,7 @@
         <v>121</v>
       </c>
       <c r="P57" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -12654,7 +12669,7 @@
         <v>2</v>
       </c>
       <c r="AQ57">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR57">
         <v>1.95</v>
@@ -12857,7 +12872,7 @@
         <v>2.2</v>
       </c>
       <c r="AP58">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ58">
         <v>1.36</v>
@@ -12985,7 +13000,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q59">
         <v>4.75</v>
@@ -13063,10 +13078,10 @@
         <v>1.4</v>
       </c>
       <c r="AP59">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ59">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR59">
         <v>1.59</v>
@@ -13191,7 +13206,7 @@
         <v>124</v>
       </c>
       <c r="P60" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Q60">
         <v>2.61</v>
@@ -13269,7 +13284,7 @@
         <v>1.8</v>
       </c>
       <c r="AP60">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ60">
         <v>1.4</v>
@@ -13397,7 +13412,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="Q61">
         <v>3.05</v>
@@ -13478,7 +13493,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ61">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AR61">
         <v>1.58</v>
@@ -13809,7 +13824,7 @@
         <v>127</v>
       </c>
       <c r="P63" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="Q63">
         <v>3.28</v>
@@ -14015,7 +14030,7 @@
         <v>128</v>
       </c>
       <c r="P64" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="Q64">
         <v>6.5</v>
@@ -14221,7 +14236,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q65">
         <v>2.04</v>
@@ -14633,7 +14648,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="Q67">
         <v>2.45</v>
@@ -14711,10 +14726,10 @@
         <v>0.33</v>
       </c>
       <c r="AP67">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ67">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AR67">
         <v>1.44</v>
@@ -14839,7 +14854,7 @@
         <v>132</v>
       </c>
       <c r="P68" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="Q68">
         <v>3.2</v>
@@ -14917,10 +14932,10 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ68">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR68">
         <v>1.65</v>
@@ -15045,7 +15060,7 @@
         <v>82</v>
       </c>
       <c r="P69" t="s">
-        <v>190</v>
+        <v>153</v>
       </c>
       <c r="Q69">
         <v>2.04</v>
@@ -15123,7 +15138,7 @@
         <v>1.29</v>
       </c>
       <c r="AP69">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ69">
         <v>1.3</v>
@@ -15329,10 +15344,10 @@
         <v>0.67</v>
       </c>
       <c r="AP70">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ70">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR70">
         <v>1.78</v>
@@ -15538,7 +15553,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ71">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR71">
         <v>1.84</v>
@@ -15663,7 +15678,7 @@
         <v>135</v>
       </c>
       <c r="P72" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q72">
         <v>3.26</v>
@@ -15741,10 +15756,10 @@
         <v>1</v>
       </c>
       <c r="AP72">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ72">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR72">
         <v>2.13</v>
@@ -15869,7 +15884,7 @@
         <v>97</v>
       </c>
       <c r="P73" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q73">
         <v>4.6</v>
@@ -15950,7 +15965,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ73">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR73">
         <v>1.54</v>
@@ -16153,7 +16168,7 @@
         <v>1.43</v>
       </c>
       <c r="AP74">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ74">
         <v>1.2</v>
@@ -16359,7 +16374,7 @@
         <v>1.71</v>
       </c>
       <c r="AP75">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ75">
         <v>1.36</v>
@@ -16487,7 +16502,7 @@
         <v>82</v>
       </c>
       <c r="P76" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q76">
         <v>3.65</v>
@@ -16568,7 +16583,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ76">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR76">
         <v>1.54</v>
@@ -16693,7 +16708,7 @@
         <v>82</v>
       </c>
       <c r="P77" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="Q77">
         <v>2.05</v>
@@ -16771,10 +16786,10 @@
         <v>0.57</v>
       </c>
       <c r="AP77">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ77">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR77">
         <v>1.74</v>
@@ -16899,7 +16914,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q78">
         <v>1.89</v>
@@ -16980,7 +16995,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ78">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AR78">
         <v>1.69</v>
@@ -17389,10 +17404,10 @@
         <v>1.43</v>
       </c>
       <c r="AP80">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ80">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR80">
         <v>1.49</v>
@@ -17517,7 +17532,7 @@
         <v>85</v>
       </c>
       <c r="P81" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q81">
         <v>5.25</v>
@@ -17595,7 +17610,7 @@
         <v>1.29</v>
       </c>
       <c r="AP81">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ81">
         <v>1.91</v>
@@ -17801,7 +17816,7 @@
         <v>1.5</v>
       </c>
       <c r="AP82">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ82">
         <v>1.36</v>
@@ -18007,10 +18022,10 @@
         <v>0.88</v>
       </c>
       <c r="AP83">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ83">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR83">
         <v>1.87</v>
@@ -18213,10 +18228,10 @@
         <v>1.5</v>
       </c>
       <c r="AP84">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ84">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR84">
         <v>1.45</v>
@@ -18341,7 +18356,7 @@
         <v>143</v>
       </c>
       <c r="P85" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="Q85">
         <v>2.2</v>
@@ -18419,10 +18434,10 @@
         <v>0.25</v>
       </c>
       <c r="AP85">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ85">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AR85">
         <v>1.76</v>
@@ -18547,7 +18562,7 @@
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q86">
         <v>2.11</v>
@@ -18625,10 +18640,10 @@
         <v>0.88</v>
       </c>
       <c r="AP86">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ86">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR86">
         <v>2.01</v>
@@ -18753,7 +18768,7 @@
         <v>145</v>
       </c>
       <c r="P87" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q87">
         <v>2.04</v>
@@ -18959,7 +18974,7 @@
         <v>146</v>
       </c>
       <c r="P88" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19246,7 +19261,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ89">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR89">
         <v>1.48</v>
@@ -19371,7 +19386,7 @@
         <v>147</v>
       </c>
       <c r="P90" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q90">
         <v>3.81</v>
@@ -19577,7 +19592,7 @@
         <v>148</v>
       </c>
       <c r="P91" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q91">
         <v>3.3</v>
@@ -19655,7 +19670,7 @@
         <v>1.44</v>
       </c>
       <c r="AP91">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ91">
         <v>1.36</v>
@@ -19864,7 +19879,7 @@
         <v>2</v>
       </c>
       <c r="AQ92">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR92">
         <v>1.96</v>
@@ -20067,7 +20082,7 @@
         <v>1.25</v>
       </c>
       <c r="AP93">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ93">
         <v>1.2</v>
@@ -20195,7 +20210,7 @@
         <v>149</v>
       </c>
       <c r="P94" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q94">
         <v>3.8</v>
@@ -20273,7 +20288,7 @@
         <v>1.67</v>
       </c>
       <c r="AP94">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ94">
         <v>1.91</v>
@@ -20607,7 +20622,7 @@
         <v>82</v>
       </c>
       <c r="P96" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q96">
         <v>4.1</v>
@@ -20688,7 +20703,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ96">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR96">
         <v>1.55</v>
@@ -21225,7 +21240,7 @@
         <v>152</v>
       </c>
       <c r="P99" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q99">
         <v>4.85</v>
@@ -21303,7 +21318,7 @@
         <v>1.8</v>
       </c>
       <c r="AP99">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ99">
         <v>1.91</v>
@@ -21588,6 +21603,1036 @@
       </c>
       <c r="BP100">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="101" spans="1:68">
+      <c r="A101" s="1">
+        <v>100</v>
+      </c>
+      <c r="B101">
+        <v>7775715</v>
+      </c>
+      <c r="C101" t="s">
+        <v>68</v>
+      </c>
+      <c r="D101" t="s">
+        <v>69</v>
+      </c>
+      <c r="E101" s="2">
+        <v>45828.65625</v>
+      </c>
+      <c r="F101">
+        <v>0</v>
+      </c>
+      <c r="G101" t="s">
+        <v>76</v>
+      </c>
+      <c r="H101" t="s">
+        <v>73</v>
+      </c>
+      <c r="I101">
+        <v>1</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>1</v>
+      </c>
+      <c r="L101">
+        <v>1</v>
+      </c>
+      <c r="M101">
+        <v>0</v>
+      </c>
+      <c r="N101">
+        <v>1</v>
+      </c>
+      <c r="O101" t="s">
+        <v>153</v>
+      </c>
+      <c r="P101" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q101">
+        <v>2.38</v>
+      </c>
+      <c r="R101">
+        <v>2.17</v>
+      </c>
+      <c r="S101">
+        <v>4.9</v>
+      </c>
+      <c r="T101">
+        <v>1.38</v>
+      </c>
+      <c r="U101">
+        <v>2.9</v>
+      </c>
+      <c r="V101">
+        <v>2.75</v>
+      </c>
+      <c r="W101">
+        <v>1.4</v>
+      </c>
+      <c r="X101">
+        <v>6.5</v>
+      </c>
+      <c r="Y101">
+        <v>1.08</v>
+      </c>
+      <c r="Z101">
+        <v>1.73</v>
+      </c>
+      <c r="AA101">
+        <v>3.76</v>
+      </c>
+      <c r="AB101">
+        <v>4.6</v>
+      </c>
+      <c r="AC101">
+        <v>1.01</v>
+      </c>
+      <c r="AD101">
+        <v>9</v>
+      </c>
+      <c r="AE101">
+        <v>1.29</v>
+      </c>
+      <c r="AF101">
+        <v>3.3</v>
+      </c>
+      <c r="AG101">
+        <v>1.83</v>
+      </c>
+      <c r="AH101">
+        <v>1.85</v>
+      </c>
+      <c r="AI101">
+        <v>1.82</v>
+      </c>
+      <c r="AJ101">
+        <v>1.99</v>
+      </c>
+      <c r="AK101">
+        <v>1.27</v>
+      </c>
+      <c r="AL101">
+        <v>1.27</v>
+      </c>
+      <c r="AM101">
+        <v>2.15</v>
+      </c>
+      <c r="AN101">
+        <v>1.6</v>
+      </c>
+      <c r="AO101">
+        <v>0.78</v>
+      </c>
+      <c r="AP101">
+        <v>1.73</v>
+      </c>
+      <c r="AQ101">
+        <v>0.7</v>
+      </c>
+      <c r="AR101">
+        <v>1.4</v>
+      </c>
+      <c r="AS101">
+        <v>1.3</v>
+      </c>
+      <c r="AT101">
+        <v>2.7</v>
+      </c>
+      <c r="AU101">
+        <v>4</v>
+      </c>
+      <c r="AV101">
+        <v>5</v>
+      </c>
+      <c r="AW101">
+        <v>6</v>
+      </c>
+      <c r="AX101">
+        <v>5</v>
+      </c>
+      <c r="AY101">
+        <v>10</v>
+      </c>
+      <c r="AZ101">
+        <v>10</v>
+      </c>
+      <c r="BA101">
+        <v>9</v>
+      </c>
+      <c r="BB101">
+        <v>6</v>
+      </c>
+      <c r="BC101">
+        <v>15</v>
+      </c>
+      <c r="BD101">
+        <v>1.58</v>
+      </c>
+      <c r="BE101">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF101">
+        <v>3.22</v>
+      </c>
+      <c r="BG101">
+        <v>1.25</v>
+      </c>
+      <c r="BH101">
+        <v>3.4</v>
+      </c>
+      <c r="BI101">
+        <v>1.44</v>
+      </c>
+      <c r="BJ101">
+        <v>2.62</v>
+      </c>
+      <c r="BK101">
+        <v>1.73</v>
+      </c>
+      <c r="BL101">
+        <v>2.04</v>
+      </c>
+      <c r="BM101">
+        <v>2.15</v>
+      </c>
+      <c r="BN101">
+        <v>1.58</v>
+      </c>
+      <c r="BO101">
+        <v>2.8</v>
+      </c>
+      <c r="BP101">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="102" spans="1:68">
+      <c r="A102" s="1">
+        <v>101</v>
+      </c>
+      <c r="B102">
+        <v>7775716</v>
+      </c>
+      <c r="C102" t="s">
+        <v>68</v>
+      </c>
+      <c r="D102" t="s">
+        <v>69</v>
+      </c>
+      <c r="E102" s="2">
+        <v>45828.65625</v>
+      </c>
+      <c r="F102">
+        <v>0</v>
+      </c>
+      <c r="G102" t="s">
+        <v>77</v>
+      </c>
+      <c r="H102" t="s">
+        <v>72</v>
+      </c>
+      <c r="I102">
+        <v>3</v>
+      </c>
+      <c r="J102">
+        <v>1</v>
+      </c>
+      <c r="K102">
+        <v>4</v>
+      </c>
+      <c r="L102">
+        <v>3</v>
+      </c>
+      <c r="M102">
+        <v>1</v>
+      </c>
+      <c r="N102">
+        <v>4</v>
+      </c>
+      <c r="O102" t="s">
+        <v>154</v>
+      </c>
+      <c r="P102" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q102">
+        <v>3.25</v>
+      </c>
+      <c r="R102">
+        <v>1.96</v>
+      </c>
+      <c r="S102">
+        <v>2.7</v>
+      </c>
+      <c r="T102">
+        <v>1.46</v>
+      </c>
+      <c r="U102">
+        <v>2.51</v>
+      </c>
+      <c r="V102">
+        <v>3</v>
+      </c>
+      <c r="W102">
+        <v>1.3</v>
+      </c>
+      <c r="X102">
+        <v>7</v>
+      </c>
+      <c r="Y102">
+        <v>1.06</v>
+      </c>
+      <c r="Z102">
+        <v>2.92</v>
+      </c>
+      <c r="AA102">
+        <v>3.14</v>
+      </c>
+      <c r="AB102">
+        <v>2.42</v>
+      </c>
+      <c r="AC102">
+        <v>1.04</v>
+      </c>
+      <c r="AD102">
+        <v>7.5</v>
+      </c>
+      <c r="AE102">
+        <v>1.33</v>
+      </c>
+      <c r="AF102">
+        <v>3</v>
+      </c>
+      <c r="AG102">
+        <v>2.1</v>
+      </c>
+      <c r="AH102">
+        <v>1.67</v>
+      </c>
+      <c r="AI102">
+        <v>1.8</v>
+      </c>
+      <c r="AJ102">
+        <v>1.99</v>
+      </c>
+      <c r="AK102">
+        <v>1.33</v>
+      </c>
+      <c r="AL102">
+        <v>1.35</v>
+      </c>
+      <c r="AM102">
+        <v>1.41</v>
+      </c>
+      <c r="AN102">
+        <v>1.44</v>
+      </c>
+      <c r="AO102">
+        <v>1</v>
+      </c>
+      <c r="AP102">
+        <v>1.6</v>
+      </c>
+      <c r="AQ102">
+        <v>0.91</v>
+      </c>
+      <c r="AR102">
+        <v>1.73</v>
+      </c>
+      <c r="AS102">
+        <v>1.58</v>
+      </c>
+      <c r="AT102">
+        <v>3.31</v>
+      </c>
+      <c r="AU102">
+        <v>7</v>
+      </c>
+      <c r="AV102">
+        <v>12</v>
+      </c>
+      <c r="AW102">
+        <v>4</v>
+      </c>
+      <c r="AX102">
+        <v>7</v>
+      </c>
+      <c r="AY102">
+        <v>11</v>
+      </c>
+      <c r="AZ102">
+        <v>19</v>
+      </c>
+      <c r="BA102">
+        <v>8</v>
+      </c>
+      <c r="BB102">
+        <v>9</v>
+      </c>
+      <c r="BC102">
+        <v>17</v>
+      </c>
+      <c r="BD102">
+        <v>2.02</v>
+      </c>
+      <c r="BE102">
+        <v>6.5</v>
+      </c>
+      <c r="BF102">
+        <v>1.95</v>
+      </c>
+      <c r="BG102">
+        <v>1.25</v>
+      </c>
+      <c r="BH102">
+        <v>3.42</v>
+      </c>
+      <c r="BI102">
+        <v>1.5</v>
+      </c>
+      <c r="BJ102">
+        <v>2.4</v>
+      </c>
+      <c r="BK102">
+        <v>1.99</v>
+      </c>
+      <c r="BL102">
+        <v>1.93</v>
+      </c>
+      <c r="BM102">
+        <v>2.18</v>
+      </c>
+      <c r="BN102">
+        <v>1.61</v>
+      </c>
+      <c r="BO102">
+        <v>2.8</v>
+      </c>
+      <c r="BP102">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="103" spans="1:68">
+      <c r="A103" s="1">
+        <v>102</v>
+      </c>
+      <c r="B103">
+        <v>7775717</v>
+      </c>
+      <c r="C103" t="s">
+        <v>68</v>
+      </c>
+      <c r="D103" t="s">
+        <v>69</v>
+      </c>
+      <c r="E103" s="2">
+        <v>45828.65625</v>
+      </c>
+      <c r="F103">
+        <v>0</v>
+      </c>
+      <c r="G103" t="s">
+        <v>71</v>
+      </c>
+      <c r="H103" t="s">
+        <v>75</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="J103">
+        <v>0</v>
+      </c>
+      <c r="K103">
+        <v>0</v>
+      </c>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="M103">
+        <v>1</v>
+      </c>
+      <c r="N103">
+        <v>1</v>
+      </c>
+      <c r="O103" t="s">
+        <v>82</v>
+      </c>
+      <c r="P103" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q103">
+        <v>3.3</v>
+      </c>
+      <c r="R103">
+        <v>1.9</v>
+      </c>
+      <c r="S103">
+        <v>3.65</v>
+      </c>
+      <c r="T103">
+        <v>1.61</v>
+      </c>
+      <c r="U103">
+        <v>2.25</v>
+      </c>
+      <c r="V103">
+        <v>3.8</v>
+      </c>
+      <c r="W103">
+        <v>1.22</v>
+      </c>
+      <c r="X103">
+        <v>13</v>
+      </c>
+      <c r="Y103">
+        <v>1.03</v>
+      </c>
+      <c r="Z103">
+        <v>2.64</v>
+      </c>
+      <c r="AA103">
+        <v>2.97</v>
+      </c>
+      <c r="AB103">
+        <v>2.9</v>
+      </c>
+      <c r="AC103">
+        <v>1.13</v>
+      </c>
+      <c r="AD103">
+        <v>5.5</v>
+      </c>
+      <c r="AE103">
+        <v>1.56</v>
+      </c>
+      <c r="AF103">
+        <v>2.25</v>
+      </c>
+      <c r="AG103">
+        <v>2.82</v>
+      </c>
+      <c r="AH103">
+        <v>1.4</v>
+      </c>
+      <c r="AI103">
+        <v>2.1</v>
+      </c>
+      <c r="AJ103">
+        <v>1.68</v>
+      </c>
+      <c r="AK103">
+        <v>1.4</v>
+      </c>
+      <c r="AL103">
+        <v>1.36</v>
+      </c>
+      <c r="AM103">
+        <v>1.45</v>
+      </c>
+      <c r="AN103">
+        <v>1.45</v>
+      </c>
+      <c r="AO103">
+        <v>1.22</v>
+      </c>
+      <c r="AP103">
+        <v>1.33</v>
+      </c>
+      <c r="AQ103">
+        <v>1.4</v>
+      </c>
+      <c r="AR103">
+        <v>1.98</v>
+      </c>
+      <c r="AS103">
+        <v>1.25</v>
+      </c>
+      <c r="AT103">
+        <v>3.23</v>
+      </c>
+      <c r="AU103">
+        <v>3</v>
+      </c>
+      <c r="AV103">
+        <v>3</v>
+      </c>
+      <c r="AW103">
+        <v>4</v>
+      </c>
+      <c r="AX103">
+        <v>4</v>
+      </c>
+      <c r="AY103">
+        <v>7</v>
+      </c>
+      <c r="AZ103">
+        <v>7</v>
+      </c>
+      <c r="BA103">
+        <v>3</v>
+      </c>
+      <c r="BB103">
+        <v>2</v>
+      </c>
+      <c r="BC103">
+        <v>5</v>
+      </c>
+      <c r="BD103">
+        <v>2.19</v>
+      </c>
+      <c r="BE103">
+        <v>6.15</v>
+      </c>
+      <c r="BF103">
+        <v>2.11</v>
+      </c>
+      <c r="BG103">
+        <v>1.51</v>
+      </c>
+      <c r="BH103">
+        <v>2.4</v>
+      </c>
+      <c r="BI103">
+        <v>1.87</v>
+      </c>
+      <c r="BJ103">
+        <v>1.87</v>
+      </c>
+      <c r="BK103">
+        <v>2.82</v>
+      </c>
+      <c r="BL103">
+        <v>1.42</v>
+      </c>
+      <c r="BM103">
+        <v>3.15</v>
+      </c>
+      <c r="BN103">
+        <v>1.31</v>
+      </c>
+      <c r="BO103">
+        <v>4.25</v>
+      </c>
+      <c r="BP103">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="104" spans="1:68">
+      <c r="A104" s="1">
+        <v>103</v>
+      </c>
+      <c r="B104">
+        <v>7775718</v>
+      </c>
+      <c r="C104" t="s">
+        <v>68</v>
+      </c>
+      <c r="D104" t="s">
+        <v>69</v>
+      </c>
+      <c r="E104" s="2">
+        <v>45828.65625</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104" t="s">
+        <v>78</v>
+      </c>
+      <c r="H104" t="s">
+        <v>74</v>
+      </c>
+      <c r="I104">
+        <v>2</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104">
+        <v>2</v>
+      </c>
+      <c r="L104">
+        <v>2</v>
+      </c>
+      <c r="M104">
+        <v>1</v>
+      </c>
+      <c r="N104">
+        <v>3</v>
+      </c>
+      <c r="O104" t="s">
+        <v>155</v>
+      </c>
+      <c r="P104" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q104">
+        <v>3.75</v>
+      </c>
+      <c r="R104">
+        <v>2.1</v>
+      </c>
+      <c r="S104">
+        <v>2.72</v>
+      </c>
+      <c r="T104">
+        <v>1.33</v>
+      </c>
+      <c r="U104">
+        <v>3</v>
+      </c>
+      <c r="V104">
+        <v>2.78</v>
+      </c>
+      <c r="W104">
+        <v>1.42</v>
+      </c>
+      <c r="X104">
+        <v>6</v>
+      </c>
+      <c r="Y104">
+        <v>1.08</v>
+      </c>
+      <c r="Z104">
+        <v>3.34</v>
+      </c>
+      <c r="AA104">
+        <v>3.25</v>
+      </c>
+      <c r="AB104">
+        <v>2</v>
+      </c>
+      <c r="AC104">
+        <v>1.04</v>
+      </c>
+      <c r="AD104">
+        <v>10.5</v>
+      </c>
+      <c r="AE104">
+        <v>1.28</v>
+      </c>
+      <c r="AF104">
+        <v>3.7</v>
+      </c>
+      <c r="AG104">
+        <v>1.8</v>
+      </c>
+      <c r="AH104">
+        <v>1.9</v>
+      </c>
+      <c r="AI104">
+        <v>1.62</v>
+      </c>
+      <c r="AJ104">
+        <v>2.1</v>
+      </c>
+      <c r="AK104">
+        <v>1.7</v>
+      </c>
+      <c r="AL104">
+        <v>1.26</v>
+      </c>
+      <c r="AM104">
+        <v>1.25</v>
+      </c>
+      <c r="AN104">
+        <v>1.11</v>
+      </c>
+      <c r="AO104">
+        <v>1.5</v>
+      </c>
+      <c r="AP104">
+        <v>1.3</v>
+      </c>
+      <c r="AQ104">
+        <v>1.36</v>
+      </c>
+      <c r="AR104">
+        <v>1.6</v>
+      </c>
+      <c r="AS104">
+        <v>1.61</v>
+      </c>
+      <c r="AT104">
+        <v>3.21</v>
+      </c>
+      <c r="AU104">
+        <v>8</v>
+      </c>
+      <c r="AV104">
+        <v>6</v>
+      </c>
+      <c r="AW104">
+        <v>7</v>
+      </c>
+      <c r="AX104">
+        <v>7</v>
+      </c>
+      <c r="AY104">
+        <v>15</v>
+      </c>
+      <c r="AZ104">
+        <v>13</v>
+      </c>
+      <c r="BA104">
+        <v>9</v>
+      </c>
+      <c r="BB104">
+        <v>7</v>
+      </c>
+      <c r="BC104">
+        <v>16</v>
+      </c>
+      <c r="BD104">
+        <v>3.5</v>
+      </c>
+      <c r="BE104">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="BF104">
+        <v>1.49</v>
+      </c>
+      <c r="BG104">
+        <v>1.21</v>
+      </c>
+      <c r="BH104">
+        <v>3.78</v>
+      </c>
+      <c r="BI104">
+        <v>1.4</v>
+      </c>
+      <c r="BJ104">
+        <v>2.72</v>
+      </c>
+      <c r="BK104">
+        <v>1.65</v>
+      </c>
+      <c r="BL104">
+        <v>2.12</v>
+      </c>
+      <c r="BM104">
+        <v>2</v>
+      </c>
+      <c r="BN104">
+        <v>1.75</v>
+      </c>
+      <c r="BO104">
+        <v>2.6</v>
+      </c>
+      <c r="BP104">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="105" spans="1:68">
+      <c r="A105" s="1">
+        <v>104</v>
+      </c>
+      <c r="B105">
+        <v>7775719</v>
+      </c>
+      <c r="C105" t="s">
+        <v>68</v>
+      </c>
+      <c r="D105" t="s">
+        <v>69</v>
+      </c>
+      <c r="E105" s="2">
+        <v>45828.65625</v>
+      </c>
+      <c r="F105">
+        <v>0</v>
+      </c>
+      <c r="G105" t="s">
+        <v>79</v>
+      </c>
+      <c r="H105" t="s">
+        <v>70</v>
+      </c>
+      <c r="I105">
+        <v>3</v>
+      </c>
+      <c r="J105">
+        <v>0</v>
+      </c>
+      <c r="K105">
+        <v>3</v>
+      </c>
+      <c r="L105">
+        <v>4</v>
+      </c>
+      <c r="M105">
+        <v>1</v>
+      </c>
+      <c r="N105">
+        <v>5</v>
+      </c>
+      <c r="O105" t="s">
+        <v>156</v>
+      </c>
+      <c r="P105" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q105">
+        <v>1.64</v>
+      </c>
+      <c r="R105">
+        <v>2.5</v>
+      </c>
+      <c r="S105">
+        <v>7.7</v>
+      </c>
+      <c r="T105">
+        <v>1.3</v>
+      </c>
+      <c r="U105">
+        <v>3.2</v>
+      </c>
+      <c r="V105">
+        <v>2.4</v>
+      </c>
+      <c r="W105">
+        <v>1.47</v>
+      </c>
+      <c r="X105">
+        <v>5.8</v>
+      </c>
+      <c r="Y105">
+        <v>1.11</v>
+      </c>
+      <c r="Z105">
+        <v>1.25</v>
+      </c>
+      <c r="AA105">
+        <v>6.05</v>
+      </c>
+      <c r="AB105">
+        <v>13</v>
+      </c>
+      <c r="AC105">
+        <v>1.02</v>
+      </c>
+      <c r="AD105">
+        <v>12</v>
+      </c>
+      <c r="AE105">
+        <v>1.22</v>
+      </c>
+      <c r="AF105">
+        <v>4.3</v>
+      </c>
+      <c r="AG105">
+        <v>1.67</v>
+      </c>
+      <c r="AH105">
+        <v>2.05</v>
+      </c>
+      <c r="AI105">
+        <v>2.26</v>
+      </c>
+      <c r="AJ105">
+        <v>1.62</v>
+      </c>
+      <c r="AK105">
+        <v>1.16</v>
+      </c>
+      <c r="AL105">
+        <v>1.15</v>
+      </c>
+      <c r="AM105">
+        <v>3.77</v>
+      </c>
+      <c r="AN105">
+        <v>2.1</v>
+      </c>
+      <c r="AO105">
+        <v>0.22</v>
+      </c>
+      <c r="AP105">
+        <v>2.18</v>
+      </c>
+      <c r="AQ105">
+        <v>0.2</v>
+      </c>
+      <c r="AR105">
+        <v>1.96</v>
+      </c>
+      <c r="AS105">
+        <v>1.1</v>
+      </c>
+      <c r="AT105">
+        <v>3.06</v>
+      </c>
+      <c r="AU105">
+        <v>9</v>
+      </c>
+      <c r="AV105">
+        <v>4</v>
+      </c>
+      <c r="AW105">
+        <v>5</v>
+      </c>
+      <c r="AX105">
+        <v>7</v>
+      </c>
+      <c r="AY105">
+        <v>14</v>
+      </c>
+      <c r="AZ105">
+        <v>11</v>
+      </c>
+      <c r="BA105">
+        <v>7</v>
+      </c>
+      <c r="BB105">
+        <v>1</v>
+      </c>
+      <c r="BC105">
+        <v>8</v>
+      </c>
+      <c r="BD105">
+        <v>1.18</v>
+      </c>
+      <c r="BE105">
+        <v>11</v>
+      </c>
+      <c r="BF105">
+        <v>6.06</v>
+      </c>
+      <c r="BG105">
+        <v>1.22</v>
+      </c>
+      <c r="BH105">
+        <v>3.95</v>
+      </c>
+      <c r="BI105">
+        <v>1.38</v>
+      </c>
+      <c r="BJ105">
+        <v>2.82</v>
+      </c>
+      <c r="BK105">
+        <v>1.6</v>
+      </c>
+      <c r="BL105">
+        <v>2.19</v>
+      </c>
+      <c r="BM105">
+        <v>2</v>
+      </c>
+      <c r="BN105">
+        <v>1.79</v>
+      </c>
+      <c r="BO105">
+        <v>2.32</v>
+      </c>
+      <c r="BP105">
+        <v>1.47</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
@@ -21745,22 +21745,22 @@
         <v>2.7</v>
       </c>
       <c r="AU101">
+        <v>3</v>
+      </c>
+      <c r="AV101">
         <v>4</v>
       </c>
-      <c r="AV101">
-        <v>5</v>
-      </c>
       <c r="AW101">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AX101">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AY101">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AZ101">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="BA101">
         <v>9</v>
@@ -21957,16 +21957,16 @@
         <v>12</v>
       </c>
       <c r="AW102">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AX102">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AY102">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AZ102">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BA102">
         <v>8</v>
@@ -22157,19 +22157,19 @@
         <v>3.23</v>
       </c>
       <c r="AU103">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV103">
         <v>3</v>
       </c>
       <c r="AW103">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AX103">
         <v>4</v>
       </c>
       <c r="AY103">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AZ103">
         <v>7</v>
@@ -22366,19 +22366,19 @@
         <v>8</v>
       </c>
       <c r="AV104">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW104">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AX104">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AY104">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AZ104">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="BA104">
         <v>9</v>
@@ -22572,19 +22572,19 @@
         <v>9</v>
       </c>
       <c r="AV105">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW105">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX105">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AY105">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ105">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA105">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="216">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -487,6 +487,18 @@
     <t>['6', '29', '26', '49']</t>
   </si>
   <si>
+    <t>['45', '73']</t>
+  </si>
+  <si>
+    <t>['90+6']</t>
+  </si>
+  <si>
+    <t>['8', '48']</t>
+  </si>
+  <si>
+    <t>['2', '40']</t>
+  </si>
+  <si>
     <t>['45+1', '81']</t>
   </si>
   <si>
@@ -641,6 +653,15 @@
   </si>
   <si>
     <t>['69']</t>
+  </si>
+  <si>
+    <t>['47']</t>
+  </si>
+  <si>
+    <t>['12']</t>
+  </si>
+  <si>
+    <t>['3', '49']</t>
   </si>
 </sst>
 </file>
@@ -1002,7 +1023,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP105"/>
+  <dimension ref="A1:BP110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1258,7 +1279,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="Q2">
         <v>4.4</v>
@@ -1336,10 +1357,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ2">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1545,7 +1566,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ3">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1748,10 +1769,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ4">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1876,7 +1897,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -1954,7 +1975,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ5">
         <v>1.3</v>
@@ -2160,10 +2181,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ6">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2700,7 +2721,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -2984,10 +3005,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ10">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3112,7 +3133,7 @@
         <v>88</v>
       </c>
       <c r="P11" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="Q11">
         <v>1.94</v>
@@ -3190,7 +3211,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ11">
         <v>0.7</v>
@@ -3318,7 +3339,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="Q12">
         <v>3.95</v>
@@ -3399,7 +3420,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ12">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR12">
         <v>1.77</v>
@@ -3524,7 +3545,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="Q13">
         <v>4.5</v>
@@ -3605,7 +3626,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ13">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR13">
         <v>1.54</v>
@@ -3730,7 +3751,7 @@
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="Q14">
         <v>3.9</v>
@@ -3808,7 +3829,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ14">
         <v>1.36</v>
@@ -3936,7 +3957,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Q15">
         <v>2.06</v>
@@ -4142,7 +4163,7 @@
         <v>82</v>
       </c>
       <c r="P16" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4220,10 +4241,10 @@
         <v>1</v>
       </c>
       <c r="AP16">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ16">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR16">
         <v>0.9399999999999999</v>
@@ -4348,7 +4369,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="Q17">
         <v>3.1</v>
@@ -4429,7 +4450,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ17">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR17">
         <v>1.58</v>
@@ -4554,7 +4575,7 @@
         <v>94</v>
       </c>
       <c r="P18" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="Q18">
         <v>4.2</v>
@@ -4632,10 +4653,10 @@
         <v>0.5</v>
       </c>
       <c r="AP18">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ18">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR18">
         <v>2.63</v>
@@ -4838,10 +4859,10 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ19">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR19">
         <v>2.01</v>
@@ -4966,7 +4987,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="Q20">
         <v>2.65</v>
@@ -5044,7 +5065,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ20">
         <v>0.2</v>
@@ -5172,7 +5193,7 @@
         <v>82</v>
       </c>
       <c r="P21" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5250,7 +5271,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ21">
         <v>1.36</v>
@@ -5665,7 +5686,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ23">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR23">
         <v>1.82</v>
@@ -5868,7 +5889,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ24">
         <v>0.7</v>
@@ -5996,7 +6017,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="Q25">
         <v>2.7</v>
@@ -6077,7 +6098,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ25">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR25">
         <v>1.72</v>
@@ -6202,7 +6223,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="Q26">
         <v>4.75</v>
@@ -6283,7 +6304,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ26">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR26">
         <v>1.55</v>
@@ -6614,7 +6635,7 @@
         <v>101</v>
       </c>
       <c r="P28" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -6898,7 +6919,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ29">
         <v>1.36</v>
@@ -7104,10 +7125,10 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ30">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR30">
         <v>1.87</v>
@@ -7232,7 +7253,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="Q31">
         <v>4.75</v>
@@ -7310,7 +7331,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ31">
         <v>0.91</v>
@@ -7438,7 +7459,7 @@
         <v>82</v>
       </c>
       <c r="P32" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="Q32">
         <v>3</v>
@@ -7516,10 +7537,10 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ32">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR32">
         <v>1.2</v>
@@ -7722,10 +7743,10 @@
         <v>2.33</v>
       </c>
       <c r="AP33">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ33">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR33">
         <v>1.68</v>
@@ -7850,7 +7871,7 @@
         <v>104</v>
       </c>
       <c r="P34" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Q34">
         <v>4.33</v>
@@ -7928,10 +7949,10 @@
         <v>2</v>
       </c>
       <c r="AP34">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ34">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR34">
         <v>1.64</v>
@@ -8137,7 +8158,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ35">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR35">
         <v>1.34</v>
@@ -8340,10 +8361,10 @@
         <v>2.33</v>
       </c>
       <c r="AP36">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ36">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR36">
         <v>1.81</v>
@@ -8468,7 +8489,7 @@
         <v>105</v>
       </c>
       <c r="P37" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="Q37">
         <v>2.38</v>
@@ -8546,7 +8567,7 @@
         <v>0.33</v>
       </c>
       <c r="AP37">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ37">
         <v>0.7</v>
@@ -9167,7 +9188,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ40">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR40">
         <v>1.69</v>
@@ -9292,7 +9313,7 @@
         <v>82</v>
       </c>
       <c r="P41" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="Q41">
         <v>5.2</v>
@@ -9370,7 +9391,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ41">
         <v>0.91</v>
@@ -9704,7 +9725,7 @@
         <v>109</v>
       </c>
       <c r="P43" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="Q43">
         <v>2.38</v>
@@ -9785,7 +9806,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ43">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR43">
         <v>2.04</v>
@@ -10116,7 +10137,7 @@
         <v>111</v>
       </c>
       <c r="P45" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="Q45">
         <v>4.04</v>
@@ -10194,10 +10215,10 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ45">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR45">
         <v>1.63</v>
@@ -10322,7 +10343,7 @@
         <v>112</v>
       </c>
       <c r="P46" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Q46">
         <v>1.7</v>
@@ -10606,7 +10627,7 @@
         <v>0.25</v>
       </c>
       <c r="AP47">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ47">
         <v>0.2</v>
@@ -10734,7 +10755,7 @@
         <v>114</v>
       </c>
       <c r="P48" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="Q48">
         <v>3.88</v>
@@ -10815,7 +10836,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ48">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR48">
         <v>1.51</v>
@@ -10940,7 +10961,7 @@
         <v>115</v>
       </c>
       <c r="P49" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="Q49">
         <v>3.55</v>
@@ -11021,7 +11042,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ49">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR49">
         <v>1.6</v>
@@ -11146,7 +11167,7 @@
         <v>116</v>
       </c>
       <c r="P50" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Q50">
         <v>3.7</v>
@@ -11224,10 +11245,10 @@
         <v>1.4</v>
       </c>
       <c r="AP50">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ50">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR50">
         <v>1.81</v>
@@ -11352,7 +11373,7 @@
         <v>82</v>
       </c>
       <c r="P51" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q51">
         <v>2.6</v>
@@ -11430,7 +11451,7 @@
         <v>0.25</v>
       </c>
       <c r="AP51">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ51">
         <v>0.7</v>
@@ -11558,7 +11579,7 @@
         <v>117</v>
       </c>
       <c r="P52" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Q52">
         <v>2.24</v>
@@ -12048,7 +12069,7 @@
         <v>1.2</v>
       </c>
       <c r="AP54">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ54">
         <v>1.3</v>
@@ -12176,7 +12197,7 @@
         <v>119</v>
       </c>
       <c r="P55" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="Q55">
         <v>2.6</v>
@@ -12257,7 +12278,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ55">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR55">
         <v>1.84</v>
@@ -12588,7 +12609,7 @@
         <v>121</v>
       </c>
       <c r="P57" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -12666,7 +12687,7 @@
         <v>1.4</v>
       </c>
       <c r="AP57">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ57">
         <v>0.91</v>
@@ -12875,7 +12896,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ58">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR58">
         <v>1.65</v>
@@ -13000,7 +13021,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="Q59">
         <v>4.75</v>
@@ -13078,10 +13099,10 @@
         <v>1.4</v>
       </c>
       <c r="AP59">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ59">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR59">
         <v>1.59</v>
@@ -13206,7 +13227,7 @@
         <v>124</v>
       </c>
       <c r="P60" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="Q60">
         <v>2.61</v>
@@ -13287,7 +13308,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ60">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR60">
         <v>1.76</v>
@@ -13412,7 +13433,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="Q61">
         <v>3.05</v>
@@ -13490,7 +13511,7 @@
         <v>0.2</v>
       </c>
       <c r="AP61">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ61">
         <v>0.2</v>
@@ -13696,10 +13717,10 @@
         <v>1.67</v>
       </c>
       <c r="AP62">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ62">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR62">
         <v>1.73</v>
@@ -13824,7 +13845,7 @@
         <v>127</v>
       </c>
       <c r="P63" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="Q63">
         <v>3.28</v>
@@ -13902,10 +13923,10 @@
         <v>1.83</v>
       </c>
       <c r="AP63">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ63">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR63">
         <v>1.53</v>
@@ -14030,7 +14051,7 @@
         <v>128</v>
       </c>
       <c r="P64" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="Q64">
         <v>6.5</v>
@@ -14108,10 +14129,10 @@
         <v>1.33</v>
       </c>
       <c r="AP64">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ64">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR64">
         <v>1.6</v>
@@ -14236,7 +14257,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="Q65">
         <v>2.04</v>
@@ -14314,7 +14335,7 @@
         <v>1</v>
       </c>
       <c r="AP65">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ65">
         <v>1.3</v>
@@ -14523,7 +14544,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ66">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR66">
         <v>1.92</v>
@@ -14648,7 +14669,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="Q67">
         <v>2.45</v>
@@ -14854,7 +14875,7 @@
         <v>132</v>
       </c>
       <c r="P68" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="Q68">
         <v>3.2</v>
@@ -15678,7 +15699,7 @@
         <v>135</v>
       </c>
       <c r="P72" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="Q72">
         <v>3.26</v>
@@ -15884,7 +15905,7 @@
         <v>97</v>
       </c>
       <c r="P73" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="Q73">
         <v>4.6</v>
@@ -15962,10 +15983,10 @@
         <v>1.17</v>
       </c>
       <c r="AP73">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ73">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR73">
         <v>1.54</v>
@@ -16168,10 +16189,10 @@
         <v>1.43</v>
       </c>
       <c r="AP74">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ74">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR74">
         <v>1.51</v>
@@ -16377,7 +16398,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ75">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR75">
         <v>1.88</v>
@@ -16502,7 +16523,7 @@
         <v>82</v>
       </c>
       <c r="P76" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="Q76">
         <v>3.65</v>
@@ -16580,7 +16601,7 @@
         <v>1.29</v>
       </c>
       <c r="AP76">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ76">
         <v>1.36</v>
@@ -16708,7 +16729,7 @@
         <v>82</v>
       </c>
       <c r="P77" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="Q77">
         <v>2.05</v>
@@ -16914,7 +16935,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="Q78">
         <v>1.89</v>
@@ -16992,7 +17013,7 @@
         <v>0.29</v>
       </c>
       <c r="AP78">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ78">
         <v>0.2</v>
@@ -17198,10 +17219,10 @@
         <v>1.43</v>
       </c>
       <c r="AP79">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ79">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR79">
         <v>1.98</v>
@@ -17407,7 +17428,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ80">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR80">
         <v>1.49</v>
@@ -17532,7 +17553,7 @@
         <v>85</v>
       </c>
       <c r="P81" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="Q81">
         <v>5.25</v>
@@ -17610,10 +17631,10 @@
         <v>1.29</v>
       </c>
       <c r="AP81">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ81">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR81">
         <v>1.57</v>
@@ -17819,7 +17840,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ82">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR82">
         <v>2.02</v>
@@ -18356,7 +18377,7 @@
         <v>143</v>
       </c>
       <c r="P85" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="Q85">
         <v>2.2</v>
@@ -18562,7 +18583,7 @@
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="Q86">
         <v>2.11</v>
@@ -18768,7 +18789,7 @@
         <v>145</v>
       </c>
       <c r="P87" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="Q87">
         <v>2.04</v>
@@ -18846,7 +18867,7 @@
         <v>1.5</v>
       </c>
       <c r="AP87">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ87">
         <v>1.3</v>
@@ -18974,7 +18995,7 @@
         <v>146</v>
       </c>
       <c r="P88" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19055,7 +19076,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ88">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR88">
         <v>1.76</v>
@@ -19258,7 +19279,7 @@
         <v>0.78</v>
       </c>
       <c r="AP89">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ89">
         <v>0.91</v>
@@ -19386,7 +19407,7 @@
         <v>147</v>
       </c>
       <c r="P90" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="Q90">
         <v>3.81</v>
@@ -19464,10 +19485,10 @@
         <v>1.25</v>
       </c>
       <c r="AP90">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ90">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR90">
         <v>1.52</v>
@@ -19592,7 +19613,7 @@
         <v>148</v>
       </c>
       <c r="P91" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="Q91">
         <v>3.3</v>
@@ -19670,10 +19691,10 @@
         <v>1.44</v>
       </c>
       <c r="AP91">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ91">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR91">
         <v>1.53</v>
@@ -19876,10 +19897,10 @@
         <v>1.38</v>
       </c>
       <c r="AP92">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ92">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR92">
         <v>1.96</v>
@@ -20085,7 +20106,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ93">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR93">
         <v>1.9</v>
@@ -20210,7 +20231,7 @@
         <v>149</v>
       </c>
       <c r="P94" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Q94">
         <v>3.8</v>
@@ -20291,7 +20312,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ94">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR94">
         <v>2.08</v>
@@ -20494,10 +20515,10 @@
         <v>1.4</v>
       </c>
       <c r="AP95">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ95">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR95">
         <v>1.63</v>
@@ -20622,7 +20643,7 @@
         <v>82</v>
       </c>
       <c r="P96" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Q96">
         <v>4.1</v>
@@ -20700,7 +20721,7 @@
         <v>1.33</v>
       </c>
       <c r="AP96">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ96">
         <v>1.36</v>
@@ -20909,7 +20930,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ97">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR97">
         <v>1.72</v>
@@ -21112,7 +21133,7 @@
         <v>1.44</v>
       </c>
       <c r="AP98">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ98">
         <v>1.3</v>
@@ -21240,7 +21261,7 @@
         <v>152</v>
       </c>
       <c r="P99" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="Q99">
         <v>4.85</v>
@@ -21321,7 +21342,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ99">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR99">
         <v>1.43</v>
@@ -21524,10 +21545,10 @@
         <v>1.22</v>
       </c>
       <c r="AP100">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ100">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR100">
         <v>1.64</v>
@@ -22064,7 +22085,7 @@
         <v>82</v>
       </c>
       <c r="P103" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Q103">
         <v>3.3</v>
@@ -22145,7 +22166,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ103">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR103">
         <v>1.98</v>
@@ -22270,7 +22291,7 @@
         <v>155</v>
       </c>
       <c r="P104" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -22348,7 +22369,7 @@
         <v>1.5</v>
       </c>
       <c r="AP104">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ104">
         <v>1.36</v>
@@ -22476,7 +22497,7 @@
         <v>156</v>
       </c>
       <c r="P105" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="Q105">
         <v>1.64</v>
@@ -22633,6 +22654,1036 @@
       </c>
       <c r="BP105">
         <v>1.47</v>
+      </c>
+    </row>
+    <row r="106" spans="1:68">
+      <c r="A106" s="1">
+        <v>105</v>
+      </c>
+      <c r="B106">
+        <v>7775722</v>
+      </c>
+      <c r="C106" t="s">
+        <v>68</v>
+      </c>
+      <c r="D106" t="s">
+        <v>69</v>
+      </c>
+      <c r="E106" s="2">
+        <v>45831.65625</v>
+      </c>
+      <c r="F106">
+        <v>0</v>
+      </c>
+      <c r="G106" t="s">
+        <v>73</v>
+      </c>
+      <c r="H106" t="s">
+        <v>77</v>
+      </c>
+      <c r="I106">
+        <v>1</v>
+      </c>
+      <c r="J106">
+        <v>0</v>
+      </c>
+      <c r="K106">
+        <v>1</v>
+      </c>
+      <c r="L106">
+        <v>2</v>
+      </c>
+      <c r="M106">
+        <v>1</v>
+      </c>
+      <c r="N106">
+        <v>3</v>
+      </c>
+      <c r="O106" t="s">
+        <v>157</v>
+      </c>
+      <c r="P106" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q106">
+        <v>3.55</v>
+      </c>
+      <c r="R106">
+        <v>2.1</v>
+      </c>
+      <c r="S106">
+        <v>2.9</v>
+      </c>
+      <c r="T106">
+        <v>1.36</v>
+      </c>
+      <c r="U106">
+        <v>2.8</v>
+      </c>
+      <c r="V106">
+        <v>2.78</v>
+      </c>
+      <c r="W106">
+        <v>1.4</v>
+      </c>
+      <c r="X106">
+        <v>6.5</v>
+      </c>
+      <c r="Y106">
+        <v>1.08</v>
+      </c>
+      <c r="Z106">
+        <v>2.98</v>
+      </c>
+      <c r="AA106">
+        <v>3.4</v>
+      </c>
+      <c r="AB106">
+        <v>2.15</v>
+      </c>
+      <c r="AC106">
+        <v>1</v>
+      </c>
+      <c r="AD106">
+        <v>9.5</v>
+      </c>
+      <c r="AE106">
+        <v>1.25</v>
+      </c>
+      <c r="AF106">
+        <v>3.5</v>
+      </c>
+      <c r="AG106">
+        <v>2.06</v>
+      </c>
+      <c r="AH106">
+        <v>1.76</v>
+      </c>
+      <c r="AI106">
+        <v>1.67</v>
+      </c>
+      <c r="AJ106">
+        <v>2.05</v>
+      </c>
+      <c r="AK106">
+        <v>1.3</v>
+      </c>
+      <c r="AL106">
+        <v>1.25</v>
+      </c>
+      <c r="AM106">
+        <v>1.33</v>
+      </c>
+      <c r="AN106">
+        <v>0.8</v>
+      </c>
+      <c r="AO106">
+        <v>1.2</v>
+      </c>
+      <c r="AP106">
+        <v>1</v>
+      </c>
+      <c r="AQ106">
+        <v>1.09</v>
+      </c>
+      <c r="AR106">
+        <v>1.39</v>
+      </c>
+      <c r="AS106">
+        <v>1.46</v>
+      </c>
+      <c r="AT106">
+        <v>2.85</v>
+      </c>
+      <c r="AU106">
+        <v>7</v>
+      </c>
+      <c r="AV106">
+        <v>9</v>
+      </c>
+      <c r="AW106">
+        <v>4</v>
+      </c>
+      <c r="AX106">
+        <v>6</v>
+      </c>
+      <c r="AY106">
+        <v>11</v>
+      </c>
+      <c r="AZ106">
+        <v>15</v>
+      </c>
+      <c r="BA106">
+        <v>3</v>
+      </c>
+      <c r="BB106">
+        <v>5</v>
+      </c>
+      <c r="BC106">
+        <v>8</v>
+      </c>
+      <c r="BD106">
+        <v>2.15</v>
+      </c>
+      <c r="BE106">
+        <v>7.2</v>
+      </c>
+      <c r="BF106">
+        <v>2</v>
+      </c>
+      <c r="BG106">
+        <v>1.23</v>
+      </c>
+      <c r="BH106">
+        <v>3.6</v>
+      </c>
+      <c r="BI106">
+        <v>1.43</v>
+      </c>
+      <c r="BJ106">
+        <v>2.55</v>
+      </c>
+      <c r="BK106">
+        <v>1.78</v>
+      </c>
+      <c r="BL106">
+        <v>2</v>
+      </c>
+      <c r="BM106">
+        <v>2.25</v>
+      </c>
+      <c r="BN106">
+        <v>1.65</v>
+      </c>
+      <c r="BO106">
+        <v>2.55</v>
+      </c>
+      <c r="BP106">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="107" spans="1:68">
+      <c r="A107" s="1">
+        <v>106</v>
+      </c>
+      <c r="B107">
+        <v>7775723</v>
+      </c>
+      <c r="C107" t="s">
+        <v>68</v>
+      </c>
+      <c r="D107" t="s">
+        <v>69</v>
+      </c>
+      <c r="E107" s="2">
+        <v>45831.65625</v>
+      </c>
+      <c r="F107">
+        <v>0</v>
+      </c>
+      <c r="G107" t="s">
+        <v>72</v>
+      </c>
+      <c r="H107" t="s">
+        <v>75</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
+      </c>
+      <c r="J107">
+        <v>1</v>
+      </c>
+      <c r="K107">
+        <v>1</v>
+      </c>
+      <c r="L107">
+        <v>0</v>
+      </c>
+      <c r="M107">
+        <v>1</v>
+      </c>
+      <c r="N107">
+        <v>1</v>
+      </c>
+      <c r="O107" t="s">
+        <v>82</v>
+      </c>
+      <c r="P107" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q107">
+        <v>2.89</v>
+      </c>
+      <c r="R107">
+        <v>1.91</v>
+      </c>
+      <c r="S107">
+        <v>3.65</v>
+      </c>
+      <c r="T107">
+        <v>1.5</v>
+      </c>
+      <c r="U107">
+        <v>2.56</v>
+      </c>
+      <c r="V107">
+        <v>3.3</v>
+      </c>
+      <c r="W107">
+        <v>1.3</v>
+      </c>
+      <c r="X107">
+        <v>9</v>
+      </c>
+      <c r="Y107">
+        <v>1.05</v>
+      </c>
+      <c r="Z107">
+        <v>2.35</v>
+      </c>
+      <c r="AA107">
+        <v>3.19</v>
+      </c>
+      <c r="AB107">
+        <v>3.15</v>
+      </c>
+      <c r="AC107">
+        <v>1.08</v>
+      </c>
+      <c r="AD107">
+        <v>7</v>
+      </c>
+      <c r="AE107">
+        <v>1.44</v>
+      </c>
+      <c r="AF107">
+        <v>2.63</v>
+      </c>
+      <c r="AG107">
+        <v>2.25</v>
+      </c>
+      <c r="AH107">
+        <v>1.53</v>
+      </c>
+      <c r="AI107">
+        <v>1.91</v>
+      </c>
+      <c r="AJ107">
+        <v>1.75</v>
+      </c>
+      <c r="AK107">
+        <v>1.29</v>
+      </c>
+      <c r="AL107">
+        <v>1.25</v>
+      </c>
+      <c r="AM107">
+        <v>1.57</v>
+      </c>
+      <c r="AN107">
+        <v>1.82</v>
+      </c>
+      <c r="AO107">
+        <v>1.4</v>
+      </c>
+      <c r="AP107">
+        <v>1.67</v>
+      </c>
+      <c r="AQ107">
+        <v>1.55</v>
+      </c>
+      <c r="AR107">
+        <v>1.66</v>
+      </c>
+      <c r="AS107">
+        <v>1.21</v>
+      </c>
+      <c r="AT107">
+        <v>2.87</v>
+      </c>
+      <c r="AU107">
+        <v>7</v>
+      </c>
+      <c r="AV107">
+        <v>2</v>
+      </c>
+      <c r="AW107">
+        <v>5</v>
+      </c>
+      <c r="AX107">
+        <v>2</v>
+      </c>
+      <c r="AY107">
+        <v>12</v>
+      </c>
+      <c r="AZ107">
+        <v>4</v>
+      </c>
+      <c r="BA107">
+        <v>7</v>
+      </c>
+      <c r="BB107">
+        <v>2</v>
+      </c>
+      <c r="BC107">
+        <v>9</v>
+      </c>
+      <c r="BD107">
+        <v>1.9</v>
+      </c>
+      <c r="BE107">
+        <v>7</v>
+      </c>
+      <c r="BF107">
+        <v>2.3</v>
+      </c>
+      <c r="BG107">
+        <v>1.32</v>
+      </c>
+      <c r="BH107">
+        <v>2.83</v>
+      </c>
+      <c r="BI107">
+        <v>1.64</v>
+      </c>
+      <c r="BJ107">
+        <v>2.18</v>
+      </c>
+      <c r="BK107">
+        <v>2.36</v>
+      </c>
+      <c r="BL107">
+        <v>1.73</v>
+      </c>
+      <c r="BM107">
+        <v>2.57</v>
+      </c>
+      <c r="BN107">
+        <v>1.44</v>
+      </c>
+      <c r="BO107">
+        <v>3.4</v>
+      </c>
+      <c r="BP107">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="108" spans="1:68">
+      <c r="A108" s="1">
+        <v>107</v>
+      </c>
+      <c r="B108">
+        <v>7775721</v>
+      </c>
+      <c r="C108" t="s">
+        <v>68</v>
+      </c>
+      <c r="D108" t="s">
+        <v>69</v>
+      </c>
+      <c r="E108" s="2">
+        <v>45831.65625</v>
+      </c>
+      <c r="F108">
+        <v>0</v>
+      </c>
+      <c r="G108" t="s">
+        <v>70</v>
+      </c>
+      <c r="H108" t="s">
+        <v>76</v>
+      </c>
+      <c r="I108">
+        <v>0</v>
+      </c>
+      <c r="J108">
+        <v>1</v>
+      </c>
+      <c r="K108">
+        <v>1</v>
+      </c>
+      <c r="L108">
+        <v>1</v>
+      </c>
+      <c r="M108">
+        <v>1</v>
+      </c>
+      <c r="N108">
+        <v>2</v>
+      </c>
+      <c r="O108" t="s">
+        <v>158</v>
+      </c>
+      <c r="P108" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q108">
+        <v>3.5</v>
+      </c>
+      <c r="R108">
+        <v>2</v>
+      </c>
+      <c r="S108">
+        <v>3.1</v>
+      </c>
+      <c r="T108">
+        <v>1.38</v>
+      </c>
+      <c r="U108">
+        <v>2.62</v>
+      </c>
+      <c r="V108">
+        <v>3</v>
+      </c>
+      <c r="W108">
+        <v>1.38</v>
+      </c>
+      <c r="X108">
+        <v>8</v>
+      </c>
+      <c r="Y108">
+        <v>1.07</v>
+      </c>
+      <c r="Z108">
+        <v>2.81</v>
+      </c>
+      <c r="AA108">
+        <v>3.1</v>
+      </c>
+      <c r="AB108">
+        <v>2.41</v>
+      </c>
+      <c r="AC108">
+        <v>1.07</v>
+      </c>
+      <c r="AD108">
+        <v>7.8</v>
+      </c>
+      <c r="AE108">
+        <v>1.33</v>
+      </c>
+      <c r="AF108">
+        <v>2.9</v>
+      </c>
+      <c r="AG108">
+        <v>2.19</v>
+      </c>
+      <c r="AH108">
+        <v>1.67</v>
+      </c>
+      <c r="AI108">
+        <v>1.92</v>
+      </c>
+      <c r="AJ108">
+        <v>1.91</v>
+      </c>
+      <c r="AK108">
+        <v>1.29</v>
+      </c>
+      <c r="AL108">
+        <v>1.25</v>
+      </c>
+      <c r="AM108">
+        <v>1.37</v>
+      </c>
+      <c r="AN108">
+        <v>1.1</v>
+      </c>
+      <c r="AO108">
+        <v>1.36</v>
+      </c>
+      <c r="AP108">
+        <v>1.09</v>
+      </c>
+      <c r="AQ108">
+        <v>1.33</v>
+      </c>
+      <c r="AR108">
+        <v>1.49</v>
+      </c>
+      <c r="AS108">
+        <v>1.39</v>
+      </c>
+      <c r="AT108">
+        <v>2.88</v>
+      </c>
+      <c r="AU108">
+        <v>7</v>
+      </c>
+      <c r="AV108">
+        <v>3</v>
+      </c>
+      <c r="AW108">
+        <v>10</v>
+      </c>
+      <c r="AX108">
+        <v>1</v>
+      </c>
+      <c r="AY108">
+        <v>17</v>
+      </c>
+      <c r="AZ108">
+        <v>4</v>
+      </c>
+      <c r="BA108">
+        <v>9</v>
+      </c>
+      <c r="BB108">
+        <v>2</v>
+      </c>
+      <c r="BC108">
+        <v>11</v>
+      </c>
+      <c r="BD108">
+        <v>1.95</v>
+      </c>
+      <c r="BE108">
+        <v>7</v>
+      </c>
+      <c r="BF108">
+        <v>2.05</v>
+      </c>
+      <c r="BG108">
+        <v>1.23</v>
+      </c>
+      <c r="BH108">
+        <v>3.55</v>
+      </c>
+      <c r="BI108">
+        <v>1.31</v>
+      </c>
+      <c r="BJ108">
+        <v>2.58</v>
+      </c>
+      <c r="BK108">
+        <v>1.57</v>
+      </c>
+      <c r="BL108">
+        <v>2</v>
+      </c>
+      <c r="BM108">
+        <v>1.98</v>
+      </c>
+      <c r="BN108">
+        <v>1.7</v>
+      </c>
+      <c r="BO108">
+        <v>2.55</v>
+      </c>
+      <c r="BP108">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="109" spans="1:68">
+      <c r="A109" s="1">
+        <v>108</v>
+      </c>
+      <c r="B109">
+        <v>7775724</v>
+      </c>
+      <c r="C109" t="s">
+        <v>68</v>
+      </c>
+      <c r="D109" t="s">
+        <v>69</v>
+      </c>
+      <c r="E109" s="2">
+        <v>45831.65625</v>
+      </c>
+      <c r="F109">
+        <v>0</v>
+      </c>
+      <c r="G109" t="s">
+        <v>78</v>
+      </c>
+      <c r="H109" t="s">
+        <v>71</v>
+      </c>
+      <c r="I109">
+        <v>1</v>
+      </c>
+      <c r="J109">
+        <v>1</v>
+      </c>
+      <c r="K109">
+        <v>2</v>
+      </c>
+      <c r="L109">
+        <v>2</v>
+      </c>
+      <c r="M109">
+        <v>2</v>
+      </c>
+      <c r="N109">
+        <v>4</v>
+      </c>
+      <c r="O109" t="s">
+        <v>159</v>
+      </c>
+      <c r="P109" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q109">
+        <v>3.4</v>
+      </c>
+      <c r="R109">
+        <v>1.95</v>
+      </c>
+      <c r="S109">
+        <v>3.2</v>
+      </c>
+      <c r="T109">
+        <v>1.42</v>
+      </c>
+      <c r="U109">
+        <v>2.57</v>
+      </c>
+      <c r="V109">
+        <v>3</v>
+      </c>
+      <c r="W109">
+        <v>1.35</v>
+      </c>
+      <c r="X109">
+        <v>8</v>
+      </c>
+      <c r="Y109">
+        <v>1.03</v>
+      </c>
+      <c r="Z109">
+        <v>2.61</v>
+      </c>
+      <c r="AA109">
+        <v>3.27</v>
+      </c>
+      <c r="AB109">
+        <v>2.48</v>
+      </c>
+      <c r="AC109">
+        <v>1.06</v>
+      </c>
+      <c r="AD109">
+        <v>8</v>
+      </c>
+      <c r="AE109">
+        <v>1.33</v>
+      </c>
+      <c r="AF109">
+        <v>2.9</v>
+      </c>
+      <c r="AG109">
+        <v>2.1</v>
+      </c>
+      <c r="AH109">
+        <v>1.7</v>
+      </c>
+      <c r="AI109">
+        <v>1.72</v>
+      </c>
+      <c r="AJ109">
+        <v>1.91</v>
+      </c>
+      <c r="AK109">
+        <v>1.33</v>
+      </c>
+      <c r="AL109">
+        <v>1.25</v>
+      </c>
+      <c r="AM109">
+        <v>1.42</v>
+      </c>
+      <c r="AN109">
+        <v>1.3</v>
+      </c>
+      <c r="AO109">
+        <v>1.4</v>
+      </c>
+      <c r="AP109">
+        <v>1.27</v>
+      </c>
+      <c r="AQ109">
+        <v>1.36</v>
+      </c>
+      <c r="AR109">
+        <v>1.65</v>
+      </c>
+      <c r="AS109">
+        <v>1.39</v>
+      </c>
+      <c r="AT109">
+        <v>3.04</v>
+      </c>
+      <c r="AU109">
+        <v>4</v>
+      </c>
+      <c r="AV109">
+        <v>7</v>
+      </c>
+      <c r="AW109">
+        <v>2</v>
+      </c>
+      <c r="AX109">
+        <v>6</v>
+      </c>
+      <c r="AY109">
+        <v>6</v>
+      </c>
+      <c r="AZ109">
+        <v>13</v>
+      </c>
+      <c r="BA109">
+        <v>2</v>
+      </c>
+      <c r="BB109">
+        <v>7</v>
+      </c>
+      <c r="BC109">
+        <v>9</v>
+      </c>
+      <c r="BD109">
+        <v>1.95</v>
+      </c>
+      <c r="BE109">
+        <v>8.5</v>
+      </c>
+      <c r="BF109">
+        <v>2.25</v>
+      </c>
+      <c r="BG109">
+        <v>1.34</v>
+      </c>
+      <c r="BH109">
+        <v>3.15</v>
+      </c>
+      <c r="BI109">
+        <v>1.57</v>
+      </c>
+      <c r="BJ109">
+        <v>2.33</v>
+      </c>
+      <c r="BK109">
+        <v>2.19</v>
+      </c>
+      <c r="BL109">
+        <v>1.83</v>
+      </c>
+      <c r="BM109">
+        <v>2.4</v>
+      </c>
+      <c r="BN109">
+        <v>1.51</v>
+      </c>
+      <c r="BO109">
+        <v>3.12</v>
+      </c>
+      <c r="BP109">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="110" spans="1:68">
+      <c r="A110" s="1">
+        <v>109</v>
+      </c>
+      <c r="B110">
+        <v>7775720</v>
+      </c>
+      <c r="C110" t="s">
+        <v>68</v>
+      </c>
+      <c r="D110" t="s">
+        <v>69</v>
+      </c>
+      <c r="E110" s="2">
+        <v>45831.65625</v>
+      </c>
+      <c r="F110">
+        <v>0</v>
+      </c>
+      <c r="G110" t="s">
+        <v>74</v>
+      </c>
+      <c r="H110" t="s">
+        <v>79</v>
+      </c>
+      <c r="I110">
+        <v>2</v>
+      </c>
+      <c r="J110">
+        <v>0</v>
+      </c>
+      <c r="K110">
+        <v>2</v>
+      </c>
+      <c r="L110">
+        <v>2</v>
+      </c>
+      <c r="M110">
+        <v>0</v>
+      </c>
+      <c r="N110">
+        <v>2</v>
+      </c>
+      <c r="O110" t="s">
+        <v>160</v>
+      </c>
+      <c r="P110" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q110">
+        <v>4</v>
+      </c>
+      <c r="R110">
+        <v>1.94</v>
+      </c>
+      <c r="S110">
+        <v>2.81</v>
+      </c>
+      <c r="T110">
+        <v>1.5</v>
+      </c>
+      <c r="U110">
+        <v>2.5</v>
+      </c>
+      <c r="V110">
+        <v>3.3</v>
+      </c>
+      <c r="W110">
+        <v>1.3</v>
+      </c>
+      <c r="X110">
+        <v>7.8</v>
+      </c>
+      <c r="Y110">
+        <v>1.05</v>
+      </c>
+      <c r="Z110">
+        <v>3.3</v>
+      </c>
+      <c r="AA110">
+        <v>3.11</v>
+      </c>
+      <c r="AB110">
+        <v>2.12</v>
+      </c>
+      <c r="AC110">
+        <v>1.04</v>
+      </c>
+      <c r="AD110">
+        <v>7</v>
+      </c>
+      <c r="AE110">
+        <v>1.44</v>
+      </c>
+      <c r="AF110">
+        <v>2.7</v>
+      </c>
+      <c r="AG110">
+        <v>2.4</v>
+      </c>
+      <c r="AH110">
+        <v>1.59</v>
+      </c>
+      <c r="AI110">
+        <v>1.96</v>
+      </c>
+      <c r="AJ110">
+        <v>1.82</v>
+      </c>
+      <c r="AK110">
+        <v>1.33</v>
+      </c>
+      <c r="AL110">
+        <v>1.25</v>
+      </c>
+      <c r="AM110">
+        <v>1.25</v>
+      </c>
+      <c r="AN110">
+        <v>2</v>
+      </c>
+      <c r="AO110">
+        <v>1.91</v>
+      </c>
+      <c r="AP110">
+        <v>2.1</v>
+      </c>
+      <c r="AQ110">
+        <v>1.75</v>
+      </c>
+      <c r="AR110">
+        <v>1.93</v>
+      </c>
+      <c r="AS110">
+        <v>1.65</v>
+      </c>
+      <c r="AT110">
+        <v>3.58</v>
+      </c>
+      <c r="AU110">
+        <v>7</v>
+      </c>
+      <c r="AV110">
+        <v>3</v>
+      </c>
+      <c r="AW110">
+        <v>7</v>
+      </c>
+      <c r="AX110">
+        <v>5</v>
+      </c>
+      <c r="AY110">
+        <v>14</v>
+      </c>
+      <c r="AZ110">
+        <v>8</v>
+      </c>
+      <c r="BA110">
+        <v>5</v>
+      </c>
+      <c r="BB110">
+        <v>9</v>
+      </c>
+      <c r="BC110">
+        <v>14</v>
+      </c>
+      <c r="BD110">
+        <v>2.1</v>
+      </c>
+      <c r="BE110">
+        <v>7.3</v>
+      </c>
+      <c r="BF110">
+        <v>2.15</v>
+      </c>
+      <c r="BG110">
+        <v>1.25</v>
+      </c>
+      <c r="BH110">
+        <v>3.6</v>
+      </c>
+      <c r="BI110">
+        <v>1.46</v>
+      </c>
+      <c r="BJ110">
+        <v>2.52</v>
+      </c>
+      <c r="BK110">
+        <v>1.98</v>
+      </c>
+      <c r="BL110">
+        <v>1.98</v>
+      </c>
+      <c r="BM110">
+        <v>2.21</v>
+      </c>
+      <c r="BN110">
+        <v>1.62</v>
+      </c>
+      <c r="BO110">
+        <v>3.2</v>
+      </c>
+      <c r="BP110">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
@@ -22802,16 +22802,16 @@
         <v>9</v>
       </c>
       <c r="AW106">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX106">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AY106">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ106">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="BA106">
         <v>3</v>
@@ -23002,22 +23002,22 @@
         <v>2.87</v>
       </c>
       <c r="AU107">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV107">
         <v>2</v>
       </c>
       <c r="AW107">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AX107">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY107">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AZ107">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BA107">
         <v>7</v>
@@ -23208,19 +23208,19 @@
         <v>2.88</v>
       </c>
       <c r="AU108">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV108">
         <v>3</v>
       </c>
       <c r="AW108">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AX108">
         <v>1</v>
       </c>
       <c r="AY108">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AZ108">
         <v>4</v>
@@ -23414,22 +23414,22 @@
         <v>3.04</v>
       </c>
       <c r="AU109">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV109">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW109">
         <v>2</v>
       </c>
       <c r="AX109">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="AY109">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ109">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="BA109">
         <v>2</v>
@@ -23620,22 +23620,22 @@
         <v>3.58</v>
       </c>
       <c r="AU110">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV110">
         <v>3</v>
       </c>
       <c r="AW110">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AX110">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AY110">
+        <v>18</v>
+      </c>
+      <c r="AZ110">
         <v>14</v>
-      </c>
-      <c r="AZ110">
-        <v>8</v>
       </c>
       <c r="BA110">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
@@ -23208,19 +23208,19 @@
         <v>2.88</v>
       </c>
       <c r="AU108">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV108">
         <v>3</v>
       </c>
       <c r="AW108">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AX108">
         <v>1</v>
       </c>
       <c r="AY108">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AZ108">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="220">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -499,6 +499,15 @@
     <t>['2', '40']</t>
   </si>
   <si>
+    <t>['90+5']</t>
+  </si>
+  <si>
+    <t>['33', '36', '90+5']</t>
+  </si>
+  <si>
+    <t>['84']</t>
+  </si>
+  <si>
     <t>['45+1', '81']</t>
   </si>
   <si>
@@ -662,6 +671,9 @@
   </si>
   <si>
     <t>['3', '49']</t>
+  </si>
+  <si>
+    <t>['28']</t>
   </si>
 </sst>
 </file>
@@ -1023,7 +1035,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP110"/>
+  <dimension ref="A1:BP115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1279,7 +1291,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="Q2">
         <v>4.4</v>
@@ -1357,7 +1369,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ2">
         <v>1.09</v>
@@ -1772,7 +1784,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ4">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1897,7 +1909,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -1978,7 +1990,7 @@
         <v>1</v>
       </c>
       <c r="AQ5">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2181,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ6">
         <v>1.75</v>
@@ -2387,7 +2399,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ7">
         <v>1.36</v>
@@ -2596,7 +2608,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ8">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2721,7 +2733,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -2799,10 +2811,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ9">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3008,7 +3020,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ10">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3133,7 +3145,7 @@
         <v>88</v>
       </c>
       <c r="P11" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="Q11">
         <v>1.94</v>
@@ -3214,7 +3226,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ11">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR11">
         <v>2.05</v>
@@ -3339,7 +3351,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="Q12">
         <v>3.95</v>
@@ -3545,7 +3557,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="Q13">
         <v>4.5</v>
@@ -3751,7 +3763,7 @@
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="Q14">
         <v>3.9</v>
@@ -3829,7 +3841,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ14">
         <v>1.36</v>
@@ -3957,7 +3969,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Q15">
         <v>2.06</v>
@@ -4035,10 +4047,10 @@
         <v>3</v>
       </c>
       <c r="AP15">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ15">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR15">
         <v>1.43</v>
@@ -4163,7 +4175,7 @@
         <v>82</v>
       </c>
       <c r="P16" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4241,10 +4253,10 @@
         <v>1</v>
       </c>
       <c r="AP16">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ16">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR16">
         <v>0.9399999999999999</v>
@@ -4369,7 +4381,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q17">
         <v>3.1</v>
@@ -4447,10 +4459,10 @@
         <v>3</v>
       </c>
       <c r="AP17">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ17">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR17">
         <v>1.58</v>
@@ -4575,7 +4587,7 @@
         <v>94</v>
       </c>
       <c r="P18" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q18">
         <v>4.2</v>
@@ -4987,7 +4999,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q20">
         <v>2.65</v>
@@ -5193,7 +5205,7 @@
         <v>82</v>
       </c>
       <c r="P21" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5477,10 +5489,10 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ22">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -5686,7 +5698,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ23">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR23">
         <v>1.82</v>
@@ -5889,10 +5901,10 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ24">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR24">
         <v>1.36</v>
@@ -6017,7 +6029,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q25">
         <v>2.7</v>
@@ -6095,7 +6107,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ25">
         <v>1.09</v>
@@ -6223,7 +6235,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q26">
         <v>4.75</v>
@@ -6507,10 +6519,10 @@
         <v>3</v>
       </c>
       <c r="AP27">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ27">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR27">
         <v>1.49</v>
@@ -6635,7 +6647,7 @@
         <v>101</v>
       </c>
       <c r="P28" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -7253,7 +7265,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q31">
         <v>4.75</v>
@@ -7334,7 +7346,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ31">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR31">
         <v>1.77</v>
@@ -7459,7 +7471,7 @@
         <v>82</v>
       </c>
       <c r="P32" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q32">
         <v>3</v>
@@ -7537,7 +7549,7 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ32">
         <v>1.09</v>
@@ -7743,10 +7755,10 @@
         <v>2.33</v>
       </c>
       <c r="AP33">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ33">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR33">
         <v>1.68</v>
@@ -7871,7 +7883,7 @@
         <v>104</v>
       </c>
       <c r="P34" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q34">
         <v>4.33</v>
@@ -7952,7 +7964,7 @@
         <v>1</v>
       </c>
       <c r="AQ34">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR34">
         <v>1.64</v>
@@ -8155,7 +8167,7 @@
         <v>1</v>
       </c>
       <c r="AP35">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ35">
         <v>1.55</v>
@@ -8364,7 +8376,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ36">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR36">
         <v>1.81</v>
@@ -8489,7 +8501,7 @@
         <v>105</v>
       </c>
       <c r="P37" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q37">
         <v>2.38</v>
@@ -8567,10 +8579,10 @@
         <v>0.33</v>
       </c>
       <c r="AP37">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ37">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR37">
         <v>1.78</v>
@@ -8773,7 +8785,7 @@
         <v>0.5</v>
       </c>
       <c r="AP38">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ38">
         <v>0.2</v>
@@ -8982,7 +8994,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ39">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR39">
         <v>1.46</v>
@@ -9185,7 +9197,7 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ40">
         <v>1.75</v>
@@ -9313,7 +9325,7 @@
         <v>82</v>
       </c>
       <c r="P41" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q41">
         <v>5.2</v>
@@ -9391,10 +9403,10 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ41">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR41">
         <v>1.63</v>
@@ -9725,7 +9737,7 @@
         <v>109</v>
       </c>
       <c r="P43" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q43">
         <v>2.38</v>
@@ -9803,10 +9815,10 @@
         <v>2</v>
       </c>
       <c r="AP43">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ43">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR43">
         <v>2.04</v>
@@ -10009,10 +10021,10 @@
         <v>1.5</v>
       </c>
       <c r="AP44">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ44">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR44">
         <v>1.38</v>
@@ -10137,7 +10149,7 @@
         <v>111</v>
       </c>
       <c r="P45" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q45">
         <v>4.04</v>
@@ -10343,7 +10355,7 @@
         <v>112</v>
       </c>
       <c r="P46" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q46">
         <v>1.7</v>
@@ -10421,7 +10433,7 @@
         <v>0.33</v>
       </c>
       <c r="AP46">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ46">
         <v>0.2</v>
@@ -10627,7 +10639,7 @@
         <v>0.25</v>
       </c>
       <c r="AP47">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ47">
         <v>0.2</v>
@@ -10755,7 +10767,7 @@
         <v>114</v>
       </c>
       <c r="P48" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q48">
         <v>3.88</v>
@@ -10836,7 +10848,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ48">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR48">
         <v>1.51</v>
@@ -10961,7 +10973,7 @@
         <v>115</v>
       </c>
       <c r="P49" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q49">
         <v>3.55</v>
@@ -11039,7 +11051,7 @@
         <v>1</v>
       </c>
       <c r="AP49">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ49">
         <v>1.55</v>
@@ -11167,7 +11179,7 @@
         <v>116</v>
       </c>
       <c r="P50" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q50">
         <v>3.7</v>
@@ -11373,7 +11385,7 @@
         <v>82</v>
       </c>
       <c r="P51" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q51">
         <v>2.6</v>
@@ -11454,7 +11466,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ51">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR51">
         <v>1.67</v>
@@ -11579,7 +11591,7 @@
         <v>117</v>
       </c>
       <c r="P52" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q52">
         <v>2.24</v>
@@ -11657,7 +11669,7 @@
         <v>0.6</v>
       </c>
       <c r="AP52">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ52">
         <v>1.36</v>
@@ -11866,7 +11878,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ53">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR53">
         <v>1.38</v>
@@ -12069,10 +12081,10 @@
         <v>1.2</v>
       </c>
       <c r="AP54">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ54">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR54">
         <v>1.59</v>
@@ -12197,7 +12209,7 @@
         <v>119</v>
       </c>
       <c r="P55" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q55">
         <v>2.6</v>
@@ -12481,10 +12493,10 @@
         <v>0.8</v>
       </c>
       <c r="AP56">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ56">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR56">
         <v>1.88</v>
@@ -12609,7 +12621,7 @@
         <v>121</v>
       </c>
       <c r="P57" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -12687,10 +12699,10 @@
         <v>1.4</v>
       </c>
       <c r="AP57">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ57">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR57">
         <v>1.95</v>
@@ -12893,10 +12905,10 @@
         <v>2.2</v>
       </c>
       <c r="AP58">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ58">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR58">
         <v>1.65</v>
@@ -13021,7 +13033,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q59">
         <v>4.75</v>
@@ -13227,7 +13239,7 @@
         <v>124</v>
       </c>
       <c r="P60" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q60">
         <v>2.61</v>
@@ -13305,10 +13317,10 @@
         <v>1.8</v>
       </c>
       <c r="AP60">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ60">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR60">
         <v>1.76</v>
@@ -13433,7 +13445,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="Q61">
         <v>3.05</v>
@@ -13845,7 +13857,7 @@
         <v>127</v>
       </c>
       <c r="P63" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q63">
         <v>3.28</v>
@@ -13926,7 +13938,7 @@
         <v>1</v>
       </c>
       <c r="AQ63">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR63">
         <v>1.53</v>
@@ -14051,7 +14063,7 @@
         <v>128</v>
       </c>
       <c r="P64" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q64">
         <v>6.5</v>
@@ -14129,7 +14141,7 @@
         <v>1.33</v>
       </c>
       <c r="AP64">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ64">
         <v>1.75</v>
@@ -14257,7 +14269,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q65">
         <v>2.04</v>
@@ -14335,10 +14347,10 @@
         <v>1</v>
       </c>
       <c r="AP65">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ65">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR65">
         <v>1.97</v>
@@ -14541,10 +14553,10 @@
         <v>1.67</v>
       </c>
       <c r="AP66">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ66">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR66">
         <v>1.92</v>
@@ -14669,7 +14681,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q67">
         <v>2.45</v>
@@ -14875,7 +14887,7 @@
         <v>132</v>
       </c>
       <c r="P68" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q68">
         <v>3.2</v>
@@ -14953,7 +14965,7 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ68">
         <v>1.36</v>
@@ -15162,7 +15174,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ69">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR69">
         <v>2.05</v>
@@ -15365,10 +15377,10 @@
         <v>0.67</v>
       </c>
       <c r="AP70">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ70">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR70">
         <v>1.78</v>
@@ -15571,10 +15583,10 @@
         <v>1.17</v>
       </c>
       <c r="AP71">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ71">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR71">
         <v>1.84</v>
@@ -15699,7 +15711,7 @@
         <v>135</v>
       </c>
       <c r="P72" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q72">
         <v>3.26</v>
@@ -15780,7 +15792,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ72">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR72">
         <v>2.13</v>
@@ -15905,7 +15917,7 @@
         <v>97</v>
       </c>
       <c r="P73" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q73">
         <v>4.6</v>
@@ -15983,7 +15995,7 @@
         <v>1.17</v>
       </c>
       <c r="AP73">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ73">
         <v>1.55</v>
@@ -16395,10 +16407,10 @@
         <v>1.71</v>
       </c>
       <c r="AP75">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ75">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR75">
         <v>1.88</v>
@@ -16523,7 +16535,7 @@
         <v>82</v>
       </c>
       <c r="P76" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q76">
         <v>3.65</v>
@@ -16729,7 +16741,7 @@
         <v>82</v>
       </c>
       <c r="P77" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q77">
         <v>2.05</v>
@@ -16807,10 +16819,10 @@
         <v>0.57</v>
       </c>
       <c r="AP77">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ77">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR77">
         <v>1.74</v>
@@ -16935,7 +16947,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q78">
         <v>1.89</v>
@@ -17219,10 +17231,10 @@
         <v>1.43</v>
       </c>
       <c r="AP79">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ79">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR79">
         <v>1.98</v>
@@ -17553,7 +17565,7 @@
         <v>85</v>
       </c>
       <c r="P81" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q81">
         <v>5.25</v>
@@ -17840,7 +17852,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ82">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR82">
         <v>2.02</v>
@@ -18043,10 +18055,10 @@
         <v>0.88</v>
       </c>
       <c r="AP83">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ83">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR83">
         <v>1.87</v>
@@ -18377,7 +18389,7 @@
         <v>143</v>
       </c>
       <c r="P85" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q85">
         <v>2.2</v>
@@ -18455,7 +18467,7 @@
         <v>0.25</v>
       </c>
       <c r="AP85">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ85">
         <v>0.2</v>
@@ -18583,7 +18595,7 @@
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q86">
         <v>2.11</v>
@@ -18664,7 +18676,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ86">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR86">
         <v>2.01</v>
@@ -18789,7 +18801,7 @@
         <v>145</v>
       </c>
       <c r="P87" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q87">
         <v>2.04</v>
@@ -18870,7 +18882,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ87">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR87">
         <v>1.69</v>
@@ -18995,7 +19007,7 @@
         <v>146</v>
       </c>
       <c r="P88" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19073,7 +19085,7 @@
         <v>1.5</v>
       </c>
       <c r="AP88">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ88">
         <v>1.75</v>
@@ -19282,7 +19294,7 @@
         <v>1</v>
       </c>
       <c r="AQ89">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR89">
         <v>1.48</v>
@@ -19407,7 +19419,7 @@
         <v>147</v>
       </c>
       <c r="P90" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q90">
         <v>3.81</v>
@@ -19485,10 +19497,10 @@
         <v>1.25</v>
       </c>
       <c r="AP90">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ90">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR90">
         <v>1.52</v>
@@ -19613,7 +19625,7 @@
         <v>148</v>
       </c>
       <c r="P91" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q91">
         <v>3.3</v>
@@ -19694,7 +19706,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ91">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR91">
         <v>1.53</v>
@@ -19897,7 +19909,7 @@
         <v>1.38</v>
       </c>
       <c r="AP92">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ92">
         <v>1.55</v>
@@ -20103,7 +20115,7 @@
         <v>1.25</v>
       </c>
       <c r="AP93">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ93">
         <v>1.09</v>
@@ -20231,7 +20243,7 @@
         <v>149</v>
       </c>
       <c r="P94" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q94">
         <v>3.8</v>
@@ -20518,7 +20530,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ95">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR95">
         <v>1.63</v>
@@ -20643,7 +20655,7 @@
         <v>82</v>
       </c>
       <c r="P96" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q96">
         <v>4.1</v>
@@ -20721,7 +20733,7 @@
         <v>1.33</v>
       </c>
       <c r="AP96">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ96">
         <v>1.36</v>
@@ -20927,7 +20939,7 @@
         <v>1.22</v>
       </c>
       <c r="AP97">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ97">
         <v>1.09</v>
@@ -21136,7 +21148,7 @@
         <v>1</v>
       </c>
       <c r="AQ98">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR98">
         <v>1.43</v>
@@ -21261,7 +21273,7 @@
         <v>152</v>
       </c>
       <c r="P99" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q99">
         <v>4.85</v>
@@ -21548,7 +21560,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ100">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR100">
         <v>1.64</v>
@@ -21754,7 +21766,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ101">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR101">
         <v>1.4</v>
@@ -21957,10 +21969,10 @@
         <v>1</v>
       </c>
       <c r="AP102">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ102">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR102">
         <v>1.73</v>
@@ -22085,7 +22097,7 @@
         <v>82</v>
       </c>
       <c r="P103" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q103">
         <v>3.3</v>
@@ -22291,7 +22303,7 @@
         <v>155</v>
       </c>
       <c r="P104" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -22497,7 +22509,7 @@
         <v>156</v>
       </c>
       <c r="P105" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q105">
         <v>1.64</v>
@@ -22575,7 +22587,7 @@
         <v>0.22</v>
       </c>
       <c r="AP105">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ105">
         <v>0.2</v>
@@ -22703,7 +22715,7 @@
         <v>157</v>
       </c>
       <c r="P106" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q106">
         <v>3.55</v>
@@ -22909,7 +22921,7 @@
         <v>82</v>
       </c>
       <c r="P107" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q107">
         <v>2.89</v>
@@ -23115,7 +23127,7 @@
         <v>158</v>
       </c>
       <c r="P108" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q108">
         <v>3.5</v>
@@ -23193,10 +23205,10 @@
         <v>1.36</v>
       </c>
       <c r="AP108">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ108">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR108">
         <v>1.49</v>
@@ -23321,7 +23333,7 @@
         <v>159</v>
       </c>
       <c r="P109" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q109">
         <v>3.4</v>
@@ -23402,7 +23414,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ109">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR109">
         <v>1.65</v>
@@ -23605,7 +23617,7 @@
         <v>1.91</v>
       </c>
       <c r="AP110">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ110">
         <v>1.75</v>
@@ -23684,6 +23696,1036 @@
       </c>
       <c r="BP110">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="111" spans="1:68">
+      <c r="A111" s="1">
+        <v>110</v>
+      </c>
+      <c r="B111">
+        <v>7775725</v>
+      </c>
+      <c r="C111" t="s">
+        <v>68</v>
+      </c>
+      <c r="D111" t="s">
+        <v>69</v>
+      </c>
+      <c r="E111" s="2">
+        <v>45835.65625</v>
+      </c>
+      <c r="F111">
+        <v>0</v>
+      </c>
+      <c r="G111" t="s">
+        <v>74</v>
+      </c>
+      <c r="H111" t="s">
+        <v>73</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="J111">
+        <v>1</v>
+      </c>
+      <c r="K111">
+        <v>1</v>
+      </c>
+      <c r="L111">
+        <v>1</v>
+      </c>
+      <c r="M111">
+        <v>1</v>
+      </c>
+      <c r="N111">
+        <v>2</v>
+      </c>
+      <c r="O111" t="s">
+        <v>161</v>
+      </c>
+      <c r="P111" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q111">
+        <v>1.86</v>
+      </c>
+      <c r="R111">
+        <v>2.71</v>
+      </c>
+      <c r="S111">
+        <v>5.3</v>
+      </c>
+      <c r="T111">
+        <v>1.25</v>
+      </c>
+      <c r="U111">
+        <v>3.5</v>
+      </c>
+      <c r="V111">
+        <v>2.35</v>
+      </c>
+      <c r="W111">
+        <v>1.6</v>
+      </c>
+      <c r="X111">
+        <v>4.9</v>
+      </c>
+      <c r="Y111">
+        <v>1.13</v>
+      </c>
+      <c r="Z111">
+        <v>1.33</v>
+      </c>
+      <c r="AA111">
+        <v>4.93</v>
+      </c>
+      <c r="AB111">
+        <v>8</v>
+      </c>
+      <c r="AC111">
+        <v>1.02</v>
+      </c>
+      <c r="AD111">
+        <v>12</v>
+      </c>
+      <c r="AE111">
+        <v>1.17</v>
+      </c>
+      <c r="AF111">
+        <v>4.72</v>
+      </c>
+      <c r="AG111">
+        <v>1.64</v>
+      </c>
+      <c r="AH111">
+        <v>2.32</v>
+      </c>
+      <c r="AI111">
+        <v>1.8</v>
+      </c>
+      <c r="AJ111">
+        <v>1.85</v>
+      </c>
+      <c r="AK111">
+        <v>1.13</v>
+      </c>
+      <c r="AL111">
+        <v>1.14</v>
+      </c>
+      <c r="AM111">
+        <v>3.3</v>
+      </c>
+      <c r="AN111">
+        <v>2.1</v>
+      </c>
+      <c r="AO111">
+        <v>0.7</v>
+      </c>
+      <c r="AP111">
+        <v>2</v>
+      </c>
+      <c r="AQ111">
+        <v>0.73</v>
+      </c>
+      <c r="AR111">
+        <v>1.93</v>
+      </c>
+      <c r="AS111">
+        <v>1.35</v>
+      </c>
+      <c r="AT111">
+        <v>3.28</v>
+      </c>
+      <c r="AU111">
+        <v>11</v>
+      </c>
+      <c r="AV111">
+        <v>5</v>
+      </c>
+      <c r="AW111">
+        <v>12</v>
+      </c>
+      <c r="AX111">
+        <v>2</v>
+      </c>
+      <c r="AY111">
+        <v>23</v>
+      </c>
+      <c r="AZ111">
+        <v>7</v>
+      </c>
+      <c r="BA111">
+        <v>10</v>
+      </c>
+      <c r="BB111">
+        <v>2</v>
+      </c>
+      <c r="BC111">
+        <v>12</v>
+      </c>
+      <c r="BD111">
+        <v>1.22</v>
+      </c>
+      <c r="BE111">
+        <v>9</v>
+      </c>
+      <c r="BF111">
+        <v>4.33</v>
+      </c>
+      <c r="BG111">
+        <v>1.18</v>
+      </c>
+      <c r="BH111">
+        <v>3.8</v>
+      </c>
+      <c r="BI111">
+        <v>1.4</v>
+      </c>
+      <c r="BJ111">
+        <v>2.7</v>
+      </c>
+      <c r="BK111">
+        <v>1.65</v>
+      </c>
+      <c r="BL111">
+        <v>2.1</v>
+      </c>
+      <c r="BM111">
+        <v>2</v>
+      </c>
+      <c r="BN111">
+        <v>1.8</v>
+      </c>
+      <c r="BO111">
+        <v>2.5</v>
+      </c>
+      <c r="BP111">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="112" spans="1:68">
+      <c r="A112" s="1">
+        <v>111</v>
+      </c>
+      <c r="B112">
+        <v>7775726</v>
+      </c>
+      <c r="C112" t="s">
+        <v>68</v>
+      </c>
+      <c r="D112" t="s">
+        <v>69</v>
+      </c>
+      <c r="E112" s="2">
+        <v>45835.65625</v>
+      </c>
+      <c r="F112">
+        <v>0</v>
+      </c>
+      <c r="G112" t="s">
+        <v>70</v>
+      </c>
+      <c r="H112" t="s">
+        <v>72</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>0</v>
+      </c>
+      <c r="K112">
+        <v>0</v>
+      </c>
+      <c r="L112">
+        <v>0</v>
+      </c>
+      <c r="M112">
+        <v>0</v>
+      </c>
+      <c r="N112">
+        <v>0</v>
+      </c>
+      <c r="O112" t="s">
+        <v>82</v>
+      </c>
+      <c r="P112" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q112">
+        <v>4.57</v>
+      </c>
+      <c r="R112">
+        <v>2.26</v>
+      </c>
+      <c r="S112">
+        <v>2.61</v>
+      </c>
+      <c r="T112">
+        <v>1.37</v>
+      </c>
+      <c r="U112">
+        <v>2.98</v>
+      </c>
+      <c r="V112">
+        <v>3.02</v>
+      </c>
+      <c r="W112">
+        <v>1.4</v>
+      </c>
+      <c r="X112">
+        <v>6.5</v>
+      </c>
+      <c r="Y112">
+        <v>1.07</v>
+      </c>
+      <c r="Z112">
+        <v>3.8</v>
+      </c>
+      <c r="AA112">
+        <v>3.35</v>
+      </c>
+      <c r="AB112">
+        <v>1.9</v>
+      </c>
+      <c r="AC112">
+        <v>1.02</v>
+      </c>
+      <c r="AD112">
+        <v>9.5</v>
+      </c>
+      <c r="AE112">
+        <v>1.32</v>
+      </c>
+      <c r="AF112">
+        <v>3.47</v>
+      </c>
+      <c r="AG112">
+        <v>2.04</v>
+      </c>
+      <c r="AH112">
+        <v>1.84</v>
+      </c>
+      <c r="AI112">
+        <v>1.87</v>
+      </c>
+      <c r="AJ112">
+        <v>1.87</v>
+      </c>
+      <c r="AK112">
+        <v>1.27</v>
+      </c>
+      <c r="AL112">
+        <v>1.25</v>
+      </c>
+      <c r="AM112">
+        <v>1.18</v>
+      </c>
+      <c r="AN112">
+        <v>1.09</v>
+      </c>
+      <c r="AO112">
+        <v>0.91</v>
+      </c>
+      <c r="AP112">
+        <v>1.08</v>
+      </c>
+      <c r="AQ112">
+        <v>0.92</v>
+      </c>
+      <c r="AR112">
+        <v>1.53</v>
+      </c>
+      <c r="AS112">
+        <v>1.69</v>
+      </c>
+      <c r="AT112">
+        <v>3.22</v>
+      </c>
+      <c r="AU112">
+        <v>4</v>
+      </c>
+      <c r="AV112">
+        <v>3</v>
+      </c>
+      <c r="AW112">
+        <v>6</v>
+      </c>
+      <c r="AX112">
+        <v>5</v>
+      </c>
+      <c r="AY112">
+        <v>10</v>
+      </c>
+      <c r="AZ112">
+        <v>8</v>
+      </c>
+      <c r="BA112">
+        <v>5</v>
+      </c>
+      <c r="BB112">
+        <v>8</v>
+      </c>
+      <c r="BC112">
+        <v>13</v>
+      </c>
+      <c r="BD112">
+        <v>2.2</v>
+      </c>
+      <c r="BE112">
+        <v>6.8</v>
+      </c>
+      <c r="BF112">
+        <v>1.8</v>
+      </c>
+      <c r="BG112">
+        <v>1.23</v>
+      </c>
+      <c r="BH112">
+        <v>3.55</v>
+      </c>
+      <c r="BI112">
+        <v>1.38</v>
+      </c>
+      <c r="BJ112">
+        <v>2.6</v>
+      </c>
+      <c r="BK112">
+        <v>1.96</v>
+      </c>
+      <c r="BL112">
+        <v>2.07</v>
+      </c>
+      <c r="BM112">
+        <v>2.1</v>
+      </c>
+      <c r="BN112">
+        <v>1.65</v>
+      </c>
+      <c r="BO112">
+        <v>2.72</v>
+      </c>
+      <c r="BP112">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:68">
+      <c r="A113" s="1">
+        <v>112</v>
+      </c>
+      <c r="B113">
+        <v>7775727</v>
+      </c>
+      <c r="C113" t="s">
+        <v>68</v>
+      </c>
+      <c r="D113" t="s">
+        <v>69</v>
+      </c>
+      <c r="E113" s="2">
+        <v>45835.65625</v>
+      </c>
+      <c r="F113">
+        <v>0</v>
+      </c>
+      <c r="G113" t="s">
+        <v>75</v>
+      </c>
+      <c r="H113" t="s">
+        <v>76</v>
+      </c>
+      <c r="I113">
+        <v>2</v>
+      </c>
+      <c r="J113">
+        <v>0</v>
+      </c>
+      <c r="K113">
+        <v>2</v>
+      </c>
+      <c r="L113">
+        <v>3</v>
+      </c>
+      <c r="M113">
+        <v>0</v>
+      </c>
+      <c r="N113">
+        <v>3</v>
+      </c>
+      <c r="O113" t="s">
+        <v>162</v>
+      </c>
+      <c r="P113" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q113">
+        <v>2.52</v>
+      </c>
+      <c r="R113">
+        <v>2.02</v>
+      </c>
+      <c r="S113">
+        <v>6.43</v>
+      </c>
+      <c r="T113">
+        <v>1.55</v>
+      </c>
+      <c r="U113">
+        <v>2.38</v>
+      </c>
+      <c r="V113">
+        <v>3.55</v>
+      </c>
+      <c r="W113">
+        <v>1.25</v>
+      </c>
+      <c r="X113">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y113">
+        <v>1.04</v>
+      </c>
+      <c r="Z113">
+        <v>1.6</v>
+      </c>
+      <c r="AA113">
+        <v>3.1</v>
+      </c>
+      <c r="AB113">
+        <v>5.73</v>
+      </c>
+      <c r="AC113">
+        <v>1.06</v>
+      </c>
+      <c r="AD113">
+        <v>7</v>
+      </c>
+      <c r="AE113">
+        <v>1.49</v>
+      </c>
+      <c r="AF113">
+        <v>2.47</v>
+      </c>
+      <c r="AG113">
+        <v>2.5</v>
+      </c>
+      <c r="AH113">
+        <v>1.5</v>
+      </c>
+      <c r="AI113">
+        <v>2.25</v>
+      </c>
+      <c r="AJ113">
+        <v>1.55</v>
+      </c>
+      <c r="AK113">
+        <v>1.23</v>
+      </c>
+      <c r="AL113">
+        <v>1.25</v>
+      </c>
+      <c r="AM113">
+        <v>2.2</v>
+      </c>
+      <c r="AN113">
+        <v>1.7</v>
+      </c>
+      <c r="AO113">
+        <v>1.33</v>
+      </c>
+      <c r="AP113">
+        <v>1.82</v>
+      </c>
+      <c r="AQ113">
+        <v>1.23</v>
+      </c>
+      <c r="AR113">
+        <v>1.74</v>
+      </c>
+      <c r="AS113">
+        <v>1.33</v>
+      </c>
+      <c r="AT113">
+        <v>3.07</v>
+      </c>
+      <c r="AU113">
+        <v>8</v>
+      </c>
+      <c r="AV113">
+        <v>2</v>
+      </c>
+      <c r="AW113">
+        <v>7</v>
+      </c>
+      <c r="AX113">
+        <v>3</v>
+      </c>
+      <c r="AY113">
+        <v>15</v>
+      </c>
+      <c r="AZ113">
+        <v>5</v>
+      </c>
+      <c r="BA113">
+        <v>5</v>
+      </c>
+      <c r="BB113">
+        <v>1</v>
+      </c>
+      <c r="BC113">
+        <v>6</v>
+      </c>
+      <c r="BD113">
+        <v>1.36</v>
+      </c>
+      <c r="BE113">
+        <v>7</v>
+      </c>
+      <c r="BF113">
+        <v>4</v>
+      </c>
+      <c r="BG113">
+        <v>1.33</v>
+      </c>
+      <c r="BH113">
+        <v>2.83</v>
+      </c>
+      <c r="BI113">
+        <v>1.68</v>
+      </c>
+      <c r="BJ113">
+        <v>2.02</v>
+      </c>
+      <c r="BK113">
+        <v>2.08</v>
+      </c>
+      <c r="BL113">
+        <v>1.63</v>
+      </c>
+      <c r="BM113">
+        <v>2.65</v>
+      </c>
+      <c r="BN113">
+        <v>1.4</v>
+      </c>
+      <c r="BO113">
+        <v>3.82</v>
+      </c>
+      <c r="BP113">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="114" spans="1:68">
+      <c r="A114" s="1">
+        <v>113</v>
+      </c>
+      <c r="B114">
+        <v>7775728</v>
+      </c>
+      <c r="C114" t="s">
+        <v>68</v>
+      </c>
+      <c r="D114" t="s">
+        <v>69</v>
+      </c>
+      <c r="E114" s="2">
+        <v>45835.65625</v>
+      </c>
+      <c r="F114">
+        <v>0</v>
+      </c>
+      <c r="G114" t="s">
+        <v>77</v>
+      </c>
+      <c r="H114" t="s">
+        <v>71</v>
+      </c>
+      <c r="I114">
+        <v>0</v>
+      </c>
+      <c r="J114">
+        <v>1</v>
+      </c>
+      <c r="K114">
+        <v>1</v>
+      </c>
+      <c r="L114">
+        <v>1</v>
+      </c>
+      <c r="M114">
+        <v>1</v>
+      </c>
+      <c r="N114">
+        <v>2</v>
+      </c>
+      <c r="O114" t="s">
+        <v>163</v>
+      </c>
+      <c r="P114" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q114">
+        <v>3.82</v>
+      </c>
+      <c r="R114">
+        <v>1.93</v>
+      </c>
+      <c r="S114">
+        <v>3.15</v>
+      </c>
+      <c r="T114">
+        <v>1.51</v>
+      </c>
+      <c r="U114">
+        <v>2.62</v>
+      </c>
+      <c r="V114">
+        <v>3.28</v>
+      </c>
+      <c r="W114">
+        <v>1.3</v>
+      </c>
+      <c r="X114">
+        <v>7.5</v>
+      </c>
+      <c r="Y114">
+        <v>1.05</v>
+      </c>
+      <c r="Z114">
+        <v>2.83</v>
+      </c>
+      <c r="AA114">
+        <v>2.9</v>
+      </c>
+      <c r="AB114">
+        <v>2.55</v>
+      </c>
+      <c r="AC114">
+        <v>1.06</v>
+      </c>
+      <c r="AD114">
+        <v>7</v>
+      </c>
+      <c r="AE114">
+        <v>1.45</v>
+      </c>
+      <c r="AF114">
+        <v>2.7</v>
+      </c>
+      <c r="AG114">
+        <v>2.38</v>
+      </c>
+      <c r="AH114">
+        <v>1.62</v>
+      </c>
+      <c r="AI114">
+        <v>1.83</v>
+      </c>
+      <c r="AJ114">
+        <v>1.85</v>
+      </c>
+      <c r="AK114">
+        <v>1.35</v>
+      </c>
+      <c r="AL114">
+        <v>1.3</v>
+      </c>
+      <c r="AM114">
+        <v>1.37</v>
+      </c>
+      <c r="AN114">
+        <v>1.6</v>
+      </c>
+      <c r="AO114">
+        <v>1.36</v>
+      </c>
+      <c r="AP114">
+        <v>1.55</v>
+      </c>
+      <c r="AQ114">
+        <v>1.33</v>
+      </c>
+      <c r="AR114">
+        <v>1.75</v>
+      </c>
+      <c r="AS114">
+        <v>1.46</v>
+      </c>
+      <c r="AT114">
+        <v>3.21</v>
+      </c>
+      <c r="AU114">
+        <v>5</v>
+      </c>
+      <c r="AV114">
+        <v>6</v>
+      </c>
+      <c r="AW114">
+        <v>6</v>
+      </c>
+      <c r="AX114">
+        <v>7</v>
+      </c>
+      <c r="AY114">
+        <v>11</v>
+      </c>
+      <c r="AZ114">
+        <v>13</v>
+      </c>
+      <c r="BA114">
+        <v>6</v>
+      </c>
+      <c r="BB114">
+        <v>8</v>
+      </c>
+      <c r="BC114">
+        <v>14</v>
+      </c>
+      <c r="BD114">
+        <v>2.21</v>
+      </c>
+      <c r="BE114">
+        <v>6.35</v>
+      </c>
+      <c r="BF114">
+        <v>2</v>
+      </c>
+      <c r="BG114">
+        <v>1.34</v>
+      </c>
+      <c r="BH114">
+        <v>2.9</v>
+      </c>
+      <c r="BI114">
+        <v>1.56</v>
+      </c>
+      <c r="BJ114">
+        <v>2.21</v>
+      </c>
+      <c r="BK114">
+        <v>2.08</v>
+      </c>
+      <c r="BL114">
+        <v>1.73</v>
+      </c>
+      <c r="BM114">
+        <v>2.6</v>
+      </c>
+      <c r="BN114">
+        <v>1.44</v>
+      </c>
+      <c r="BO114">
+        <v>3.4</v>
+      </c>
+      <c r="BP114">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="115" spans="1:68">
+      <c r="A115" s="1">
+        <v>114</v>
+      </c>
+      <c r="B115">
+        <v>7775729</v>
+      </c>
+      <c r="C115" t="s">
+        <v>68</v>
+      </c>
+      <c r="D115" t="s">
+        <v>69</v>
+      </c>
+      <c r="E115" s="2">
+        <v>45835.66666666666</v>
+      </c>
+      <c r="F115">
+        <v>0</v>
+      </c>
+      <c r="G115" t="s">
+        <v>79</v>
+      </c>
+      <c r="H115" t="s">
+        <v>78</v>
+      </c>
+      <c r="I115">
+        <v>0</v>
+      </c>
+      <c r="J115">
+        <v>0</v>
+      </c>
+      <c r="K115">
+        <v>0</v>
+      </c>
+      <c r="L115">
+        <v>1</v>
+      </c>
+      <c r="M115">
+        <v>0</v>
+      </c>
+      <c r="N115">
+        <v>1</v>
+      </c>
+      <c r="O115" t="s">
+        <v>128</v>
+      </c>
+      <c r="P115" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q115">
+        <v>1.81</v>
+      </c>
+      <c r="R115">
+        <v>2.35</v>
+      </c>
+      <c r="S115">
+        <v>5.9</v>
+      </c>
+      <c r="T115">
+        <v>1.3</v>
+      </c>
+      <c r="U115">
+        <v>3.2</v>
+      </c>
+      <c r="V115">
+        <v>2.47</v>
+      </c>
+      <c r="W115">
+        <v>1.54</v>
+      </c>
+      <c r="X115">
+        <v>5.6</v>
+      </c>
+      <c r="Y115">
+        <v>1.11</v>
+      </c>
+      <c r="Z115">
+        <v>1.33</v>
+      </c>
+      <c r="AA115">
+        <v>5</v>
+      </c>
+      <c r="AB115">
+        <v>7.2</v>
+      </c>
+      <c r="AC115">
+        <v>1.03</v>
+      </c>
+      <c r="AD115">
+        <v>12</v>
+      </c>
+      <c r="AE115">
+        <v>1.23</v>
+      </c>
+      <c r="AF115">
+        <v>4.34</v>
+      </c>
+      <c r="AG115">
+        <v>1.7</v>
+      </c>
+      <c r="AH115">
+        <v>2.21</v>
+      </c>
+      <c r="AI115">
+        <v>2.01</v>
+      </c>
+      <c r="AJ115">
+        <v>1.68</v>
+      </c>
+      <c r="AK115">
+        <v>1.12</v>
+      </c>
+      <c r="AL115">
+        <v>1.14</v>
+      </c>
+      <c r="AM115">
+        <v>3.04</v>
+      </c>
+      <c r="AN115">
+        <v>2.18</v>
+      </c>
+      <c r="AO115">
+        <v>1.3</v>
+      </c>
+      <c r="AP115">
+        <v>2.25</v>
+      </c>
+      <c r="AQ115">
+        <v>1.18</v>
+      </c>
+      <c r="AR115">
+        <v>1.95</v>
+      </c>
+      <c r="AS115">
+        <v>1.16</v>
+      </c>
+      <c r="AT115">
+        <v>3.11</v>
+      </c>
+      <c r="AU115">
+        <v>8</v>
+      </c>
+      <c r="AV115">
+        <v>5</v>
+      </c>
+      <c r="AW115">
+        <v>12</v>
+      </c>
+      <c r="AX115">
+        <v>1</v>
+      </c>
+      <c r="AY115">
+        <v>20</v>
+      </c>
+      <c r="AZ115">
+        <v>6</v>
+      </c>
+      <c r="BA115">
+        <v>4</v>
+      </c>
+      <c r="BB115">
+        <v>0</v>
+      </c>
+      <c r="BC115">
+        <v>4</v>
+      </c>
+      <c r="BD115">
+        <v>1.29</v>
+      </c>
+      <c r="BE115">
+        <v>9</v>
+      </c>
+      <c r="BF115">
+        <v>4.75</v>
+      </c>
+      <c r="BG115">
+        <v>1.19</v>
+      </c>
+      <c r="BH115">
+        <v>3.9</v>
+      </c>
+      <c r="BI115">
+        <v>1.44</v>
+      </c>
+      <c r="BJ115">
+        <v>2.6</v>
+      </c>
+      <c r="BK115">
+        <v>1.66</v>
+      </c>
+      <c r="BL115">
+        <v>2</v>
+      </c>
+      <c r="BM115">
+        <v>2.15</v>
+      </c>
+      <c r="BN115">
+        <v>1.6</v>
+      </c>
+      <c r="BO115">
+        <v>2.87</v>
+      </c>
+      <c r="BP115">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
@@ -23838,22 +23838,22 @@
         <v>3.28</v>
       </c>
       <c r="AU111">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV111">
         <v>5</v>
       </c>
       <c r="AW111">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AX111">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY111">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AZ111">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA111">
         <v>10</v>
@@ -24047,28 +24047,28 @@
         <v>4</v>
       </c>
       <c r="AV112">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW112">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX112">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AY112">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ112">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BA112">
         <v>5</v>
       </c>
       <c r="BB112">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC112">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD112">
         <v>2.2</v>
@@ -24250,22 +24250,22 @@
         <v>3.07</v>
       </c>
       <c r="AU113">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AV113">
         <v>2</v>
       </c>
       <c r="AW113">
+        <v>12</v>
+      </c>
+      <c r="AX113">
+        <v>5</v>
+      </c>
+      <c r="AY113">
+        <v>18</v>
+      </c>
+      <c r="AZ113">
         <v>7</v>
-      </c>
-      <c r="AX113">
-        <v>3</v>
-      </c>
-      <c r="AY113">
-        <v>15</v>
-      </c>
-      <c r="AZ113">
-        <v>5</v>
       </c>
       <c r="BA113">
         <v>5</v>
@@ -24459,19 +24459,19 @@
         <v>5</v>
       </c>
       <c r="AV114">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW114">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AX114">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AY114">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AZ114">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="BA114">
         <v>6</v>
@@ -24662,22 +24662,22 @@
         <v>3.11</v>
       </c>
       <c r="AU115">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV115">
         <v>5</v>
       </c>
       <c r="AW115">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AX115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY115">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AZ115">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA115">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
@@ -23838,22 +23838,22 @@
         <v>3.28</v>
       </c>
       <c r="AU111">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV111">
         <v>5</v>
       </c>
       <c r="AW111">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AX111">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY111">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AZ111">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA111">
         <v>10</v>
@@ -24044,22 +24044,22 @@
         <v>3.22</v>
       </c>
       <c r="AU112">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV112">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW112">
+        <v>6</v>
+      </c>
+      <c r="AX112">
+        <v>5</v>
+      </c>
+      <c r="AY112">
+        <v>11</v>
+      </c>
+      <c r="AZ112">
         <v>8</v>
-      </c>
-      <c r="AX112">
-        <v>9</v>
-      </c>
-      <c r="AY112">
-        <v>12</v>
-      </c>
-      <c r="AZ112">
-        <v>11</v>
       </c>
       <c r="BA112">
         <v>5</v>
@@ -24250,22 +24250,22 @@
         <v>3.07</v>
       </c>
       <c r="AU113">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AV113">
         <v>2</v>
       </c>
       <c r="AW113">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AX113">
+        <v>3</v>
+      </c>
+      <c r="AY113">
+        <v>15</v>
+      </c>
+      <c r="AZ113">
         <v>5</v>
-      </c>
-      <c r="AY113">
-        <v>18</v>
-      </c>
-      <c r="AZ113">
-        <v>7</v>
       </c>
       <c r="BA113">
         <v>5</v>
@@ -24459,19 +24459,19 @@
         <v>5</v>
       </c>
       <c r="AV114">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW114">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AX114">
+        <v>7</v>
+      </c>
+      <c r="AY114">
+        <v>11</v>
+      </c>
+      <c r="AZ114">
         <v>13</v>
-      </c>
-      <c r="AY114">
-        <v>15</v>
-      </c>
-      <c r="AZ114">
-        <v>18</v>
       </c>
       <c r="BA114">
         <v>6</v>
@@ -24662,22 +24662,22 @@
         <v>3.11</v>
       </c>
       <c r="AU115">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV115">
         <v>5</v>
       </c>
       <c r="AW115">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AX115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY115">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AZ115">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA115">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
@@ -23838,22 +23838,22 @@
         <v>3.28</v>
       </c>
       <c r="AU111">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV111">
         <v>5</v>
       </c>
       <c r="AW111">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AX111">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY111">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AZ111">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA111">
         <v>10</v>
@@ -24044,22 +24044,22 @@
         <v>3.22</v>
       </c>
       <c r="AU112">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV112">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW112">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX112">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AY112">
+        <v>12</v>
+      </c>
+      <c r="AZ112">
         <v>11</v>
-      </c>
-      <c r="AZ112">
-        <v>8</v>
       </c>
       <c r="BA112">
         <v>5</v>
@@ -24250,22 +24250,22 @@
         <v>3.07</v>
       </c>
       <c r="AU113">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AV113">
         <v>2</v>
       </c>
       <c r="AW113">
+        <v>12</v>
+      </c>
+      <c r="AX113">
+        <v>5</v>
+      </c>
+      <c r="AY113">
+        <v>18</v>
+      </c>
+      <c r="AZ113">
         <v>7</v>
-      </c>
-      <c r="AX113">
-        <v>3</v>
-      </c>
-      <c r="AY113">
-        <v>15</v>
-      </c>
-      <c r="AZ113">
-        <v>5</v>
       </c>
       <c r="BA113">
         <v>5</v>
@@ -24459,19 +24459,19 @@
         <v>5</v>
       </c>
       <c r="AV114">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW114">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AX114">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AY114">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AZ114">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="BA114">
         <v>6</v>
@@ -24662,22 +24662,22 @@
         <v>3.11</v>
       </c>
       <c r="AU115">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV115">
         <v>5</v>
       </c>
       <c r="AW115">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AX115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY115">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AZ115">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA115">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="224">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -508,6 +508,15 @@
     <t>['84']</t>
   </si>
   <si>
+    <t>['2', '6', '83']</t>
+  </si>
+  <si>
+    <t>['50']</t>
+  </si>
+  <si>
+    <t>['24', '5', '41', '36', '52', '57', '73']</t>
+  </si>
+  <si>
     <t>['45+1', '81']</t>
   </si>
   <si>
@@ -551,9 +560,6 @@
   </si>
   <si>
     <t>['41', '70']</t>
-  </si>
-  <si>
-    <t>['50']</t>
   </si>
   <si>
     <t>['88', '90']</t>
@@ -674,6 +680,12 @@
   </si>
   <si>
     <t>['28']</t>
+  </si>
+  <si>
+    <t>['42']</t>
+  </si>
+  <si>
+    <t>['49', '79']</t>
   </si>
 </sst>
 </file>
@@ -1035,7 +1047,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP115"/>
+  <dimension ref="A1:BP119"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1291,7 +1303,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="Q2">
         <v>4.4</v>
@@ -1372,7 +1384,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ2">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1575,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ3">
         <v>1.55</v>
@@ -1781,7 +1793,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ4">
         <v>1.23</v>
@@ -1909,7 +1921,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -1990,7 +2002,7 @@
         <v>1</v>
       </c>
       <c r="AQ5">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2399,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ7">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2605,7 +2617,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ8">
         <v>0.73</v>
@@ -2733,7 +2745,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3145,7 +3157,7 @@
         <v>88</v>
       </c>
       <c r="P11" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="Q11">
         <v>1.94</v>
@@ -3223,7 +3235,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ11">
         <v>0.73</v>
@@ -3351,7 +3363,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Q12">
         <v>3.95</v>
@@ -3429,7 +3441,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ12">
         <v>1.75</v>
@@ -3557,7 +3569,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q13">
         <v>4.5</v>
@@ -3635,10 +3647,10 @@
         <v>1</v>
       </c>
       <c r="AP13">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ13">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR13">
         <v>1.54</v>
@@ -3763,7 +3775,7 @@
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q14">
         <v>3.9</v>
@@ -3844,7 +3856,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ14">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR14">
         <v>1.46</v>
@@ -3969,7 +3981,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q15">
         <v>2.06</v>
@@ -4047,10 +4059,10 @@
         <v>3</v>
       </c>
       <c r="AP15">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ15">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR15">
         <v>1.43</v>
@@ -4175,7 +4187,7 @@
         <v>82</v>
       </c>
       <c r="P16" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4381,7 +4393,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q17">
         <v>3.1</v>
@@ -4587,7 +4599,7 @@
         <v>94</v>
       </c>
       <c r="P18" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q18">
         <v>4.2</v>
@@ -4871,7 +4883,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ19">
         <v>1.55</v>
@@ -4999,7 +5011,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q20">
         <v>2.65</v>
@@ -5080,7 +5092,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ20">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR20">
         <v>0.9</v>
@@ -5205,7 +5217,7 @@
         <v>82</v>
       </c>
       <c r="P21" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5286,7 +5298,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ21">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR21">
         <v>1.81</v>
@@ -5695,7 +5707,7 @@
         <v>2</v>
       </c>
       <c r="AP23">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ23">
         <v>1.23</v>
@@ -6029,7 +6041,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q25">
         <v>2.7</v>
@@ -6107,10 +6119,10 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ25">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR25">
         <v>1.72</v>
@@ -6235,7 +6247,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q26">
         <v>4.75</v>
@@ -6313,7 +6325,7 @@
         <v>0.33</v>
       </c>
       <c r="AP26">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ26">
         <v>1.75</v>
@@ -6522,7 +6534,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ27">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR27">
         <v>1.49</v>
@@ -6647,7 +6659,7 @@
         <v>101</v>
       </c>
       <c r="P28" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="Q28">
         <v>2.3</v>
@@ -6725,10 +6737,10 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ28">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR28">
         <v>1.81</v>
@@ -6931,10 +6943,10 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ29">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR29">
         <v>1.92</v>
@@ -7265,7 +7277,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q31">
         <v>4.75</v>
@@ -7471,7 +7483,7 @@
         <v>82</v>
       </c>
       <c r="P32" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q32">
         <v>3</v>
@@ -7552,7 +7564,7 @@
         <v>2</v>
       </c>
       <c r="AQ32">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR32">
         <v>1.2</v>
@@ -7883,7 +7895,7 @@
         <v>104</v>
       </c>
       <c r="P34" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q34">
         <v>4.33</v>
@@ -8373,7 +8385,7 @@
         <v>2.33</v>
       </c>
       <c r="AP36">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ36">
         <v>1.33</v>
@@ -8501,7 +8513,7 @@
         <v>105</v>
       </c>
       <c r="P37" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q37">
         <v>2.38</v>
@@ -8785,10 +8797,10 @@
         <v>0.5</v>
       </c>
       <c r="AP38">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ38">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR38">
         <v>1.99</v>
@@ -8991,10 +9003,10 @@
         <v>2</v>
       </c>
       <c r="AP39">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ39">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR39">
         <v>1.46</v>
@@ -9325,7 +9337,7 @@
         <v>82</v>
       </c>
       <c r="P41" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q41">
         <v>5.2</v>
@@ -9609,10 +9621,10 @@
         <v>0.75</v>
       </c>
       <c r="AP42">
+        <v>1.46</v>
+      </c>
+      <c r="AQ42">
         <v>1.33</v>
-      </c>
-      <c r="AQ42">
-        <v>1.36</v>
       </c>
       <c r="AR42">
         <v>1.9</v>
@@ -9737,7 +9749,7 @@
         <v>109</v>
       </c>
       <c r="P43" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q43">
         <v>2.38</v>
@@ -9815,7 +9827,7 @@
         <v>2</v>
       </c>
       <c r="AP43">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ43">
         <v>1.23</v>
@@ -10024,7 +10036,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ44">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR44">
         <v>1.38</v>
@@ -10149,7 +10161,7 @@
         <v>111</v>
       </c>
       <c r="P45" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q45">
         <v>4.04</v>
@@ -10230,7 +10242,7 @@
         <v>1</v>
       </c>
       <c r="AQ45">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR45">
         <v>1.63</v>
@@ -10355,7 +10367,7 @@
         <v>112</v>
       </c>
       <c r="P46" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q46">
         <v>1.7</v>
@@ -10436,7 +10448,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ46">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR46">
         <v>1.69</v>
@@ -10642,7 +10654,7 @@
         <v>2</v>
       </c>
       <c r="AQ47">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR47">
         <v>1.97</v>
@@ -10767,7 +10779,7 @@
         <v>114</v>
       </c>
       <c r="P48" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q48">
         <v>3.88</v>
@@ -10845,7 +10857,7 @@
         <v>2</v>
       </c>
       <c r="AP48">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ48">
         <v>1.33</v>
@@ -10973,7 +10985,7 @@
         <v>115</v>
       </c>
       <c r="P49" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q49">
         <v>3.55</v>
@@ -11179,7 +11191,7 @@
         <v>116</v>
       </c>
       <c r="P50" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q50">
         <v>3.7</v>
@@ -11257,7 +11269,7 @@
         <v>1.4</v>
       </c>
       <c r="AP50">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ50">
         <v>1.75</v>
@@ -11385,7 +11397,7 @@
         <v>82</v>
       </c>
       <c r="P51" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q51">
         <v>2.6</v>
@@ -11591,7 +11603,7 @@
         <v>117</v>
       </c>
       <c r="P52" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q52">
         <v>2.24</v>
@@ -11672,7 +11684,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ52">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR52">
         <v>1.89</v>
@@ -11875,7 +11887,7 @@
         <v>1.5</v>
       </c>
       <c r="AP53">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ53">
         <v>0.92</v>
@@ -12084,7 +12096,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ54">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR54">
         <v>1.59</v>
@@ -12209,7 +12221,7 @@
         <v>119</v>
       </c>
       <c r="P55" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q55">
         <v>2.6</v>
@@ -12287,10 +12299,10 @@
         <v>1.8</v>
       </c>
       <c r="AP55">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ55">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR55">
         <v>1.84</v>
@@ -12493,7 +12505,7 @@
         <v>0.8</v>
       </c>
       <c r="AP56">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ56">
         <v>0.73</v>
@@ -12621,7 +12633,7 @@
         <v>121</v>
       </c>
       <c r="P57" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -13033,7 +13045,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q59">
         <v>4.75</v>
@@ -13239,7 +13251,7 @@
         <v>124</v>
       </c>
       <c r="P60" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q60">
         <v>2.61</v>
@@ -13445,7 +13457,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q61">
         <v>3.05</v>
@@ -13526,7 +13538,7 @@
         <v>1</v>
       </c>
       <c r="AQ61">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR61">
         <v>1.58</v>
@@ -13729,10 +13741,10 @@
         <v>1.67</v>
       </c>
       <c r="AP62">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ62">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR62">
         <v>1.73</v>
@@ -13857,7 +13869,7 @@
         <v>127</v>
       </c>
       <c r="P63" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q63">
         <v>3.28</v>
@@ -14063,7 +14075,7 @@
         <v>128</v>
       </c>
       <c r="P64" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q64">
         <v>6.5</v>
@@ -14269,7 +14281,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q65">
         <v>2.04</v>
@@ -14350,7 +14362,7 @@
         <v>2</v>
       </c>
       <c r="AQ65">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR65">
         <v>1.97</v>
@@ -14553,7 +14565,7 @@
         <v>1.67</v>
       </c>
       <c r="AP66">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ66">
         <v>1.33</v>
@@ -14681,7 +14693,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q67">
         <v>2.45</v>
@@ -14759,10 +14771,10 @@
         <v>0.33</v>
       </c>
       <c r="AP67">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ67">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR67">
         <v>1.44</v>
@@ -14887,7 +14899,7 @@
         <v>132</v>
       </c>
       <c r="P68" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q68">
         <v>3.2</v>
@@ -14968,7 +14980,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ68">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR68">
         <v>1.65</v>
@@ -15171,10 +15183,10 @@
         <v>1.29</v>
       </c>
       <c r="AP69">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ69">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR69">
         <v>2.05</v>
@@ -15583,7 +15595,7 @@
         <v>1.17</v>
       </c>
       <c r="AP71">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ71">
         <v>0.92</v>
@@ -15711,7 +15723,7 @@
         <v>135</v>
       </c>
       <c r="P72" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q72">
         <v>3.26</v>
@@ -15789,7 +15801,7 @@
         <v>1</v>
       </c>
       <c r="AP72">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ72">
         <v>0.92</v>
@@ -15917,7 +15929,7 @@
         <v>97</v>
       </c>
       <c r="P73" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q73">
         <v>4.6</v>
@@ -16204,7 +16216,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ74">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR74">
         <v>1.51</v>
@@ -16535,7 +16547,7 @@
         <v>82</v>
       </c>
       <c r="P76" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q76">
         <v>3.65</v>
@@ -16616,7 +16628,7 @@
         <v>1</v>
       </c>
       <c r="AQ76">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR76">
         <v>1.54</v>
@@ -16741,7 +16753,7 @@
         <v>82</v>
       </c>
       <c r="P77" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q77">
         <v>2.05</v>
@@ -16947,7 +16959,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q78">
         <v>1.89</v>
@@ -17025,10 +17037,10 @@
         <v>0.29</v>
       </c>
       <c r="AP78">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ78">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR78">
         <v>1.69</v>
@@ -17437,7 +17449,7 @@
         <v>1.43</v>
       </c>
       <c r="AP80">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ80">
         <v>1.55</v>
@@ -17565,7 +17577,7 @@
         <v>85</v>
       </c>
       <c r="P81" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q81">
         <v>5.25</v>
@@ -17849,7 +17861,7 @@
         <v>1.5</v>
       </c>
       <c r="AP82">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ82">
         <v>1.23</v>
@@ -18261,10 +18273,10 @@
         <v>1.5</v>
       </c>
       <c r="AP84">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ84">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR84">
         <v>1.45</v>
@@ -18389,7 +18401,7 @@
         <v>143</v>
       </c>
       <c r="P85" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q85">
         <v>2.2</v>
@@ -18470,7 +18482,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ85">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR85">
         <v>1.76</v>
@@ -18595,7 +18607,7 @@
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q86">
         <v>2.11</v>
@@ -18673,7 +18685,7 @@
         <v>0.88</v>
       </c>
       <c r="AP86">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ86">
         <v>0.73</v>
@@ -18801,7 +18813,7 @@
         <v>145</v>
       </c>
       <c r="P87" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q87">
         <v>2.04</v>
@@ -18879,10 +18891,10 @@
         <v>1.5</v>
       </c>
       <c r="AP87">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ87">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR87">
         <v>1.69</v>
@@ -19007,7 +19019,7 @@
         <v>146</v>
       </c>
       <c r="P88" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19085,7 +19097,7 @@
         <v>1.5</v>
       </c>
       <c r="AP88">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ88">
         <v>1.75</v>
@@ -19419,7 +19431,7 @@
         <v>147</v>
       </c>
       <c r="P90" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q90">
         <v>3.81</v>
@@ -19625,7 +19637,7 @@
         <v>148</v>
       </c>
       <c r="P91" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q91">
         <v>3.3</v>
@@ -20118,7 +20130,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ93">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR93">
         <v>1.9</v>
@@ -20243,7 +20255,7 @@
         <v>149</v>
       </c>
       <c r="P94" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q94">
         <v>3.8</v>
@@ -20321,7 +20333,7 @@
         <v>1.67</v>
       </c>
       <c r="AP94">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ94">
         <v>1.75</v>
@@ -20527,7 +20539,7 @@
         <v>1.4</v>
       </c>
       <c r="AP95">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ95">
         <v>1.23</v>
@@ -20655,7 +20667,7 @@
         <v>82</v>
       </c>
       <c r="P96" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q96">
         <v>4.1</v>
@@ -20736,7 +20748,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ96">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR96">
         <v>1.55</v>
@@ -20939,10 +20951,10 @@
         <v>1.22</v>
       </c>
       <c r="AP97">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ97">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR97">
         <v>1.72</v>
@@ -21148,7 +21160,7 @@
         <v>1</v>
       </c>
       <c r="AQ98">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR98">
         <v>1.43</v>
@@ -21273,7 +21285,7 @@
         <v>152</v>
       </c>
       <c r="P99" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q99">
         <v>4.85</v>
@@ -21351,7 +21363,7 @@
         <v>1.8</v>
       </c>
       <c r="AP99">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ99">
         <v>1.75</v>
@@ -21557,7 +21569,7 @@
         <v>1.22</v>
       </c>
       <c r="AP100">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ100">
         <v>1.33</v>
@@ -21763,7 +21775,7 @@
         <v>0.78</v>
       </c>
       <c r="AP101">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ101">
         <v>0.73</v>
@@ -22097,7 +22109,7 @@
         <v>82</v>
       </c>
       <c r="P103" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q103">
         <v>3.3</v>
@@ -22175,7 +22187,7 @@
         <v>1.22</v>
       </c>
       <c r="AP103">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ103">
         <v>1.55</v>
@@ -22303,7 +22315,7 @@
         <v>155</v>
       </c>
       <c r="P104" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -22384,7 +22396,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ104">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR104">
         <v>1.6</v>
@@ -22509,7 +22521,7 @@
         <v>156</v>
       </c>
       <c r="P105" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q105">
         <v>1.64</v>
@@ -22590,7 +22602,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ105">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AR105">
         <v>1.96</v>
@@ -22715,7 +22727,7 @@
         <v>157</v>
       </c>
       <c r="P106" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q106">
         <v>3.55</v>
@@ -22796,7 +22808,7 @@
         <v>1</v>
       </c>
       <c r="AQ106">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR106">
         <v>1.39</v>
@@ -22921,7 +22933,7 @@
         <v>82</v>
       </c>
       <c r="P107" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q107">
         <v>2.89</v>
@@ -22999,7 +23011,7 @@
         <v>1.4</v>
       </c>
       <c r="AP107">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ107">
         <v>1.55</v>
@@ -23127,7 +23139,7 @@
         <v>158</v>
       </c>
       <c r="P108" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q108">
         <v>3.5</v>
@@ -23333,7 +23345,7 @@
         <v>159</v>
       </c>
       <c r="P109" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q109">
         <v>3.4</v>
@@ -23745,7 +23757,7 @@
         <v>161</v>
       </c>
       <c r="P111" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q111">
         <v>1.86</v>
@@ -24235,7 +24247,7 @@
         <v>1.33</v>
       </c>
       <c r="AP113">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ113">
         <v>1.23</v>
@@ -24650,7 +24662,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ115">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR115">
         <v>1.95</v>
@@ -24726,6 +24738,830 @@
       </c>
       <c r="BP115">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="116" spans="1:68">
+      <c r="A116" s="1">
+        <v>115</v>
+      </c>
+      <c r="B116">
+        <v>7775732</v>
+      </c>
+      <c r="C116" t="s">
+        <v>68</v>
+      </c>
+      <c r="D116" t="s">
+        <v>69</v>
+      </c>
+      <c r="E116" s="2">
+        <v>45842.65625</v>
+      </c>
+      <c r="F116">
+        <v>0</v>
+      </c>
+      <c r="G116" t="s">
+        <v>71</v>
+      </c>
+      <c r="H116" t="s">
+        <v>70</v>
+      </c>
+      <c r="I116">
+        <v>2</v>
+      </c>
+      <c r="J116">
+        <v>1</v>
+      </c>
+      <c r="K116">
+        <v>3</v>
+      </c>
+      <c r="L116">
+        <v>3</v>
+      </c>
+      <c r="M116">
+        <v>1</v>
+      </c>
+      <c r="N116">
+        <v>4</v>
+      </c>
+      <c r="O116" t="s">
+        <v>164</v>
+      </c>
+      <c r="P116" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q116">
+        <v>2.15</v>
+      </c>
+      <c r="R116">
+        <v>2.19</v>
+      </c>
+      <c r="S116">
+        <v>6.7</v>
+      </c>
+      <c r="T116">
+        <v>1.36</v>
+      </c>
+      <c r="U116">
+        <v>2.8</v>
+      </c>
+      <c r="V116">
+        <v>2.75</v>
+      </c>
+      <c r="W116">
+        <v>1.36</v>
+      </c>
+      <c r="X116">
+        <v>6.2</v>
+      </c>
+      <c r="Y116">
+        <v>1.08</v>
+      </c>
+      <c r="Z116">
+        <v>1.4</v>
+      </c>
+      <c r="AA116">
+        <v>3.95</v>
+      </c>
+      <c r="AB116">
+        <v>5.4</v>
+      </c>
+      <c r="AC116">
+        <v>1.01</v>
+      </c>
+      <c r="AD116">
+        <v>8.5</v>
+      </c>
+      <c r="AE116">
+        <v>1.3</v>
+      </c>
+      <c r="AF116">
+        <v>3.25</v>
+      </c>
+      <c r="AG116">
+        <v>2</v>
+      </c>
+      <c r="AH116">
+        <v>1.8</v>
+      </c>
+      <c r="AI116">
+        <v>2.1</v>
+      </c>
+      <c r="AJ116">
+        <v>1.66</v>
+      </c>
+      <c r="AK116">
+        <v>1.22</v>
+      </c>
+      <c r="AL116">
+        <v>1.2</v>
+      </c>
+      <c r="AM116">
+        <v>2.3</v>
+      </c>
+      <c r="AN116">
+        <v>1.33</v>
+      </c>
+      <c r="AO116">
+        <v>0.2</v>
+      </c>
+      <c r="AP116">
+        <v>1.46</v>
+      </c>
+      <c r="AQ116">
+        <v>0.18</v>
+      </c>
+      <c r="AR116">
+        <v>1.93</v>
+      </c>
+      <c r="AS116">
+        <v>1.12</v>
+      </c>
+      <c r="AT116">
+        <v>3.05</v>
+      </c>
+      <c r="AU116">
+        <v>6</v>
+      </c>
+      <c r="AV116">
+        <v>3</v>
+      </c>
+      <c r="AW116">
+        <v>8</v>
+      </c>
+      <c r="AX116">
+        <v>3</v>
+      </c>
+      <c r="AY116">
+        <v>14</v>
+      </c>
+      <c r="AZ116">
+        <v>6</v>
+      </c>
+      <c r="BA116">
+        <v>7</v>
+      </c>
+      <c r="BB116">
+        <v>2</v>
+      </c>
+      <c r="BC116">
+        <v>9</v>
+      </c>
+      <c r="BD116">
+        <v>1.4</v>
+      </c>
+      <c r="BE116">
+        <v>9.5</v>
+      </c>
+      <c r="BF116">
+        <v>4.46</v>
+      </c>
+      <c r="BG116">
+        <v>1.34</v>
+      </c>
+      <c r="BH116">
+        <v>3.3</v>
+      </c>
+      <c r="BI116">
+        <v>1.44</v>
+      </c>
+      <c r="BJ116">
+        <v>2.25</v>
+      </c>
+      <c r="BK116">
+        <v>2.04</v>
+      </c>
+      <c r="BL116">
+        <v>1.9</v>
+      </c>
+      <c r="BM116">
+        <v>2.25</v>
+      </c>
+      <c r="BN116">
+        <v>1.57</v>
+      </c>
+      <c r="BO116">
+        <v>2.9</v>
+      </c>
+      <c r="BP116">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="117" spans="1:68">
+      <c r="A117" s="1">
+        <v>116</v>
+      </c>
+      <c r="B117">
+        <v>7775731</v>
+      </c>
+      <c r="C117" t="s">
+        <v>68</v>
+      </c>
+      <c r="D117" t="s">
+        <v>69</v>
+      </c>
+      <c r="E117" s="2">
+        <v>45842.65625</v>
+      </c>
+      <c r="F117">
+        <v>0</v>
+      </c>
+      <c r="G117" t="s">
+        <v>76</v>
+      </c>
+      <c r="H117" t="s">
+        <v>77</v>
+      </c>
+      <c r="I117">
+        <v>0</v>
+      </c>
+      <c r="J117">
+        <v>0</v>
+      </c>
+      <c r="K117">
+        <v>0</v>
+      </c>
+      <c r="L117">
+        <v>1</v>
+      </c>
+      <c r="M117">
+        <v>0</v>
+      </c>
+      <c r="N117">
+        <v>1</v>
+      </c>
+      <c r="O117" t="s">
+        <v>165</v>
+      </c>
+      <c r="P117" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q117">
+        <v>3.05</v>
+      </c>
+      <c r="R117">
+        <v>2</v>
+      </c>
+      <c r="S117">
+        <v>3.6</v>
+      </c>
+      <c r="T117">
+        <v>1.5</v>
+      </c>
+      <c r="U117">
+        <v>2.4</v>
+      </c>
+      <c r="V117">
+        <v>3.33</v>
+      </c>
+      <c r="W117">
+        <v>1.31</v>
+      </c>
+      <c r="X117">
+        <v>8.5</v>
+      </c>
+      <c r="Y117">
+        <v>1.03</v>
+      </c>
+      <c r="Z117">
+        <v>2.62</v>
+      </c>
+      <c r="AA117">
+        <v>3.15</v>
+      </c>
+      <c r="AB117">
+        <v>3.04</v>
+      </c>
+      <c r="AC117">
+        <v>1.06</v>
+      </c>
+      <c r="AD117">
+        <v>7.5</v>
+      </c>
+      <c r="AE117">
+        <v>1.42</v>
+      </c>
+      <c r="AF117">
+        <v>2.7</v>
+      </c>
+      <c r="AG117">
+        <v>2.42</v>
+      </c>
+      <c r="AH117">
+        <v>1.61</v>
+      </c>
+      <c r="AI117">
+        <v>1.93</v>
+      </c>
+      <c r="AJ117">
+        <v>1.77</v>
+      </c>
+      <c r="AK117">
+        <v>1.33</v>
+      </c>
+      <c r="AL117">
+        <v>1.3</v>
+      </c>
+      <c r="AM117">
+        <v>1.47</v>
+      </c>
+      <c r="AN117">
+        <v>1.73</v>
+      </c>
+      <c r="AO117">
+        <v>1.09</v>
+      </c>
+      <c r="AP117">
+        <v>1.83</v>
+      </c>
+      <c r="AQ117">
+        <v>1</v>
+      </c>
+      <c r="AR117">
+        <v>1.43</v>
+      </c>
+      <c r="AS117">
+        <v>1.56</v>
+      </c>
+      <c r="AT117">
+        <v>2.99</v>
+      </c>
+      <c r="AU117">
+        <v>2</v>
+      </c>
+      <c r="AV117">
+        <v>2</v>
+      </c>
+      <c r="AW117">
+        <v>4</v>
+      </c>
+      <c r="AX117">
+        <v>7</v>
+      </c>
+      <c r="AY117">
+        <v>6</v>
+      </c>
+      <c r="AZ117">
+        <v>9</v>
+      </c>
+      <c r="BA117">
+        <v>1</v>
+      </c>
+      <c r="BB117">
+        <v>7</v>
+      </c>
+      <c r="BC117">
+        <v>8</v>
+      </c>
+      <c r="BD117">
+        <v>1.86</v>
+      </c>
+      <c r="BE117">
+        <v>7.27</v>
+      </c>
+      <c r="BF117">
+        <v>2.48</v>
+      </c>
+      <c r="BG117">
+        <v>1.3</v>
+      </c>
+      <c r="BH117">
+        <v>3.2</v>
+      </c>
+      <c r="BI117">
+        <v>1.53</v>
+      </c>
+      <c r="BJ117">
+        <v>2.5</v>
+      </c>
+      <c r="BK117">
+        <v>1.99</v>
+      </c>
+      <c r="BL117">
+        <v>1.99</v>
+      </c>
+      <c r="BM117">
+        <v>2.22</v>
+      </c>
+      <c r="BN117">
+        <v>1.59</v>
+      </c>
+      <c r="BO117">
+        <v>3</v>
+      </c>
+      <c r="BP117">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="118" spans="1:68">
+      <c r="A118" s="1">
+        <v>117</v>
+      </c>
+      <c r="B118">
+        <v>7775730</v>
+      </c>
+      <c r="C118" t="s">
+        <v>68</v>
+      </c>
+      <c r="D118" t="s">
+        <v>69</v>
+      </c>
+      <c r="E118" s="2">
+        <v>45842.65625</v>
+      </c>
+      <c r="F118">
+        <v>0</v>
+      </c>
+      <c r="G118" t="s">
+        <v>75</v>
+      </c>
+      <c r="H118" t="s">
+        <v>78</v>
+      </c>
+      <c r="I118">
+        <v>4</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+      <c r="K118">
+        <v>4</v>
+      </c>
+      <c r="L118">
+        <v>7</v>
+      </c>
+      <c r="M118">
+        <v>2</v>
+      </c>
+      <c r="N118">
+        <v>9</v>
+      </c>
+      <c r="O118" t="s">
+        <v>166</v>
+      </c>
+      <c r="P118" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q118">
+        <v>2.08</v>
+      </c>
+      <c r="R118">
+        <v>2.18</v>
+      </c>
+      <c r="S118">
+        <v>5.5</v>
+      </c>
+      <c r="T118">
+        <v>1.36</v>
+      </c>
+      <c r="U118">
+        <v>2.7</v>
+      </c>
+      <c r="V118">
+        <v>3.06</v>
+      </c>
+      <c r="W118">
+        <v>1.36</v>
+      </c>
+      <c r="X118">
+        <v>6.2</v>
+      </c>
+      <c r="Y118">
+        <v>1.07</v>
+      </c>
+      <c r="Z118">
+        <v>1.55</v>
+      </c>
+      <c r="AA118">
+        <v>4</v>
+      </c>
+      <c r="AB118">
+        <v>5.5</v>
+      </c>
+      <c r="AC118">
+        <v>1</v>
+      </c>
+      <c r="AD118">
+        <v>8.5</v>
+      </c>
+      <c r="AE118">
+        <v>1.3</v>
+      </c>
+      <c r="AF118">
+        <v>3</v>
+      </c>
+      <c r="AG118">
+        <v>1.93</v>
+      </c>
+      <c r="AH118">
+        <v>1.78</v>
+      </c>
+      <c r="AI118">
+        <v>2.11</v>
+      </c>
+      <c r="AJ118">
+        <v>1.7</v>
+      </c>
+      <c r="AK118">
+        <v>1.25</v>
+      </c>
+      <c r="AL118">
+        <v>1.2</v>
+      </c>
+      <c r="AM118">
+        <v>2.35</v>
+      </c>
+      <c r="AN118">
+        <v>1.82</v>
+      </c>
+      <c r="AO118">
+        <v>1.18</v>
+      </c>
+      <c r="AP118">
+        <v>1.92</v>
+      </c>
+      <c r="AQ118">
+        <v>1.08</v>
+      </c>
+      <c r="AR118">
+        <v>1.77</v>
+      </c>
+      <c r="AS118">
+        <v>1.14</v>
+      </c>
+      <c r="AT118">
+        <v>2.91</v>
+      </c>
+      <c r="AU118">
+        <v>12</v>
+      </c>
+      <c r="AV118">
+        <v>4</v>
+      </c>
+      <c r="AW118">
+        <v>1</v>
+      </c>
+      <c r="AX118">
+        <v>2</v>
+      </c>
+      <c r="AY118">
+        <v>13</v>
+      </c>
+      <c r="AZ118">
+        <v>6</v>
+      </c>
+      <c r="BA118">
+        <v>6</v>
+      </c>
+      <c r="BB118">
+        <v>2</v>
+      </c>
+      <c r="BC118">
+        <v>8</v>
+      </c>
+      <c r="BD118">
+        <v>1.34</v>
+      </c>
+      <c r="BE118">
+        <v>9.85</v>
+      </c>
+      <c r="BF118">
+        <v>6.35</v>
+      </c>
+      <c r="BG118">
+        <v>1.48</v>
+      </c>
+      <c r="BH118">
+        <v>2.7</v>
+      </c>
+      <c r="BI118">
+        <v>1.67</v>
+      </c>
+      <c r="BJ118">
+        <v>2.03</v>
+      </c>
+      <c r="BK118">
+        <v>2.3</v>
+      </c>
+      <c r="BL118">
+        <v>1.62</v>
+      </c>
+      <c r="BM118">
+        <v>2.88</v>
+      </c>
+      <c r="BN118">
+        <v>1.34</v>
+      </c>
+      <c r="BO118">
+        <v>3.98</v>
+      </c>
+      <c r="BP118">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="119" spans="1:68">
+      <c r="A119" s="1">
+        <v>118</v>
+      </c>
+      <c r="B119">
+        <v>7775733</v>
+      </c>
+      <c r="C119" t="s">
+        <v>68</v>
+      </c>
+      <c r="D119" t="s">
+        <v>69</v>
+      </c>
+      <c r="E119" s="2">
+        <v>45842.65625</v>
+      </c>
+      <c r="F119">
+        <v>0</v>
+      </c>
+      <c r="G119" t="s">
+        <v>72</v>
+      </c>
+      <c r="H119" t="s">
+        <v>74</v>
+      </c>
+      <c r="I119">
+        <v>0</v>
+      </c>
+      <c r="J119">
+        <v>0</v>
+      </c>
+      <c r="K119">
+        <v>0</v>
+      </c>
+      <c r="L119">
+        <v>0</v>
+      </c>
+      <c r="M119">
+        <v>0</v>
+      </c>
+      <c r="N119">
+        <v>0</v>
+      </c>
+      <c r="O119" t="s">
+        <v>82</v>
+      </c>
+      <c r="P119" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q119">
+        <v>2.9</v>
+      </c>
+      <c r="R119">
+        <v>2.1</v>
+      </c>
+      <c r="S119">
+        <v>3.35</v>
+      </c>
+      <c r="T119">
+        <v>1.36</v>
+      </c>
+      <c r="U119">
+        <v>2.55</v>
+      </c>
+      <c r="V119">
+        <v>2.84</v>
+      </c>
+      <c r="W119">
+        <v>1.33</v>
+      </c>
+      <c r="X119">
+        <v>6.5</v>
+      </c>
+      <c r="Y119">
+        <v>1.08</v>
+      </c>
+      <c r="Z119">
+        <v>2.2</v>
+      </c>
+      <c r="AA119">
+        <v>3.2</v>
+      </c>
+      <c r="AB119">
+        <v>2.73</v>
+      </c>
+      <c r="AC119">
+        <v>1.03</v>
+      </c>
+      <c r="AD119">
+        <v>7.75</v>
+      </c>
+      <c r="AE119">
+        <v>1.29</v>
+      </c>
+      <c r="AF119">
+        <v>3.3</v>
+      </c>
+      <c r="AG119">
+        <v>2.02</v>
+      </c>
+      <c r="AH119">
+        <v>1.8</v>
+      </c>
+      <c r="AI119">
+        <v>1.88</v>
+      </c>
+      <c r="AJ119">
+        <v>1.8</v>
+      </c>
+      <c r="AK119">
+        <v>1.32</v>
+      </c>
+      <c r="AL119">
+        <v>1.28</v>
+      </c>
+      <c r="AM119">
+        <v>1.55</v>
+      </c>
+      <c r="AN119">
+        <v>1.67</v>
+      </c>
+      <c r="AO119">
+        <v>1.36</v>
+      </c>
+      <c r="AP119">
+        <v>1.62</v>
+      </c>
+      <c r="AQ119">
+        <v>1.33</v>
+      </c>
+      <c r="AR119">
+        <v>1.68</v>
+      </c>
+      <c r="AS119">
+        <v>1.62</v>
+      </c>
+      <c r="AT119">
+        <v>3.3</v>
+      </c>
+      <c r="AU119">
+        <v>6</v>
+      </c>
+      <c r="AV119">
+        <v>3</v>
+      </c>
+      <c r="AW119">
+        <v>3</v>
+      </c>
+      <c r="AX119">
+        <v>4</v>
+      </c>
+      <c r="AY119">
+        <v>9</v>
+      </c>
+      <c r="AZ119">
+        <v>7</v>
+      </c>
+      <c r="BA119">
+        <v>2</v>
+      </c>
+      <c r="BB119">
+        <v>5</v>
+      </c>
+      <c r="BC119">
+        <v>7</v>
+      </c>
+      <c r="BD119">
+        <v>1.94</v>
+      </c>
+      <c r="BE119">
+        <v>8.5</v>
+      </c>
+      <c r="BF119">
+        <v>2.22</v>
+      </c>
+      <c r="BG119">
+        <v>1.22</v>
+      </c>
+      <c r="BH119">
+        <v>3.82</v>
+      </c>
+      <c r="BI119">
+        <v>1.38</v>
+      </c>
+      <c r="BJ119">
+        <v>2.67</v>
+      </c>
+      <c r="BK119">
+        <v>1.67</v>
+      </c>
+      <c r="BL119">
+        <v>2.07</v>
+      </c>
+      <c r="BM119">
+        <v>2.11</v>
+      </c>
+      <c r="BN119">
+        <v>1.64</v>
+      </c>
+      <c r="BO119">
+        <v>2.78</v>
+      </c>
+      <c r="BP119">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
@@ -24886,13 +24886,13 @@
         <v>3</v>
       </c>
       <c r="AW116">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX116">
         <v>3</v>
       </c>
       <c r="AY116">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AZ116">
         <v>6</v>
@@ -25092,16 +25092,16 @@
         <v>2</v>
       </c>
       <c r="AW117">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AX117">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AY117">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AZ117">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="BA117">
         <v>1</v>
@@ -25292,22 +25292,22 @@
         <v>2.91</v>
       </c>
       <c r="AU118">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV118">
+        <v>5</v>
+      </c>
+      <c r="AW118">
         <v>4</v>
       </c>
-      <c r="AW118">
-        <v>1</v>
-      </c>
       <c r="AX118">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY118">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AZ118">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BA118">
         <v>6</v>
@@ -25504,16 +25504,16 @@
         <v>3</v>
       </c>
       <c r="AW119">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AX119">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AY119">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AZ119">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BA119">
         <v>2</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="226">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -517,6 +517,9 @@
     <t>['24', '5', '41', '36', '52', '57', '73']</t>
   </si>
   <si>
+    <t>['9', '24']</t>
+  </si>
+  <si>
     <t>['45+1', '81']</t>
   </si>
   <si>
@@ -686,6 +689,9 @@
   </si>
   <si>
     <t>['49', '79']</t>
+  </si>
+  <si>
+    <t>['63', '33']</t>
   </si>
 </sst>
 </file>
@@ -1047,7 +1053,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP119"/>
+  <dimension ref="A1:BP120"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1303,7 +1309,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q2">
         <v>4.4</v>
@@ -1921,7 +1927,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -2208,7 +2214,7 @@
         <v>2</v>
       </c>
       <c r="AQ6">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2745,7 +2751,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3157,7 +3163,7 @@
         <v>88</v>
       </c>
       <c r="P11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q11">
         <v>1.94</v>
@@ -3363,7 +3369,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q12">
         <v>3.95</v>
@@ -3444,7 +3450,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ12">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR12">
         <v>1.77</v>
@@ -3569,7 +3575,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q13">
         <v>4.5</v>
@@ -3775,7 +3781,7 @@
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q14">
         <v>3.9</v>
@@ -3981,7 +3987,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q15">
         <v>2.06</v>
@@ -4187,7 +4193,7 @@
         <v>82</v>
       </c>
       <c r="P16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4393,7 +4399,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q17">
         <v>3.1</v>
@@ -4599,7 +4605,7 @@
         <v>94</v>
       </c>
       <c r="P18" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q18">
         <v>4.2</v>
@@ -4680,7 +4686,7 @@
         <v>1</v>
       </c>
       <c r="AQ18">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR18">
         <v>2.63</v>
@@ -5011,7 +5017,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q20">
         <v>2.65</v>
@@ -5217,7 +5223,7 @@
         <v>82</v>
       </c>
       <c r="P21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -6041,7 +6047,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q25">
         <v>2.7</v>
@@ -6247,7 +6253,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q26">
         <v>4.75</v>
@@ -6328,7 +6334,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ26">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR26">
         <v>1.55</v>
@@ -7277,7 +7283,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q31">
         <v>4.75</v>
@@ -7483,7 +7489,7 @@
         <v>82</v>
       </c>
       <c r="P32" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q32">
         <v>3</v>
@@ -7895,7 +7901,7 @@
         <v>104</v>
       </c>
       <c r="P34" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q34">
         <v>4.33</v>
@@ -8513,7 +8519,7 @@
         <v>105</v>
       </c>
       <c r="P37" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q37">
         <v>2.38</v>
@@ -9212,7 +9218,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ40">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR40">
         <v>1.69</v>
@@ -9337,7 +9343,7 @@
         <v>82</v>
       </c>
       <c r="P41" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q41">
         <v>5.2</v>
@@ -9749,7 +9755,7 @@
         <v>109</v>
       </c>
       <c r="P43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q43">
         <v>2.38</v>
@@ -10161,7 +10167,7 @@
         <v>111</v>
       </c>
       <c r="P45" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q45">
         <v>4.04</v>
@@ -10367,7 +10373,7 @@
         <v>112</v>
       </c>
       <c r="P46" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q46">
         <v>1.7</v>
@@ -10779,7 +10785,7 @@
         <v>114</v>
       </c>
       <c r="P48" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q48">
         <v>3.88</v>
@@ -10985,7 +10991,7 @@
         <v>115</v>
       </c>
       <c r="P49" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q49">
         <v>3.55</v>
@@ -11191,7 +11197,7 @@
         <v>116</v>
       </c>
       <c r="P50" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q50">
         <v>3.7</v>
@@ -11272,7 +11278,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ50">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR50">
         <v>1.81</v>
@@ -11397,7 +11403,7 @@
         <v>82</v>
       </c>
       <c r="P51" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q51">
         <v>2.6</v>
@@ -11603,7 +11609,7 @@
         <v>117</v>
       </c>
       <c r="P52" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q52">
         <v>2.24</v>
@@ -12221,7 +12227,7 @@
         <v>119</v>
       </c>
       <c r="P55" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q55">
         <v>2.6</v>
@@ -12633,7 +12639,7 @@
         <v>121</v>
       </c>
       <c r="P57" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -13045,7 +13051,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q59">
         <v>4.75</v>
@@ -13251,7 +13257,7 @@
         <v>124</v>
       </c>
       <c r="P60" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q60">
         <v>2.61</v>
@@ -13457,7 +13463,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q61">
         <v>3.05</v>
@@ -13869,7 +13875,7 @@
         <v>127</v>
       </c>
       <c r="P63" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q63">
         <v>3.28</v>
@@ -14075,7 +14081,7 @@
         <v>128</v>
       </c>
       <c r="P64" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q64">
         <v>6.5</v>
@@ -14156,7 +14162,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ64">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR64">
         <v>1.6</v>
@@ -14281,7 +14287,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q65">
         <v>2.04</v>
@@ -14693,7 +14699,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q67">
         <v>2.45</v>
@@ -14899,7 +14905,7 @@
         <v>132</v>
       </c>
       <c r="P68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q68">
         <v>3.2</v>
@@ -15723,7 +15729,7 @@
         <v>135</v>
       </c>
       <c r="P72" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q72">
         <v>3.26</v>
@@ -15929,7 +15935,7 @@
         <v>97</v>
       </c>
       <c r="P73" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q73">
         <v>4.6</v>
@@ -16547,7 +16553,7 @@
         <v>82</v>
       </c>
       <c r="P76" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q76">
         <v>3.65</v>
@@ -16753,7 +16759,7 @@
         <v>82</v>
       </c>
       <c r="P77" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q77">
         <v>2.05</v>
@@ -16959,7 +16965,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q78">
         <v>1.89</v>
@@ -17577,7 +17583,7 @@
         <v>85</v>
       </c>
       <c r="P81" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q81">
         <v>5.25</v>
@@ -17658,7 +17664,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ81">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR81">
         <v>1.57</v>
@@ -18401,7 +18407,7 @@
         <v>143</v>
       </c>
       <c r="P85" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q85">
         <v>2.2</v>
@@ -18607,7 +18613,7 @@
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q86">
         <v>2.11</v>
@@ -18813,7 +18819,7 @@
         <v>145</v>
       </c>
       <c r="P87" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q87">
         <v>2.04</v>
@@ -19019,7 +19025,7 @@
         <v>146</v>
       </c>
       <c r="P88" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19100,7 +19106,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ88">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR88">
         <v>1.76</v>
@@ -19431,7 +19437,7 @@
         <v>147</v>
       </c>
       <c r="P90" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q90">
         <v>3.81</v>
@@ -19637,7 +19643,7 @@
         <v>148</v>
       </c>
       <c r="P91" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q91">
         <v>3.3</v>
@@ -20255,7 +20261,7 @@
         <v>149</v>
       </c>
       <c r="P94" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q94">
         <v>3.8</v>
@@ -20336,7 +20342,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ94">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR94">
         <v>2.08</v>
@@ -20667,7 +20673,7 @@
         <v>82</v>
       </c>
       <c r="P96" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q96">
         <v>4.1</v>
@@ -21285,7 +21291,7 @@
         <v>152</v>
       </c>
       <c r="P99" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q99">
         <v>4.85</v>
@@ -21366,7 +21372,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ99">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR99">
         <v>1.43</v>
@@ -22109,7 +22115,7 @@
         <v>82</v>
       </c>
       <c r="P103" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q103">
         <v>3.3</v>
@@ -22315,7 +22321,7 @@
         <v>155</v>
       </c>
       <c r="P104" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -22521,7 +22527,7 @@
         <v>156</v>
       </c>
       <c r="P105" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q105">
         <v>1.64</v>
@@ -22727,7 +22733,7 @@
         <v>157</v>
       </c>
       <c r="P106" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q106">
         <v>3.55</v>
@@ -22933,7 +22939,7 @@
         <v>82</v>
       </c>
       <c r="P107" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q107">
         <v>2.89</v>
@@ -23139,7 +23145,7 @@
         <v>158</v>
       </c>
       <c r="P108" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q108">
         <v>3.5</v>
@@ -23345,7 +23351,7 @@
         <v>159</v>
       </c>
       <c r="P109" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q109">
         <v>3.4</v>
@@ -23632,7 +23638,7 @@
         <v>2</v>
       </c>
       <c r="AQ110">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR110">
         <v>1.93</v>
@@ -23757,7 +23763,7 @@
         <v>161</v>
       </c>
       <c r="P111" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q111">
         <v>1.86</v>
@@ -24787,7 +24793,7 @@
         <v>164</v>
       </c>
       <c r="P116" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q116">
         <v>2.15</v>
@@ -24886,13 +24892,13 @@
         <v>3</v>
       </c>
       <c r="AW116">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AX116">
         <v>3</v>
       </c>
       <c r="AY116">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ116">
         <v>6</v>
@@ -25092,16 +25098,16 @@
         <v>2</v>
       </c>
       <c r="AW117">
+        <v>4</v>
+      </c>
+      <c r="AX117">
+        <v>7</v>
+      </c>
+      <c r="AY117">
+        <v>6</v>
+      </c>
+      <c r="AZ117">
         <v>9</v>
-      </c>
-      <c r="AX117">
-        <v>12</v>
-      </c>
-      <c r="AY117">
-        <v>11</v>
-      </c>
-      <c r="AZ117">
-        <v>14</v>
       </c>
       <c r="BA117">
         <v>1</v>
@@ -25199,7 +25205,7 @@
         <v>166</v>
       </c>
       <c r="P118" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q118">
         <v>2.08</v>
@@ -25292,22 +25298,22 @@
         <v>2.91</v>
       </c>
       <c r="AU118">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV118">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW118">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AX118">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY118">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ118">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA118">
         <v>6</v>
@@ -25504,16 +25510,16 @@
         <v>3</v>
       </c>
       <c r="AW119">
+        <v>3</v>
+      </c>
+      <c r="AX119">
+        <v>4</v>
+      </c>
+      <c r="AY119">
         <v>9</v>
       </c>
-      <c r="AX119">
-        <v>8</v>
-      </c>
-      <c r="AY119">
-        <v>15</v>
-      </c>
       <c r="AZ119">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BA119">
         <v>2</v>
@@ -25562,6 +25568,212 @@
       </c>
       <c r="BP119">
         <v>1.48</v>
+      </c>
+    </row>
+    <row r="120" spans="1:68">
+      <c r="A120" s="1">
+        <v>119</v>
+      </c>
+      <c r="B120">
+        <v>7775734</v>
+      </c>
+      <c r="C120" t="s">
+        <v>68</v>
+      </c>
+      <c r="D120" t="s">
+        <v>69</v>
+      </c>
+      <c r="E120" s="2">
+        <v>45843.65625</v>
+      </c>
+      <c r="F120">
+        <v>0</v>
+      </c>
+      <c r="G120" t="s">
+        <v>73</v>
+      </c>
+      <c r="H120" t="s">
+        <v>79</v>
+      </c>
+      <c r="I120">
+        <v>2</v>
+      </c>
+      <c r="J120">
+        <v>1</v>
+      </c>
+      <c r="K120">
+        <v>3</v>
+      </c>
+      <c r="L120">
+        <v>2</v>
+      </c>
+      <c r="M120">
+        <v>2</v>
+      </c>
+      <c r="N120">
+        <v>4</v>
+      </c>
+      <c r="O120" t="s">
+        <v>167</v>
+      </c>
+      <c r="P120" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q120">
+        <v>6</v>
+      </c>
+      <c r="R120">
+        <v>2.4</v>
+      </c>
+      <c r="S120">
+        <v>1.75</v>
+      </c>
+      <c r="T120">
+        <v>1.34</v>
+      </c>
+      <c r="U120">
+        <v>3.32</v>
+      </c>
+      <c r="V120">
+        <v>2.45</v>
+      </c>
+      <c r="W120">
+        <v>1.4</v>
+      </c>
+      <c r="X120">
+        <v>5.8</v>
+      </c>
+      <c r="Y120">
+        <v>1.04</v>
+      </c>
+      <c r="Z120">
+        <v>6.75</v>
+      </c>
+      <c r="AA120">
+        <v>4.2</v>
+      </c>
+      <c r="AB120">
+        <v>1.42</v>
+      </c>
+      <c r="AC120">
+        <v>1.04</v>
+      </c>
+      <c r="AD120">
+        <v>11</v>
+      </c>
+      <c r="AE120">
+        <v>1.27</v>
+      </c>
+      <c r="AF120">
+        <v>3.6</v>
+      </c>
+      <c r="AG120">
+        <v>1.77</v>
+      </c>
+      <c r="AH120">
+        <v>1.98</v>
+      </c>
+      <c r="AI120">
+        <v>2</v>
+      </c>
+      <c r="AJ120">
+        <v>1.73</v>
+      </c>
+      <c r="AK120">
+        <v>1.15</v>
+      </c>
+      <c r="AL120">
+        <v>1.15</v>
+      </c>
+      <c r="AM120">
+        <v>1.1</v>
+      </c>
+      <c r="AN120">
+        <v>1</v>
+      </c>
+      <c r="AO120">
+        <v>1.75</v>
+      </c>
+      <c r="AP120">
+        <v>1</v>
+      </c>
+      <c r="AQ120">
+        <v>1.69</v>
+      </c>
+      <c r="AR120">
+        <v>1.4</v>
+      </c>
+      <c r="AS120">
+        <v>1.63</v>
+      </c>
+      <c r="AT120">
+        <v>3.03</v>
+      </c>
+      <c r="AU120">
+        <v>3</v>
+      </c>
+      <c r="AV120">
+        <v>9</v>
+      </c>
+      <c r="AW120">
+        <v>3</v>
+      </c>
+      <c r="AX120">
+        <v>7</v>
+      </c>
+      <c r="AY120">
+        <v>6</v>
+      </c>
+      <c r="AZ120">
+        <v>16</v>
+      </c>
+      <c r="BA120">
+        <v>2</v>
+      </c>
+      <c r="BB120">
+        <v>7</v>
+      </c>
+      <c r="BC120">
+        <v>9</v>
+      </c>
+      <c r="BD120">
+        <v>6.2</v>
+      </c>
+      <c r="BE120">
+        <v>10.3</v>
+      </c>
+      <c r="BF120">
+        <v>1.27</v>
+      </c>
+      <c r="BG120">
+        <v>1.2</v>
+      </c>
+      <c r="BH120">
+        <v>3.64</v>
+      </c>
+      <c r="BI120">
+        <v>1.38</v>
+      </c>
+      <c r="BJ120">
+        <v>2.7</v>
+      </c>
+      <c r="BK120">
+        <v>2.01</v>
+      </c>
+      <c r="BL120">
+        <v>1.95</v>
+      </c>
+      <c r="BM120">
+        <v>2.15</v>
+      </c>
+      <c r="BN120">
+        <v>1.61</v>
+      </c>
+      <c r="BO120">
+        <v>2.89</v>
+      </c>
+      <c r="BP120">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
@@ -24892,13 +24892,13 @@
         <v>3</v>
       </c>
       <c r="AW116">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX116">
         <v>3</v>
       </c>
       <c r="AY116">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AZ116">
         <v>6</v>
@@ -25098,16 +25098,16 @@
         <v>2</v>
       </c>
       <c r="AW117">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AX117">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AY117">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AZ117">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="BA117">
         <v>1</v>
@@ -25298,22 +25298,22 @@
         <v>2.91</v>
       </c>
       <c r="AU118">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV118">
+        <v>5</v>
+      </c>
+      <c r="AW118">
         <v>4</v>
       </c>
-      <c r="AW118">
-        <v>1</v>
-      </c>
       <c r="AX118">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY118">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AZ118">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BA118">
         <v>6</v>
@@ -25510,16 +25510,16 @@
         <v>3</v>
       </c>
       <c r="AW119">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AX119">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AY119">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AZ119">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BA119">
         <v>2</v>
@@ -25716,16 +25716,16 @@
         <v>9</v>
       </c>
       <c r="AW120">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX120">
+        <v>12</v>
+      </c>
+      <c r="AY120">
         <v>7</v>
       </c>
-      <c r="AY120">
-        <v>6</v>
-      </c>
       <c r="AZ120">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="BA120">
         <v>2</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
@@ -25716,16 +25716,16 @@
         <v>9</v>
       </c>
       <c r="AW120">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX120">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AY120">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ120">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="BA120">
         <v>2</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
@@ -25716,16 +25716,16 @@
         <v>9</v>
       </c>
       <c r="AW120">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX120">
+        <v>12</v>
+      </c>
+      <c r="AY120">
         <v>7</v>
       </c>
-      <c r="AY120">
-        <v>6</v>
-      </c>
       <c r="AZ120">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="BA120">
         <v>2</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="228">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -518,6 +518,12 @@
   </si>
   <si>
     <t>['9', '24']</t>
+  </si>
+  <si>
+    <t>['47', '72', '61']</t>
+  </si>
+  <si>
+    <t>['36', '21']</t>
   </si>
   <si>
     <t>['45+1', '81']</t>
@@ -1053,7 +1059,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP120"/>
+  <dimension ref="A1:BP122"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1309,7 +1315,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q2">
         <v>4.4</v>
@@ -1390,7 +1396,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ2">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1927,7 +1933,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -2211,7 +2217,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ6">
         <v>1.69</v>
@@ -2751,7 +2757,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3035,7 +3041,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ10">
         <v>1.33</v>
@@ -3163,7 +3169,7 @@
         <v>88</v>
       </c>
       <c r="P11" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q11">
         <v>1.94</v>
@@ -3369,7 +3375,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q12">
         <v>3.95</v>
@@ -3575,7 +3581,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q13">
         <v>4.5</v>
@@ -3656,7 +3662,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ13">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR13">
         <v>1.54</v>
@@ -3781,7 +3787,7 @@
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q14">
         <v>3.9</v>
@@ -3987,7 +3993,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q15">
         <v>2.06</v>
@@ -4193,7 +4199,7 @@
         <v>82</v>
       </c>
       <c r="P16" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4271,7 +4277,7 @@
         <v>1</v>
       </c>
       <c r="AP16">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ16">
         <v>1.23</v>
@@ -4399,7 +4405,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q17">
         <v>3.1</v>
@@ -4605,7 +4611,7 @@
         <v>94</v>
       </c>
       <c r="P18" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q18">
         <v>4.2</v>
@@ -5017,7 +5023,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q20">
         <v>2.65</v>
@@ -5095,10 +5101,10 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ20">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR20">
         <v>0.9</v>
@@ -5223,7 +5229,7 @@
         <v>82</v>
       </c>
       <c r="P21" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5301,7 +5307,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ21">
         <v>1.33</v>
@@ -6047,7 +6053,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q25">
         <v>2.7</v>
@@ -6128,7 +6134,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ25">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR25">
         <v>1.72</v>
@@ -6253,7 +6259,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q26">
         <v>4.75</v>
@@ -6746,7 +6752,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ28">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR28">
         <v>1.81</v>
@@ -7283,7 +7289,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q31">
         <v>4.75</v>
@@ -7361,7 +7367,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ31">
         <v>0.92</v>
@@ -7489,7 +7495,7 @@
         <v>82</v>
       </c>
       <c r="P32" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q32">
         <v>3</v>
@@ -7567,10 +7573,10 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ32">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR32">
         <v>1.2</v>
@@ -7901,7 +7907,7 @@
         <v>104</v>
       </c>
       <c r="P34" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q34">
         <v>4.33</v>
@@ -8519,7 +8525,7 @@
         <v>105</v>
       </c>
       <c r="P37" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q37">
         <v>2.38</v>
@@ -8597,7 +8603,7 @@
         <v>0.33</v>
       </c>
       <c r="AP37">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ37">
         <v>0.73</v>
@@ -8806,7 +8812,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ38">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR38">
         <v>1.99</v>
@@ -9343,7 +9349,7 @@
         <v>82</v>
       </c>
       <c r="P41" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q41">
         <v>5.2</v>
@@ -9755,7 +9761,7 @@
         <v>109</v>
       </c>
       <c r="P43" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q43">
         <v>2.38</v>
@@ -10167,7 +10173,7 @@
         <v>111</v>
       </c>
       <c r="P45" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q45">
         <v>4.04</v>
@@ -10248,7 +10254,7 @@
         <v>1</v>
       </c>
       <c r="AQ45">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR45">
         <v>1.63</v>
@@ -10373,7 +10379,7 @@
         <v>112</v>
       </c>
       <c r="P46" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q46">
         <v>1.7</v>
@@ -10454,7 +10460,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ46">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR46">
         <v>1.69</v>
@@ -10657,10 +10663,10 @@
         <v>0.25</v>
       </c>
       <c r="AP47">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ47">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR47">
         <v>1.97</v>
@@ -10785,7 +10791,7 @@
         <v>114</v>
       </c>
       <c r="P48" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q48">
         <v>3.88</v>
@@ -10991,7 +10997,7 @@
         <v>115</v>
       </c>
       <c r="P49" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q49">
         <v>3.55</v>
@@ -11197,7 +11203,7 @@
         <v>116</v>
       </c>
       <c r="P50" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q50">
         <v>3.7</v>
@@ -11403,7 +11409,7 @@
         <v>82</v>
       </c>
       <c r="P51" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q51">
         <v>2.6</v>
@@ -11481,7 +11487,7 @@
         <v>0.25</v>
       </c>
       <c r="AP51">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ51">
         <v>0.73</v>
@@ -11609,7 +11615,7 @@
         <v>117</v>
       </c>
       <c r="P52" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q52">
         <v>2.24</v>
@@ -12227,7 +12233,7 @@
         <v>119</v>
       </c>
       <c r="P55" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q55">
         <v>2.6</v>
@@ -12308,7 +12314,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ55">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR55">
         <v>1.84</v>
@@ -12639,7 +12645,7 @@
         <v>121</v>
       </c>
       <c r="P57" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -12717,7 +12723,7 @@
         <v>1.4</v>
       </c>
       <c r="AP57">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ57">
         <v>0.92</v>
@@ -13051,7 +13057,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q59">
         <v>4.75</v>
@@ -13129,7 +13135,7 @@
         <v>1.4</v>
       </c>
       <c r="AP59">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ59">
         <v>1.55</v>
@@ -13257,7 +13263,7 @@
         <v>124</v>
       </c>
       <c r="P60" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q60">
         <v>2.61</v>
@@ -13463,7 +13469,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q61">
         <v>3.05</v>
@@ -13544,7 +13550,7 @@
         <v>1</v>
       </c>
       <c r="AQ61">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR61">
         <v>1.58</v>
@@ -13750,7 +13756,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ62">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR62">
         <v>1.73</v>
@@ -13875,7 +13881,7 @@
         <v>127</v>
       </c>
       <c r="P63" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q63">
         <v>3.28</v>
@@ -14081,7 +14087,7 @@
         <v>128</v>
       </c>
       <c r="P64" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q64">
         <v>6.5</v>
@@ -14287,7 +14293,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q65">
         <v>2.04</v>
@@ -14365,7 +14371,7 @@
         <v>1</v>
       </c>
       <c r="AP65">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ65">
         <v>1.08</v>
@@ -14699,7 +14705,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q67">
         <v>2.45</v>
@@ -14780,7 +14786,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ67">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR67">
         <v>1.44</v>
@@ -14905,7 +14911,7 @@
         <v>132</v>
       </c>
       <c r="P68" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q68">
         <v>3.2</v>
@@ -15729,7 +15735,7 @@
         <v>135</v>
       </c>
       <c r="P72" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q72">
         <v>3.26</v>
@@ -15935,7 +15941,7 @@
         <v>97</v>
       </c>
       <c r="P73" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q73">
         <v>4.6</v>
@@ -16219,10 +16225,10 @@
         <v>1.43</v>
       </c>
       <c r="AP74">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ74">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR74">
         <v>1.51</v>
@@ -16553,7 +16559,7 @@
         <v>82</v>
       </c>
       <c r="P76" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q76">
         <v>3.65</v>
@@ -16759,7 +16765,7 @@
         <v>82</v>
       </c>
       <c r="P77" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q77">
         <v>2.05</v>
@@ -16965,7 +16971,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q78">
         <v>1.89</v>
@@ -17046,7 +17052,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ78">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR78">
         <v>1.69</v>
@@ -17249,7 +17255,7 @@
         <v>1.43</v>
       </c>
       <c r="AP79">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ79">
         <v>1.33</v>
@@ -17583,7 +17589,7 @@
         <v>85</v>
       </c>
       <c r="P81" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q81">
         <v>5.25</v>
@@ -17661,7 +17667,7 @@
         <v>1.29</v>
       </c>
       <c r="AP81">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ81">
         <v>1.69</v>
@@ -18407,7 +18413,7 @@
         <v>143</v>
       </c>
       <c r="P85" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q85">
         <v>2.2</v>
@@ -18488,7 +18494,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ85">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR85">
         <v>1.76</v>
@@ -18613,7 +18619,7 @@
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q86">
         <v>2.11</v>
@@ -18819,7 +18825,7 @@
         <v>145</v>
       </c>
       <c r="P87" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q87">
         <v>2.04</v>
@@ -19025,7 +19031,7 @@
         <v>146</v>
       </c>
       <c r="P88" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19437,7 +19443,7 @@
         <v>147</v>
       </c>
       <c r="P90" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q90">
         <v>3.81</v>
@@ -19643,7 +19649,7 @@
         <v>148</v>
       </c>
       <c r="P91" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q91">
         <v>3.3</v>
@@ -19721,7 +19727,7 @@
         <v>1.44</v>
       </c>
       <c r="AP91">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ91">
         <v>1.23</v>
@@ -19927,7 +19933,7 @@
         <v>1.38</v>
       </c>
       <c r="AP92">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ92">
         <v>1.55</v>
@@ -20136,7 +20142,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ93">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR93">
         <v>1.9</v>
@@ -20261,7 +20267,7 @@
         <v>149</v>
       </c>
       <c r="P94" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q94">
         <v>3.8</v>
@@ -20673,7 +20679,7 @@
         <v>82</v>
       </c>
       <c r="P96" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q96">
         <v>4.1</v>
@@ -20960,7 +20966,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ97">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR97">
         <v>1.72</v>
@@ -21291,7 +21297,7 @@
         <v>152</v>
       </c>
       <c r="P99" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q99">
         <v>4.85</v>
@@ -22115,7 +22121,7 @@
         <v>82</v>
       </c>
       <c r="P103" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q103">
         <v>3.3</v>
@@ -22321,7 +22327,7 @@
         <v>155</v>
       </c>
       <c r="P104" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -22399,7 +22405,7 @@
         <v>1.5</v>
       </c>
       <c r="AP104">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ104">
         <v>1.33</v>
@@ -22527,7 +22533,7 @@
         <v>156</v>
       </c>
       <c r="P105" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q105">
         <v>1.64</v>
@@ -22608,7 +22614,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ105">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR105">
         <v>1.96</v>
@@ -22733,7 +22739,7 @@
         <v>157</v>
       </c>
       <c r="P106" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q106">
         <v>3.55</v>
@@ -22814,7 +22820,7 @@
         <v>1</v>
       </c>
       <c r="AQ106">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR106">
         <v>1.39</v>
@@ -22939,7 +22945,7 @@
         <v>82</v>
       </c>
       <c r="P107" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q107">
         <v>2.89</v>
@@ -23145,7 +23151,7 @@
         <v>158</v>
       </c>
       <c r="P108" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q108">
         <v>3.5</v>
@@ -23351,7 +23357,7 @@
         <v>159</v>
       </c>
       <c r="P109" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q109">
         <v>3.4</v>
@@ -23429,7 +23435,7 @@
         <v>1.4</v>
       </c>
       <c r="AP109">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ109">
         <v>1.33</v>
@@ -23635,7 +23641,7 @@
         <v>1.91</v>
       </c>
       <c r="AP110">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ110">
         <v>1.69</v>
@@ -23763,7 +23769,7 @@
         <v>161</v>
       </c>
       <c r="P111" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q111">
         <v>1.86</v>
@@ -23841,7 +23847,7 @@
         <v>0.7</v>
       </c>
       <c r="AP111">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ111">
         <v>0.73</v>
@@ -24793,7 +24799,7 @@
         <v>164</v>
       </c>
       <c r="P116" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q116">
         <v>2.15</v>
@@ -24874,7 +24880,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ116">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR116">
         <v>1.93</v>
@@ -25080,7 +25086,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ117">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR117">
         <v>1.43</v>
@@ -25205,7 +25211,7 @@
         <v>166</v>
       </c>
       <c r="P118" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q118">
         <v>2.08</v>
@@ -25617,7 +25623,7 @@
         <v>167</v>
       </c>
       <c r="P120" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q120">
         <v>6</v>
@@ -25774,6 +25780,418 @@
       </c>
       <c r="BP120">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="121" spans="1:68">
+      <c r="A121" s="1">
+        <v>120</v>
+      </c>
+      <c r="B121">
+        <v>7775737</v>
+      </c>
+      <c r="C121" t="s">
+        <v>68</v>
+      </c>
+      <c r="D121" t="s">
+        <v>69</v>
+      </c>
+      <c r="E121" s="2">
+        <v>45849.65625</v>
+      </c>
+      <c r="F121">
+        <v>0</v>
+      </c>
+      <c r="G121" t="s">
+        <v>74</v>
+      </c>
+      <c r="H121" t="s">
+        <v>77</v>
+      </c>
+      <c r="I121">
+        <v>0</v>
+      </c>
+      <c r="J121">
+        <v>0</v>
+      </c>
+      <c r="K121">
+        <v>0</v>
+      </c>
+      <c r="L121">
+        <v>3</v>
+      </c>
+      <c r="M121">
+        <v>0</v>
+      </c>
+      <c r="N121">
+        <v>3</v>
+      </c>
+      <c r="O121" t="s">
+        <v>168</v>
+      </c>
+      <c r="P121" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q121">
+        <v>2.21</v>
+      </c>
+      <c r="R121">
+        <v>2.2</v>
+      </c>
+      <c r="S121">
+        <v>4.7</v>
+      </c>
+      <c r="T121">
+        <v>1.33</v>
+      </c>
+      <c r="U121">
+        <v>2.9</v>
+      </c>
+      <c r="V121">
+        <v>2.71</v>
+      </c>
+      <c r="W121">
+        <v>1.43</v>
+      </c>
+      <c r="X121">
+        <v>6.5</v>
+      </c>
+      <c r="Y121">
+        <v>1.09</v>
+      </c>
+      <c r="Z121">
+        <v>1.61</v>
+      </c>
+      <c r="AA121">
+        <v>4.04</v>
+      </c>
+      <c r="AB121">
+        <v>5.4</v>
+      </c>
+      <c r="AC121">
+        <v>1.05</v>
+      </c>
+      <c r="AD121">
+        <v>10.5</v>
+      </c>
+      <c r="AE121">
+        <v>1.25</v>
+      </c>
+      <c r="AF121">
+        <v>3.45</v>
+      </c>
+      <c r="AG121">
+        <v>1.9</v>
+      </c>
+      <c r="AH121">
+        <v>1.8</v>
+      </c>
+      <c r="AI121">
+        <v>1.92</v>
+      </c>
+      <c r="AJ121">
+        <v>1.83</v>
+      </c>
+      <c r="AK121">
+        <v>1.24</v>
+      </c>
+      <c r="AL121">
+        <v>1.2</v>
+      </c>
+      <c r="AM121">
+        <v>2.25</v>
+      </c>
+      <c r="AN121">
+        <v>2</v>
+      </c>
+      <c r="AO121">
+        <v>1</v>
+      </c>
+      <c r="AP121">
+        <v>2.08</v>
+      </c>
+      <c r="AQ121">
+        <v>0.92</v>
+      </c>
+      <c r="AR121">
+        <v>2.05</v>
+      </c>
+      <c r="AS121">
+        <v>1.54</v>
+      </c>
+      <c r="AT121">
+        <v>3.59</v>
+      </c>
+      <c r="AU121">
+        <v>6</v>
+      </c>
+      <c r="AV121">
+        <v>5</v>
+      </c>
+      <c r="AW121">
+        <v>9</v>
+      </c>
+      <c r="AX121">
+        <v>12</v>
+      </c>
+      <c r="AY121">
+        <v>15</v>
+      </c>
+      <c r="AZ121">
+        <v>17</v>
+      </c>
+      <c r="BA121">
+        <v>6</v>
+      </c>
+      <c r="BB121">
+        <v>0</v>
+      </c>
+      <c r="BC121">
+        <v>6</v>
+      </c>
+      <c r="BD121">
+        <v>1.32</v>
+      </c>
+      <c r="BE121">
+        <v>7.5</v>
+      </c>
+      <c r="BF121">
+        <v>3.7</v>
+      </c>
+      <c r="BG121">
+        <v>1.19</v>
+      </c>
+      <c r="BH121">
+        <v>3.95</v>
+      </c>
+      <c r="BI121">
+        <v>1.38</v>
+      </c>
+      <c r="BJ121">
+        <v>2.75</v>
+      </c>
+      <c r="BK121">
+        <v>1.79</v>
+      </c>
+      <c r="BL121">
+        <v>2.23</v>
+      </c>
+      <c r="BM121">
+        <v>1.94</v>
+      </c>
+      <c r="BN121">
+        <v>1.76</v>
+      </c>
+      <c r="BO121">
+        <v>2.4</v>
+      </c>
+      <c r="BP121">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="122" spans="1:68">
+      <c r="A122" s="1">
+        <v>121</v>
+      </c>
+      <c r="B122">
+        <v>7775738</v>
+      </c>
+      <c r="C122" t="s">
+        <v>68</v>
+      </c>
+      <c r="D122" t="s">
+        <v>69</v>
+      </c>
+      <c r="E122" s="2">
+        <v>45849.65625</v>
+      </c>
+      <c r="F122">
+        <v>0</v>
+      </c>
+      <c r="G122" t="s">
+        <v>78</v>
+      </c>
+      <c r="H122" t="s">
+        <v>70</v>
+      </c>
+      <c r="I122">
+        <v>2</v>
+      </c>
+      <c r="J122">
+        <v>0</v>
+      </c>
+      <c r="K122">
+        <v>2</v>
+      </c>
+      <c r="L122">
+        <v>2</v>
+      </c>
+      <c r="M122">
+        <v>0</v>
+      </c>
+      <c r="N122">
+        <v>2</v>
+      </c>
+      <c r="O122" t="s">
+        <v>169</v>
+      </c>
+      <c r="P122" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q122">
+        <v>2.5</v>
+      </c>
+      <c r="R122">
+        <v>2.2</v>
+      </c>
+      <c r="S122">
+        <v>3.8</v>
+      </c>
+      <c r="T122">
+        <v>1.36</v>
+      </c>
+      <c r="U122">
+        <v>2.85</v>
+      </c>
+      <c r="V122">
+        <v>2.62</v>
+      </c>
+      <c r="W122">
+        <v>1.42</v>
+      </c>
+      <c r="X122">
+        <v>6.2</v>
+      </c>
+      <c r="Y122">
+        <v>1.09</v>
+      </c>
+      <c r="Z122">
+        <v>2</v>
+      </c>
+      <c r="AA122">
+        <v>3.25</v>
+      </c>
+      <c r="AB122">
+        <v>3.35</v>
+      </c>
+      <c r="AC122">
+        <v>1.06</v>
+      </c>
+      <c r="AD122">
+        <v>10</v>
+      </c>
+      <c r="AE122">
+        <v>1.29</v>
+      </c>
+      <c r="AF122">
+        <v>3.5</v>
+      </c>
+      <c r="AG122">
+        <v>1.85</v>
+      </c>
+      <c r="AH122">
+        <v>1.87</v>
+      </c>
+      <c r="AI122">
+        <v>1.71</v>
+      </c>
+      <c r="AJ122">
+        <v>2</v>
+      </c>
+      <c r="AK122">
+        <v>1.3</v>
+      </c>
+      <c r="AL122">
+        <v>1.22</v>
+      </c>
+      <c r="AM122">
+        <v>1.73</v>
+      </c>
+      <c r="AN122">
+        <v>1.27</v>
+      </c>
+      <c r="AO122">
+        <v>0.18</v>
+      </c>
+      <c r="AP122">
+        <v>1.42</v>
+      </c>
+      <c r="AQ122">
+        <v>0.17</v>
+      </c>
+      <c r="AR122">
+        <v>1.57</v>
+      </c>
+      <c r="AS122">
+        <v>1.09</v>
+      </c>
+      <c r="AT122">
+        <v>2.66</v>
+      </c>
+      <c r="AU122">
+        <v>3</v>
+      </c>
+      <c r="AV122">
+        <v>5</v>
+      </c>
+      <c r="AW122">
+        <v>15</v>
+      </c>
+      <c r="AX122">
+        <v>15</v>
+      </c>
+      <c r="AY122">
+        <v>18</v>
+      </c>
+      <c r="AZ122">
+        <v>20</v>
+      </c>
+      <c r="BA122">
+        <v>6</v>
+      </c>
+      <c r="BB122">
+        <v>6</v>
+      </c>
+      <c r="BC122">
+        <v>12</v>
+      </c>
+      <c r="BD122">
+        <v>1.65</v>
+      </c>
+      <c r="BE122">
+        <v>7.75</v>
+      </c>
+      <c r="BF122">
+        <v>2.6</v>
+      </c>
+      <c r="BG122">
+        <v>1.22</v>
+      </c>
+      <c r="BH122">
+        <v>3.8</v>
+      </c>
+      <c r="BI122">
+        <v>1.36</v>
+      </c>
+      <c r="BJ122">
+        <v>3.4</v>
+      </c>
+      <c r="BK122">
+        <v>1.66</v>
+      </c>
+      <c r="BL122">
+        <v>2.4</v>
+      </c>
+      <c r="BM122">
+        <v>1.8</v>
+      </c>
+      <c r="BN122">
+        <v>1.74</v>
+      </c>
+      <c r="BO122">
+        <v>2.5</v>
+      </c>
+      <c r="BP122">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
@@ -25925,19 +25925,19 @@
         <v>6</v>
       </c>
       <c r="AV121">
+        <v>6</v>
+      </c>
+      <c r="AW121">
         <v>5</v>
       </c>
-      <c r="AW121">
+      <c r="AX121">
         <v>9</v>
       </c>
-      <c r="AX121">
-        <v>12</v>
-      </c>
       <c r="AY121">
+        <v>11</v>
+      </c>
+      <c r="AZ121">
         <v>15</v>
-      </c>
-      <c r="AZ121">
-        <v>17</v>
       </c>
       <c r="BA121">
         <v>6</v>
@@ -26134,16 +26134,16 @@
         <v>5</v>
       </c>
       <c r="AW122">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="AX122">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AY122">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AZ122">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="BA122">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="229">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -524,6 +524,9 @@
   </si>
   <si>
     <t>['36', '21']</t>
+  </si>
+  <si>
+    <t>['19', '45+1']</t>
   </si>
   <si>
     <t>['45+1', '81']</t>
@@ -1059,7 +1062,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP122"/>
+  <dimension ref="A1:BP123"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1315,7 +1318,7 @@
         <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q2">
         <v>4.4</v>
@@ -1602,7 +1605,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ3">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1933,7 +1936,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -2011,7 +2014,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ5">
         <v>1.08</v>
@@ -2757,7 +2760,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q9">
         <v>3.5</v>
@@ -3169,7 +3172,7 @@
         <v>88</v>
       </c>
       <c r="P11" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q11">
         <v>1.94</v>
@@ -3375,7 +3378,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q12">
         <v>3.95</v>
@@ -3581,7 +3584,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q13">
         <v>4.5</v>
@@ -3787,7 +3790,7 @@
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q14">
         <v>3.9</v>
@@ -3993,7 +3996,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q15">
         <v>2.06</v>
@@ -4199,7 +4202,7 @@
         <v>82</v>
       </c>
       <c r="P16" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4405,7 +4408,7 @@
         <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q17">
         <v>3.1</v>
@@ -4611,7 +4614,7 @@
         <v>94</v>
       </c>
       <c r="P18" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q18">
         <v>4.2</v>
@@ -4689,7 +4692,7 @@
         <v>0.5</v>
       </c>
       <c r="AP18">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ18">
         <v>1.69</v>
@@ -4898,7 +4901,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ19">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR19">
         <v>2.01</v>
@@ -5023,7 +5026,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q20">
         <v>2.65</v>
@@ -5229,7 +5232,7 @@
         <v>82</v>
       </c>
       <c r="P21" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -6053,7 +6056,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q25">
         <v>2.7</v>
@@ -6259,7 +6262,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q26">
         <v>4.75</v>
@@ -7161,10 +7164,10 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ30">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR30">
         <v>1.87</v>
@@ -7289,7 +7292,7 @@
         <v>103</v>
       </c>
       <c r="P31" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q31">
         <v>4.75</v>
@@ -7495,7 +7498,7 @@
         <v>82</v>
       </c>
       <c r="P32" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q32">
         <v>3</v>
@@ -7907,7 +7910,7 @@
         <v>104</v>
       </c>
       <c r="P34" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q34">
         <v>4.33</v>
@@ -7985,7 +7988,7 @@
         <v>2</v>
       </c>
       <c r="AP34">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ34">
         <v>1.33</v>
@@ -8194,7 +8197,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ35">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR35">
         <v>1.34</v>
@@ -8525,7 +8528,7 @@
         <v>105</v>
       </c>
       <c r="P37" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q37">
         <v>2.38</v>
@@ -9349,7 +9352,7 @@
         <v>82</v>
       </c>
       <c r="P41" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q41">
         <v>5.2</v>
@@ -9761,7 +9764,7 @@
         <v>109</v>
       </c>
       <c r="P43" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q43">
         <v>2.38</v>
@@ -10173,7 +10176,7 @@
         <v>111</v>
       </c>
       <c r="P45" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q45">
         <v>4.04</v>
@@ -10251,7 +10254,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ45">
         <v>0.92</v>
@@ -10379,7 +10382,7 @@
         <v>112</v>
       </c>
       <c r="P46" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q46">
         <v>1.7</v>
@@ -10791,7 +10794,7 @@
         <v>114</v>
       </c>
       <c r="P48" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q48">
         <v>3.88</v>
@@ -10997,7 +11000,7 @@
         <v>115</v>
       </c>
       <c r="P49" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q49">
         <v>3.55</v>
@@ -11078,7 +11081,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ49">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR49">
         <v>1.6</v>
@@ -11203,7 +11206,7 @@
         <v>116</v>
       </c>
       <c r="P50" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q50">
         <v>3.7</v>
@@ -11409,7 +11412,7 @@
         <v>82</v>
       </c>
       <c r="P51" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q51">
         <v>2.6</v>
@@ -11615,7 +11618,7 @@
         <v>117</v>
       </c>
       <c r="P52" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q52">
         <v>2.24</v>
@@ -12233,7 +12236,7 @@
         <v>119</v>
       </c>
       <c r="P55" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q55">
         <v>2.6</v>
@@ -12645,7 +12648,7 @@
         <v>121</v>
       </c>
       <c r="P57" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q57">
         <v>3.5</v>
@@ -13057,7 +13060,7 @@
         <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q59">
         <v>4.75</v>
@@ -13138,7 +13141,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ59">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR59">
         <v>1.59</v>
@@ -13263,7 +13266,7 @@
         <v>124</v>
       </c>
       <c r="P60" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q60">
         <v>2.61</v>
@@ -13469,7 +13472,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q61">
         <v>3.05</v>
@@ -13547,7 +13550,7 @@
         <v>0.2</v>
       </c>
       <c r="AP61">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ61">
         <v>0.17</v>
@@ -13881,7 +13884,7 @@
         <v>127</v>
       </c>
       <c r="P63" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q63">
         <v>3.28</v>
@@ -13959,7 +13962,7 @@
         <v>1.83</v>
       </c>
       <c r="AP63">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ63">
         <v>1.23</v>
@@ -14087,7 +14090,7 @@
         <v>128</v>
       </c>
       <c r="P64" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q64">
         <v>6.5</v>
@@ -14293,7 +14296,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q65">
         <v>2.04</v>
@@ -14705,7 +14708,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q67">
         <v>2.45</v>
@@ -14911,7 +14914,7 @@
         <v>132</v>
       </c>
       <c r="P68" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q68">
         <v>3.2</v>
@@ -15735,7 +15738,7 @@
         <v>135</v>
       </c>
       <c r="P72" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q72">
         <v>3.26</v>
@@ -15941,7 +15944,7 @@
         <v>97</v>
       </c>
       <c r="P73" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q73">
         <v>4.6</v>
@@ -16022,7 +16025,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ73">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR73">
         <v>1.54</v>
@@ -16559,7 +16562,7 @@
         <v>82</v>
       </c>
       <c r="P76" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q76">
         <v>3.65</v>
@@ -16637,7 +16640,7 @@
         <v>1.29</v>
       </c>
       <c r="AP76">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ76">
         <v>1.33</v>
@@ -16765,7 +16768,7 @@
         <v>82</v>
       </c>
       <c r="P77" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q77">
         <v>2.05</v>
@@ -16971,7 +16974,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q78">
         <v>1.89</v>
@@ -17464,7 +17467,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ80">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR80">
         <v>1.49</v>
@@ -17589,7 +17592,7 @@
         <v>85</v>
       </c>
       <c r="P81" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q81">
         <v>5.25</v>
@@ -18413,7 +18416,7 @@
         <v>143</v>
       </c>
       <c r="P85" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q85">
         <v>2.2</v>
@@ -18619,7 +18622,7 @@
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q86">
         <v>2.11</v>
@@ -18825,7 +18828,7 @@
         <v>145</v>
       </c>
       <c r="P87" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q87">
         <v>2.04</v>
@@ -19031,7 +19034,7 @@
         <v>146</v>
       </c>
       <c r="P88" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19315,7 +19318,7 @@
         <v>0.78</v>
       </c>
       <c r="AP89">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ89">
         <v>0.92</v>
@@ -19443,7 +19446,7 @@
         <v>147</v>
       </c>
       <c r="P90" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q90">
         <v>3.81</v>
@@ -19649,7 +19652,7 @@
         <v>148</v>
       </c>
       <c r="P91" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q91">
         <v>3.3</v>
@@ -19936,7 +19939,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ92">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR92">
         <v>1.96</v>
@@ -20267,7 +20270,7 @@
         <v>149</v>
       </c>
       <c r="P94" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q94">
         <v>3.8</v>
@@ -20679,7 +20682,7 @@
         <v>82</v>
       </c>
       <c r="P96" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q96">
         <v>4.1</v>
@@ -21169,7 +21172,7 @@
         <v>1.44</v>
       </c>
       <c r="AP98">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ98">
         <v>1.08</v>
@@ -21297,7 +21300,7 @@
         <v>152</v>
       </c>
       <c r="P99" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q99">
         <v>4.85</v>
@@ -22121,7 +22124,7 @@
         <v>82</v>
       </c>
       <c r="P103" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q103">
         <v>3.3</v>
@@ -22202,7 +22205,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ103">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR103">
         <v>1.98</v>
@@ -22327,7 +22330,7 @@
         <v>155</v>
       </c>
       <c r="P104" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -22533,7 +22536,7 @@
         <v>156</v>
       </c>
       <c r="P105" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q105">
         <v>1.64</v>
@@ -22739,7 +22742,7 @@
         <v>157</v>
       </c>
       <c r="P106" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q106">
         <v>3.55</v>
@@ -22817,7 +22820,7 @@
         <v>1.2</v>
       </c>
       <c r="AP106">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ106">
         <v>0.92</v>
@@ -22945,7 +22948,7 @@
         <v>82</v>
       </c>
       <c r="P107" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q107">
         <v>2.89</v>
@@ -23026,7 +23029,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ107">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR107">
         <v>1.66</v>
@@ -23151,7 +23154,7 @@
         <v>158</v>
       </c>
       <c r="P108" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q108">
         <v>3.5</v>
@@ -23357,7 +23360,7 @@
         <v>159</v>
       </c>
       <c r="P109" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q109">
         <v>3.4</v>
@@ -23769,7 +23772,7 @@
         <v>161</v>
       </c>
       <c r="P111" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q111">
         <v>1.86</v>
@@ -24799,7 +24802,7 @@
         <v>164</v>
       </c>
       <c r="P116" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q116">
         <v>2.15</v>
@@ -25211,7 +25214,7 @@
         <v>166</v>
       </c>
       <c r="P118" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q118">
         <v>2.08</v>
@@ -25623,7 +25626,7 @@
         <v>167</v>
       </c>
       <c r="P120" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q120">
         <v>6</v>
@@ -25701,7 +25704,7 @@
         <v>1.75</v>
       </c>
       <c r="AP120">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ120">
         <v>1.69</v>
@@ -26192,6 +26195,212 @@
       </c>
       <c r="BP122">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="123" spans="1:68">
+      <c r="A123" s="1">
+        <v>122</v>
+      </c>
+      <c r="B123">
+        <v>7775739</v>
+      </c>
+      <c r="C123" t="s">
+        <v>68</v>
+      </c>
+      <c r="D123" t="s">
+        <v>69</v>
+      </c>
+      <c r="E123" s="2">
+        <v>45850.65625</v>
+      </c>
+      <c r="F123">
+        <v>0</v>
+      </c>
+      <c r="G123" t="s">
+        <v>73</v>
+      </c>
+      <c r="H123" t="s">
+        <v>75</v>
+      </c>
+      <c r="I123">
+        <v>2</v>
+      </c>
+      <c r="J123">
+        <v>0</v>
+      </c>
+      <c r="K123">
+        <v>2</v>
+      </c>
+      <c r="L123">
+        <v>2</v>
+      </c>
+      <c r="M123">
+        <v>0</v>
+      </c>
+      <c r="N123">
+        <v>2</v>
+      </c>
+      <c r="O123" t="s">
+        <v>170</v>
+      </c>
+      <c r="P123" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q123">
+        <v>4.65</v>
+      </c>
+      <c r="R123">
+        <v>1.99</v>
+      </c>
+      <c r="S123">
+        <v>2.49</v>
+      </c>
+      <c r="T123">
+        <v>1.4</v>
+      </c>
+      <c r="U123">
+        <v>2.6</v>
+      </c>
+      <c r="V123">
+        <v>3</v>
+      </c>
+      <c r="W123">
+        <v>1.3</v>
+      </c>
+      <c r="X123">
+        <v>8.5</v>
+      </c>
+      <c r="Y123">
+        <v>1.06</v>
+      </c>
+      <c r="Z123">
+        <v>4.92</v>
+      </c>
+      <c r="AA123">
+        <v>3.5</v>
+      </c>
+      <c r="AB123">
+        <v>1.74</v>
+      </c>
+      <c r="AC123">
+        <v>1.06</v>
+      </c>
+      <c r="AD123">
+        <v>7.5</v>
+      </c>
+      <c r="AE123">
+        <v>1.36</v>
+      </c>
+      <c r="AF123">
+        <v>2.83</v>
+      </c>
+      <c r="AG123">
+        <v>2.15</v>
+      </c>
+      <c r="AH123">
+        <v>1.65</v>
+      </c>
+      <c r="AI123">
+        <v>2.05</v>
+      </c>
+      <c r="AJ123">
+        <v>1.67</v>
+      </c>
+      <c r="AK123">
+        <v>1.3</v>
+      </c>
+      <c r="AL123">
+        <v>1.25</v>
+      </c>
+      <c r="AM123">
+        <v>1.17</v>
+      </c>
+      <c r="AN123">
+        <v>1</v>
+      </c>
+      <c r="AO123">
+        <v>1.55</v>
+      </c>
+      <c r="AP123">
+        <v>1.15</v>
+      </c>
+      <c r="AQ123">
+        <v>1.42</v>
+      </c>
+      <c r="AR123">
+        <v>1.35</v>
+      </c>
+      <c r="AS123">
+        <v>1.15</v>
+      </c>
+      <c r="AT123">
+        <v>2.5</v>
+      </c>
+      <c r="AU123">
+        <v>7</v>
+      </c>
+      <c r="AV123">
+        <v>5</v>
+      </c>
+      <c r="AW123">
+        <v>6</v>
+      </c>
+      <c r="AX123">
+        <v>5</v>
+      </c>
+      <c r="AY123">
+        <v>13</v>
+      </c>
+      <c r="AZ123">
+        <v>10</v>
+      </c>
+      <c r="BA123">
+        <v>4</v>
+      </c>
+      <c r="BB123">
+        <v>5</v>
+      </c>
+      <c r="BC123">
+        <v>9</v>
+      </c>
+      <c r="BD123">
+        <v>3.76</v>
+      </c>
+      <c r="BE123">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF123">
+        <v>1.49</v>
+      </c>
+      <c r="BG123">
+        <v>1.5</v>
+      </c>
+      <c r="BH123">
+        <v>2.4</v>
+      </c>
+      <c r="BI123">
+        <v>1.8</v>
+      </c>
+      <c r="BJ123">
+        <v>1.91</v>
+      </c>
+      <c r="BK123">
+        <v>2.25</v>
+      </c>
+      <c r="BL123">
+        <v>1.57</v>
+      </c>
+      <c r="BM123">
+        <v>3</v>
+      </c>
+      <c r="BN123">
+        <v>1.33</v>
+      </c>
+      <c r="BO123">
+        <v>3.8</v>
+      </c>
+      <c r="BP123">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
@@ -25928,19 +25928,19 @@
         <v>6</v>
       </c>
       <c r="AV121">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW121">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AX121">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AY121">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AZ121">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA121">
         <v>6</v>
@@ -26137,16 +26137,16 @@
         <v>5</v>
       </c>
       <c r="AW122">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="AX122">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AY122">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="AZ122">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="BA122">
         <v>6</v>
@@ -26340,19 +26340,19 @@
         <v>7</v>
       </c>
       <c r="AV123">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW123">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX123">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AY123">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ123">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA123">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
@@ -26340,19 +26340,19 @@
         <v>7</v>
       </c>
       <c r="AV123">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW123">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX123">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AY123">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ123">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA123">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Republic of Ireland Premier Division_2025.xlsx
@@ -26340,19 +26340,19 @@
         <v>7</v>
       </c>
       <c r="AV123">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW123">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX123">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AY123">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ123">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA123">
         <v>4</v>
